--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="164011"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edugarcia\OneDrive - Transportes Tamaulipas SA de CV\Documentos\2026\Proyectos\Indicadores IA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\edugarcia\Downloads\30 Nuevos Indicadores IA\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7530"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -19,7 +19,11 @@
     <sheet name="5.0E" sheetId="14" r:id="rId5"/>
     <sheet name="5.0F" sheetId="9" r:id="rId6"/>
     <sheet name="5.0G" sheetId="15" r:id="rId7"/>
+    <sheet name="5.3A" sheetId="16" r:id="rId8"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId9"/>
+  </externalReferences>
   <definedNames>
     <definedName name="__A313546">#N/A</definedName>
     <definedName name="__A313546_1">#N/A</definedName>
@@ -28,14 +32,17 @@
     <definedName name="__xlnm._FilterDatabase" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase" localSheetId="4">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase" localSheetId="6">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase" localSheetId="7">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="4">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="6">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase_1" localSheetId="7">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="4">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="6">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase_3" localSheetId="7">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_4">#N/A</definedName>
     <definedName name="__xlnm.Database">#N/A</definedName>
@@ -7879,6 +7886,7 @@
     <definedName name="UILUI" localSheetId="3">#REF!</definedName>
     <definedName name="UILUI" localSheetId="4">#REF!</definedName>
     <definedName name="UILUI" localSheetId="6">#REF!</definedName>
+    <definedName name="UILUI" localSheetId="7">#REF!</definedName>
     <definedName name="UILUI">#REF!</definedName>
     <definedName name="unnn">"#REF!"</definedName>
     <definedName name="unnn_1">"#REF!"</definedName>
@@ -7964,7 +7972,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="440" uniqueCount="49">
   <si>
     <t>Mes</t>
   </si>
@@ -8031,6 +8039,87 @@
   <si>
     <t>AÑO</t>
   </si>
+  <si>
+    <t>Cumplimiento al programa de mantenimiento semanal</t>
+  </si>
+  <si>
+    <t>SUBZONAS</t>
+  </si>
+  <si>
+    <t>DIVISIONES</t>
+  </si>
+  <si>
+    <t>Semana</t>
+  </si>
+  <si>
+    <t>CENTRO</t>
+  </si>
+  <si>
+    <t>METROS</t>
+  </si>
+  <si>
+    <t>NORTE</t>
+  </si>
+  <si>
+    <t>ORIENTE</t>
+  </si>
+  <si>
+    <t>PONIENTE</t>
+  </si>
+  <si>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>NUEVO LAREDO</t>
+  </si>
+  <si>
+    <t>REYNOSA</t>
+  </si>
+  <si>
+    <t>SAN LUIS POTOSI</t>
+  </si>
+  <si>
+    <t>VICTORIA</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>F</t>
+  </si>
+  <si>
+    <t>G</t>
+  </si>
+  <si>
+    <t>H</t>
+  </si>
+  <si>
+    <t>J</t>
+  </si>
+  <si>
+    <t>PREMETRO</t>
+  </si>
+  <si>
+    <t>SENDERO</t>
+  </si>
+  <si>
+    <t>JUAREZ A</t>
+  </si>
+  <si>
+    <t>JUAREZ B</t>
+  </si>
 </sst>
 </file>
 
@@ -8041,7 +8130,7 @@
     <numFmt numFmtId="165" formatCode="0.0%"/>
     <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -8064,8 +8153,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -8087,6 +8184,36 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="0" tint="-0.34998626667073579"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC00000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF9797"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -8119,7 +8246,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8178,6 +8305,33 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -8208,6 +8362,35 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <sheetNames>
+      <sheetName val="DIAGRAMA CITI"/>
+      <sheetName val="5.0A"/>
+      <sheetName val="5.0B"/>
+      <sheetName val="5.0C"/>
+      <sheetName val="5.0D"/>
+      <sheetName val="5.0E"/>
+      <sheetName val="5.0F"/>
+      <sheetName val="5.0G"/>
+      <sheetName val="5.3A"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0"/>
+      <sheetData sheetId="1"/>
+      <sheetData sheetId="2"/>
+      <sheetData sheetId="3"/>
+      <sheetData sheetId="4"/>
+      <sheetData sheetId="5"/>
+      <sheetData sheetId="6"/>
+      <sheetData sheetId="7"/>
+      <sheetData sheetId="8"/>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -12512,4 +12695,7908 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AG108"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="5.140625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8" bestFit="1" customWidth="1"/>
+    <col min="4" max="33" width="16.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
+      <c r="L1" s="22"/>
+      <c r="M1" s="22"/>
+      <c r="N1" s="22"/>
+      <c r="O1" s="22"/>
+      <c r="P1" s="22"/>
+      <c r="Q1" s="22" t="s">
+        <v>24</v>
+      </c>
+      <c r="R1" s="22"/>
+      <c r="S1" s="22"/>
+      <c r="T1" s="22"/>
+      <c r="U1" s="22"/>
+      <c r="V1" s="22"/>
+      <c r="W1" s="22"/>
+      <c r="X1" s="22"/>
+      <c r="Y1" s="22"/>
+      <c r="Z1" s="22"/>
+      <c r="AA1" s="22"/>
+      <c r="AB1" s="22"/>
+      <c r="AC1" s="22"/>
+      <c r="AD1" s="22"/>
+      <c r="AE1" s="22"/>
+      <c r="AF1" s="22"/>
+      <c r="AG1" s="22"/>
+    </row>
+    <row r="2" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A2" s="23" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="23" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="23" t="s">
+        <v>25</v>
+      </c>
+      <c r="D2" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" s="28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="28" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="28" t="s">
+        <v>26</v>
+      </c>
+      <c r="H2" s="28" t="s">
+        <v>27</v>
+      </c>
+      <c r="I2" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="J2" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="K2" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="28" t="s">
+        <v>31</v>
+      </c>
+      <c r="M2" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="N2" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="O2" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="P2" s="28" t="s">
+        <v>35</v>
+      </c>
+      <c r="Q2" s="28" t="s">
+        <v>36</v>
+      </c>
+      <c r="R2" s="28" t="s">
+        <v>37</v>
+      </c>
+      <c r="S2" s="28" t="s">
+        <v>38</v>
+      </c>
+      <c r="T2" s="28" t="s">
+        <v>39</v>
+      </c>
+      <c r="U2" s="28" t="s">
+        <v>40</v>
+      </c>
+      <c r="V2" s="28" t="s">
+        <v>41</v>
+      </c>
+      <c r="W2" s="28" t="s">
+        <v>42</v>
+      </c>
+      <c r="X2" s="28" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y2" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="Z2" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="AA2" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="AB2" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="AC2" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="AD2" s="28" t="s">
+        <v>32</v>
+      </c>
+      <c r="AE2" s="28" t="s">
+        <v>33</v>
+      </c>
+      <c r="AF2" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AG2" s="28" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="3" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A3" s="24">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="25">
+        <v>1</v>
+      </c>
+      <c r="D3" s="29">
+        <v>0.97979797979797978</v>
+      </c>
+      <c r="E3" s="29">
+        <v>0.97435897435897434</v>
+      </c>
+      <c r="F3" s="29">
+        <v>0.98765432098765427</v>
+      </c>
+      <c r="G3" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="H3" s="29">
+        <v>1</v>
+      </c>
+      <c r="I3" s="29">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="J3" s="29">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="K3" s="29">
+        <v>1</v>
+      </c>
+      <c r="L3" s="29">
+        <v>1</v>
+      </c>
+      <c r="M3" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="N3" s="29">
+        <v>1</v>
+      </c>
+      <c r="O3" s="29">
+        <v>1</v>
+      </c>
+      <c r="P3" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q3" s="29">
+        <v>1</v>
+      </c>
+      <c r="R3" s="29">
+        <v>1</v>
+      </c>
+      <c r="S3" s="29">
+        <v>1</v>
+      </c>
+      <c r="T3" s="29">
+        <v>1</v>
+      </c>
+      <c r="U3" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="V3" s="29">
+        <v>1</v>
+      </c>
+      <c r="W3" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="X3" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="Y3" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="29"/>
+      <c r="AB3" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD3" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="AE3" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG3" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A4" s="24"/>
+      <c r="B4" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C4" s="25">
+        <v>2</v>
+      </c>
+      <c r="D4" s="29">
+        <v>0.99672131147540988</v>
+      </c>
+      <c r="E4" s="29">
+        <v>0.99328859060402686</v>
+      </c>
+      <c r="F4" s="29">
+        <v>1</v>
+      </c>
+      <c r="G4" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="H4" s="29">
+        <v>1</v>
+      </c>
+      <c r="I4" s="29">
+        <v>1</v>
+      </c>
+      <c r="J4" s="29">
+        <v>1</v>
+      </c>
+      <c r="K4" s="29">
+        <v>1</v>
+      </c>
+      <c r="L4" s="29">
+        <v>1</v>
+      </c>
+      <c r="M4" s="29">
+        <v>1</v>
+      </c>
+      <c r="N4" s="29">
+        <v>1</v>
+      </c>
+      <c r="O4" s="29">
+        <v>1</v>
+      </c>
+      <c r="P4" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q4" s="29">
+        <v>1</v>
+      </c>
+      <c r="R4" s="29">
+        <v>1</v>
+      </c>
+      <c r="S4" s="29">
+        <v>1</v>
+      </c>
+      <c r="T4" s="29">
+        <v>1</v>
+      </c>
+      <c r="U4" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="V4" s="29">
+        <v>1</v>
+      </c>
+      <c r="W4" s="29">
+        <v>1</v>
+      </c>
+      <c r="X4" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA4" s="29"/>
+      <c r="AB4" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC4" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG4" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="25">
+        <v>3</v>
+      </c>
+      <c r="D5" s="29">
+        <v>0.98620689655172411</v>
+      </c>
+      <c r="E5" s="29">
+        <v>0.97315436241610742</v>
+      </c>
+      <c r="F5" s="29">
+        <v>1</v>
+      </c>
+      <c r="G5" s="29">
+        <v>0.92</v>
+      </c>
+      <c r="H5" s="29">
+        <v>1</v>
+      </c>
+      <c r="I5" s="29">
+        <v>1</v>
+      </c>
+      <c r="J5" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="K5" s="29">
+        <v>1</v>
+      </c>
+      <c r="L5" s="29">
+        <v>1</v>
+      </c>
+      <c r="M5" s="29">
+        <v>1</v>
+      </c>
+      <c r="N5" s="29">
+        <v>1</v>
+      </c>
+      <c r="O5" s="29">
+        <v>1</v>
+      </c>
+      <c r="P5" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="29">
+        <v>1</v>
+      </c>
+      <c r="R5" s="29">
+        <v>1</v>
+      </c>
+      <c r="S5" s="29">
+        <v>1</v>
+      </c>
+      <c r="T5" s="29">
+        <v>1</v>
+      </c>
+      <c r="U5" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="V5" s="29">
+        <v>1</v>
+      </c>
+      <c r="W5" s="29">
+        <v>1</v>
+      </c>
+      <c r="X5" s="29">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Y5" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="29"/>
+      <c r="AB5" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC5" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG5" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A6" s="24"/>
+      <c r="B6" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C6" s="25">
+        <v>4</v>
+      </c>
+      <c r="D6" s="29">
+        <v>0.97388059701492535</v>
+      </c>
+      <c r="E6" s="29">
+        <v>0.97744360902255634</v>
+      </c>
+      <c r="F6" s="29">
+        <v>0.97037037037037033</v>
+      </c>
+      <c r="G6" s="29">
+        <v>0.92</v>
+      </c>
+      <c r="H6" s="29">
+        <v>1</v>
+      </c>
+      <c r="I6" s="29">
+        <v>1</v>
+      </c>
+      <c r="J6" s="29">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="K6" s="29">
+        <v>1</v>
+      </c>
+      <c r="L6" s="29">
+        <v>1</v>
+      </c>
+      <c r="M6" s="29">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="N6" s="29">
+        <v>1</v>
+      </c>
+      <c r="O6" s="29">
+        <v>1</v>
+      </c>
+      <c r="P6" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q6" s="29">
+        <v>1</v>
+      </c>
+      <c r="R6" s="29">
+        <v>1</v>
+      </c>
+      <c r="S6" s="29">
+        <v>1</v>
+      </c>
+      <c r="T6" s="29">
+        <v>1</v>
+      </c>
+      <c r="U6" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="V6" s="29">
+        <v>1</v>
+      </c>
+      <c r="W6" s="29">
+        <v>1</v>
+      </c>
+      <c r="X6" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="Y6" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA6" s="29"/>
+      <c r="AB6" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC6" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="29">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="AE6" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG6" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A7" s="24"/>
+      <c r="B7" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="25">
+        <v>5</v>
+      </c>
+      <c r="D7" s="29">
+        <v>0.98007968127490042</v>
+      </c>
+      <c r="E7" s="29">
+        <v>0.98333333333333328</v>
+      </c>
+      <c r="F7" s="29">
+        <v>0.97709923664122134</v>
+      </c>
+      <c r="G7" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="H7" s="29">
+        <v>1</v>
+      </c>
+      <c r="I7" s="29">
+        <v>1</v>
+      </c>
+      <c r="J7" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="K7" s="29">
+        <v>1</v>
+      </c>
+      <c r="L7" s="29">
+        <v>1</v>
+      </c>
+      <c r="M7" s="29">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="N7" s="29">
+        <v>1</v>
+      </c>
+      <c r="O7" s="29">
+        <v>1</v>
+      </c>
+      <c r="P7" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q7" s="29">
+        <v>1</v>
+      </c>
+      <c r="R7" s="29">
+        <v>1</v>
+      </c>
+      <c r="S7" s="29">
+        <v>1</v>
+      </c>
+      <c r="T7" s="29">
+        <v>1</v>
+      </c>
+      <c r="U7" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="V7" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="W7" s="29">
+        <v>1</v>
+      </c>
+      <c r="X7" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z7" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA7" s="29"/>
+      <c r="AB7" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC7" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="29">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="AE7" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG7" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A8" s="24"/>
+      <c r="B8" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="25">
+        <v>6</v>
+      </c>
+      <c r="D8" s="29">
+        <v>1</v>
+      </c>
+      <c r="E8" s="29">
+        <v>1</v>
+      </c>
+      <c r="F8" s="29">
+        <v>1</v>
+      </c>
+      <c r="G8" s="29">
+        <v>1</v>
+      </c>
+      <c r="H8" s="29">
+        <v>1</v>
+      </c>
+      <c r="I8" s="29">
+        <v>1</v>
+      </c>
+      <c r="J8" s="29">
+        <v>1</v>
+      </c>
+      <c r="K8" s="29">
+        <v>1</v>
+      </c>
+      <c r="L8" s="29">
+        <v>1</v>
+      </c>
+      <c r="M8" s="29">
+        <v>1</v>
+      </c>
+      <c r="N8" s="29">
+        <v>1</v>
+      </c>
+      <c r="O8" s="29">
+        <v>1</v>
+      </c>
+      <c r="P8" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q8" s="29">
+        <v>1</v>
+      </c>
+      <c r="R8" s="29">
+        <v>1</v>
+      </c>
+      <c r="S8" s="29">
+        <v>1</v>
+      </c>
+      <c r="T8" s="29">
+        <v>1</v>
+      </c>
+      <c r="U8" s="29">
+        <v>1</v>
+      </c>
+      <c r="V8" s="29">
+        <v>1</v>
+      </c>
+      <c r="W8" s="29">
+        <v>1</v>
+      </c>
+      <c r="X8" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z8" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA8" s="29"/>
+      <c r="AB8" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC8" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG8" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A9" s="24"/>
+      <c r="B9" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C9" s="25">
+        <v>7</v>
+      </c>
+      <c r="D9" s="29">
+        <v>0.99088145896656532</v>
+      </c>
+      <c r="E9" s="29">
+        <v>0.99411764705882355</v>
+      </c>
+      <c r="F9" s="29">
+        <v>0.98742138364779874</v>
+      </c>
+      <c r="G9" s="29">
+        <v>1</v>
+      </c>
+      <c r="H9" s="29">
+        <v>1</v>
+      </c>
+      <c r="I9" s="29">
+        <v>1</v>
+      </c>
+      <c r="J9" s="29">
+        <v>0.97560975609756095</v>
+      </c>
+      <c r="K9" s="29">
+        <v>1</v>
+      </c>
+      <c r="L9" s="29">
+        <v>1</v>
+      </c>
+      <c r="M9" s="29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="N9" s="29">
+        <v>1</v>
+      </c>
+      <c r="O9" s="29">
+        <v>1</v>
+      </c>
+      <c r="P9" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q9" s="29">
+        <v>1</v>
+      </c>
+      <c r="R9" s="29">
+        <v>1</v>
+      </c>
+      <c r="S9" s="29">
+        <v>1</v>
+      </c>
+      <c r="T9" s="29">
+        <v>1</v>
+      </c>
+      <c r="U9" s="29">
+        <v>1</v>
+      </c>
+      <c r="V9" s="29">
+        <v>1</v>
+      </c>
+      <c r="W9" s="29">
+        <v>1</v>
+      </c>
+      <c r="X9" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="Y9" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z9" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA9" s="29">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC9" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="AE9" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG9" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A10" s="24"/>
+      <c r="B10" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C10" s="25">
+        <v>8</v>
+      </c>
+      <c r="D10" s="29">
+        <v>0.97206703910614523</v>
+      </c>
+      <c r="E10" s="29">
+        <v>0.96039603960396036</v>
+      </c>
+      <c r="F10" s="29">
+        <v>0.98717948717948723</v>
+      </c>
+      <c r="G10" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="H10" s="29">
+        <v>1</v>
+      </c>
+      <c r="I10" s="29">
+        <v>1</v>
+      </c>
+      <c r="J10" s="29">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="K10" s="29">
+        <v>1</v>
+      </c>
+      <c r="L10" s="29">
+        <v>1</v>
+      </c>
+      <c r="M10" s="29">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="N10" s="29">
+        <v>1</v>
+      </c>
+      <c r="O10" s="29">
+        <v>1</v>
+      </c>
+      <c r="P10" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q10" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="R10" s="29">
+        <v>1</v>
+      </c>
+      <c r="S10" s="29">
+        <v>1</v>
+      </c>
+      <c r="T10" s="29">
+        <v>1</v>
+      </c>
+      <c r="U10" s="29">
+        <v>1</v>
+      </c>
+      <c r="V10" s="29">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="W10" s="29">
+        <v>1</v>
+      </c>
+      <c r="X10" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z10" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA10" s="29"/>
+      <c r="AB10" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC10" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="29">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="AE10" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG10" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A11" s="24"/>
+      <c r="B11" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C11" s="25">
+        <v>9</v>
+      </c>
+      <c r="D11" s="29">
+        <v>0.9101123595505618</v>
+      </c>
+      <c r="E11" s="29">
+        <v>0.9197860962566845</v>
+      </c>
+      <c r="F11" s="29">
+        <v>0.89940828402366868</v>
+      </c>
+      <c r="G11" s="29">
+        <v>0.62857142857142856</v>
+      </c>
+      <c r="H11" s="29">
+        <v>1</v>
+      </c>
+      <c r="I11" s="29">
+        <v>1</v>
+      </c>
+      <c r="J11" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="K11" s="29">
+        <v>1</v>
+      </c>
+      <c r="L11" s="29">
+        <v>0.96078431372549022</v>
+      </c>
+      <c r="M11" s="29">
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="N11" s="29">
+        <v>1</v>
+      </c>
+      <c r="O11" s="29">
+        <v>1</v>
+      </c>
+      <c r="P11" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q11" s="29">
+        <v>0.53333333333333333</v>
+      </c>
+      <c r="R11" s="29">
+        <v>1</v>
+      </c>
+      <c r="S11" s="29">
+        <v>1</v>
+      </c>
+      <c r="T11" s="29">
+        <v>1</v>
+      </c>
+      <c r="U11" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="V11" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="W11" s="29">
+        <v>1</v>
+      </c>
+      <c r="X11" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="Y11" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z11" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA11" s="29"/>
+      <c r="AB11" s="29">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="AC11" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD11" s="29">
+        <v>0.34782608695652173</v>
+      </c>
+      <c r="AE11" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF11" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG11" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A12" s="24"/>
+      <c r="B12" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C12" s="25">
+        <v>10</v>
+      </c>
+      <c r="D12" s="29">
+        <v>1</v>
+      </c>
+      <c r="E12" s="29">
+        <v>1</v>
+      </c>
+      <c r="F12" s="29">
+        <v>1</v>
+      </c>
+      <c r="G12" s="29">
+        <v>1</v>
+      </c>
+      <c r="H12" s="29">
+        <v>1</v>
+      </c>
+      <c r="I12" s="29">
+        <v>1</v>
+      </c>
+      <c r="J12" s="29">
+        <v>1</v>
+      </c>
+      <c r="K12" s="29">
+        <v>1</v>
+      </c>
+      <c r="L12" s="29">
+        <v>1</v>
+      </c>
+      <c r="M12" s="29">
+        <v>1</v>
+      </c>
+      <c r="N12" s="29">
+        <v>1</v>
+      </c>
+      <c r="O12" s="29">
+        <v>1</v>
+      </c>
+      <c r="P12" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q12" s="29">
+        <v>1</v>
+      </c>
+      <c r="R12" s="29">
+        <v>1</v>
+      </c>
+      <c r="S12" s="29">
+        <v>1</v>
+      </c>
+      <c r="T12" s="29">
+        <v>1</v>
+      </c>
+      <c r="U12" s="29">
+        <v>1</v>
+      </c>
+      <c r="V12" s="29">
+        <v>1</v>
+      </c>
+      <c r="W12" s="29">
+        <v>1</v>
+      </c>
+      <c r="X12" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y12" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z12" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA12" s="29"/>
+      <c r="AB12" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC12" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG12" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A13" s="24"/>
+      <c r="B13" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C13" s="25">
+        <v>11</v>
+      </c>
+      <c r="D13" s="29">
+        <v>0.9939577039274925</v>
+      </c>
+      <c r="E13" s="29">
+        <v>0.98795180722891562</v>
+      </c>
+      <c r="F13" s="29">
+        <v>1</v>
+      </c>
+      <c r="G13" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="H13" s="29">
+        <v>1</v>
+      </c>
+      <c r="I13" s="29">
+        <v>1</v>
+      </c>
+      <c r="J13" s="29">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="K13" s="29">
+        <v>1</v>
+      </c>
+      <c r="L13" s="29">
+        <v>1</v>
+      </c>
+      <c r="M13" s="29">
+        <v>1</v>
+      </c>
+      <c r="N13" s="29">
+        <v>1</v>
+      </c>
+      <c r="O13" s="29">
+        <v>1</v>
+      </c>
+      <c r="P13" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="R13" s="29">
+        <v>1</v>
+      </c>
+      <c r="S13" s="29">
+        <v>1</v>
+      </c>
+      <c r="T13" s="29">
+        <v>1</v>
+      </c>
+      <c r="U13" s="29">
+        <v>1</v>
+      </c>
+      <c r="V13" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="W13" s="29">
+        <v>1</v>
+      </c>
+      <c r="X13" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y13" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z13" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA13" s="29"/>
+      <c r="AB13" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE13" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG13" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A14" s="24"/>
+      <c r="B14" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C14" s="25">
+        <v>12</v>
+      </c>
+      <c r="D14" s="29">
+        <v>0.94647887323943658</v>
+      </c>
+      <c r="E14" s="29">
+        <v>0.91219512195121955</v>
+      </c>
+      <c r="F14" s="29">
+        <v>0.99333333333333329</v>
+      </c>
+      <c r="G14" s="29">
+        <v>0.71794871794871795</v>
+      </c>
+      <c r="H14" s="29">
+        <v>1</v>
+      </c>
+      <c r="I14" s="29">
+        <v>1</v>
+      </c>
+      <c r="J14" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="K14" s="29">
+        <v>1</v>
+      </c>
+      <c r="L14" s="29">
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="M14" s="29">
+        <v>1</v>
+      </c>
+      <c r="N14" s="29">
+        <v>1</v>
+      </c>
+      <c r="O14" s="29">
+        <v>1</v>
+      </c>
+      <c r="P14" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q14" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="R14" s="29">
+        <v>1</v>
+      </c>
+      <c r="S14" s="29">
+        <v>1</v>
+      </c>
+      <c r="T14" s="29">
+        <v>1</v>
+      </c>
+      <c r="U14" s="29">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="V14" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="W14" s="29">
+        <v>1</v>
+      </c>
+      <c r="X14" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="Y14" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z14" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA14" s="29"/>
+      <c r="AB14" s="29">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="AC14" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD14" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG14" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A15" s="24"/>
+      <c r="B15" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C15" s="25">
+        <v>13</v>
+      </c>
+      <c r="D15" s="29">
+        <v>0.90934844192634556</v>
+      </c>
+      <c r="E15" s="29">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="F15" s="29">
+        <v>0.98773006134969321</v>
+      </c>
+      <c r="G15" s="29">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="H15" s="29">
+        <v>1</v>
+      </c>
+      <c r="I15" s="29">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="J15" s="29">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="K15" s="29">
+        <v>0.98461538461538467</v>
+      </c>
+      <c r="L15" s="29">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="M15" s="29">
+        <v>1</v>
+      </c>
+      <c r="N15" s="29">
+        <v>1</v>
+      </c>
+      <c r="O15" s="29">
+        <v>1</v>
+      </c>
+      <c r="P15" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q15" s="29">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="R15" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="S15" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="T15" s="29">
+        <v>1</v>
+      </c>
+      <c r="U15" s="29">
+        <v>0.38095238095238093</v>
+      </c>
+      <c r="V15" s="29">
+        <v>0.68</v>
+      </c>
+      <c r="W15" s="29">
+        <v>1</v>
+      </c>
+      <c r="X15" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="Y15" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z15" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA15" s="29"/>
+      <c r="AB15" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="AC15" s="29">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="AD15" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG15" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A16" s="24"/>
+      <c r="B16" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C16" s="25">
+        <v>14</v>
+      </c>
+      <c r="D16" s="29">
+        <v>0.98275862068965514</v>
+      </c>
+      <c r="E16" s="29">
+        <v>0.96323529411764708</v>
+      </c>
+      <c r="F16" s="29">
+        <v>1</v>
+      </c>
+      <c r="G16" s="29">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="H16" s="29">
+        <v>1</v>
+      </c>
+      <c r="I16" s="29">
+        <v>1</v>
+      </c>
+      <c r="J16" s="29">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="K16" s="29">
+        <v>1</v>
+      </c>
+      <c r="L16" s="29">
+        <v>1</v>
+      </c>
+      <c r="M16" s="29">
+        <v>1</v>
+      </c>
+      <c r="N16" s="29">
+        <v>1</v>
+      </c>
+      <c r="O16" s="29">
+        <v>1</v>
+      </c>
+      <c r="P16" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q16" s="29">
+        <v>1</v>
+      </c>
+      <c r="R16" s="29">
+        <v>1</v>
+      </c>
+      <c r="S16" s="29">
+        <v>1</v>
+      </c>
+      <c r="T16" s="29">
+        <v>1</v>
+      </c>
+      <c r="U16" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="V16" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="W16" s="29">
+        <v>1</v>
+      </c>
+      <c r="X16" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="Y16" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AB16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG16" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A17" s="24"/>
+      <c r="B17" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="25">
+        <v>15</v>
+      </c>
+      <c r="D17" s="29">
+        <v>0.96031746031746035</v>
+      </c>
+      <c r="E17" s="29">
+        <v>0.96850393700787396</v>
+      </c>
+      <c r="F17" s="29">
+        <v>0.95199999999999996</v>
+      </c>
+      <c r="G17" s="29">
+        <v>1</v>
+      </c>
+      <c r="H17" s="29">
+        <v>1</v>
+      </c>
+      <c r="I17" s="29">
+        <v>1</v>
+      </c>
+      <c r="J17" s="29">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="K17" s="29">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="L17" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="M17" s="29">
+        <v>1</v>
+      </c>
+      <c r="N17" s="29">
+        <v>1</v>
+      </c>
+      <c r="O17" s="29">
+        <v>1</v>
+      </c>
+      <c r="P17" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="29">
+        <v>1</v>
+      </c>
+      <c r="R17" s="29">
+        <v>1</v>
+      </c>
+      <c r="S17" s="29">
+        <v>1</v>
+      </c>
+      <c r="T17" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="U17" s="29">
+        <v>1</v>
+      </c>
+      <c r="V17" s="29">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="W17" s="29">
+        <v>1</v>
+      </c>
+      <c r="X17" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="Y17" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z17" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA17" s="29"/>
+      <c r="AB17" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC17" s="29">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="AD17" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG17" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A18" s="24"/>
+      <c r="B18" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C18" s="25">
+        <v>16</v>
+      </c>
+      <c r="D18" s="29">
+        <v>0.97530864197530864</v>
+      </c>
+      <c r="E18" s="29">
+        <v>0.95049504950495045</v>
+      </c>
+      <c r="F18" s="29">
+        <v>0.99295774647887325</v>
+      </c>
+      <c r="G18" s="29">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H18" s="29">
+        <v>1</v>
+      </c>
+      <c r="I18" s="29">
+        <v>1</v>
+      </c>
+      <c r="J18" s="29">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="K18" s="29">
+        <v>1</v>
+      </c>
+      <c r="L18" s="29">
+        <v>0.97368421052631582</v>
+      </c>
+      <c r="M18" s="29">
+        <v>1</v>
+      </c>
+      <c r="N18" s="29">
+        <v>1</v>
+      </c>
+      <c r="O18" s="29">
+        <v>1</v>
+      </c>
+      <c r="P18" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q18" s="29">
+        <v>1</v>
+      </c>
+      <c r="R18" s="29">
+        <v>1</v>
+      </c>
+      <c r="S18" s="29">
+        <v>1</v>
+      </c>
+      <c r="T18" s="29">
+        <v>1</v>
+      </c>
+      <c r="U18" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="V18" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="W18" s="29">
+        <v>1</v>
+      </c>
+      <c r="X18" s="29">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Y18" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z18" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA18" s="29"/>
+      <c r="AB18" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="AC18" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD18" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE18" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF18" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG18" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A19" s="24"/>
+      <c r="B19" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C19" s="25">
+        <v>17</v>
+      </c>
+      <c r="D19" s="29">
+        <v>0.96755162241887904</v>
+      </c>
+      <c r="E19" s="29">
+        <v>0.94680851063829785</v>
+      </c>
+      <c r="F19" s="29">
+        <v>0.99337748344370858</v>
+      </c>
+      <c r="G19" s="29">
+        <v>0.77419354838709675</v>
+      </c>
+      <c r="H19" s="29">
+        <v>1</v>
+      </c>
+      <c r="I19" s="29">
+        <v>1</v>
+      </c>
+      <c r="J19" s="29">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="K19" s="29">
+        <v>1</v>
+      </c>
+      <c r="L19" s="29">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="M19" s="29">
+        <v>1</v>
+      </c>
+      <c r="N19" s="29">
+        <v>1</v>
+      </c>
+      <c r="O19" s="29">
+        <v>1</v>
+      </c>
+      <c r="P19" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q19" s="29">
+        <v>1</v>
+      </c>
+      <c r="R19" s="29">
+        <v>1</v>
+      </c>
+      <c r="S19" s="29">
+        <v>1</v>
+      </c>
+      <c r="T19" s="29">
+        <v>1</v>
+      </c>
+      <c r="U19" s="29">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="V19" s="29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="W19" s="29">
+        <v>1</v>
+      </c>
+      <c r="X19" s="29">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Y19" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z19" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA19" s="29"/>
+      <c r="AB19" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="AC19" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG19" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A20" s="24"/>
+      <c r="B20" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="25">
+        <v>18</v>
+      </c>
+      <c r="D20" s="29">
+        <v>0.99629629629629635</v>
+      </c>
+      <c r="E20" s="29">
+        <v>0.99270072992700731</v>
+      </c>
+      <c r="F20" s="29">
+        <v>1</v>
+      </c>
+      <c r="G20" s="29">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="H20" s="29">
+        <v>1</v>
+      </c>
+      <c r="I20" s="29">
+        <v>1</v>
+      </c>
+      <c r="J20" s="29">
+        <v>1</v>
+      </c>
+      <c r="K20" s="29">
+        <v>1</v>
+      </c>
+      <c r="L20" s="29">
+        <v>1</v>
+      </c>
+      <c r="M20" s="29">
+        <v>1</v>
+      </c>
+      <c r="N20" s="29">
+        <v>1</v>
+      </c>
+      <c r="O20" s="29">
+        <v>1</v>
+      </c>
+      <c r="P20" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="R20" s="29">
+        <v>1</v>
+      </c>
+      <c r="S20" s="29">
+        <v>1</v>
+      </c>
+      <c r="T20" s="29">
+        <v>1</v>
+      </c>
+      <c r="U20" s="29">
+        <v>1</v>
+      </c>
+      <c r="V20" s="29">
+        <v>1</v>
+      </c>
+      <c r="W20" s="29">
+        <v>1</v>
+      </c>
+      <c r="X20" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y20" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z20" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA20" s="29"/>
+      <c r="AB20" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC20" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD20" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE20" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF20" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG20" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A21" s="24"/>
+      <c r="B21" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C21" s="25">
+        <v>19</v>
+      </c>
+      <c r="D21" s="29">
+        <v>0.99411764705882355</v>
+      </c>
+      <c r="E21" s="29">
+        <v>0.99390243902439024</v>
+      </c>
+      <c r="F21" s="29">
+        <v>0.99431818181818177</v>
+      </c>
+      <c r="G21" s="29">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="H21" s="29">
+        <v>1</v>
+      </c>
+      <c r="I21" s="29">
+        <v>1</v>
+      </c>
+      <c r="J21" s="29">
+        <v>1</v>
+      </c>
+      <c r="K21" s="29">
+        <v>1</v>
+      </c>
+      <c r="L21" s="29">
+        <v>0.98305084745762716</v>
+      </c>
+      <c r="M21" s="29">
+        <v>1</v>
+      </c>
+      <c r="N21" s="29">
+        <v>1</v>
+      </c>
+      <c r="O21" s="29">
+        <v>1</v>
+      </c>
+      <c r="P21" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q21" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="R21" s="29">
+        <v>1</v>
+      </c>
+      <c r="S21" s="29">
+        <v>1</v>
+      </c>
+      <c r="T21" s="29">
+        <v>1</v>
+      </c>
+      <c r="U21" s="29">
+        <v>1</v>
+      </c>
+      <c r="V21" s="29">
+        <v>1</v>
+      </c>
+      <c r="W21" s="29">
+        <v>1</v>
+      </c>
+      <c r="X21" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y21" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z21" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA21" s="29"/>
+      <c r="AB21" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC21" s="29">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="AD21" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE21" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF21" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A22" s="24"/>
+      <c r="B22" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C22" s="25">
+        <v>20</v>
+      </c>
+      <c r="D22" s="29">
+        <v>0.98432601880877746</v>
+      </c>
+      <c r="E22" s="29">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="F22" s="29">
+        <v>1</v>
+      </c>
+      <c r="G22" s="29">
+        <v>0.86206896551724133</v>
+      </c>
+      <c r="H22" s="29">
+        <v>1</v>
+      </c>
+      <c r="I22" s="29">
+        <v>1</v>
+      </c>
+      <c r="J22" s="29">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="K22" s="29">
+        <v>1</v>
+      </c>
+      <c r="L22" s="29">
+        <v>1</v>
+      </c>
+      <c r="M22" s="29">
+        <v>1</v>
+      </c>
+      <c r="N22" s="29">
+        <v>1</v>
+      </c>
+      <c r="O22" s="29">
+        <v>1</v>
+      </c>
+      <c r="P22" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q22" s="29">
+        <v>1</v>
+      </c>
+      <c r="R22" s="29">
+        <v>1</v>
+      </c>
+      <c r="S22" s="29">
+        <v>1</v>
+      </c>
+      <c r="T22" s="29">
+        <v>1</v>
+      </c>
+      <c r="U22" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V22" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="W22" s="29">
+        <v>1</v>
+      </c>
+      <c r="X22" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y22" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z22" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA22" s="29"/>
+      <c r="AB22" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC22" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD22" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE22" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF22" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG22" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A23" s="24"/>
+      <c r="B23" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="25">
+        <v>21</v>
+      </c>
+      <c r="D23" s="29">
+        <v>0.93805309734513276</v>
+      </c>
+      <c r="E23" s="29">
+        <v>0.89637305699481862</v>
+      </c>
+      <c r="F23" s="29">
+        <v>0.99315068493150682</v>
+      </c>
+      <c r="G23" s="29">
+        <v>0.70731707317073167</v>
+      </c>
+      <c r="H23" s="29">
+        <v>1</v>
+      </c>
+      <c r="I23" s="29">
+        <v>1</v>
+      </c>
+      <c r="J23" s="29">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="K23" s="29">
+        <v>1</v>
+      </c>
+      <c r="L23" s="29">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="M23" s="29">
+        <v>1</v>
+      </c>
+      <c r="N23" s="29">
+        <v>1</v>
+      </c>
+      <c r="O23" s="29">
+        <v>1</v>
+      </c>
+      <c r="P23" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q23" s="29">
+        <v>1</v>
+      </c>
+      <c r="R23" s="29">
+        <v>1</v>
+      </c>
+      <c r="S23" s="29">
+        <v>1</v>
+      </c>
+      <c r="T23" s="29">
+        <v>1</v>
+      </c>
+      <c r="U23" s="29">
+        <v>0.45454545454545453</v>
+      </c>
+      <c r="V23" s="29">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="W23" s="29">
+        <v>1</v>
+      </c>
+      <c r="X23" s="29">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="Y23" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z23" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA23" s="29"/>
+      <c r="AB23" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC23" s="29">
+        <v>0.96875</v>
+      </c>
+      <c r="AD23" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE23" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF23" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG23" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A24" s="24"/>
+      <c r="B24" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C24" s="25">
+        <v>22</v>
+      </c>
+      <c r="D24" s="29">
+        <v>0.9196428571428571</v>
+      </c>
+      <c r="E24" s="29">
+        <v>0.86263736263736268</v>
+      </c>
+      <c r="F24" s="29">
+        <v>0.98701298701298701</v>
+      </c>
+      <c r="G24" s="29">
+        <v>0.63888888888888884</v>
+      </c>
+      <c r="H24" s="29"/>
+      <c r="I24" s="29">
+        <v>1</v>
+      </c>
+      <c r="J24" s="29">
+        <v>0.75555555555555554</v>
+      </c>
+      <c r="K24" s="29">
+        <v>0.98076923076923073</v>
+      </c>
+      <c r="L24" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="M24" s="29">
+        <v>1</v>
+      </c>
+      <c r="N24" s="29">
+        <v>1</v>
+      </c>
+      <c r="O24" s="29">
+        <v>1</v>
+      </c>
+      <c r="P24" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q24" s="29">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="R24" s="29">
+        <v>1</v>
+      </c>
+      <c r="S24" s="29">
+        <v>1</v>
+      </c>
+      <c r="T24" s="29">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="U24" s="29">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="V24" s="29">
+        <v>0.70588235294117652</v>
+      </c>
+      <c r="W24" s="29">
+        <v>1</v>
+      </c>
+      <c r="X24" s="29">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="Y24" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z24" s="29">
+        <v>1</v>
+      </c>
+      <c r="AA24" s="29"/>
+      <c r="AB24" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="AC24" s="29">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="AD24" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE24" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF24" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG24" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A25" s="24"/>
+      <c r="B25" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="25">
+        <v>23</v>
+      </c>
+      <c r="D25" s="29">
+        <v>0.99044585987261147</v>
+      </c>
+      <c r="E25" s="29">
+        <v>0.98265895953757221</v>
+      </c>
+      <c r="F25" s="29">
+        <v>1</v>
+      </c>
+      <c r="G25" s="29">
+        <v>0.90625</v>
+      </c>
+      <c r="H25" s="29"/>
+      <c r="I25" s="29">
+        <v>1</v>
+      </c>
+      <c r="J25" s="29">
+        <v>1</v>
+      </c>
+      <c r="K25" s="29">
+        <v>1</v>
+      </c>
+      <c r="L25" s="29">
+        <v>1</v>
+      </c>
+      <c r="M25" s="29">
+        <v>1</v>
+      </c>
+      <c r="N25" s="29">
+        <v>1</v>
+      </c>
+      <c r="O25" s="29">
+        <v>1</v>
+      </c>
+      <c r="P25" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q25" s="29">
+        <v>1</v>
+      </c>
+      <c r="R25" s="29">
+        <v>1</v>
+      </c>
+      <c r="S25" s="29">
+        <v>1</v>
+      </c>
+      <c r="T25" s="29">
+        <v>1</v>
+      </c>
+      <c r="U25" s="29">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="V25" s="29">
+        <v>1</v>
+      </c>
+      <c r="W25" s="29">
+        <v>1</v>
+      </c>
+      <c r="X25" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y25" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z25" s="29"/>
+      <c r="AA25" s="29"/>
+      <c r="AB25" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC25" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD25" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE25" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF25" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG25" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A26" s="24"/>
+      <c r="B26" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C26" s="25">
+        <v>24</v>
+      </c>
+      <c r="D26" s="29">
+        <v>0.99392097264437695</v>
+      </c>
+      <c r="E26" s="29">
+        <v>0.98870056497175141</v>
+      </c>
+      <c r="F26" s="29">
+        <v>1</v>
+      </c>
+      <c r="G26" s="29">
+        <v>1</v>
+      </c>
+      <c r="H26" s="29"/>
+      <c r="I26" s="29">
+        <v>1</v>
+      </c>
+      <c r="J26" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="K26" s="29">
+        <v>1</v>
+      </c>
+      <c r="L26" s="29">
+        <v>1</v>
+      </c>
+      <c r="M26" s="29">
+        <v>1</v>
+      </c>
+      <c r="N26" s="29">
+        <v>1</v>
+      </c>
+      <c r="O26" s="29">
+        <v>1</v>
+      </c>
+      <c r="P26" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q26" s="29">
+        <v>1</v>
+      </c>
+      <c r="R26" s="29">
+        <v>1</v>
+      </c>
+      <c r="S26" s="29">
+        <v>1</v>
+      </c>
+      <c r="T26" s="29">
+        <v>1</v>
+      </c>
+      <c r="U26" s="29">
+        <v>1</v>
+      </c>
+      <c r="V26" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="W26" s="29">
+        <v>1</v>
+      </c>
+      <c r="X26" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="Y26" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z26" s="29"/>
+      <c r="AA26" s="29"/>
+      <c r="AB26" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC26" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD26" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE26" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A27" s="24"/>
+      <c r="B27" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" s="25">
+        <v>25</v>
+      </c>
+      <c r="D27" s="29">
+        <v>0.91267605633802817</v>
+      </c>
+      <c r="E27" s="29">
+        <v>0.88717948717948714</v>
+      </c>
+      <c r="F27" s="29">
+        <v>0.94374999999999998</v>
+      </c>
+      <c r="G27" s="29">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="H27" s="29"/>
+      <c r="I27" s="29">
+        <v>0.97872340425531912</v>
+      </c>
+      <c r="J27" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="K27" s="29">
+        <v>1</v>
+      </c>
+      <c r="L27" s="29">
+        <v>0.8125</v>
+      </c>
+      <c r="M27" s="29">
+        <v>1</v>
+      </c>
+      <c r="N27" s="29">
+        <v>1</v>
+      </c>
+      <c r="O27" s="29">
+        <v>1</v>
+      </c>
+      <c r="P27" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q27" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="R27" s="29">
+        <v>1</v>
+      </c>
+      <c r="S27" s="29">
+        <v>1</v>
+      </c>
+      <c r="T27" s="29">
+        <v>1</v>
+      </c>
+      <c r="U27" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V27" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="W27" s="29">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="X27" s="29">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="Y27" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z27" s="29"/>
+      <c r="AA27" s="29"/>
+      <c r="AB27" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="AC27" s="29">
+        <v>0.77142857142857146</v>
+      </c>
+      <c r="AD27" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE27" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF27" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG27" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A28" s="24"/>
+      <c r="B28" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="25">
+        <v>26</v>
+      </c>
+      <c r="D28" s="29">
+        <v>0.9027027027027027</v>
+      </c>
+      <c r="E28" s="29">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="F28" s="29">
+        <v>0.94478527607361962</v>
+      </c>
+      <c r="G28" s="29">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="H28" s="29"/>
+      <c r="I28" s="29">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J28" s="29">
+        <v>0.73584905660377353</v>
+      </c>
+      <c r="K28" s="29">
+        <v>1</v>
+      </c>
+      <c r="L28" s="29">
+        <v>0.81632653061224492</v>
+      </c>
+      <c r="M28" s="29">
+        <v>1</v>
+      </c>
+      <c r="N28" s="29">
+        <v>1</v>
+      </c>
+      <c r="O28" s="29">
+        <v>1</v>
+      </c>
+      <c r="P28" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q28" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="R28" s="29">
+        <v>1</v>
+      </c>
+      <c r="S28" s="29">
+        <v>1</v>
+      </c>
+      <c r="T28" s="29">
+        <v>1</v>
+      </c>
+      <c r="U28" s="29">
+        <v>0.59259259259259256</v>
+      </c>
+      <c r="V28" s="29">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="W28" s="29">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="X28" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="Y28" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z28" s="29"/>
+      <c r="AA28" s="29"/>
+      <c r="AB28" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="AC28" s="29">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AD28" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE28" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF28" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG28" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A29" s="24"/>
+      <c r="B29" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C29" s="25">
+        <v>27</v>
+      </c>
+      <c r="D29" s="29">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="E29" s="29">
+        <v>0.95394736842105265</v>
+      </c>
+      <c r="F29" s="29">
+        <v>0.99264705882352944</v>
+      </c>
+      <c r="G29" s="29">
+        <v>1</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="29">
+        <v>0.97368421052631582</v>
+      </c>
+      <c r="J29" s="29">
+        <v>0.7931034482758621</v>
+      </c>
+      <c r="K29" s="29">
+        <v>1</v>
+      </c>
+      <c r="L29" s="29">
+        <v>1</v>
+      </c>
+      <c r="M29" s="29">
+        <v>1</v>
+      </c>
+      <c r="N29" s="29">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="O29" s="29">
+        <v>1</v>
+      </c>
+      <c r="P29" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q29" s="29">
+        <v>1</v>
+      </c>
+      <c r="R29" s="29">
+        <v>1</v>
+      </c>
+      <c r="S29" s="29">
+        <v>1</v>
+      </c>
+      <c r="T29" s="29">
+        <v>1</v>
+      </c>
+      <c r="U29" s="29">
+        <v>1</v>
+      </c>
+      <c r="V29" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="W29" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="X29" s="29">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="Y29" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z29" s="29"/>
+      <c r="AA29" s="29"/>
+      <c r="AB29" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC29" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD29" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE29" s="29">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="AF29" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG29" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A30" s="24"/>
+      <c r="B30" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C30" s="25">
+        <v>28</v>
+      </c>
+      <c r="D30" s="29">
+        <v>0.99132947976878616</v>
+      </c>
+      <c r="E30" s="29">
+        <v>0.9838709677419355</v>
+      </c>
+      <c r="F30" s="29">
+        <v>1</v>
+      </c>
+      <c r="G30" s="29">
+        <v>1</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="29">
+        <v>1</v>
+      </c>
+      <c r="J30" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="K30" s="29">
+        <v>1</v>
+      </c>
+      <c r="L30" s="29">
+        <v>1</v>
+      </c>
+      <c r="M30" s="29">
+        <v>1</v>
+      </c>
+      <c r="N30" s="29">
+        <v>1</v>
+      </c>
+      <c r="O30" s="29">
+        <v>1</v>
+      </c>
+      <c r="P30" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q30" s="29">
+        <v>1</v>
+      </c>
+      <c r="R30" s="29">
+        <v>1</v>
+      </c>
+      <c r="S30" s="29">
+        <v>1</v>
+      </c>
+      <c r="T30" s="29">
+        <v>1</v>
+      </c>
+      <c r="U30" s="29">
+        <v>1</v>
+      </c>
+      <c r="V30" s="29">
+        <v>1</v>
+      </c>
+      <c r="W30" s="29">
+        <v>1</v>
+      </c>
+      <c r="X30" s="29">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="Y30" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z30" s="29"/>
+      <c r="AA30" s="29"/>
+      <c r="AB30" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC30" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD30" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE30" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF30" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG30" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A31" s="24"/>
+      <c r="B31" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C31" s="25">
+        <v>29</v>
+      </c>
+      <c r="D31" s="29">
+        <v>0.94925373134328361</v>
+      </c>
+      <c r="E31" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="F31" s="29">
+        <v>0.95483870967741935</v>
+      </c>
+      <c r="G31" s="29">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="H31" s="29"/>
+      <c r="I31" s="29">
+        <v>1</v>
+      </c>
+      <c r="J31" s="29">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="K31" s="29">
+        <v>0.98360655737704916</v>
+      </c>
+      <c r="L31" s="29">
+        <v>0.86538461538461542</v>
+      </c>
+      <c r="M31" s="29">
+        <v>1</v>
+      </c>
+      <c r="N31" s="29">
+        <v>1</v>
+      </c>
+      <c r="O31" s="29">
+        <v>1</v>
+      </c>
+      <c r="P31" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q31" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="R31" s="29">
+        <v>1</v>
+      </c>
+      <c r="S31" s="29">
+        <v>1</v>
+      </c>
+      <c r="T31" s="29">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="U31" s="29">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="V31" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="W31" s="29">
+        <v>1</v>
+      </c>
+      <c r="X31" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y31" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z31" s="29"/>
+      <c r="AA31" s="29"/>
+      <c r="AB31" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="AC31" s="29">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="AD31" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE31" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF31" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG31" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A32" s="24"/>
+      <c r="B32" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="25">
+        <v>30</v>
+      </c>
+      <c r="D32" s="29">
+        <v>0.971830985915493</v>
+      </c>
+      <c r="E32" s="29">
+        <v>0.95811518324607325</v>
+      </c>
+      <c r="F32" s="29">
+        <v>0.98780487804878048</v>
+      </c>
+      <c r="G32" s="29">
+        <v>0.87804878048780488</v>
+      </c>
+      <c r="H32" s="29"/>
+      <c r="I32" s="29">
+        <v>1</v>
+      </c>
+      <c r="J32" s="29">
+        <v>0.93023255813953487</v>
+      </c>
+      <c r="K32" s="29">
+        <v>1</v>
+      </c>
+      <c r="L32" s="29">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="M32" s="29">
+        <v>1</v>
+      </c>
+      <c r="N32" s="29">
+        <v>1</v>
+      </c>
+      <c r="O32" s="29">
+        <v>1</v>
+      </c>
+      <c r="P32" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q32" s="29">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="R32" s="29">
+        <v>1</v>
+      </c>
+      <c r="S32" s="29">
+        <v>1</v>
+      </c>
+      <c r="T32" s="29">
+        <v>1</v>
+      </c>
+      <c r="U32" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="V32" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="W32" s="29">
+        <v>1</v>
+      </c>
+      <c r="X32" s="29">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="Y32" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z32" s="29"/>
+      <c r="AA32" s="29"/>
+      <c r="AB32" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC32" s="29">
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="AD32" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE32" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF32" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG32" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A33" s="24"/>
+      <c r="B33" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C33" s="25">
+        <v>31</v>
+      </c>
+      <c r="D33" s="29">
+        <v>0.97385620915032678</v>
+      </c>
+      <c r="E33" s="29">
+        <v>0.97005988023952094</v>
+      </c>
+      <c r="F33" s="29">
+        <v>0.97841726618705038</v>
+      </c>
+      <c r="G33" s="29">
+        <v>1</v>
+      </c>
+      <c r="H33" s="29"/>
+      <c r="I33" s="29">
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="J33" s="29">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="K33" s="29">
+        <v>1</v>
+      </c>
+      <c r="L33" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="M33" s="29">
+        <v>1</v>
+      </c>
+      <c r="N33" s="29">
+        <v>1</v>
+      </c>
+      <c r="O33" s="29">
+        <v>1</v>
+      </c>
+      <c r="P33" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q33" s="29">
+        <v>1</v>
+      </c>
+      <c r="R33" s="29">
+        <v>1</v>
+      </c>
+      <c r="S33" s="29">
+        <v>1</v>
+      </c>
+      <c r="T33" s="29">
+        <v>1</v>
+      </c>
+      <c r="U33" s="29">
+        <v>1</v>
+      </c>
+      <c r="V33" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="W33" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="X33" s="29">
+        <v>0.85</v>
+      </c>
+      <c r="Y33" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z33" s="29"/>
+      <c r="AA33" s="29"/>
+      <c r="AB33" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="AC33" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD33" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE33" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF33" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG33" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A34" s="24"/>
+      <c r="B34" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C34" s="25">
+        <v>32</v>
+      </c>
+      <c r="D34" s="29">
+        <v>0.98305084745762716</v>
+      </c>
+      <c r="E34" s="29">
+        <v>0.97841726618705038</v>
+      </c>
+      <c r="F34" s="29">
+        <v>0.98717948717948723</v>
+      </c>
+      <c r="G34" s="29">
+        <v>0.92</v>
+      </c>
+      <c r="H34" s="29"/>
+      <c r="I34" s="29">
+        <v>1</v>
+      </c>
+      <c r="J34" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="K34" s="29">
+        <v>1</v>
+      </c>
+      <c r="L34" s="29">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="M34" s="29">
+        <v>1</v>
+      </c>
+      <c r="N34" s="29">
+        <v>1</v>
+      </c>
+      <c r="O34" s="29">
+        <v>1</v>
+      </c>
+      <c r="P34" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q34" s="29">
+        <v>1</v>
+      </c>
+      <c r="R34" s="29">
+        <v>1</v>
+      </c>
+      <c r="S34" s="29">
+        <v>1</v>
+      </c>
+      <c r="T34" s="29">
+        <v>1</v>
+      </c>
+      <c r="U34" s="29">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="V34" s="29">
+        <v>1</v>
+      </c>
+      <c r="W34" s="29">
+        <v>1</v>
+      </c>
+      <c r="X34" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="Y34" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z34" s="29"/>
+      <c r="AA34" s="29"/>
+      <c r="AB34" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC34" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="AD34" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE34" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF34" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG34" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A35" s="24"/>
+      <c r="B35" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C35" s="25">
+        <v>33</v>
+      </c>
+      <c r="D35" s="29">
+        <v>0.98717948717948723</v>
+      </c>
+      <c r="E35" s="29">
+        <v>0.97452229299363058</v>
+      </c>
+      <c r="F35" s="29">
+        <v>1</v>
+      </c>
+      <c r="G35" s="29">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="H35" s="29"/>
+      <c r="I35" s="29">
+        <v>0.95744680851063835</v>
+      </c>
+      <c r="J35" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="K35" s="29">
+        <v>1</v>
+      </c>
+      <c r="L35" s="29">
+        <v>1</v>
+      </c>
+      <c r="M35" s="29">
+        <v>1</v>
+      </c>
+      <c r="N35" s="29">
+        <v>1</v>
+      </c>
+      <c r="O35" s="29">
+        <v>1</v>
+      </c>
+      <c r="P35" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q35" s="29">
+        <v>1</v>
+      </c>
+      <c r="R35" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="S35" s="29">
+        <v>1</v>
+      </c>
+      <c r="T35" s="29">
+        <v>1</v>
+      </c>
+      <c r="U35" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="V35" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="W35" s="29">
+        <v>1</v>
+      </c>
+      <c r="X35" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y35" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z35" s="29"/>
+      <c r="AA35" s="29"/>
+      <c r="AB35" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC35" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD35" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE35" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG35" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A36" s="24"/>
+      <c r="B36" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C36" s="25">
+        <v>34</v>
+      </c>
+      <c r="D36" s="29">
+        <v>0.989247311827957</v>
+      </c>
+      <c r="E36" s="29">
+        <v>0.9859154929577465</v>
+      </c>
+      <c r="F36" s="29">
+        <v>0.99270072992700731</v>
+      </c>
+      <c r="G36" s="29">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="H36" s="29"/>
+      <c r="I36" s="29">
+        <v>1</v>
+      </c>
+      <c r="J36" s="29">
+        <v>1</v>
+      </c>
+      <c r="K36" s="29">
+        <v>1</v>
+      </c>
+      <c r="L36" s="29">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="M36" s="29">
+        <v>1</v>
+      </c>
+      <c r="N36" s="29">
+        <v>1</v>
+      </c>
+      <c r="O36" s="29">
+        <v>1</v>
+      </c>
+      <c r="P36" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q36" s="29">
+        <v>1</v>
+      </c>
+      <c r="R36" s="29">
+        <v>1</v>
+      </c>
+      <c r="S36" s="29">
+        <v>1</v>
+      </c>
+      <c r="T36" s="29">
+        <v>1</v>
+      </c>
+      <c r="U36" s="29">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="V36" s="29">
+        <v>1</v>
+      </c>
+      <c r="W36" s="29">
+        <v>1</v>
+      </c>
+      <c r="X36" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y36" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z36" s="29"/>
+      <c r="AA36" s="29"/>
+      <c r="AB36" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC36" s="29">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="AD36" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE36" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF36" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG36" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A37" s="24"/>
+      <c r="B37" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C37" s="25">
+        <v>35</v>
+      </c>
+      <c r="D37" s="29">
+        <v>0.84146341463414631</v>
+      </c>
+      <c r="E37" s="29">
+        <v>0.72972972972972971</v>
+      </c>
+      <c r="F37" s="29">
+        <v>0.98601398601398604</v>
+      </c>
+      <c r="G37" s="29">
+        <v>0.55102040816326525</v>
+      </c>
+      <c r="H37" s="29"/>
+      <c r="I37" s="29">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="J37" s="29">
+        <v>0.46511627906976744</v>
+      </c>
+      <c r="K37" s="29">
+        <v>0.98275862068965514</v>
+      </c>
+      <c r="L37" s="29">
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="M37" s="29">
+        <v>1</v>
+      </c>
+      <c r="N37" s="29">
+        <v>1</v>
+      </c>
+      <c r="O37" s="29">
+        <v>1</v>
+      </c>
+      <c r="P37" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q37" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="R37" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="S37" s="29">
+        <v>1</v>
+      </c>
+      <c r="T37" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="U37" s="29">
+        <v>0.27586206896551724</v>
+      </c>
+      <c r="V37" s="29">
+        <v>0.5</v>
+      </c>
+      <c r="W37" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="X37" s="29">
+        <v>0.44</v>
+      </c>
+      <c r="Y37" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="29"/>
+      <c r="AA37" s="29"/>
+      <c r="AB37" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC37" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="AD37" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE37" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF37" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG37" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A38" s="24"/>
+      <c r="B38" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C38" s="25">
+        <v>36</v>
+      </c>
+      <c r="D38" s="29">
+        <v>0.89523809523809528</v>
+      </c>
+      <c r="E38" s="29">
+        <v>0.82702702702702702</v>
+      </c>
+      <c r="F38" s="29">
+        <v>0.99230769230769234</v>
+      </c>
+      <c r="G38" s="29">
+        <v>0.69767441860465118</v>
+      </c>
+      <c r="H38" s="29"/>
+      <c r="I38" s="29">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="J38" s="29">
+        <v>0.6875</v>
+      </c>
+      <c r="K38" s="29">
+        <v>0.94827586206896552</v>
+      </c>
+      <c r="L38" s="29">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="M38" s="29">
+        <v>1</v>
+      </c>
+      <c r="N38" s="29">
+        <v>1</v>
+      </c>
+      <c r="O38" s="29">
+        <v>1</v>
+      </c>
+      <c r="P38" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q38" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="R38" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="S38" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="T38" s="29">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="U38" s="29">
+        <v>0.62068965517241381</v>
+      </c>
+      <c r="V38" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="W38" s="29">
+        <v>0.81481481481481477</v>
+      </c>
+      <c r="X38" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Y38" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z38" s="29"/>
+      <c r="AA38" s="29"/>
+      <c r="AB38" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC38" s="29">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="AD38" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE38" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF38" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG38" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A39" s="24"/>
+      <c r="B39" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C39" s="25">
+        <v>37</v>
+      </c>
+      <c r="D39" s="29">
+        <v>0.93811074918566772</v>
+      </c>
+      <c r="E39" s="29">
+        <v>0.89308176100628933</v>
+      </c>
+      <c r="F39" s="29">
+        <v>0.98648648648648651</v>
+      </c>
+      <c r="G39" s="29">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="H39" s="29"/>
+      <c r="I39" s="29">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J39" s="29">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="K39" s="29">
+        <v>1</v>
+      </c>
+      <c r="L39" s="29">
+        <v>0.95348837209302328</v>
+      </c>
+      <c r="M39" s="29">
+        <v>1</v>
+      </c>
+      <c r="N39" s="29">
+        <v>1</v>
+      </c>
+      <c r="O39" s="29">
+        <v>1</v>
+      </c>
+      <c r="P39" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q39" s="29">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="R39" s="29">
+        <v>1</v>
+      </c>
+      <c r="S39" s="29">
+        <v>1</v>
+      </c>
+      <c r="T39" s="29">
+        <v>1</v>
+      </c>
+      <c r="U39" s="29">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="V39" s="29">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="W39" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="X39" s="29">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="Y39" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z39" s="29"/>
+      <c r="AA39" s="29"/>
+      <c r="AB39" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="AC39" s="29">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="AD39" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE39" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF39" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG39" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A40" s="24"/>
+      <c r="B40" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C40" s="25">
+        <v>38</v>
+      </c>
+      <c r="D40" s="29">
+        <v>0.84403669724770647</v>
+      </c>
+      <c r="E40" s="29">
+        <v>0.7528089887640449</v>
+      </c>
+      <c r="F40" s="29">
+        <v>0.95302013422818788</v>
+      </c>
+      <c r="G40" s="29">
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="H40" s="29"/>
+      <c r="I40" s="29">
+        <v>0.97619047619047616</v>
+      </c>
+      <c r="J40" s="29">
+        <v>0.26829268292682928</v>
+      </c>
+      <c r="K40" s="29">
+        <v>1</v>
+      </c>
+      <c r="L40" s="29">
+        <v>0.87234042553191493</v>
+      </c>
+      <c r="M40" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="N40" s="29">
+        <v>1</v>
+      </c>
+      <c r="O40" s="29">
+        <v>1</v>
+      </c>
+      <c r="P40" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q40" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="R40" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="S40" s="29">
+        <v>1</v>
+      </c>
+      <c r="T40" s="29">
+        <v>1</v>
+      </c>
+      <c r="U40" s="29">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="V40" s="29">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="W40" s="29">
+        <v>1</v>
+      </c>
+      <c r="X40" s="29">
+        <v>0.21739130434782608</v>
+      </c>
+      <c r="Y40" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z40" s="29"/>
+      <c r="AA40" s="29"/>
+      <c r="AB40" s="29">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="AC40" s="29">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="AD40" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="AE40" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF40" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG40" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A41" s="24"/>
+      <c r="B41" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C41" s="25">
+        <v>39</v>
+      </c>
+      <c r="D41" s="29">
+        <v>0.84139784946236562</v>
+      </c>
+      <c r="E41" s="29">
+        <v>0.71052631578947367</v>
+      </c>
+      <c r="F41" s="29">
+        <v>0.97802197802197799</v>
+      </c>
+      <c r="G41" s="29">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="H41" s="29"/>
+      <c r="I41" s="29">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="J41" s="29">
+        <v>7.1428571428571425E-2</v>
+      </c>
+      <c r="K41" s="29">
+        <v>1</v>
+      </c>
+      <c r="L41" s="29">
+        <v>0.94230769230769229</v>
+      </c>
+      <c r="M41" s="29">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="N41" s="29">
+        <v>1</v>
+      </c>
+      <c r="O41" s="29">
+        <v>1</v>
+      </c>
+      <c r="P41" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q41" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="R41" s="29">
+        <v>1</v>
+      </c>
+      <c r="S41" s="29">
+        <v>1</v>
+      </c>
+      <c r="T41" s="29">
+        <v>1</v>
+      </c>
+      <c r="U41" s="29">
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="V41" s="29">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="W41" s="29">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="X41" s="29">
+        <v>0</v>
+      </c>
+      <c r="Y41" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z41" s="29"/>
+      <c r="AA41" s="29"/>
+      <c r="AB41" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="AC41" s="29">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="AD41" s="29">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="AE41" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF41" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG41" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A42" s="24"/>
+      <c r="B42" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C42" s="25">
+        <v>40</v>
+      </c>
+      <c r="D42" s="29">
+        <v>0.97689768976897695</v>
+      </c>
+      <c r="E42" s="29">
+        <v>0.94927536231884058</v>
+      </c>
+      <c r="F42" s="29">
+        <v>1</v>
+      </c>
+      <c r="G42" s="29">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="H42" s="29"/>
+      <c r="I42" s="29">
+        <v>0.97619047619047616</v>
+      </c>
+      <c r="J42" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="K42" s="29">
+        <v>1</v>
+      </c>
+      <c r="L42" s="29">
+        <v>1</v>
+      </c>
+      <c r="M42" s="29">
+        <v>1</v>
+      </c>
+      <c r="N42" s="29">
+        <v>1</v>
+      </c>
+      <c r="O42" s="29">
+        <v>1</v>
+      </c>
+      <c r="P42" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q42" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="R42" s="29">
+        <v>1</v>
+      </c>
+      <c r="S42" s="29">
+        <v>1</v>
+      </c>
+      <c r="T42" s="29">
+        <v>1</v>
+      </c>
+      <c r="U42" s="29">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="V42" s="29">
+        <v>1</v>
+      </c>
+      <c r="W42" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="X42" s="29">
+        <v>0.8125</v>
+      </c>
+      <c r="Y42" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z42" s="29"/>
+      <c r="AA42" s="29"/>
+      <c r="AB42" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC42" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD42" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE42" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF42" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG42" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A43" s="24"/>
+      <c r="B43" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C43" s="25">
+        <v>41</v>
+      </c>
+      <c r="D43" s="29">
+        <v>0.99346405228758172</v>
+      </c>
+      <c r="E43" s="29">
+        <v>0.98496240601503759</v>
+      </c>
+      <c r="F43" s="29">
+        <v>1</v>
+      </c>
+      <c r="G43" s="29">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="H43" s="29"/>
+      <c r="I43" s="29">
+        <v>1</v>
+      </c>
+      <c r="J43" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="K43" s="29">
+        <v>1</v>
+      </c>
+      <c r="L43" s="29">
+        <v>1</v>
+      </c>
+      <c r="M43" s="29">
+        <v>1</v>
+      </c>
+      <c r="N43" s="29">
+        <v>1</v>
+      </c>
+      <c r="O43" s="29">
+        <v>1</v>
+      </c>
+      <c r="P43" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q43" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="R43" s="29">
+        <v>1</v>
+      </c>
+      <c r="S43" s="29">
+        <v>1</v>
+      </c>
+      <c r="T43" s="29">
+        <v>1</v>
+      </c>
+      <c r="U43" s="29">
+        <v>1</v>
+      </c>
+      <c r="V43" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="W43" s="29">
+        <v>1</v>
+      </c>
+      <c r="X43" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y43" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z43" s="29"/>
+      <c r="AA43" s="29"/>
+      <c r="AB43" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC43" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD43" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE43" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF43" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG43" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A44" s="24"/>
+      <c r="B44" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C44" s="25">
+        <v>42</v>
+      </c>
+      <c r="D44" s="29">
+        <v>0.97491039426523296</v>
+      </c>
+      <c r="E44" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="F44" s="29">
+        <v>0.99224806201550386</v>
+      </c>
+      <c r="G44" s="29">
+        <v>0.9375</v>
+      </c>
+      <c r="H44" s="29"/>
+      <c r="I44" s="29">
+        <v>1</v>
+      </c>
+      <c r="J44" s="29">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="K44" s="29">
+        <v>1</v>
+      </c>
+      <c r="L44" s="29">
+        <v>0.96875</v>
+      </c>
+      <c r="M44" s="29">
+        <v>1</v>
+      </c>
+      <c r="N44" s="29">
+        <v>1</v>
+      </c>
+      <c r="O44" s="29">
+        <v>1</v>
+      </c>
+      <c r="P44" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q44" s="29">
+        <v>1</v>
+      </c>
+      <c r="R44" s="29">
+        <v>1</v>
+      </c>
+      <c r="S44" s="29">
+        <v>1</v>
+      </c>
+      <c r="T44" s="29">
+        <v>1</v>
+      </c>
+      <c r="U44" s="29">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="V44" s="29">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="W44" s="29">
+        <v>1</v>
+      </c>
+      <c r="X44" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Y44" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z44" s="29"/>
+      <c r="AA44" s="29"/>
+      <c r="AB44" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC44" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="AD44" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE44" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF44" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG44" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A45" s="24"/>
+      <c r="B45" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C45" s="25">
+        <v>43</v>
+      </c>
+      <c r="D45" s="29">
+        <v>0.96463022508038587</v>
+      </c>
+      <c r="E45" s="29">
+        <v>0.95394736842105265</v>
+      </c>
+      <c r="F45" s="29">
+        <v>0.97484276729559749</v>
+      </c>
+      <c r="G45" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="H45" s="29"/>
+      <c r="I45" s="29">
+        <v>1</v>
+      </c>
+      <c r="J45" s="29">
+        <v>0.86206896551724133</v>
+      </c>
+      <c r="K45" s="29">
+        <v>1</v>
+      </c>
+      <c r="L45" s="29">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="M45" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="N45" s="29">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="O45" s="29">
+        <v>1</v>
+      </c>
+      <c r="P45" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q45" s="29">
+        <v>1</v>
+      </c>
+      <c r="R45" s="29">
+        <v>1</v>
+      </c>
+      <c r="S45" s="29">
+        <v>1</v>
+      </c>
+      <c r="T45" s="29">
+        <v>1</v>
+      </c>
+      <c r="U45" s="29">
+        <v>0.875</v>
+      </c>
+      <c r="V45" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="W45" s="29">
+        <v>1</v>
+      </c>
+      <c r="X45" s="29">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Y45" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z45" s="29"/>
+      <c r="AA45" s="29"/>
+      <c r="AB45" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC45" s="29">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="AD45" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="AE45" s="29">
+        <v>0.97222222222222221</v>
+      </c>
+      <c r="AF45" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG45" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A46" s="24"/>
+      <c r="B46" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C46" s="25">
+        <v>44</v>
+      </c>
+      <c r="D46" s="29">
+        <v>0.96440129449838186</v>
+      </c>
+      <c r="E46" s="29">
+        <v>0.9419354838709677</v>
+      </c>
+      <c r="F46" s="29">
+        <v>0.98701298701298701</v>
+      </c>
+      <c r="G46" s="29">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="H46" s="29"/>
+      <c r="I46" s="29">
+        <v>0.95918367346938771</v>
+      </c>
+      <c r="J46" s="29">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="K46" s="29">
+        <v>1</v>
+      </c>
+      <c r="L46" s="29">
+        <v>0.98</v>
+      </c>
+      <c r="M46" s="29">
+        <v>1</v>
+      </c>
+      <c r="N46" s="29">
+        <v>1</v>
+      </c>
+      <c r="O46" s="29">
+        <v>0.97727272727272729</v>
+      </c>
+      <c r="P46" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q46" s="29">
+        <v>1</v>
+      </c>
+      <c r="R46" s="29">
+        <v>1</v>
+      </c>
+      <c r="S46" s="29">
+        <v>1</v>
+      </c>
+      <c r="T46" s="29">
+        <v>1</v>
+      </c>
+      <c r="U46" s="29">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="V46" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="W46" s="29">
+        <v>0.92</v>
+      </c>
+      <c r="X46" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="Y46" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z46" s="29"/>
+      <c r="AA46" s="29"/>
+      <c r="AB46" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC46" s="29">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="AD46" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE46" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF46" s="29">
+        <v>0.97727272727272729</v>
+      </c>
+      <c r="AG46" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A47" s="24"/>
+      <c r="B47" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="25">
+        <v>45</v>
+      </c>
+      <c r="D47" s="29">
+        <v>0.99322033898305084</v>
+      </c>
+      <c r="E47" s="29">
+        <v>0.98742138364779874</v>
+      </c>
+      <c r="F47" s="29">
+        <v>1</v>
+      </c>
+      <c r="G47" s="29">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="H47" s="29"/>
+      <c r="I47" s="29">
+        <v>0.97674418604651159</v>
+      </c>
+      <c r="J47" s="29">
+        <v>1</v>
+      </c>
+      <c r="K47" s="29">
+        <v>1</v>
+      </c>
+      <c r="L47" s="29">
+        <v>1</v>
+      </c>
+      <c r="M47" s="29">
+        <v>1</v>
+      </c>
+      <c r="N47" s="29">
+        <v>1</v>
+      </c>
+      <c r="O47" s="29">
+        <v>1</v>
+      </c>
+      <c r="P47" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q47" s="29">
+        <v>1</v>
+      </c>
+      <c r="R47" s="29">
+        <v>1</v>
+      </c>
+      <c r="S47" s="29">
+        <v>1</v>
+      </c>
+      <c r="T47" s="29">
+        <v>1</v>
+      </c>
+      <c r="U47" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="V47" s="29">
+        <v>1</v>
+      </c>
+      <c r="W47" s="29">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="X47" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y47" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z47" s="29"/>
+      <c r="AA47" s="29"/>
+      <c r="AB47" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC47" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD47" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE47" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF47" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG47" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A48" s="24"/>
+      <c r="B48" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="25">
+        <v>46</v>
+      </c>
+      <c r="D48" s="29">
+        <v>0.94385026737967914</v>
+      </c>
+      <c r="E48" s="29">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="F48" s="29">
+        <v>0.9885057471264368</v>
+      </c>
+      <c r="G48" s="29">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="H48" s="29"/>
+      <c r="I48" s="29">
+        <v>1</v>
+      </c>
+      <c r="J48" s="29">
+        <v>1</v>
+      </c>
+      <c r="K48" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="L48" s="29">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="M48" s="29">
+        <v>1</v>
+      </c>
+      <c r="N48" s="29">
+        <v>1</v>
+      </c>
+      <c r="O48" s="29">
+        <v>1</v>
+      </c>
+      <c r="P48" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q48" s="29">
+        <v>1</v>
+      </c>
+      <c r="R48" s="29">
+        <v>1</v>
+      </c>
+      <c r="S48" s="29">
+        <v>1</v>
+      </c>
+      <c r="T48" s="29">
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="U48" s="29">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="V48" s="29">
+        <v>1</v>
+      </c>
+      <c r="W48" s="29">
+        <v>1</v>
+      </c>
+      <c r="X48" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y48" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="Z48" s="29"/>
+      <c r="AA48" s="29"/>
+      <c r="AB48" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="AC48" s="29">
+        <v>0.97142857142857142</v>
+      </c>
+      <c r="AD48" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE48" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A49" s="24"/>
+      <c r="B49" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="25">
+        <v>47</v>
+      </c>
+      <c r="D49" s="29">
+        <v>0.83934426229508197</v>
+      </c>
+      <c r="E49" s="29">
+        <v>0.70658682634730541</v>
+      </c>
+      <c r="F49" s="29">
+        <v>1</v>
+      </c>
+      <c r="G49" s="29">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="H49" s="29"/>
+      <c r="I49" s="29">
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="J49" s="29">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="K49" s="29">
+        <v>0.40384615384615385</v>
+      </c>
+      <c r="L49" s="29">
+        <v>1</v>
+      </c>
+      <c r="M49" s="29">
+        <v>1</v>
+      </c>
+      <c r="N49" s="29">
+        <v>1</v>
+      </c>
+      <c r="O49" s="29">
+        <v>1</v>
+      </c>
+      <c r="P49" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q49" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="R49" s="29">
+        <v>1</v>
+      </c>
+      <c r="S49" s="29">
+        <v>1</v>
+      </c>
+      <c r="T49" s="29">
+        <v>0</v>
+      </c>
+      <c r="U49" s="29">
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="V49" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="W49" s="29">
+        <v>0.96</v>
+      </c>
+      <c r="X49" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="Y49" s="29">
+        <v>0.1</v>
+      </c>
+      <c r="Z49" s="29"/>
+      <c r="AA49" s="29"/>
+      <c r="AB49" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC49" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD49" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE49" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF49" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG49" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A50" s="24"/>
+      <c r="B50" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="25">
+        <v>48</v>
+      </c>
+      <c r="D50" s="29">
+        <v>0.8262108262108262</v>
+      </c>
+      <c r="E50" s="29">
+        <v>0.70769230769230773</v>
+      </c>
+      <c r="F50" s="29">
+        <v>0.97435897435897434</v>
+      </c>
+      <c r="G50" s="29">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="H50" s="29"/>
+      <c r="I50" s="29">
+        <v>0.97959183673469385</v>
+      </c>
+      <c r="J50" s="29">
+        <v>0.73170731707317072</v>
+      </c>
+      <c r="K50" s="29">
+        <v>0.40677966101694918</v>
+      </c>
+      <c r="L50" s="29">
+        <v>0.89743589743589747</v>
+      </c>
+      <c r="M50" s="29">
+        <v>1</v>
+      </c>
+      <c r="N50" s="29">
+        <v>1</v>
+      </c>
+      <c r="O50" s="29">
+        <v>1</v>
+      </c>
+      <c r="P50" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q50" s="29">
+        <v>1</v>
+      </c>
+      <c r="R50" s="29">
+        <v>1</v>
+      </c>
+      <c r="S50" s="29">
+        <v>1</v>
+      </c>
+      <c r="T50" s="29">
+        <v>3.4482758620689655E-2</v>
+      </c>
+      <c r="U50" s="29">
+        <v>0.62962962962962965</v>
+      </c>
+      <c r="V50" s="29">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="W50" s="29">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="X50" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Y50" s="29">
+        <v>0</v>
+      </c>
+      <c r="Z50" s="29"/>
+      <c r="AA50" s="29"/>
+      <c r="AB50" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC50" s="29">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="AD50" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE50" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF50" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG50" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A51" s="24"/>
+      <c r="B51" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C51" s="25">
+        <v>49</v>
+      </c>
+      <c r="D51" s="29">
+        <v>0.98091603053435117</v>
+      </c>
+      <c r="E51" s="29">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="F51" s="29">
+        <v>1</v>
+      </c>
+      <c r="G51" s="29">
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="H51" s="29"/>
+      <c r="I51" s="29">
+        <v>1</v>
+      </c>
+      <c r="J51" s="29">
+        <v>1</v>
+      </c>
+      <c r="K51" s="29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="L51" s="29">
+        <v>1</v>
+      </c>
+      <c r="M51" s="29">
+        <v>1</v>
+      </c>
+      <c r="N51" s="29">
+        <v>1</v>
+      </c>
+      <c r="O51" s="29">
+        <v>1</v>
+      </c>
+      <c r="P51" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q51" s="29">
+        <v>1</v>
+      </c>
+      <c r="R51" s="29">
+        <v>1</v>
+      </c>
+      <c r="S51" s="29">
+        <v>1</v>
+      </c>
+      <c r="T51" s="29">
+        <v>1</v>
+      </c>
+      <c r="U51" s="29">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="V51" s="29">
+        <v>1</v>
+      </c>
+      <c r="W51" s="29">
+        <v>1</v>
+      </c>
+      <c r="X51" s="29">
+        <v>1</v>
+      </c>
+      <c r="Y51" s="29">
+        <v>0.25</v>
+      </c>
+      <c r="Z51" s="29"/>
+      <c r="AA51" s="29"/>
+      <c r="AB51" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC51" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD51" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE51" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF51" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG51" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A52" s="24"/>
+      <c r="B52" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C52" s="25">
+        <v>50</v>
+      </c>
+      <c r="D52" s="29">
+        <v>0.96491228070175439</v>
+      </c>
+      <c r="E52" s="29">
+        <v>0.9337349397590361</v>
+      </c>
+      <c r="F52" s="29">
+        <v>0.99431818181818177</v>
+      </c>
+      <c r="G52" s="29">
+        <v>0.94871794871794868</v>
+      </c>
+      <c r="H52" s="29"/>
+      <c r="I52" s="29">
+        <v>0.97916666666666663</v>
+      </c>
+      <c r="J52" s="29">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K52" s="29">
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="L52" s="29">
+        <v>1</v>
+      </c>
+      <c r="M52" s="29">
+        <v>1</v>
+      </c>
+      <c r="N52" s="29">
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="O52" s="29">
+        <v>1</v>
+      </c>
+      <c r="P52" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q52" s="29">
+        <v>1</v>
+      </c>
+      <c r="R52" s="29">
+        <v>1</v>
+      </c>
+      <c r="S52" s="29">
+        <v>1</v>
+      </c>
+      <c r="T52" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="U52" s="29">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="V52" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="W52" s="29">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="X52" s="29">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Y52" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="Z52" s="29"/>
+      <c r="AA52" s="29"/>
+      <c r="AB52" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC52" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD52" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE52" s="29">
+        <v>0.97058823529411764</v>
+      </c>
+      <c r="AF52" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG52" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A53" s="24"/>
+      <c r="B53" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C53" s="25">
+        <v>51</v>
+      </c>
+      <c r="D53" s="29">
+        <v>0.92356687898089174</v>
+      </c>
+      <c r="E53" s="29">
+        <v>0.90963855421686746</v>
+      </c>
+      <c r="F53" s="29">
+        <v>0.93918918918918914</v>
+      </c>
+      <c r="G53" s="29">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="H53" s="29"/>
+      <c r="I53" s="29">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="J53" s="29">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="K53" s="29">
+        <v>0.95</v>
+      </c>
+      <c r="L53" s="29">
+        <v>0.82692307692307687</v>
+      </c>
+      <c r="M53" s="29">
+        <v>1</v>
+      </c>
+      <c r="N53" s="29">
+        <v>1</v>
+      </c>
+      <c r="O53" s="29">
+        <v>1</v>
+      </c>
+      <c r="P53" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q53" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="R53" s="29">
+        <v>1</v>
+      </c>
+      <c r="S53" s="29">
+        <v>1</v>
+      </c>
+      <c r="T53" s="29">
+        <v>1</v>
+      </c>
+      <c r="U53" s="29">
+        <v>0.63157894736842102</v>
+      </c>
+      <c r="V53" s="29">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="W53" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="X53" s="29">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="Y53" s="29">
+        <v>0.8125</v>
+      </c>
+      <c r="Z53" s="29"/>
+      <c r="AA53" s="29"/>
+      <c r="AB53" s="29">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="AC53" s="29">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="AD53" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE53" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF53" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG53" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A54" s="24"/>
+      <c r="B54" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C54" s="25">
+        <v>52</v>
+      </c>
+      <c r="D54" s="29">
+        <v>0.92567567567567566</v>
+      </c>
+      <c r="E54" s="29">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="F54" s="29">
+        <v>0.97202797202797198</v>
+      </c>
+      <c r="G54" s="29">
+        <v>0.65714285714285714</v>
+      </c>
+      <c r="H54" s="29"/>
+      <c r="I54" s="29">
+        <v>1</v>
+      </c>
+      <c r="J54" s="29">
+        <v>0.8</v>
+      </c>
+      <c r="K54" s="29">
+        <v>1</v>
+      </c>
+      <c r="L54" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="M54" s="29">
+        <v>1</v>
+      </c>
+      <c r="N54" s="29">
+        <v>1</v>
+      </c>
+      <c r="O54" s="29">
+        <v>1</v>
+      </c>
+      <c r="P54" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q54" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="R54" s="29">
+        <v>1</v>
+      </c>
+      <c r="S54" s="29">
+        <v>1</v>
+      </c>
+      <c r="T54" s="29">
+        <v>1</v>
+      </c>
+      <c r="U54" s="29">
+        <v>0.45</v>
+      </c>
+      <c r="V54" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="W54" s="29">
+        <v>1</v>
+      </c>
+      <c r="X54" s="29">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Y54" s="29">
+        <v>1</v>
+      </c>
+      <c r="Z54" s="29"/>
+      <c r="AA54" s="29"/>
+      <c r="AB54" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC54" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="AD54" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE54" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF54" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG54" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A55" s="24"/>
+      <c r="B55" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C55" s="25">
+        <v>53</v>
+      </c>
+      <c r="D55" s="29">
+        <v>0.86602870813397126</v>
+      </c>
+      <c r="E55" s="29">
+        <v>0.7807017543859649</v>
+      </c>
+      <c r="F55" s="29">
+        <v>0.96842105263157896</v>
+      </c>
+      <c r="G55" s="29">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="H55" s="29"/>
+      <c r="I55" s="29">
+        <v>0.78125</v>
+      </c>
+      <c r="J55" s="29">
+        <v>0.65</v>
+      </c>
+      <c r="K55" s="29">
+        <v>0.86046511627906974</v>
+      </c>
+      <c r="L55" s="29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="M55" s="29">
+        <v>1</v>
+      </c>
+      <c r="N55" s="29">
+        <v>1</v>
+      </c>
+      <c r="O55" s="29">
+        <v>1</v>
+      </c>
+      <c r="P55" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="29">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="R55" s="29">
+        <v>1</v>
+      </c>
+      <c r="S55" s="29">
+        <v>1</v>
+      </c>
+      <c r="T55" s="29">
+        <v>0.84</v>
+      </c>
+      <c r="U55" s="29">
+        <v>1</v>
+      </c>
+      <c r="V55" s="29">
+        <v>1</v>
+      </c>
+      <c r="W55" s="29">
+        <v>0.65</v>
+      </c>
+      <c r="X55" s="29">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="Y55" s="29">
+        <v>0.6</v>
+      </c>
+      <c r="Z55" s="29"/>
+      <c r="AA55" s="29"/>
+      <c r="AB55" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="AC55" s="29">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="AD55" s="29">
+        <v>1</v>
+      </c>
+      <c r="AE55" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A56" s="26">
+        <v>2026</v>
+      </c>
+      <c r="B56" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C56" s="25">
+        <v>1</v>
+      </c>
+      <c r="D56" s="29">
+        <v>0.95438596491228067</v>
+      </c>
+      <c r="E56" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="F56" s="29">
+        <v>0.97391304347826091</v>
+      </c>
+      <c r="G56" s="29">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="H56" s="29"/>
+      <c r="I56" s="29">
+        <v>1</v>
+      </c>
+      <c r="J56" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="K56" s="29">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="L56" s="29">
+        <v>1</v>
+      </c>
+      <c r="M56" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N56" s="29">
+        <v>1</v>
+      </c>
+      <c r="O56" s="29">
+        <v>1</v>
+      </c>
+      <c r="P56" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="29">
+        <v>1</v>
+      </c>
+      <c r="R56" s="29">
+        <v>1</v>
+      </c>
+      <c r="S56" s="29">
+        <v>1</v>
+      </c>
+      <c r="T56" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="U56" s="29">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="V56" s="29">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="W56" s="29">
+        <v>1</v>
+      </c>
+      <c r="X56" s="29">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Y56" s="29">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="Z56" s="29"/>
+      <c r="AA56" s="29"/>
+      <c r="AB56" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="29">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="AE56" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A57" s="26"/>
+      <c r="B57" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C57" s="25">
+        <v>2</v>
+      </c>
+      <c r="D57" s="29">
+        <v>0.89308176100628933</v>
+      </c>
+      <c r="E57" s="29">
+        <v>0.86082474226804129</v>
+      </c>
+      <c r="F57" s="29">
+        <v>0.94354838709677424</v>
+      </c>
+      <c r="G57" s="29">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="H57" s="29"/>
+      <c r="I57" s="29">
+        <v>0.98148148148148151</v>
+      </c>
+      <c r="J57" s="29">
+        <v>0.77083333333333337</v>
+      </c>
+      <c r="K57" s="29">
+        <v>0.88</v>
+      </c>
+      <c r="L57" s="29">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="M57" s="29">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="N57" s="29">
+        <v>1</v>
+      </c>
+      <c r="O57" s="29">
+        <v>1</v>
+      </c>
+      <c r="P57" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="29">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="R57" s="29">
+        <v>1</v>
+      </c>
+      <c r="S57" s="29">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="T57" s="29">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="U57" s="29">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="V57" s="29">
+        <v>0.8214285714285714</v>
+      </c>
+      <c r="W57" s="29">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="X57" s="29">
+        <v>0.7</v>
+      </c>
+      <c r="Y57" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="Z57" s="29"/>
+      <c r="AA57" s="29"/>
+      <c r="AB57" s="29">
+        <v>1</v>
+      </c>
+      <c r="AC57" s="29">
+        <v>0.84210526315789469</v>
+      </c>
+      <c r="AD57" s="29">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="AE57" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG57" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A58" s="26"/>
+      <c r="B58" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C58" s="25">
+        <v>3</v>
+      </c>
+      <c r="D58" s="29">
+        <v>0.80712166172106825</v>
+      </c>
+      <c r="E58" s="29">
+        <v>0.80981595092024539</v>
+      </c>
+      <c r="F58" s="29">
+        <v>0.8045977011494253</v>
+      </c>
+      <c r="G58" s="29">
+        <v>0.69444444444444442</v>
+      </c>
+      <c r="H58" s="29"/>
+      <c r="I58" s="29">
+        <v>0.9</v>
+      </c>
+      <c r="J58" s="29">
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="K58" s="29">
+        <v>0.86046511627906974</v>
+      </c>
+      <c r="L58" s="29">
+        <v>0.6607142857142857</v>
+      </c>
+      <c r="M58" s="29">
+        <v>0.48275862068965519</v>
+      </c>
+      <c r="N58" s="29">
+        <v>1</v>
+      </c>
+      <c r="O58" s="29">
+        <v>1</v>
+      </c>
+      <c r="P58" s="29">
+        <v>1</v>
+      </c>
+      <c r="Q58" s="29">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="R58" s="29">
+        <v>1</v>
+      </c>
+      <c r="S58" s="29">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="T58" s="29">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="U58" s="29">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="V58" s="29">
+        <v>0.75</v>
+      </c>
+      <c r="W58" s="29">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="X58" s="29">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="Y58" s="29">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="Z58" s="29"/>
+      <c r="AA58" s="29"/>
+      <c r="AB58" s="29">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="AC58" s="29">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="AD58" s="29">
+        <v>0.48275862068965519</v>
+      </c>
+      <c r="AE58" s="29">
+        <v>1</v>
+      </c>
+      <c r="AF58" s="29">
+        <v>1</v>
+      </c>
+      <c r="AG58" s="29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A59" s="26"/>
+      <c r="B59" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C59" s="25">
+        <v>4</v>
+      </c>
+      <c r="D59" s="30">
+        <v>0.93157894736842106</v>
+      </c>
+      <c r="E59" s="30">
+        <v>0.91</v>
+      </c>
+      <c r="F59" s="30">
+        <v>0.9555555555555556</v>
+      </c>
+      <c r="G59" s="30">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="H59" s="30"/>
+      <c r="I59" s="30">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="J59" s="30">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="K59" s="30">
+        <v>0.84375</v>
+      </c>
+      <c r="L59" s="30">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="M59" s="30">
+        <v>1</v>
+      </c>
+      <c r="N59" s="30">
+        <v>1</v>
+      </c>
+      <c r="O59" s="30">
+        <v>1</v>
+      </c>
+      <c r="P59" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q59" s="30">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="R59" s="30">
+        <v>1</v>
+      </c>
+      <c r="S59" s="30">
+        <v>1</v>
+      </c>
+      <c r="T59" s="30">
+        <v>0.7</v>
+      </c>
+      <c r="U59" s="30">
+        <v>1</v>
+      </c>
+      <c r="V59" s="30">
+        <v>1</v>
+      </c>
+      <c r="W59" s="30">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="X59" s="30">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="Y59" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="Z59" s="30"/>
+      <c r="AA59" s="30"/>
+      <c r="AB59" s="30">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AC59" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="AD59" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE59" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF59" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG59" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A60" s="26"/>
+      <c r="B60" s="25" t="s">
+        <v>4</v>
+      </c>
+      <c r="C60" s="25">
+        <v>5</v>
+      </c>
+      <c r="D60" s="30">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="E60" s="30">
+        <v>0.9213483146067416</v>
+      </c>
+      <c r="F60" s="30">
+        <v>1</v>
+      </c>
+      <c r="G60" s="30">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="H60" s="30"/>
+      <c r="I60" s="30">
+        <v>0.95</v>
+      </c>
+      <c r="J60" s="30">
+        <v>0.95</v>
+      </c>
+      <c r="K60" s="30">
+        <v>1</v>
+      </c>
+      <c r="L60" s="30">
+        <v>1</v>
+      </c>
+      <c r="M60" s="30">
+        <v>1</v>
+      </c>
+      <c r="N60" s="30">
+        <v>1</v>
+      </c>
+      <c r="O60" s="30">
+        <v>1</v>
+      </c>
+      <c r="P60" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q60" s="30">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="R60" s="30">
+        <v>1</v>
+      </c>
+      <c r="S60" s="30">
+        <v>1</v>
+      </c>
+      <c r="T60" s="30">
+        <v>1</v>
+      </c>
+      <c r="U60" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="V60" s="30">
+        <v>1</v>
+      </c>
+      <c r="W60" s="30">
+        <v>0.875</v>
+      </c>
+      <c r="X60" s="30">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Y60" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z60" s="30"/>
+      <c r="AA60" s="30"/>
+      <c r="AB60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF60" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG60" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A61" s="26"/>
+      <c r="B61" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C61" s="25">
+        <v>6</v>
+      </c>
+      <c r="D61" s="30">
+        <v>0.99465240641711228</v>
+      </c>
+      <c r="E61" s="30">
+        <v>0.99038461538461542</v>
+      </c>
+      <c r="F61" s="30">
+        <v>1</v>
+      </c>
+      <c r="G61" s="30">
+        <v>1</v>
+      </c>
+      <c r="H61" s="30"/>
+      <c r="I61" s="30">
+        <v>1</v>
+      </c>
+      <c r="J61" s="30">
+        <v>1</v>
+      </c>
+      <c r="K61" s="30">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="L61" s="30">
+        <v>1</v>
+      </c>
+      <c r="M61" s="30">
+        <v>1</v>
+      </c>
+      <c r="N61" s="30">
+        <v>1</v>
+      </c>
+      <c r="O61" s="30">
+        <v>1</v>
+      </c>
+      <c r="P61" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q61" s="30">
+        <v>1</v>
+      </c>
+      <c r="R61" s="30">
+        <v>1</v>
+      </c>
+      <c r="S61" s="30">
+        <v>1</v>
+      </c>
+      <c r="T61" s="30">
+        <v>1</v>
+      </c>
+      <c r="U61" s="30">
+        <v>1</v>
+      </c>
+      <c r="V61" s="30">
+        <v>1</v>
+      </c>
+      <c r="W61" s="30">
+        <v>1</v>
+      </c>
+      <c r="X61" s="30">
+        <v>1</v>
+      </c>
+      <c r="Y61" s="30">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z61" s="30"/>
+      <c r="AA61" s="30"/>
+      <c r="AB61" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC61" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD61" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE61" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF61" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG61" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A62" s="26"/>
+      <c r="B62" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C62" s="25">
+        <v>7</v>
+      </c>
+      <c r="D62" s="30">
+        <v>0.87111111111111106</v>
+      </c>
+      <c r="E62" s="30">
+        <v>0.79032258064516125</v>
+      </c>
+      <c r="F62" s="30">
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="G62" s="30">
+        <v>0.72413793103448276</v>
+      </c>
+      <c r="H62" s="30"/>
+      <c r="I62" s="30">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="J62" s="30">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="K62" s="30">
+        <v>0.81578947368421051</v>
+      </c>
+      <c r="L62" s="30">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="M62" s="30">
+        <v>1</v>
+      </c>
+      <c r="N62" s="30">
+        <v>1</v>
+      </c>
+      <c r="O62" s="30">
+        <v>1</v>
+      </c>
+      <c r="P62" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q62" s="30">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="R62" s="30">
+        <v>1</v>
+      </c>
+      <c r="S62" s="30">
+        <v>0.875</v>
+      </c>
+      <c r="T62" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="U62" s="30">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="V62" s="30">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="W62" s="30">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="X62" s="30">
+        <v>0.35714285714285715</v>
+      </c>
+      <c r="Y62" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="Z62" s="30"/>
+      <c r="AA62" s="30"/>
+      <c r="AB62" s="30">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="AC62" s="30">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="AD62" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE62" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG62" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A63" s="26"/>
+      <c r="B63" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C63" s="25">
+        <v>8</v>
+      </c>
+      <c r="D63" s="30">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="E63" s="30">
+        <v>0.77358490566037741</v>
+      </c>
+      <c r="F63" s="30">
+        <v>0.96808510638297873</v>
+      </c>
+      <c r="G63" s="30">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="H63" s="30"/>
+      <c r="I63" s="30">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="J63" s="30">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="K63" s="30">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="L63" s="30">
+        <v>0.8928571428571429</v>
+      </c>
+      <c r="M63" s="30">
+        <v>1</v>
+      </c>
+      <c r="N63" s="30">
+        <v>1</v>
+      </c>
+      <c r="O63" s="30">
+        <v>1</v>
+      </c>
+      <c r="P63" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q63" s="30">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="R63" s="30">
+        <v>1</v>
+      </c>
+      <c r="S63" s="30">
+        <v>1</v>
+      </c>
+      <c r="T63" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U63" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="V63" s="30">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="W63" s="30">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="X63" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Y63" s="30">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z63" s="30"/>
+      <c r="AA63" s="30"/>
+      <c r="AB63" s="30">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="AC63" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="AD63" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE63" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF63" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG63" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A64" s="26"/>
+      <c r="B64" s="25" t="s">
+        <v>5</v>
+      </c>
+      <c r="C64" s="25">
+        <v>9</v>
+      </c>
+      <c r="D64" s="30">
+        <v>0.97607655502392343</v>
+      </c>
+      <c r="E64" s="30">
+        <v>0.95283018867924529</v>
+      </c>
+      <c r="F64" s="30">
+        <v>1</v>
+      </c>
+      <c r="G64" s="30">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="H64" s="30"/>
+      <c r="I64" s="30">
+        <v>0.97368421052631582</v>
+      </c>
+      <c r="J64" s="30">
+        <v>0.88</v>
+      </c>
+      <c r="K64" s="30">
+        <v>1</v>
+      </c>
+      <c r="L64" s="30">
+        <v>1</v>
+      </c>
+      <c r="M64" s="30">
+        <v>1</v>
+      </c>
+      <c r="N64" s="30">
+        <v>1</v>
+      </c>
+      <c r="O64" s="30">
+        <v>1</v>
+      </c>
+      <c r="P64" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q64" s="30">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="R64" s="30">
+        <v>1</v>
+      </c>
+      <c r="S64" s="30">
+        <v>1</v>
+      </c>
+      <c r="T64" s="30">
+        <v>1</v>
+      </c>
+      <c r="U64" s="30">
+        <v>1</v>
+      </c>
+      <c r="V64" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="W64" s="30">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="X64" s="30">
+        <v>1</v>
+      </c>
+      <c r="Y64" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z64" s="30"/>
+      <c r="AA64" s="30"/>
+      <c r="AB64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AC64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF64" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG64" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A65" s="26"/>
+      <c r="B65" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C65" s="25">
+        <v>10</v>
+      </c>
+      <c r="D65" s="30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="E65" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="F65" s="30">
+        <v>0.93859649122807021</v>
+      </c>
+      <c r="G65" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="H65" s="30"/>
+      <c r="I65" s="30">
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="J65" s="30">
+        <v>0.45714285714285713</v>
+      </c>
+      <c r="K65" s="30">
+        <v>0.84090909090909094</v>
+      </c>
+      <c r="L65" s="30">
+        <v>0.80555555555555558</v>
+      </c>
+      <c r="M65" s="30">
+        <v>1</v>
+      </c>
+      <c r="N65" s="30">
+        <v>1</v>
+      </c>
+      <c r="O65" s="30">
+        <v>1</v>
+      </c>
+      <c r="P65" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q65" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="R65" s="30">
+        <v>1</v>
+      </c>
+      <c r="S65" s="30">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="T65" s="30">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U65" s="30">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="V65" s="30">
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="W65" s="30">
+        <v>0.9</v>
+      </c>
+      <c r="X65" s="30">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="Y65" s="30">
+        <v>1</v>
+      </c>
+      <c r="Z65" s="30"/>
+      <c r="AA65" s="30"/>
+      <c r="AB65" s="30">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AC65" s="30">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="AD65" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE65" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF65" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG65" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A66" s="26"/>
+      <c r="B66" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="25">
+        <v>11</v>
+      </c>
+      <c r="D66" s="30">
+        <v>0.78181818181818186</v>
+      </c>
+      <c r="E66" s="30">
+        <v>0.65573770491803274</v>
+      </c>
+      <c r="F66" s="30">
+        <v>0.93877551020408168</v>
+      </c>
+      <c r="G66" s="30">
+        <v>0.3</v>
+      </c>
+      <c r="H66" s="30"/>
+      <c r="I66" s="30">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="J66" s="30">
+        <v>0.875</v>
+      </c>
+      <c r="K66" s="30">
+        <v>0.55263157894736847</v>
+      </c>
+      <c r="L66" s="30">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="M66" s="30">
+        <v>1</v>
+      </c>
+      <c r="N66" s="30">
+        <v>1</v>
+      </c>
+      <c r="O66" s="30">
+        <v>1</v>
+      </c>
+      <c r="P66" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q66" s="30">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="R66" s="30">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="S66" s="30">
+        <v>0.47058823529411764</v>
+      </c>
+      <c r="T66" s="30">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="U66" s="30">
+        <v>0.26666666666666666</v>
+      </c>
+      <c r="V66" s="30">
+        <v>1</v>
+      </c>
+      <c r="W66" s="30">
+        <v>1</v>
+      </c>
+      <c r="X66" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="Y66" s="30">
+        <v>0.7</v>
+      </c>
+      <c r="Z66" s="30"/>
+      <c r="AA66" s="30"/>
+      <c r="AB66" s="30">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="AC66" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="AD66" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE66" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF66" s="30">
+        <v>1</v>
+      </c>
+      <c r="AG66" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A67" s="26"/>
+      <c r="B67" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C67" s="25">
+        <v>12</v>
+      </c>
+      <c r="D67" s="30">
+        <v>0.79253112033195017</v>
+      </c>
+      <c r="E67" s="30">
+        <v>0.67479674796747968</v>
+      </c>
+      <c r="F67" s="30">
+        <v>0.9152542372881356</v>
+      </c>
+      <c r="G67" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="H67" s="30"/>
+      <c r="I67" s="30">
+        <v>0.73529411764705888</v>
+      </c>
+      <c r="J67" s="30">
+        <v>0.79166666666666663</v>
+      </c>
+      <c r="K67" s="30">
+        <v>0.65853658536585369</v>
+      </c>
+      <c r="L67" s="30">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="M67" s="30">
+        <v>1</v>
+      </c>
+      <c r="N67" s="30">
+        <v>1</v>
+      </c>
+      <c r="O67" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="P67" s="30">
+        <v>1</v>
+      </c>
+      <c r="Q67" s="30">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="R67" s="30">
+        <v>1</v>
+      </c>
+      <c r="S67" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="T67" s="30">
+        <v>0.75</v>
+      </c>
+      <c r="U67" s="30">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="V67" s="30">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="W67" s="30">
+        <v>0.4375</v>
+      </c>
+      <c r="X67" s="30">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Y67" s="30">
+        <v>0.54545454545454541</v>
+      </c>
+      <c r="Z67" s="30"/>
+      <c r="AA67" s="30"/>
+      <c r="AB67" s="30">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="AC67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AD67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AE67" s="30">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="30">
+        <v>0.8</v>
+      </c>
+      <c r="AG67" s="30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A68" s="26"/>
+      <c r="B68" s="25" t="s">
+        <v>6</v>
+      </c>
+      <c r="C68" s="25">
+        <v>13</v>
+      </c>
+      <c r="D68" s="27"/>
+      <c r="E68" s="27"/>
+      <c r="F68" s="27"/>
+      <c r="G68" s="27"/>
+      <c r="H68" s="27"/>
+      <c r="I68" s="27"/>
+      <c r="J68" s="27"/>
+      <c r="K68" s="27"/>
+      <c r="L68" s="27"/>
+      <c r="M68" s="27"/>
+      <c r="N68" s="27"/>
+      <c r="O68" s="27"/>
+      <c r="P68" s="27"/>
+      <c r="Q68" s="27"/>
+      <c r="R68" s="27"/>
+      <c r="S68" s="27"/>
+      <c r="T68" s="27"/>
+      <c r="U68" s="27"/>
+      <c r="V68" s="27"/>
+      <c r="W68" s="27"/>
+      <c r="X68" s="27"/>
+      <c r="Y68" s="27"/>
+      <c r="Z68" s="27"/>
+      <c r="AA68" s="27"/>
+      <c r="AB68" s="27"/>
+      <c r="AC68" s="27"/>
+      <c r="AD68" s="27"/>
+      <c r="AE68" s="27"/>
+      <c r="AF68" s="27"/>
+      <c r="AG68" s="27"/>
+    </row>
+    <row r="69" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A69" s="26"/>
+      <c r="B69" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C69" s="25">
+        <v>14</v>
+      </c>
+      <c r="D69" s="27"/>
+      <c r="E69" s="27"/>
+      <c r="F69" s="27"/>
+      <c r="G69" s="27"/>
+      <c r="H69" s="27"/>
+      <c r="I69" s="27"/>
+      <c r="J69" s="27"/>
+      <c r="K69" s="27"/>
+      <c r="L69" s="27"/>
+      <c r="M69" s="27"/>
+      <c r="N69" s="27"/>
+      <c r="O69" s="27"/>
+      <c r="P69" s="27"/>
+      <c r="Q69" s="27"/>
+      <c r="R69" s="27"/>
+      <c r="S69" s="27"/>
+      <c r="T69" s="27"/>
+      <c r="U69" s="27"/>
+      <c r="V69" s="27"/>
+      <c r="W69" s="27"/>
+      <c r="X69" s="27"/>
+      <c r="Y69" s="27"/>
+      <c r="Z69" s="27"/>
+      <c r="AA69" s="27"/>
+      <c r="AB69" s="27"/>
+      <c r="AC69" s="27"/>
+      <c r="AD69" s="27"/>
+      <c r="AE69" s="27"/>
+      <c r="AF69" s="27"/>
+      <c r="AG69" s="27"/>
+    </row>
+    <row r="70" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A70" s="26"/>
+      <c r="B70" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C70" s="25">
+        <v>15</v>
+      </c>
+      <c r="D70" s="27"/>
+      <c r="E70" s="27"/>
+      <c r="F70" s="27"/>
+      <c r="G70" s="27"/>
+      <c r="H70" s="27"/>
+      <c r="I70" s="27"/>
+      <c r="J70" s="27"/>
+      <c r="K70" s="27"/>
+      <c r="L70" s="27"/>
+      <c r="M70" s="27"/>
+      <c r="N70" s="27"/>
+      <c r="O70" s="27"/>
+      <c r="P70" s="27"/>
+      <c r="Q70" s="27"/>
+      <c r="R70" s="27"/>
+      <c r="S70" s="27"/>
+      <c r="T70" s="27"/>
+      <c r="U70" s="27"/>
+      <c r="V70" s="27"/>
+      <c r="W70" s="27"/>
+      <c r="X70" s="27"/>
+      <c r="Y70" s="27"/>
+      <c r="Z70" s="27"/>
+      <c r="AA70" s="27"/>
+      <c r="AB70" s="27"/>
+      <c r="AC70" s="27"/>
+      <c r="AD70" s="27"/>
+      <c r="AE70" s="27"/>
+      <c r="AF70" s="27"/>
+      <c r="AG70" s="27"/>
+    </row>
+    <row r="71" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A71" s="26"/>
+      <c r="B71" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C71" s="25">
+        <v>16</v>
+      </c>
+      <c r="D71" s="27"/>
+      <c r="E71" s="27"/>
+      <c r="F71" s="27"/>
+      <c r="G71" s="27"/>
+      <c r="H71" s="27"/>
+      <c r="I71" s="27"/>
+      <c r="J71" s="27"/>
+      <c r="K71" s="27"/>
+      <c r="L71" s="27"/>
+      <c r="M71" s="27"/>
+      <c r="N71" s="27"/>
+      <c r="O71" s="27"/>
+      <c r="P71" s="27"/>
+      <c r="Q71" s="27"/>
+      <c r="R71" s="27"/>
+      <c r="S71" s="27"/>
+      <c r="T71" s="27"/>
+      <c r="U71" s="27"/>
+      <c r="V71" s="27"/>
+      <c r="W71" s="27"/>
+      <c r="X71" s="27"/>
+      <c r="Y71" s="27"/>
+      <c r="Z71" s="27"/>
+      <c r="AA71" s="27"/>
+      <c r="AB71" s="27"/>
+      <c r="AC71" s="27"/>
+      <c r="AD71" s="27"/>
+      <c r="AE71" s="27"/>
+      <c r="AF71" s="27"/>
+      <c r="AG71" s="27"/>
+    </row>
+    <row r="72" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A72" s="26"/>
+      <c r="B72" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="25">
+        <v>17</v>
+      </c>
+      <c r="D72" s="27"/>
+      <c r="E72" s="27"/>
+      <c r="F72" s="27"/>
+      <c r="G72" s="27"/>
+      <c r="H72" s="27"/>
+      <c r="I72" s="27"/>
+      <c r="J72" s="27"/>
+      <c r="K72" s="27"/>
+      <c r="L72" s="27"/>
+      <c r="M72" s="27"/>
+      <c r="N72" s="27"/>
+      <c r="O72" s="27"/>
+      <c r="P72" s="27"/>
+      <c r="Q72" s="27"/>
+      <c r="R72" s="27"/>
+      <c r="S72" s="27"/>
+      <c r="T72" s="27"/>
+      <c r="U72" s="27"/>
+      <c r="V72" s="27"/>
+      <c r="W72" s="27"/>
+      <c r="X72" s="27"/>
+      <c r="Y72" s="27"/>
+      <c r="Z72" s="27"/>
+      <c r="AA72" s="27"/>
+      <c r="AB72" s="27"/>
+      <c r="AC72" s="27"/>
+      <c r="AD72" s="27"/>
+      <c r="AE72" s="27"/>
+      <c r="AF72" s="27"/>
+      <c r="AG72" s="27"/>
+    </row>
+    <row r="73" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A73" s="26"/>
+      <c r="B73" s="25" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="25">
+        <v>18</v>
+      </c>
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="27"/>
+      <c r="G73" s="27"/>
+      <c r="H73" s="27"/>
+      <c r="I73" s="27"/>
+      <c r="J73" s="27"/>
+      <c r="K73" s="27"/>
+      <c r="L73" s="27"/>
+      <c r="M73" s="27"/>
+      <c r="N73" s="27"/>
+      <c r="O73" s="27"/>
+      <c r="P73" s="27"/>
+      <c r="Q73" s="27"/>
+      <c r="R73" s="27"/>
+      <c r="S73" s="27"/>
+      <c r="T73" s="27"/>
+      <c r="U73" s="27"/>
+      <c r="V73" s="27"/>
+      <c r="W73" s="27"/>
+      <c r="X73" s="27"/>
+      <c r="Y73" s="27"/>
+      <c r="Z73" s="27"/>
+      <c r="AA73" s="27"/>
+      <c r="AB73" s="27"/>
+      <c r="AC73" s="27"/>
+      <c r="AD73" s="27"/>
+      <c r="AE73" s="27"/>
+      <c r="AF73" s="27"/>
+      <c r="AG73" s="27"/>
+    </row>
+    <row r="74" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A74" s="26"/>
+      <c r="B74" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C74" s="25">
+        <v>19</v>
+      </c>
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="27"/>
+      <c r="G74" s="27"/>
+      <c r="H74" s="27"/>
+      <c r="I74" s="27"/>
+      <c r="J74" s="27"/>
+      <c r="K74" s="27"/>
+      <c r="L74" s="27"/>
+      <c r="M74" s="27"/>
+      <c r="N74" s="27"/>
+      <c r="O74" s="27"/>
+      <c r="P74" s="27"/>
+      <c r="Q74" s="27"/>
+      <c r="R74" s="27"/>
+      <c r="S74" s="27"/>
+      <c r="T74" s="27"/>
+      <c r="U74" s="27"/>
+      <c r="V74" s="27"/>
+      <c r="W74" s="27"/>
+      <c r="X74" s="27"/>
+      <c r="Y74" s="27"/>
+      <c r="Z74" s="27"/>
+      <c r="AA74" s="27"/>
+      <c r="AB74" s="27"/>
+      <c r="AC74" s="27"/>
+      <c r="AD74" s="27"/>
+      <c r="AE74" s="27"/>
+      <c r="AF74" s="27"/>
+      <c r="AG74" s="27"/>
+    </row>
+    <row r="75" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A75" s="26"/>
+      <c r="B75" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C75" s="25">
+        <v>20</v>
+      </c>
+      <c r="D75" s="27"/>
+      <c r="E75" s="27"/>
+      <c r="F75" s="27"/>
+      <c r="G75" s="27"/>
+      <c r="H75" s="27"/>
+      <c r="I75" s="27"/>
+      <c r="J75" s="27"/>
+      <c r="K75" s="27"/>
+      <c r="L75" s="27"/>
+      <c r="M75" s="27"/>
+      <c r="N75" s="27"/>
+      <c r="O75" s="27"/>
+      <c r="P75" s="27"/>
+      <c r="Q75" s="27"/>
+      <c r="R75" s="27"/>
+      <c r="S75" s="27"/>
+      <c r="T75" s="27"/>
+      <c r="U75" s="27"/>
+      <c r="V75" s="27"/>
+      <c r="W75" s="27"/>
+      <c r="X75" s="27"/>
+      <c r="Y75" s="27"/>
+      <c r="Z75" s="27"/>
+      <c r="AA75" s="27"/>
+      <c r="AB75" s="27"/>
+      <c r="AC75" s="27"/>
+      <c r="AD75" s="27"/>
+      <c r="AE75" s="27"/>
+      <c r="AF75" s="27"/>
+      <c r="AG75" s="27"/>
+    </row>
+    <row r="76" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A76" s="26"/>
+      <c r="B76" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C76" s="25">
+        <v>21</v>
+      </c>
+      <c r="D76" s="27"/>
+      <c r="E76" s="27"/>
+      <c r="F76" s="27"/>
+      <c r="G76" s="27"/>
+      <c r="H76" s="27"/>
+      <c r="I76" s="27"/>
+      <c r="J76" s="27"/>
+      <c r="K76" s="27"/>
+      <c r="L76" s="27"/>
+      <c r="M76" s="27"/>
+      <c r="N76" s="27"/>
+      <c r="O76" s="27"/>
+      <c r="P76" s="27"/>
+      <c r="Q76" s="27"/>
+      <c r="R76" s="27"/>
+      <c r="S76" s="27"/>
+      <c r="T76" s="27"/>
+      <c r="U76" s="27"/>
+      <c r="V76" s="27"/>
+      <c r="W76" s="27"/>
+      <c r="X76" s="27"/>
+      <c r="Y76" s="27"/>
+      <c r="Z76" s="27"/>
+      <c r="AA76" s="27"/>
+      <c r="AB76" s="27"/>
+      <c r="AC76" s="27"/>
+      <c r="AD76" s="27"/>
+      <c r="AE76" s="27"/>
+      <c r="AF76" s="27"/>
+      <c r="AG76" s="27"/>
+    </row>
+    <row r="77" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A77" s="26"/>
+      <c r="B77" s="25" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="25">
+        <v>22</v>
+      </c>
+      <c r="D77" s="27"/>
+      <c r="E77" s="27"/>
+      <c r="F77" s="27"/>
+      <c r="G77" s="27"/>
+      <c r="H77" s="27"/>
+      <c r="I77" s="27"/>
+      <c r="J77" s="27"/>
+      <c r="K77" s="27"/>
+      <c r="L77" s="27"/>
+      <c r="M77" s="27"/>
+      <c r="N77" s="27"/>
+      <c r="O77" s="27"/>
+      <c r="P77" s="27"/>
+      <c r="Q77" s="27"/>
+      <c r="R77" s="27"/>
+      <c r="S77" s="27"/>
+      <c r="T77" s="27"/>
+      <c r="U77" s="27"/>
+      <c r="V77" s="27"/>
+      <c r="W77" s="27"/>
+      <c r="X77" s="27"/>
+      <c r="Y77" s="27"/>
+      <c r="Z77" s="27"/>
+      <c r="AA77" s="27"/>
+      <c r="AB77" s="27"/>
+      <c r="AC77" s="27"/>
+      <c r="AD77" s="27"/>
+      <c r="AE77" s="27"/>
+      <c r="AF77" s="27"/>
+      <c r="AG77" s="27"/>
+    </row>
+    <row r="78" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A78" s="26"/>
+      <c r="B78" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C78" s="25">
+        <v>23</v>
+      </c>
+      <c r="D78" s="27"/>
+      <c r="E78" s="27"/>
+      <c r="F78" s="27"/>
+      <c r="G78" s="27"/>
+      <c r="H78" s="27"/>
+      <c r="I78" s="27"/>
+      <c r="J78" s="27"/>
+      <c r="K78" s="27"/>
+      <c r="L78" s="27"/>
+      <c r="M78" s="27"/>
+      <c r="N78" s="27"/>
+      <c r="O78" s="27"/>
+      <c r="P78" s="27"/>
+      <c r="Q78" s="27"/>
+      <c r="R78" s="27"/>
+      <c r="S78" s="27"/>
+      <c r="T78" s="27"/>
+      <c r="U78" s="27"/>
+      <c r="V78" s="27"/>
+      <c r="W78" s="27"/>
+      <c r="X78" s="27"/>
+      <c r="Y78" s="27"/>
+      <c r="Z78" s="27"/>
+      <c r="AA78" s="27"/>
+      <c r="AB78" s="27"/>
+      <c r="AC78" s="27"/>
+      <c r="AD78" s="27"/>
+      <c r="AE78" s="27"/>
+      <c r="AF78" s="27"/>
+      <c r="AG78" s="27"/>
+    </row>
+    <row r="79" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A79" s="26"/>
+      <c r="B79" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C79" s="25">
+        <v>24</v>
+      </c>
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="27"/>
+      <c r="G79" s="27"/>
+      <c r="H79" s="27"/>
+      <c r="I79" s="27"/>
+      <c r="J79" s="27"/>
+      <c r="K79" s="27"/>
+      <c r="L79" s="27"/>
+      <c r="M79" s="27"/>
+      <c r="N79" s="27"/>
+      <c r="O79" s="27"/>
+      <c r="P79" s="27"/>
+      <c r="Q79" s="27"/>
+      <c r="R79" s="27"/>
+      <c r="S79" s="27"/>
+      <c r="T79" s="27"/>
+      <c r="U79" s="27"/>
+      <c r="V79" s="27"/>
+      <c r="W79" s="27"/>
+      <c r="X79" s="27"/>
+      <c r="Y79" s="27"/>
+      <c r="Z79" s="27"/>
+      <c r="AA79" s="27"/>
+      <c r="AB79" s="27"/>
+      <c r="AC79" s="27"/>
+      <c r="AD79" s="27"/>
+      <c r="AE79" s="27"/>
+      <c r="AF79" s="27"/>
+      <c r="AG79" s="27"/>
+    </row>
+    <row r="80" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A80" s="26"/>
+      <c r="B80" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C80" s="25">
+        <v>25</v>
+      </c>
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="27"/>
+      <c r="G80" s="27"/>
+      <c r="H80" s="27"/>
+      <c r="I80" s="27"/>
+      <c r="J80" s="27"/>
+      <c r="K80" s="27"/>
+      <c r="L80" s="27"/>
+      <c r="M80" s="27"/>
+      <c r="N80" s="27"/>
+      <c r="O80" s="27"/>
+      <c r="P80" s="27"/>
+      <c r="Q80" s="27"/>
+      <c r="R80" s="27"/>
+      <c r="S80" s="27"/>
+      <c r="T80" s="27"/>
+      <c r="U80" s="27"/>
+      <c r="V80" s="27"/>
+      <c r="W80" s="27"/>
+      <c r="X80" s="27"/>
+      <c r="Y80" s="27"/>
+      <c r="Z80" s="27"/>
+      <c r="AA80" s="27"/>
+      <c r="AB80" s="27"/>
+      <c r="AC80" s="27"/>
+      <c r="AD80" s="27"/>
+      <c r="AE80" s="27"/>
+      <c r="AF80" s="27"/>
+      <c r="AG80" s="27"/>
+    </row>
+    <row r="81" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A81" s="26"/>
+      <c r="B81" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="25">
+        <v>26</v>
+      </c>
+      <c r="D81" s="27"/>
+      <c r="E81" s="27"/>
+      <c r="F81" s="27"/>
+      <c r="G81" s="27"/>
+      <c r="H81" s="27"/>
+      <c r="I81" s="27"/>
+      <c r="J81" s="27"/>
+      <c r="K81" s="27"/>
+      <c r="L81" s="27"/>
+      <c r="M81" s="27"/>
+      <c r="N81" s="27"/>
+      <c r="O81" s="27"/>
+      <c r="P81" s="27"/>
+      <c r="Q81" s="27"/>
+      <c r="R81" s="27"/>
+      <c r="S81" s="27"/>
+      <c r="T81" s="27"/>
+      <c r="U81" s="27"/>
+      <c r="V81" s="27"/>
+      <c r="W81" s="27"/>
+      <c r="X81" s="27"/>
+      <c r="Y81" s="27"/>
+      <c r="Z81" s="27"/>
+      <c r="AA81" s="27"/>
+      <c r="AB81" s="27"/>
+      <c r="AC81" s="27"/>
+      <c r="AD81" s="27"/>
+      <c r="AE81" s="27"/>
+      <c r="AF81" s="27"/>
+      <c r="AG81" s="27"/>
+    </row>
+    <row r="82" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A82" s="26"/>
+      <c r="B82" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C82" s="25">
+        <v>27</v>
+      </c>
+      <c r="D82" s="27"/>
+      <c r="E82" s="27"/>
+      <c r="F82" s="27"/>
+      <c r="G82" s="27"/>
+      <c r="H82" s="27"/>
+      <c r="I82" s="27"/>
+      <c r="J82" s="27"/>
+      <c r="K82" s="27"/>
+      <c r="L82" s="27"/>
+      <c r="M82" s="27"/>
+      <c r="N82" s="27"/>
+      <c r="O82" s="27"/>
+      <c r="P82" s="27"/>
+      <c r="Q82" s="27"/>
+      <c r="R82" s="27"/>
+      <c r="S82" s="27"/>
+      <c r="T82" s="27"/>
+      <c r="U82" s="27"/>
+      <c r="V82" s="27"/>
+      <c r="W82" s="27"/>
+      <c r="X82" s="27"/>
+      <c r="Y82" s="27"/>
+      <c r="Z82" s="27"/>
+      <c r="AA82" s="27"/>
+      <c r="AB82" s="27"/>
+      <c r="AC82" s="27"/>
+      <c r="AD82" s="27"/>
+      <c r="AE82" s="27"/>
+      <c r="AF82" s="27"/>
+      <c r="AG82" s="27"/>
+    </row>
+    <row r="83" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A83" s="26"/>
+      <c r="B83" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C83" s="25">
+        <v>28</v>
+      </c>
+      <c r="D83" s="27"/>
+      <c r="E83" s="27"/>
+      <c r="F83" s="27"/>
+      <c r="G83" s="27"/>
+      <c r="H83" s="27"/>
+      <c r="I83" s="27"/>
+      <c r="J83" s="27"/>
+      <c r="K83" s="27"/>
+      <c r="L83" s="27"/>
+      <c r="M83" s="27"/>
+      <c r="N83" s="27"/>
+      <c r="O83" s="27"/>
+      <c r="P83" s="27"/>
+      <c r="Q83" s="27"/>
+      <c r="R83" s="27"/>
+      <c r="S83" s="27"/>
+      <c r="T83" s="27"/>
+      <c r="U83" s="27"/>
+      <c r="V83" s="27"/>
+      <c r="W83" s="27"/>
+      <c r="X83" s="27"/>
+      <c r="Y83" s="27"/>
+      <c r="Z83" s="27"/>
+      <c r="AA83" s="27"/>
+      <c r="AB83" s="27"/>
+      <c r="AC83" s="27"/>
+      <c r="AD83" s="27"/>
+      <c r="AE83" s="27"/>
+      <c r="AF83" s="27"/>
+      <c r="AG83" s="27"/>
+    </row>
+    <row r="84" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A84" s="26"/>
+      <c r="B84" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C84" s="25">
+        <v>29</v>
+      </c>
+      <c r="D84" s="27"/>
+      <c r="E84" s="27"/>
+      <c r="F84" s="27"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="27"/>
+      <c r="I84" s="27"/>
+      <c r="J84" s="27"/>
+      <c r="K84" s="27"/>
+      <c r="L84" s="27"/>
+      <c r="M84" s="27"/>
+      <c r="N84" s="27"/>
+      <c r="O84" s="27"/>
+      <c r="P84" s="27"/>
+      <c r="Q84" s="27"/>
+      <c r="R84" s="27"/>
+      <c r="S84" s="27"/>
+      <c r="T84" s="27"/>
+      <c r="U84" s="27"/>
+      <c r="V84" s="27"/>
+      <c r="W84" s="27"/>
+      <c r="X84" s="27"/>
+      <c r="Y84" s="27"/>
+      <c r="Z84" s="27"/>
+      <c r="AA84" s="27"/>
+      <c r="AB84" s="27"/>
+      <c r="AC84" s="27"/>
+      <c r="AD84" s="27"/>
+      <c r="AE84" s="27"/>
+      <c r="AF84" s="27"/>
+      <c r="AG84" s="27"/>
+    </row>
+    <row r="85" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A85" s="26"/>
+      <c r="B85" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C85" s="25">
+        <v>30</v>
+      </c>
+      <c r="D85" s="27"/>
+      <c r="E85" s="27"/>
+      <c r="F85" s="27"/>
+      <c r="G85" s="27"/>
+      <c r="H85" s="27"/>
+      <c r="I85" s="27"/>
+      <c r="J85" s="27"/>
+      <c r="K85" s="27"/>
+      <c r="L85" s="27"/>
+      <c r="M85" s="27"/>
+      <c r="N85" s="27"/>
+      <c r="O85" s="27"/>
+      <c r="P85" s="27"/>
+      <c r="Q85" s="27"/>
+      <c r="R85" s="27"/>
+      <c r="S85" s="27"/>
+      <c r="T85" s="27"/>
+      <c r="U85" s="27"/>
+      <c r="V85" s="27"/>
+      <c r="W85" s="27"/>
+      <c r="X85" s="27"/>
+      <c r="Y85" s="27"/>
+      <c r="Z85" s="27"/>
+      <c r="AA85" s="27"/>
+      <c r="AB85" s="27"/>
+      <c r="AC85" s="27"/>
+      <c r="AD85" s="27"/>
+      <c r="AE85" s="27"/>
+      <c r="AF85" s="27"/>
+      <c r="AG85" s="27"/>
+    </row>
+    <row r="86" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A86" s="26"/>
+      <c r="B86" s="25" t="s">
+        <v>10</v>
+      </c>
+      <c r="C86" s="25">
+        <v>31</v>
+      </c>
+      <c r="D86" s="27"/>
+      <c r="E86" s="27"/>
+      <c r="F86" s="27"/>
+      <c r="G86" s="27"/>
+      <c r="H86" s="27"/>
+      <c r="I86" s="27"/>
+      <c r="J86" s="27"/>
+      <c r="K86" s="27"/>
+      <c r="L86" s="27"/>
+      <c r="M86" s="27"/>
+      <c r="N86" s="27"/>
+      <c r="O86" s="27"/>
+      <c r="P86" s="27"/>
+      <c r="Q86" s="27"/>
+      <c r="R86" s="27"/>
+      <c r="S86" s="27"/>
+      <c r="T86" s="27"/>
+      <c r="U86" s="27"/>
+      <c r="V86" s="27"/>
+      <c r="W86" s="27"/>
+      <c r="X86" s="27"/>
+      <c r="Y86" s="27"/>
+      <c r="Z86" s="27"/>
+      <c r="AA86" s="27"/>
+      <c r="AB86" s="27"/>
+      <c r="AC86" s="27"/>
+      <c r="AD86" s="27"/>
+      <c r="AE86" s="27"/>
+      <c r="AF86" s="27"/>
+      <c r="AG86" s="27"/>
+    </row>
+    <row r="87" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A87" s="26"/>
+      <c r="B87" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C87" s="25">
+        <v>32</v>
+      </c>
+      <c r="D87" s="27"/>
+      <c r="E87" s="27"/>
+      <c r="F87" s="27"/>
+      <c r="G87" s="27"/>
+      <c r="H87" s="27"/>
+      <c r="I87" s="27"/>
+      <c r="J87" s="27"/>
+      <c r="K87" s="27"/>
+      <c r="L87" s="27"/>
+      <c r="M87" s="27"/>
+      <c r="N87" s="27"/>
+      <c r="O87" s="27"/>
+      <c r="P87" s="27"/>
+      <c r="Q87" s="27"/>
+      <c r="R87" s="27"/>
+      <c r="S87" s="27"/>
+      <c r="T87" s="27"/>
+      <c r="U87" s="27"/>
+      <c r="V87" s="27"/>
+      <c r="W87" s="27"/>
+      <c r="X87" s="27"/>
+      <c r="Y87" s="27"/>
+      <c r="Z87" s="27"/>
+      <c r="AA87" s="27"/>
+      <c r="AB87" s="27"/>
+      <c r="AC87" s="27"/>
+      <c r="AD87" s="27"/>
+      <c r="AE87" s="27"/>
+      <c r="AF87" s="27"/>
+      <c r="AG87" s="27"/>
+    </row>
+    <row r="88" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A88" s="26"/>
+      <c r="B88" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C88" s="25">
+        <v>33</v>
+      </c>
+      <c r="D88" s="27"/>
+      <c r="E88" s="27"/>
+      <c r="F88" s="27"/>
+      <c r="G88" s="27"/>
+      <c r="H88" s="27"/>
+      <c r="I88" s="27"/>
+      <c r="J88" s="27"/>
+      <c r="K88" s="27"/>
+      <c r="L88" s="27"/>
+      <c r="M88" s="27"/>
+      <c r="N88" s="27"/>
+      <c r="O88" s="27"/>
+      <c r="P88" s="27"/>
+      <c r="Q88" s="27"/>
+      <c r="R88" s="27"/>
+      <c r="S88" s="27"/>
+      <c r="T88" s="27"/>
+      <c r="U88" s="27"/>
+      <c r="V88" s="27"/>
+      <c r="W88" s="27"/>
+      <c r="X88" s="27"/>
+      <c r="Y88" s="27"/>
+      <c r="Z88" s="27"/>
+      <c r="AA88" s="27"/>
+      <c r="AB88" s="27"/>
+      <c r="AC88" s="27"/>
+      <c r="AD88" s="27"/>
+      <c r="AE88" s="27"/>
+      <c r="AF88" s="27"/>
+      <c r="AG88" s="27"/>
+    </row>
+    <row r="89" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A89" s="26"/>
+      <c r="B89" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" s="25">
+        <v>34</v>
+      </c>
+      <c r="D89" s="27"/>
+      <c r="E89" s="27"/>
+      <c r="F89" s="27"/>
+      <c r="G89" s="27"/>
+      <c r="H89" s="27"/>
+      <c r="I89" s="27"/>
+      <c r="J89" s="27"/>
+      <c r="K89" s="27"/>
+      <c r="L89" s="27"/>
+      <c r="M89" s="27"/>
+      <c r="N89" s="27"/>
+      <c r="O89" s="27"/>
+      <c r="P89" s="27"/>
+      <c r="Q89" s="27"/>
+      <c r="R89" s="27"/>
+      <c r="S89" s="27"/>
+      <c r="T89" s="27"/>
+      <c r="U89" s="27"/>
+      <c r="V89" s="27"/>
+      <c r="W89" s="27"/>
+      <c r="X89" s="27"/>
+      <c r="Y89" s="27"/>
+      <c r="Z89" s="27"/>
+      <c r="AA89" s="27"/>
+      <c r="AB89" s="27"/>
+      <c r="AC89" s="27"/>
+      <c r="AD89" s="27"/>
+      <c r="AE89" s="27"/>
+      <c r="AF89" s="27"/>
+      <c r="AG89" s="27"/>
+    </row>
+    <row r="90" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A90" s="26"/>
+      <c r="B90" s="25" t="s">
+        <v>11</v>
+      </c>
+      <c r="C90" s="25">
+        <v>35</v>
+      </c>
+      <c r="D90" s="27"/>
+      <c r="E90" s="27"/>
+      <c r="F90" s="27"/>
+      <c r="G90" s="27"/>
+      <c r="H90" s="27"/>
+      <c r="I90" s="27"/>
+      <c r="J90" s="27"/>
+      <c r="K90" s="27"/>
+      <c r="L90" s="27"/>
+      <c r="M90" s="27"/>
+      <c r="N90" s="27"/>
+      <c r="O90" s="27"/>
+      <c r="P90" s="27"/>
+      <c r="Q90" s="27"/>
+      <c r="R90" s="27"/>
+      <c r="S90" s="27"/>
+      <c r="T90" s="27"/>
+      <c r="U90" s="27"/>
+      <c r="V90" s="27"/>
+      <c r="W90" s="27"/>
+      <c r="X90" s="27"/>
+      <c r="Y90" s="27"/>
+      <c r="Z90" s="27"/>
+      <c r="AA90" s="27"/>
+      <c r="AB90" s="27"/>
+      <c r="AC90" s="27"/>
+      <c r="AD90" s="27"/>
+      <c r="AE90" s="27"/>
+      <c r="AF90" s="27"/>
+      <c r="AG90" s="27"/>
+    </row>
+    <row r="91" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A91" s="26"/>
+      <c r="B91" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C91" s="25">
+        <v>36</v>
+      </c>
+      <c r="D91" s="27"/>
+      <c r="E91" s="27"/>
+      <c r="F91" s="27"/>
+      <c r="G91" s="27"/>
+      <c r="H91" s="27"/>
+      <c r="I91" s="27"/>
+      <c r="J91" s="27"/>
+      <c r="K91" s="27"/>
+      <c r="L91" s="27"/>
+      <c r="M91" s="27"/>
+      <c r="N91" s="27"/>
+      <c r="O91" s="27"/>
+      <c r="P91" s="27"/>
+      <c r="Q91" s="27"/>
+      <c r="R91" s="27"/>
+      <c r="S91" s="27"/>
+      <c r="T91" s="27"/>
+      <c r="U91" s="27"/>
+      <c r="V91" s="27"/>
+      <c r="W91" s="27"/>
+      <c r="X91" s="27"/>
+      <c r="Y91" s="27"/>
+      <c r="Z91" s="27"/>
+      <c r="AA91" s="27"/>
+      <c r="AB91" s="27"/>
+      <c r="AC91" s="27"/>
+      <c r="AD91" s="27"/>
+      <c r="AE91" s="27"/>
+      <c r="AF91" s="27"/>
+      <c r="AG91" s="27"/>
+    </row>
+    <row r="92" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A92" s="26"/>
+      <c r="B92" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C92" s="25">
+        <v>37</v>
+      </c>
+      <c r="D92" s="27"/>
+      <c r="E92" s="27"/>
+      <c r="F92" s="27"/>
+      <c r="G92" s="27"/>
+      <c r="H92" s="27"/>
+      <c r="I92" s="27"/>
+      <c r="J92" s="27"/>
+      <c r="K92" s="27"/>
+      <c r="L92" s="27"/>
+      <c r="M92" s="27"/>
+      <c r="N92" s="27"/>
+      <c r="O92" s="27"/>
+      <c r="P92" s="27"/>
+      <c r="Q92" s="27"/>
+      <c r="R92" s="27"/>
+      <c r="S92" s="27"/>
+      <c r="T92" s="27"/>
+      <c r="U92" s="27"/>
+      <c r="V92" s="27"/>
+      <c r="W92" s="27"/>
+      <c r="X92" s="27"/>
+      <c r="Y92" s="27"/>
+      <c r="Z92" s="27"/>
+      <c r="AA92" s="27"/>
+      <c r="AB92" s="27"/>
+      <c r="AC92" s="27"/>
+      <c r="AD92" s="27"/>
+      <c r="AE92" s="27"/>
+      <c r="AF92" s="27"/>
+      <c r="AG92" s="27"/>
+    </row>
+    <row r="93" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A93" s="26"/>
+      <c r="B93" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C93" s="25">
+        <v>38</v>
+      </c>
+      <c r="D93" s="27"/>
+      <c r="E93" s="27"/>
+      <c r="F93" s="27"/>
+      <c r="G93" s="27"/>
+      <c r="H93" s="27"/>
+      <c r="I93" s="27"/>
+      <c r="J93" s="27"/>
+      <c r="K93" s="27"/>
+      <c r="L93" s="27"/>
+      <c r="M93" s="27"/>
+      <c r="N93" s="27"/>
+      <c r="O93" s="27"/>
+      <c r="P93" s="27"/>
+      <c r="Q93" s="27"/>
+      <c r="R93" s="27"/>
+      <c r="S93" s="27"/>
+      <c r="T93" s="27"/>
+      <c r="U93" s="27"/>
+      <c r="V93" s="27"/>
+      <c r="W93" s="27"/>
+      <c r="X93" s="27"/>
+      <c r="Y93" s="27"/>
+      <c r="Z93" s="27"/>
+      <c r="AA93" s="27"/>
+      <c r="AB93" s="27"/>
+      <c r="AC93" s="27"/>
+      <c r="AD93" s="27"/>
+      <c r="AE93" s="27"/>
+      <c r="AF93" s="27"/>
+      <c r="AG93" s="27"/>
+    </row>
+    <row r="94" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A94" s="26"/>
+      <c r="B94" s="25" t="s">
+        <v>12</v>
+      </c>
+      <c r="C94" s="25">
+        <v>39</v>
+      </c>
+      <c r="D94" s="27"/>
+      <c r="E94" s="27"/>
+      <c r="F94" s="27"/>
+      <c r="G94" s="27"/>
+      <c r="H94" s="27"/>
+      <c r="I94" s="27"/>
+      <c r="J94" s="27"/>
+      <c r="K94" s="27"/>
+      <c r="L94" s="27"/>
+      <c r="M94" s="27"/>
+      <c r="N94" s="27"/>
+      <c r="O94" s="27"/>
+      <c r="P94" s="27"/>
+      <c r="Q94" s="27"/>
+      <c r="R94" s="27"/>
+      <c r="S94" s="27"/>
+      <c r="T94" s="27"/>
+      <c r="U94" s="27"/>
+      <c r="V94" s="27"/>
+      <c r="W94" s="27"/>
+      <c r="X94" s="27"/>
+      <c r="Y94" s="27"/>
+      <c r="Z94" s="27"/>
+      <c r="AA94" s="27"/>
+      <c r="AB94" s="27"/>
+      <c r="AC94" s="27"/>
+      <c r="AD94" s="27"/>
+      <c r="AE94" s="27"/>
+      <c r="AF94" s="27"/>
+      <c r="AG94" s="27"/>
+    </row>
+    <row r="95" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A95" s="26"/>
+      <c r="B95" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C95" s="25">
+        <v>40</v>
+      </c>
+      <c r="D95" s="27"/>
+      <c r="E95" s="27"/>
+      <c r="F95" s="27"/>
+      <c r="G95" s="27"/>
+      <c r="H95" s="27"/>
+      <c r="I95" s="27"/>
+      <c r="J95" s="27"/>
+      <c r="K95" s="27"/>
+      <c r="L95" s="27"/>
+      <c r="M95" s="27"/>
+      <c r="N95" s="27"/>
+      <c r="O95" s="27"/>
+      <c r="P95" s="27"/>
+      <c r="Q95" s="27"/>
+      <c r="R95" s="27"/>
+      <c r="S95" s="27"/>
+      <c r="T95" s="27"/>
+      <c r="U95" s="27"/>
+      <c r="V95" s="27"/>
+      <c r="W95" s="27"/>
+      <c r="X95" s="27"/>
+      <c r="Y95" s="27"/>
+      <c r="Z95" s="27"/>
+      <c r="AA95" s="27"/>
+      <c r="AB95" s="27"/>
+      <c r="AC95" s="27"/>
+      <c r="AD95" s="27"/>
+      <c r="AE95" s="27"/>
+      <c r="AF95" s="27"/>
+      <c r="AG95" s="27"/>
+    </row>
+    <row r="96" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A96" s="26"/>
+      <c r="B96" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C96" s="25">
+        <v>41</v>
+      </c>
+      <c r="D96" s="27"/>
+      <c r="E96" s="27"/>
+      <c r="F96" s="27"/>
+      <c r="G96" s="27"/>
+      <c r="H96" s="27"/>
+      <c r="I96" s="27"/>
+      <c r="J96" s="27"/>
+      <c r="K96" s="27"/>
+      <c r="L96" s="27"/>
+      <c r="M96" s="27"/>
+      <c r="N96" s="27"/>
+      <c r="O96" s="27"/>
+      <c r="P96" s="27"/>
+      <c r="Q96" s="27"/>
+      <c r="R96" s="27"/>
+      <c r="S96" s="27"/>
+      <c r="T96" s="27"/>
+      <c r="U96" s="27"/>
+      <c r="V96" s="27"/>
+      <c r="W96" s="27"/>
+      <c r="X96" s="27"/>
+      <c r="Y96" s="27"/>
+      <c r="Z96" s="27"/>
+      <c r="AA96" s="27"/>
+      <c r="AB96" s="27"/>
+      <c r="AC96" s="27"/>
+      <c r="AD96" s="27"/>
+      <c r="AE96" s="27"/>
+      <c r="AF96" s="27"/>
+      <c r="AG96" s="27"/>
+    </row>
+    <row r="97" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A97" s="26"/>
+      <c r="B97" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C97" s="25">
+        <v>42</v>
+      </c>
+      <c r="D97" s="27"/>
+      <c r="E97" s="27"/>
+      <c r="F97" s="27"/>
+      <c r="G97" s="27"/>
+      <c r="H97" s="27"/>
+      <c r="I97" s="27"/>
+      <c r="J97" s="27"/>
+      <c r="K97" s="27"/>
+      <c r="L97" s="27"/>
+      <c r="M97" s="27"/>
+      <c r="N97" s="27"/>
+      <c r="O97" s="27"/>
+      <c r="P97" s="27"/>
+      <c r="Q97" s="27"/>
+      <c r="R97" s="27"/>
+      <c r="S97" s="27"/>
+      <c r="T97" s="27"/>
+      <c r="U97" s="27"/>
+      <c r="V97" s="27"/>
+      <c r="W97" s="27"/>
+      <c r="X97" s="27"/>
+      <c r="Y97" s="27"/>
+      <c r="Z97" s="27"/>
+      <c r="AA97" s="27"/>
+      <c r="AB97" s="27"/>
+      <c r="AC97" s="27"/>
+      <c r="AD97" s="27"/>
+      <c r="AE97" s="27"/>
+      <c r="AF97" s="27"/>
+      <c r="AG97" s="27"/>
+    </row>
+    <row r="98" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A98" s="26"/>
+      <c r="B98" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C98" s="25">
+        <v>43</v>
+      </c>
+      <c r="D98" s="27"/>
+      <c r="E98" s="27"/>
+      <c r="F98" s="27"/>
+      <c r="G98" s="27"/>
+      <c r="H98" s="27"/>
+      <c r="I98" s="27"/>
+      <c r="J98" s="27"/>
+      <c r="K98" s="27"/>
+      <c r="L98" s="27"/>
+      <c r="M98" s="27"/>
+      <c r="N98" s="27"/>
+      <c r="O98" s="27"/>
+      <c r="P98" s="27"/>
+      <c r="Q98" s="27"/>
+      <c r="R98" s="27"/>
+      <c r="S98" s="27"/>
+      <c r="T98" s="27"/>
+      <c r="U98" s="27"/>
+      <c r="V98" s="27"/>
+      <c r="W98" s="27"/>
+      <c r="X98" s="27"/>
+      <c r="Y98" s="27"/>
+      <c r="Z98" s="27"/>
+      <c r="AA98" s="27"/>
+      <c r="AB98" s="27"/>
+      <c r="AC98" s="27"/>
+      <c r="AD98" s="27"/>
+      <c r="AE98" s="27"/>
+      <c r="AF98" s="27"/>
+      <c r="AG98" s="27"/>
+    </row>
+    <row r="99" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A99" s="26"/>
+      <c r="B99" s="25" t="s">
+        <v>13</v>
+      </c>
+      <c r="C99" s="25">
+        <v>44</v>
+      </c>
+      <c r="D99" s="27"/>
+      <c r="E99" s="27"/>
+      <c r="F99" s="27"/>
+      <c r="G99" s="27"/>
+      <c r="H99" s="27"/>
+      <c r="I99" s="27"/>
+      <c r="J99" s="27"/>
+      <c r="K99" s="27"/>
+      <c r="L99" s="27"/>
+      <c r="M99" s="27"/>
+      <c r="N99" s="27"/>
+      <c r="O99" s="27"/>
+      <c r="P99" s="27"/>
+      <c r="Q99" s="27"/>
+      <c r="R99" s="27"/>
+      <c r="S99" s="27"/>
+      <c r="T99" s="27"/>
+      <c r="U99" s="27"/>
+      <c r="V99" s="27"/>
+      <c r="W99" s="27"/>
+      <c r="X99" s="27"/>
+      <c r="Y99" s="27"/>
+      <c r="Z99" s="27"/>
+      <c r="AA99" s="27"/>
+      <c r="AB99" s="27"/>
+      <c r="AC99" s="27"/>
+      <c r="AD99" s="27"/>
+      <c r="AE99" s="27"/>
+      <c r="AF99" s="27"/>
+      <c r="AG99" s="27"/>
+    </row>
+    <row r="100" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A100" s="26"/>
+      <c r="B100" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C100" s="25">
+        <v>45</v>
+      </c>
+      <c r="D100" s="27"/>
+      <c r="E100" s="27"/>
+      <c r="F100" s="27"/>
+      <c r="G100" s="27"/>
+      <c r="H100" s="27"/>
+      <c r="I100" s="27"/>
+      <c r="J100" s="27"/>
+      <c r="K100" s="27"/>
+      <c r="L100" s="27"/>
+      <c r="M100" s="27"/>
+      <c r="N100" s="27"/>
+      <c r="O100" s="27"/>
+      <c r="P100" s="27"/>
+      <c r="Q100" s="27"/>
+      <c r="R100" s="27"/>
+      <c r="S100" s="27"/>
+      <c r="T100" s="27"/>
+      <c r="U100" s="27"/>
+      <c r="V100" s="27"/>
+      <c r="W100" s="27"/>
+      <c r="X100" s="27"/>
+      <c r="Y100" s="27"/>
+      <c r="Z100" s="27"/>
+      <c r="AA100" s="27"/>
+      <c r="AB100" s="27"/>
+      <c r="AC100" s="27"/>
+      <c r="AD100" s="27"/>
+      <c r="AE100" s="27"/>
+      <c r="AF100" s="27"/>
+      <c r="AG100" s="27"/>
+    </row>
+    <row r="101" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A101" s="26"/>
+      <c r="B101" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" s="25">
+        <v>46</v>
+      </c>
+      <c r="D101" s="27"/>
+      <c r="E101" s="27"/>
+      <c r="F101" s="27"/>
+      <c r="G101" s="27"/>
+      <c r="H101" s="27"/>
+      <c r="I101" s="27"/>
+      <c r="J101" s="27"/>
+      <c r="K101" s="27"/>
+      <c r="L101" s="27"/>
+      <c r="M101" s="27"/>
+      <c r="N101" s="27"/>
+      <c r="O101" s="27"/>
+      <c r="P101" s="27"/>
+      <c r="Q101" s="27"/>
+      <c r="R101" s="27"/>
+      <c r="S101" s="27"/>
+      <c r="T101" s="27"/>
+      <c r="U101" s="27"/>
+      <c r="V101" s="27"/>
+      <c r="W101" s="27"/>
+      <c r="X101" s="27"/>
+      <c r="Y101" s="27"/>
+      <c r="Z101" s="27"/>
+      <c r="AA101" s="27"/>
+      <c r="AB101" s="27"/>
+      <c r="AC101" s="27"/>
+      <c r="AD101" s="27"/>
+      <c r="AE101" s="27"/>
+      <c r="AF101" s="27"/>
+      <c r="AG101" s="27"/>
+    </row>
+    <row r="102" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A102" s="26"/>
+      <c r="B102" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C102" s="25">
+        <v>47</v>
+      </c>
+      <c r="D102" s="27"/>
+      <c r="E102" s="27"/>
+      <c r="F102" s="27"/>
+      <c r="G102" s="27"/>
+      <c r="H102" s="27"/>
+      <c r="I102" s="27"/>
+      <c r="J102" s="27"/>
+      <c r="K102" s="27"/>
+      <c r="L102" s="27"/>
+      <c r="M102" s="27"/>
+      <c r="N102" s="27"/>
+      <c r="O102" s="27"/>
+      <c r="P102" s="27"/>
+      <c r="Q102" s="27"/>
+      <c r="R102" s="27"/>
+      <c r="S102" s="27"/>
+      <c r="T102" s="27"/>
+      <c r="U102" s="27"/>
+      <c r="V102" s="27"/>
+      <c r="W102" s="27"/>
+      <c r="X102" s="27"/>
+      <c r="Y102" s="27"/>
+      <c r="Z102" s="27"/>
+      <c r="AA102" s="27"/>
+      <c r="AB102" s="27"/>
+      <c r="AC102" s="27"/>
+      <c r="AD102" s="27"/>
+      <c r="AE102" s="27"/>
+      <c r="AF102" s="27"/>
+      <c r="AG102" s="27"/>
+    </row>
+    <row r="103" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A103" s="26"/>
+      <c r="B103" s="25" t="s">
+        <v>14</v>
+      </c>
+      <c r="C103" s="25">
+        <v>48</v>
+      </c>
+      <c r="D103" s="27"/>
+      <c r="E103" s="27"/>
+      <c r="F103" s="27"/>
+      <c r="G103" s="27"/>
+      <c r="H103" s="27"/>
+      <c r="I103" s="27"/>
+      <c r="J103" s="27"/>
+      <c r="K103" s="27"/>
+      <c r="L103" s="27"/>
+      <c r="M103" s="27"/>
+      <c r="N103" s="27"/>
+      <c r="O103" s="27"/>
+      <c r="P103" s="27"/>
+      <c r="Q103" s="27"/>
+      <c r="R103" s="27"/>
+      <c r="S103" s="27"/>
+      <c r="T103" s="27"/>
+      <c r="U103" s="27"/>
+      <c r="V103" s="27"/>
+      <c r="W103" s="27"/>
+      <c r="X103" s="27"/>
+      <c r="Y103" s="27"/>
+      <c r="Z103" s="27"/>
+      <c r="AA103" s="27"/>
+      <c r="AB103" s="27"/>
+      <c r="AC103" s="27"/>
+      <c r="AD103" s="27"/>
+      <c r="AE103" s="27"/>
+      <c r="AF103" s="27"/>
+      <c r="AG103" s="27"/>
+    </row>
+    <row r="104" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A104" s="26"/>
+      <c r="B104" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C104" s="25">
+        <v>49</v>
+      </c>
+      <c r="D104" s="27"/>
+      <c r="E104" s="27"/>
+      <c r="F104" s="27"/>
+      <c r="G104" s="27"/>
+      <c r="H104" s="27"/>
+      <c r="I104" s="27"/>
+      <c r="J104" s="27"/>
+      <c r="K104" s="27"/>
+      <c r="L104" s="27"/>
+      <c r="M104" s="27"/>
+      <c r="N104" s="27"/>
+      <c r="O104" s="27"/>
+      <c r="P104" s="27"/>
+      <c r="Q104" s="27"/>
+      <c r="R104" s="27"/>
+      <c r="S104" s="27"/>
+      <c r="T104" s="27"/>
+      <c r="U104" s="27"/>
+      <c r="V104" s="27"/>
+      <c r="W104" s="27"/>
+      <c r="X104" s="27"/>
+      <c r="Y104" s="27"/>
+      <c r="Z104" s="27"/>
+      <c r="AA104" s="27"/>
+      <c r="AB104" s="27"/>
+      <c r="AC104" s="27"/>
+      <c r="AD104" s="27"/>
+      <c r="AE104" s="27"/>
+      <c r="AF104" s="27"/>
+      <c r="AG104" s="27"/>
+    </row>
+    <row r="105" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A105" s="26"/>
+      <c r="B105" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C105" s="25">
+        <v>50</v>
+      </c>
+      <c r="D105" s="27"/>
+      <c r="E105" s="27"/>
+      <c r="F105" s="27"/>
+      <c r="G105" s="27"/>
+      <c r="H105" s="27"/>
+      <c r="I105" s="27"/>
+      <c r="J105" s="27"/>
+      <c r="K105" s="27"/>
+      <c r="L105" s="27"/>
+      <c r="M105" s="27"/>
+      <c r="N105" s="27"/>
+      <c r="O105" s="27"/>
+      <c r="P105" s="27"/>
+      <c r="Q105" s="27"/>
+      <c r="R105" s="27"/>
+      <c r="S105" s="27"/>
+      <c r="T105" s="27"/>
+      <c r="U105" s="27"/>
+      <c r="V105" s="27"/>
+      <c r="W105" s="27"/>
+      <c r="X105" s="27"/>
+      <c r="Y105" s="27"/>
+      <c r="Z105" s="27"/>
+      <c r="AA105" s="27"/>
+      <c r="AB105" s="27"/>
+      <c r="AC105" s="27"/>
+      <c r="AD105" s="27"/>
+      <c r="AE105" s="27"/>
+      <c r="AF105" s="27"/>
+      <c r="AG105" s="27"/>
+    </row>
+    <row r="106" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A106" s="26"/>
+      <c r="B106" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C106" s="25">
+        <v>51</v>
+      </c>
+      <c r="D106" s="27"/>
+      <c r="E106" s="27"/>
+      <c r="F106" s="27"/>
+      <c r="G106" s="27"/>
+      <c r="H106" s="27"/>
+      <c r="I106" s="27"/>
+      <c r="J106" s="27"/>
+      <c r="K106" s="27"/>
+      <c r="L106" s="27"/>
+      <c r="M106" s="27"/>
+      <c r="N106" s="27"/>
+      <c r="O106" s="27"/>
+      <c r="P106" s="27"/>
+      <c r="Q106" s="27"/>
+      <c r="R106" s="27"/>
+      <c r="S106" s="27"/>
+      <c r="T106" s="27"/>
+      <c r="U106" s="27"/>
+      <c r="V106" s="27"/>
+      <c r="W106" s="27"/>
+      <c r="X106" s="27"/>
+      <c r="Y106" s="27"/>
+      <c r="Z106" s="27"/>
+      <c r="AA106" s="27"/>
+      <c r="AB106" s="27"/>
+      <c r="AC106" s="27"/>
+      <c r="AD106" s="27"/>
+      <c r="AE106" s="27"/>
+      <c r="AF106" s="27"/>
+      <c r="AG106" s="27"/>
+    </row>
+    <row r="107" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A107" s="26"/>
+      <c r="B107" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C107" s="25">
+        <v>52</v>
+      </c>
+      <c r="D107" s="27"/>
+      <c r="E107" s="27"/>
+      <c r="F107" s="27"/>
+      <c r="G107" s="27"/>
+      <c r="H107" s="27"/>
+      <c r="I107" s="27"/>
+      <c r="J107" s="27"/>
+      <c r="K107" s="27"/>
+      <c r="L107" s="27"/>
+      <c r="M107" s="27"/>
+      <c r="N107" s="27"/>
+      <c r="O107" s="27"/>
+      <c r="P107" s="27"/>
+      <c r="Q107" s="27"/>
+      <c r="R107" s="27"/>
+      <c r="S107" s="27"/>
+      <c r="T107" s="27"/>
+      <c r="U107" s="27"/>
+      <c r="V107" s="27"/>
+      <c r="W107" s="27"/>
+      <c r="X107" s="27"/>
+      <c r="Y107" s="27"/>
+      <c r="Z107" s="27"/>
+      <c r="AA107" s="27"/>
+      <c r="AB107" s="27"/>
+      <c r="AC107" s="27"/>
+      <c r="AD107" s="27"/>
+      <c r="AE107" s="27"/>
+      <c r="AF107" s="27"/>
+      <c r="AG107" s="27"/>
+    </row>
+    <row r="108" spans="1:33" x14ac:dyDescent="0.25">
+      <c r="A108" s="26"/>
+      <c r="B108" s="25" t="s">
+        <v>15</v>
+      </c>
+      <c r="C108" s="25">
+        <v>53</v>
+      </c>
+      <c r="D108" s="5"/>
+      <c r="E108" s="5"/>
+      <c r="F108" s="5"/>
+      <c r="G108" s="5"/>
+      <c r="H108" s="5"/>
+      <c r="I108" s="5"/>
+      <c r="J108" s="5"/>
+      <c r="K108" s="5"/>
+      <c r="L108" s="5"/>
+      <c r="M108" s="5"/>
+      <c r="N108" s="5"/>
+      <c r="O108" s="5"/>
+      <c r="P108" s="5"/>
+      <c r="Q108" s="5"/>
+      <c r="R108" s="5"/>
+      <c r="S108" s="5"/>
+      <c r="T108" s="5"/>
+      <c r="U108" s="5"/>
+      <c r="V108" s="5"/>
+      <c r="W108" s="5"/>
+      <c r="X108" s="5"/>
+      <c r="Y108" s="5"/>
+      <c r="Z108" s="5"/>
+      <c r="AA108" s="5"/>
+      <c r="AB108" s="5"/>
+      <c r="AC108" s="5"/>
+      <c r="AD108" s="5"/>
+      <c r="AE108" s="5"/>
+      <c r="AF108" s="5"/>
+      <c r="AG108" s="5"/>
+    </row>
+  </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:P1"/>
+    <mergeCell ref="Q1:AG1"/>
+    <mergeCell ref="A3:A55"/>
+    <mergeCell ref="A56:A108"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
 </file>
--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -8298,10 +8298,10 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -12851,7 +12851,9 @@
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A3" s="28"/>
+      <c r="A3" s="28">
+        <v>2025</v>
+      </c>
       <c r="B3" s="23" t="s">
         <v>4</v>
       </c>
@@ -12948,7 +12950,9 @@
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A4" s="28"/>
+      <c r="A4" s="28">
+        <v>2025</v>
+      </c>
       <c r="B4" s="23" t="s">
         <v>4</v>
       </c>
@@ -13045,7 +13049,9 @@
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A5" s="28"/>
+      <c r="A5" s="28">
+        <v>2025</v>
+      </c>
       <c r="B5" s="23" t="s">
         <v>4</v>
       </c>
@@ -13142,7 +13148,9 @@
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A6" s="28"/>
+      <c r="A6" s="28">
+        <v>2025</v>
+      </c>
       <c r="B6" s="23" t="s">
         <v>4</v>
       </c>
@@ -13239,7 +13247,9 @@
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A7" s="28"/>
+      <c r="A7" s="28">
+        <v>2025</v>
+      </c>
       <c r="B7" s="23" t="s">
         <v>5</v>
       </c>
@@ -13336,7 +13346,9 @@
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A8" s="28"/>
+      <c r="A8" s="28">
+        <v>2025</v>
+      </c>
       <c r="B8" s="23" t="s">
         <v>5</v>
       </c>
@@ -13435,7 +13447,9 @@
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A9" s="28"/>
+      <c r="A9" s="28">
+        <v>2025</v>
+      </c>
       <c r="B9" s="23" t="s">
         <v>5</v>
       </c>
@@ -13532,7 +13546,9 @@
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A10" s="28"/>
+      <c r="A10" s="28">
+        <v>2025</v>
+      </c>
       <c r="B10" s="23" t="s">
         <v>5</v>
       </c>
@@ -13629,7 +13645,9 @@
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A11" s="28"/>
+      <c r="A11" s="28">
+        <v>2025</v>
+      </c>
       <c r="B11" s="23" t="s">
         <v>6</v>
       </c>
@@ -13726,7 +13744,9 @@
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A12" s="28"/>
+      <c r="A12" s="28">
+        <v>2025</v>
+      </c>
       <c r="B12" s="23" t="s">
         <v>6</v>
       </c>
@@ -13823,7 +13843,9 @@
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A13" s="28"/>
+      <c r="A13" s="28">
+        <v>2025</v>
+      </c>
       <c r="B13" s="23" t="s">
         <v>6</v>
       </c>
@@ -13920,7 +13942,9 @@
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A14" s="28"/>
+      <c r="A14" s="28">
+        <v>2025</v>
+      </c>
       <c r="B14" s="23" t="s">
         <v>6</v>
       </c>
@@ -14017,7 +14041,9 @@
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A15" s="28"/>
+      <c r="A15" s="28">
+        <v>2025</v>
+      </c>
       <c r="B15" s="23" t="s">
         <v>7</v>
       </c>
@@ -14116,7 +14142,9 @@
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A16" s="28"/>
+      <c r="A16" s="28">
+        <v>2025</v>
+      </c>
       <c r="B16" s="23" t="s">
         <v>7</v>
       </c>
@@ -14213,7 +14241,9 @@
       </c>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A17" s="28"/>
+      <c r="A17" s="28">
+        <v>2025</v>
+      </c>
       <c r="B17" s="23" t="s">
         <v>7</v>
       </c>
@@ -14310,7 +14340,9 @@
       </c>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A18" s="28"/>
+      <c r="A18" s="28">
+        <v>2025</v>
+      </c>
       <c r="B18" s="23" t="s">
         <v>7</v>
       </c>
@@ -14407,7 +14439,9 @@
       </c>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A19" s="28"/>
+      <c r="A19" s="28">
+        <v>2025</v>
+      </c>
       <c r="B19" s="23" t="s">
         <v>8</v>
       </c>
@@ -14504,7 +14538,9 @@
       </c>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A20" s="28"/>
+      <c r="A20" s="28">
+        <v>2025</v>
+      </c>
       <c r="B20" s="23" t="s">
         <v>8</v>
       </c>
@@ -14601,7 +14637,9 @@
       </c>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A21" s="28"/>
+      <c r="A21" s="28">
+        <v>2025</v>
+      </c>
       <c r="B21" s="23" t="s">
         <v>8</v>
       </c>
@@ -14698,7 +14736,9 @@
       </c>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A22" s="28"/>
+      <c r="A22" s="28">
+        <v>2025</v>
+      </c>
       <c r="B22" s="23" t="s">
         <v>8</v>
       </c>
@@ -14795,7 +14835,9 @@
       </c>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A23" s="28"/>
+      <c r="A23" s="28">
+        <v>2025</v>
+      </c>
       <c r="B23" s="23" t="s">
         <v>8</v>
       </c>
@@ -14890,7 +14932,9 @@
       </c>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A24" s="28"/>
+      <c r="A24" s="28">
+        <v>2025</v>
+      </c>
       <c r="B24" s="23" t="s">
         <v>9</v>
       </c>
@@ -14983,7 +15027,9 @@
       </c>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A25" s="28"/>
+      <c r="A25" s="28">
+        <v>2025</v>
+      </c>
       <c r="B25" s="23" t="s">
         <v>9</v>
       </c>
@@ -15076,7 +15122,9 @@
       </c>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A26" s="28"/>
+      <c r="A26" s="28">
+        <v>2025</v>
+      </c>
       <c r="B26" s="23" t="s">
         <v>9</v>
       </c>
@@ -15169,7 +15217,9 @@
       </c>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A27" s="28"/>
+      <c r="A27" s="28">
+        <v>2025</v>
+      </c>
       <c r="B27" s="23" t="s">
         <v>9</v>
       </c>
@@ -15262,7 +15312,9 @@
       </c>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A28" s="28"/>
+      <c r="A28" s="28">
+        <v>2025</v>
+      </c>
       <c r="B28" s="23" t="s">
         <v>10</v>
       </c>
@@ -15355,7 +15407,9 @@
       </c>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A29" s="28"/>
+      <c r="A29" s="28">
+        <v>2025</v>
+      </c>
       <c r="B29" s="23" t="s">
         <v>10</v>
       </c>
@@ -15448,7 +15502,9 @@
       </c>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A30" s="28"/>
+      <c r="A30" s="28">
+        <v>2025</v>
+      </c>
       <c r="B30" s="23" t="s">
         <v>10</v>
       </c>
@@ -15541,7 +15597,9 @@
       </c>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A31" s="28"/>
+      <c r="A31" s="28">
+        <v>2025</v>
+      </c>
       <c r="B31" s="23" t="s">
         <v>10</v>
       </c>
@@ -15634,7 +15692,9 @@
       </c>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A32" s="28"/>
+      <c r="A32" s="28">
+        <v>2025</v>
+      </c>
       <c r="B32" s="23" t="s">
         <v>10</v>
       </c>
@@ -15727,7 +15787,9 @@
       </c>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A33" s="28"/>
+      <c r="A33" s="28">
+        <v>2025</v>
+      </c>
       <c r="B33" s="23" t="s">
         <v>11</v>
       </c>
@@ -15820,7 +15882,9 @@
       </c>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A34" s="28"/>
+      <c r="A34" s="28">
+        <v>2025</v>
+      </c>
       <c r="B34" s="23" t="s">
         <v>11</v>
       </c>
@@ -15913,7 +15977,9 @@
       </c>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A35" s="28"/>
+      <c r="A35" s="28">
+        <v>2025</v>
+      </c>
       <c r="B35" s="23" t="s">
         <v>11</v>
       </c>
@@ -16006,7 +16072,9 @@
       </c>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A36" s="28"/>
+      <c r="A36" s="28">
+        <v>2025</v>
+      </c>
       <c r="B36" s="23" t="s">
         <v>11</v>
       </c>
@@ -16099,7 +16167,9 @@
       </c>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A37" s="28"/>
+      <c r="A37" s="28">
+        <v>2025</v>
+      </c>
       <c r="B37" s="23" t="s">
         <v>12</v>
       </c>
@@ -16192,7 +16262,9 @@
       </c>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A38" s="28"/>
+      <c r="A38" s="28">
+        <v>2025</v>
+      </c>
       <c r="B38" s="23" t="s">
         <v>12</v>
       </c>
@@ -16285,7 +16357,9 @@
       </c>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A39" s="28"/>
+      <c r="A39" s="28">
+        <v>2025</v>
+      </c>
       <c r="B39" s="23" t="s">
         <v>12</v>
       </c>
@@ -16378,7 +16452,9 @@
       </c>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A40" s="28"/>
+      <c r="A40" s="28">
+        <v>2025</v>
+      </c>
       <c r="B40" s="23" t="s">
         <v>12</v>
       </c>
@@ -16471,7 +16547,9 @@
       </c>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A41" s="28"/>
+      <c r="A41" s="28">
+        <v>2025</v>
+      </c>
       <c r="B41" s="23" t="s">
         <v>13</v>
       </c>
@@ -16564,7 +16642,9 @@
       </c>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A42" s="28"/>
+      <c r="A42" s="28">
+        <v>2025</v>
+      </c>
       <c r="B42" s="23" t="s">
         <v>13</v>
       </c>
@@ -16657,7 +16737,9 @@
       </c>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A43" s="28"/>
+      <c r="A43" s="28">
+        <v>2025</v>
+      </c>
       <c r="B43" s="23" t="s">
         <v>13</v>
       </c>
@@ -16750,7 +16832,9 @@
       </c>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A44" s="28"/>
+      <c r="A44" s="28">
+        <v>2025</v>
+      </c>
       <c r="B44" s="23" t="s">
         <v>13</v>
       </c>
@@ -16843,7 +16927,9 @@
       </c>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A45" s="28"/>
+      <c r="A45" s="28">
+        <v>2025</v>
+      </c>
       <c r="B45" s="23" t="s">
         <v>13</v>
       </c>
@@ -16936,7 +17022,9 @@
       </c>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A46" s="28"/>
+      <c r="A46" s="28">
+        <v>2025</v>
+      </c>
       <c r="B46" s="23" t="s">
         <v>14</v>
       </c>
@@ -17029,7 +17117,9 @@
       </c>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A47" s="28"/>
+      <c r="A47" s="28">
+        <v>2025</v>
+      </c>
       <c r="B47" s="23" t="s">
         <v>14</v>
       </c>
@@ -17122,7 +17212,9 @@
       </c>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A48" s="28"/>
+      <c r="A48" s="28">
+        <v>2025</v>
+      </c>
       <c r="B48" s="23" t="s">
         <v>14</v>
       </c>
@@ -17215,7 +17307,9 @@
       </c>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A49" s="28"/>
+      <c r="A49" s="28">
+        <v>2025</v>
+      </c>
       <c r="B49" s="23" t="s">
         <v>14</v>
       </c>
@@ -17308,7 +17402,9 @@
       </c>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A50" s="28"/>
+      <c r="A50" s="28">
+        <v>2025</v>
+      </c>
       <c r="B50" s="23" t="s">
         <v>15</v>
       </c>
@@ -17401,7 +17497,9 @@
       </c>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A51" s="28"/>
+      <c r="A51" s="28">
+        <v>2025</v>
+      </c>
       <c r="B51" s="23" t="s">
         <v>15</v>
       </c>
@@ -17494,7 +17592,9 @@
       </c>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A52" s="28"/>
+      <c r="A52" s="28">
+        <v>2025</v>
+      </c>
       <c r="B52" s="23" t="s">
         <v>15</v>
       </c>
@@ -17587,7 +17687,9 @@
       </c>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A53" s="28"/>
+      <c r="A53" s="28">
+        <v>2025</v>
+      </c>
       <c r="B53" s="23" t="s">
         <v>15</v>
       </c>
@@ -17680,7 +17782,9 @@
       </c>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A54" s="28"/>
+      <c r="A54" s="28">
+        <v>2025</v>
+      </c>
       <c r="B54" s="23" t="s">
         <v>15</v>
       </c>
@@ -17868,7 +17972,9 @@
       </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A56" s="29"/>
+      <c r="A56" s="29">
+        <v>2026</v>
+      </c>
       <c r="B56" s="23" t="s">
         <v>4</v>
       </c>
@@ -17961,7 +18067,9 @@
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A57" s="29"/>
+      <c r="A57" s="29">
+        <v>2026</v>
+      </c>
       <c r="B57" s="23" t="s">
         <v>4</v>
       </c>
@@ -18054,7 +18162,9 @@
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A58" s="29"/>
+      <c r="A58" s="29">
+        <v>2026</v>
+      </c>
       <c r="B58" s="23" t="s">
         <v>4</v>
       </c>
@@ -18147,7 +18257,9 @@
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A59" s="29"/>
+      <c r="A59" s="29">
+        <v>2026</v>
+      </c>
       <c r="B59" s="23" t="s">
         <v>4</v>
       </c>
@@ -18240,7 +18352,9 @@
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A60" s="29"/>
+      <c r="A60" s="29">
+        <v>2026</v>
+      </c>
       <c r="B60" s="23" t="s">
         <v>5</v>
       </c>
@@ -18333,7 +18447,9 @@
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A61" s="29"/>
+      <c r="A61" s="29">
+        <v>2026</v>
+      </c>
       <c r="B61" s="23" t="s">
         <v>5</v>
       </c>
@@ -18426,7 +18542,9 @@
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A62" s="29"/>
+      <c r="A62" s="29">
+        <v>2026</v>
+      </c>
       <c r="B62" s="23" t="s">
         <v>5</v>
       </c>
@@ -18519,7 +18637,9 @@
       </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A63" s="29"/>
+      <c r="A63" s="29">
+        <v>2026</v>
+      </c>
       <c r="B63" s="23" t="s">
         <v>5</v>
       </c>
@@ -18612,7 +18732,9 @@
       </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A64" s="29"/>
+      <c r="A64" s="29">
+        <v>2026</v>
+      </c>
       <c r="B64" s="23" t="s">
         <v>6</v>
       </c>
@@ -18705,7 +18827,9 @@
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A65" s="29"/>
+      <c r="A65" s="29">
+        <v>2026</v>
+      </c>
       <c r="B65" s="23" t="s">
         <v>6</v>
       </c>
@@ -18798,7 +18922,9 @@
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A66" s="29"/>
+      <c r="A66" s="29">
+        <v>2026</v>
+      </c>
       <c r="B66" s="23" t="s">
         <v>6</v>
       </c>
@@ -18891,7 +19017,9 @@
       </c>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A67" s="29"/>
+      <c r="A67" s="29">
+        <v>2026</v>
+      </c>
       <c r="B67" s="23" t="s">
         <v>6</v>
       </c>
@@ -18930,7 +19058,9 @@
       <c r="AG67" s="24"/>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A68" s="29"/>
+      <c r="A68" s="29">
+        <v>2026</v>
+      </c>
       <c r="B68" s="23" t="s">
         <v>7</v>
       </c>
@@ -18969,7 +19099,9 @@
       <c r="AG68" s="24"/>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A69" s="29"/>
+      <c r="A69" s="29">
+        <v>2026</v>
+      </c>
       <c r="B69" s="23" t="s">
         <v>7</v>
       </c>
@@ -19008,7 +19140,9 @@
       <c r="AG69" s="24"/>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A70" s="29"/>
+      <c r="A70" s="29">
+        <v>2026</v>
+      </c>
       <c r="B70" s="23" t="s">
         <v>7</v>
       </c>
@@ -19047,7 +19181,9 @@
       <c r="AG70" s="24"/>
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A71" s="29"/>
+      <c r="A71" s="29">
+        <v>2026</v>
+      </c>
       <c r="B71" s="23" t="s">
         <v>7</v>
       </c>
@@ -19086,7 +19222,9 @@
       <c r="AG71" s="24"/>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A72" s="29"/>
+      <c r="A72" s="29">
+        <v>2026</v>
+      </c>
       <c r="B72" s="23" t="s">
         <v>7</v>
       </c>
@@ -19125,7 +19263,9 @@
       <c r="AG72" s="24"/>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A73" s="29"/>
+      <c r="A73" s="29">
+        <v>2026</v>
+      </c>
       <c r="B73" s="23" t="s">
         <v>8</v>
       </c>
@@ -19164,7 +19304,9 @@
       <c r="AG73" s="24"/>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A74" s="29"/>
+      <c r="A74" s="29">
+        <v>2026</v>
+      </c>
       <c r="B74" s="23" t="s">
         <v>8</v>
       </c>
@@ -19203,7 +19345,9 @@
       <c r="AG74" s="24"/>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A75" s="29"/>
+      <c r="A75" s="29">
+        <v>2026</v>
+      </c>
       <c r="B75" s="23" t="s">
         <v>8</v>
       </c>
@@ -19242,7 +19386,9 @@
       <c r="AG75" s="24"/>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A76" s="29"/>
+      <c r="A76" s="29">
+        <v>2026</v>
+      </c>
       <c r="B76" s="23" t="s">
         <v>8</v>
       </c>
@@ -19281,7 +19427,9 @@
       <c r="AG76" s="24"/>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A77" s="29"/>
+      <c r="A77" s="29">
+        <v>2026</v>
+      </c>
       <c r="B77" s="23" t="s">
         <v>9</v>
       </c>
@@ -19320,7 +19468,9 @@
       <c r="AG77" s="24"/>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A78" s="29"/>
+      <c r="A78" s="29">
+        <v>2026</v>
+      </c>
       <c r="B78" s="23" t="s">
         <v>9</v>
       </c>
@@ -19359,7 +19509,9 @@
       <c r="AG78" s="24"/>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A79" s="29"/>
+      <c r="A79" s="29">
+        <v>2026</v>
+      </c>
       <c r="B79" s="23" t="s">
         <v>9</v>
       </c>
@@ -19398,7 +19550,9 @@
       <c r="AG79" s="24"/>
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A80" s="29"/>
+      <c r="A80" s="29">
+        <v>2026</v>
+      </c>
       <c r="B80" s="23" t="s">
         <v>9</v>
       </c>
@@ -19437,7 +19591,9 @@
       <c r="AG80" s="24"/>
     </row>
     <row r="81" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A81" s="29"/>
+      <c r="A81" s="29">
+        <v>2026</v>
+      </c>
       <c r="B81" s="23" t="s">
         <v>10</v>
       </c>
@@ -19476,7 +19632,9 @@
       <c r="AG81" s="24"/>
     </row>
     <row r="82" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A82" s="29"/>
+      <c r="A82" s="29">
+        <v>2026</v>
+      </c>
       <c r="B82" s="23" t="s">
         <v>10</v>
       </c>
@@ -19515,7 +19673,9 @@
       <c r="AG82" s="24"/>
     </row>
     <row r="83" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A83" s="29"/>
+      <c r="A83" s="29">
+        <v>2026</v>
+      </c>
       <c r="B83" s="23" t="s">
         <v>10</v>
       </c>
@@ -19554,7 +19714,9 @@
       <c r="AG83" s="24"/>
     </row>
     <row r="84" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A84" s="29"/>
+      <c r="A84" s="29">
+        <v>2026</v>
+      </c>
       <c r="B84" s="23" t="s">
         <v>10</v>
       </c>
@@ -19593,7 +19755,9 @@
       <c r="AG84" s="24"/>
     </row>
     <row r="85" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A85" s="29"/>
+      <c r="A85" s="29">
+        <v>2026</v>
+      </c>
       <c r="B85" s="23" t="s">
         <v>10</v>
       </c>
@@ -19632,7 +19796,9 @@
       <c r="AG85" s="24"/>
     </row>
     <row r="86" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A86" s="29"/>
+      <c r="A86" s="29">
+        <v>2026</v>
+      </c>
       <c r="B86" s="23" t="s">
         <v>11</v>
       </c>
@@ -19671,7 +19837,9 @@
       <c r="AG86" s="24"/>
     </row>
     <row r="87" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A87" s="29"/>
+      <c r="A87" s="29">
+        <v>2026</v>
+      </c>
       <c r="B87" s="23" t="s">
         <v>11</v>
       </c>
@@ -19710,7 +19878,9 @@
       <c r="AG87" s="24"/>
     </row>
     <row r="88" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A88" s="29"/>
+      <c r="A88" s="29">
+        <v>2026</v>
+      </c>
       <c r="B88" s="23" t="s">
         <v>11</v>
       </c>
@@ -19749,7 +19919,9 @@
       <c r="AG88" s="24"/>
     </row>
     <row r="89" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A89" s="29"/>
+      <c r="A89" s="29">
+        <v>2026</v>
+      </c>
       <c r="B89" s="23" t="s">
         <v>11</v>
       </c>
@@ -19788,7 +19960,9 @@
       <c r="AG89" s="24"/>
     </row>
     <row r="90" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A90" s="29"/>
+      <c r="A90" s="29">
+        <v>2026</v>
+      </c>
       <c r="B90" s="23" t="s">
         <v>12</v>
       </c>
@@ -19827,7 +20001,9 @@
       <c r="AG90" s="24"/>
     </row>
     <row r="91" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A91" s="29"/>
+      <c r="A91" s="29">
+        <v>2026</v>
+      </c>
       <c r="B91" s="23" t="s">
         <v>12</v>
       </c>
@@ -19866,7 +20042,9 @@
       <c r="AG91" s="24"/>
     </row>
     <row r="92" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A92" s="29"/>
+      <c r="A92" s="29">
+        <v>2026</v>
+      </c>
       <c r="B92" s="23" t="s">
         <v>12</v>
       </c>
@@ -19905,7 +20083,9 @@
       <c r="AG92" s="24"/>
     </row>
     <row r="93" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A93" s="29"/>
+      <c r="A93" s="29">
+        <v>2026</v>
+      </c>
       <c r="B93" s="23" t="s">
         <v>12</v>
       </c>
@@ -19944,7 +20124,9 @@
       <c r="AG93" s="24"/>
     </row>
     <row r="94" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A94" s="29"/>
+      <c r="A94" s="29">
+        <v>2026</v>
+      </c>
       <c r="B94" s="23" t="s">
         <v>13</v>
       </c>
@@ -19983,7 +20165,9 @@
       <c r="AG94" s="24"/>
     </row>
     <row r="95" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A95" s="29"/>
+      <c r="A95" s="29">
+        <v>2026</v>
+      </c>
       <c r="B95" s="23" t="s">
         <v>13</v>
       </c>
@@ -20022,7 +20206,9 @@
       <c r="AG95" s="24"/>
     </row>
     <row r="96" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A96" s="29"/>
+      <c r="A96" s="29">
+        <v>2026</v>
+      </c>
       <c r="B96" s="23" t="s">
         <v>13</v>
       </c>
@@ -20061,7 +20247,9 @@
       <c r="AG96" s="24"/>
     </row>
     <row r="97" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A97" s="29"/>
+      <c r="A97" s="29">
+        <v>2026</v>
+      </c>
       <c r="B97" s="23" t="s">
         <v>13</v>
       </c>
@@ -20100,7 +20288,9 @@
       <c r="AG97" s="24"/>
     </row>
     <row r="98" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A98" s="29"/>
+      <c r="A98" s="29">
+        <v>2026</v>
+      </c>
       <c r="B98" s="23" t="s">
         <v>13</v>
       </c>
@@ -20139,7 +20329,9 @@
       <c r="AG98" s="24"/>
     </row>
     <row r="99" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A99" s="29"/>
+      <c r="A99" s="29">
+        <v>2026</v>
+      </c>
       <c r="B99" s="23" t="s">
         <v>14</v>
       </c>
@@ -20178,7 +20370,9 @@
       <c r="AG99" s="24"/>
     </row>
     <row r="100" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A100" s="29"/>
+      <c r="A100" s="29">
+        <v>2026</v>
+      </c>
       <c r="B100" s="23" t="s">
         <v>14</v>
       </c>
@@ -20217,7 +20411,9 @@
       <c r="AG100" s="24"/>
     </row>
     <row r="101" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A101" s="29"/>
+      <c r="A101" s="29">
+        <v>2026</v>
+      </c>
       <c r="B101" s="23" t="s">
         <v>14</v>
       </c>
@@ -20256,7 +20452,9 @@
       <c r="AG101" s="24"/>
     </row>
     <row r="102" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A102" s="29"/>
+      <c r="A102" s="29">
+        <v>2026</v>
+      </c>
       <c r="B102" s="23" t="s">
         <v>14</v>
       </c>
@@ -20295,7 +20493,9 @@
       <c r="AG102" s="24"/>
     </row>
     <row r="103" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A103" s="29"/>
+      <c r="A103" s="29">
+        <v>2026</v>
+      </c>
       <c r="B103" s="23" t="s">
         <v>15</v>
       </c>
@@ -20334,7 +20534,9 @@
       <c r="AG103" s="24"/>
     </row>
     <row r="104" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A104" s="29"/>
+      <c r="A104" s="29">
+        <v>2026</v>
+      </c>
       <c r="B104" s="23" t="s">
         <v>15</v>
       </c>
@@ -20373,7 +20575,9 @@
       <c r="AG104" s="24"/>
     </row>
     <row r="105" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A105" s="29"/>
+      <c r="A105" s="29">
+        <v>2026</v>
+      </c>
       <c r="B105" s="23" t="s">
         <v>15</v>
       </c>
@@ -20412,7 +20616,9 @@
       <c r="AG105" s="24"/>
     </row>
     <row r="106" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A106" s="29"/>
+      <c r="A106" s="29">
+        <v>2026</v>
+      </c>
       <c r="B106" s="23" t="s">
         <v>15</v>
       </c>
@@ -20451,7 +20657,9 @@
       <c r="AG106" s="24"/>
     </row>
     <row r="107" spans="1:33" x14ac:dyDescent="0.25">
-      <c r="A107" s="29"/>
+      <c r="A107" s="29">
+        <v>2026</v>
+      </c>
       <c r="B107" s="23" t="s">
         <v>15</v>
       </c>
@@ -20490,10 +20698,6 @@
       <c r="AG107" s="5"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:A54"/>
-    <mergeCell ref="A55:A107"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="7"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -7969,7 +7969,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="437" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="46">
   <si>
     <t>Mes</t>
   </si>
@@ -12124,13 +12124,13 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:E37"/>
+  <dimension ref="A1:AF37"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="5" width="20.7109375" customWidth="1"/>
+    <col min="3" max="32" width="20.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A1" s="12" t="s">
         <v>21</v>
       </c>
@@ -12146,8 +12146,89 @@
       <c r="E1" s="12" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A2" s="17">
         <v>2025</v>
       </c>
@@ -12161,10 +12242,89 @@
         <v>0.98053892215568861</v>
       </c>
       <c r="E2" s="20">
-        <v>0.9839939024390244</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.98757763975155277</v>
+      </c>
+      <c r="F2" s="20">
+        <v>0.93269230769230771</v>
+      </c>
+      <c r="G2" s="20">
+        <v>1</v>
+      </c>
+      <c r="H2" s="20">
+        <v>0.9939393939393939</v>
+      </c>
+      <c r="I2" s="20">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="J2" s="20">
+        <v>1</v>
+      </c>
+      <c r="K2" s="20">
+        <v>1</v>
+      </c>
+      <c r="L2" s="20">
+        <v>0.92792792792792789</v>
+      </c>
+      <c r="M2" s="20">
+        <v>1</v>
+      </c>
+      <c r="N2" s="20">
+        <v>1</v>
+      </c>
+      <c r="O2" s="20">
+        <v>1</v>
+      </c>
+      <c r="P2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="20">
+        <v>1</v>
+      </c>
+      <c r="R2" s="20">
+        <v>1</v>
+      </c>
+      <c r="S2" s="20">
+        <v>1</v>
+      </c>
+      <c r="T2" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="U2" s="20">
+        <v>0.98461538461538467</v>
+      </c>
+      <c r="V2" s="20">
+        <v>0.989247311827957</v>
+      </c>
+      <c r="W2" s="20">
+        <v>0.94666666666666666</v>
+      </c>
+      <c r="X2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="20">
+        <v>0.92792792792792789</v>
+      </c>
+      <c r="AD2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A3" s="17">
         <v>2025</v>
       </c>
@@ -12172,16 +12332,97 @@
         <v>5</v>
       </c>
       <c r="C3" s="20">
-        <v>0.95233265720081139</v>
+        <v>0.9662921348314607</v>
       </c>
       <c r="D3" s="20">
-        <v>0.93129770992366412</v>
+        <v>0.96610169491525422</v>
       </c>
       <c r="E3" s="20">
-        <v>0.95233265720081139</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.96650717703349287</v>
+      </c>
+      <c r="F3" s="20">
+        <v>0.86086956521739133</v>
+      </c>
+      <c r="G3" s="20">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20">
+        <v>1</v>
+      </c>
+      <c r="I3" s="20">
+        <v>0.94771241830065356</v>
+      </c>
+      <c r="J3" s="20">
+        <v>1</v>
+      </c>
+      <c r="K3" s="20">
+        <v>0.98843930635838151</v>
+      </c>
+      <c r="L3" s="20">
+        <v>0.79347826086956519</v>
+      </c>
+      <c r="M3" s="20">
+        <v>1</v>
+      </c>
+      <c r="N3" s="20">
+        <v>1</v>
+      </c>
+      <c r="O3" s="20">
+        <v>1</v>
+      </c>
+      <c r="P3" s="20">
+        <v>0.81132075471698117</v>
+      </c>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+      <c r="R3" s="20">
+        <v>1</v>
+      </c>
+      <c r="S3" s="20">
+        <v>1</v>
+      </c>
+      <c r="T3" s="20">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="U3" s="20">
+        <v>0.91176470588235292</v>
+      </c>
+      <c r="V3" s="20">
+        <v>1</v>
+      </c>
+      <c r="W3" s="20">
+        <v>0.97647058823529409</v>
+      </c>
+      <c r="X3" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="20">
+        <v>0.96363636363636362</v>
+      </c>
+      <c r="AB3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="20">
+        <v>0.79347826086956519</v>
+      </c>
+      <c r="AD3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A4" s="17">
         <v>2025</v>
       </c>
@@ -12195,10 +12436,89 @@
         <v>0.93188010899182561</v>
       </c>
       <c r="E4" s="20">
-        <v>0.96153846153846156</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.99534161490683226</v>
+      </c>
+      <c r="F4" s="20">
+        <v>0.75206611570247939</v>
+      </c>
+      <c r="G4" s="20">
+        <v>1</v>
+      </c>
+      <c r="H4" s="20">
+        <v>0.99444444444444446</v>
+      </c>
+      <c r="I4" s="20">
+        <v>0.89090909090909087</v>
+      </c>
+      <c r="J4" s="20">
+        <v>0.99601593625498008</v>
+      </c>
+      <c r="K4" s="20">
+        <v>0.9854368932038835</v>
+      </c>
+      <c r="L4" s="20">
+        <v>1</v>
+      </c>
+      <c r="M4" s="20">
+        <v>1</v>
+      </c>
+      <c r="N4" s="20">
+        <v>1</v>
+      </c>
+      <c r="O4" s="20">
+        <v>1</v>
+      </c>
+      <c r="P4" s="20">
+        <v>0.86885245901639341</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>0.98913043478260865</v>
+      </c>
+      <c r="R4" s="20">
+        <v>0.98936170212765961</v>
+      </c>
+      <c r="S4" s="20">
+        <v>1</v>
+      </c>
+      <c r="T4" s="20">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="U4" s="20">
+        <v>0.86075949367088611</v>
+      </c>
+      <c r="V4" s="20">
+        <v>1</v>
+      </c>
+      <c r="W4" s="20">
+        <v>0.91860465116279066</v>
+      </c>
+      <c r="X4" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="AB4" s="20">
+        <v>0.99206349206349209</v>
+      </c>
+      <c r="AC4" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A5" s="17">
         <v>2025</v>
       </c>
@@ -12206,16 +12526,97 @@
         <v>7</v>
       </c>
       <c r="C5" s="20">
-        <v>0.97150489759572578</v>
+        <v>0.97153024911032027</v>
       </c>
       <c r="D5" s="20">
-        <v>0.95644283121597096</v>
+        <v>0.95652173913043481</v>
       </c>
       <c r="E5" s="20">
-        <v>0.97150489759572578</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.98601398601398604</v>
+      </c>
+      <c r="F5" s="20">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="G5" s="20">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20">
+        <v>1</v>
+      </c>
+      <c r="I5" s="20">
+        <v>0.87610619469026552</v>
+      </c>
+      <c r="J5" s="20">
+        <v>0.9946236559139785</v>
+      </c>
+      <c r="K5" s="20">
+        <v>0.9526627218934911</v>
+      </c>
+      <c r="L5" s="20">
+        <v>1</v>
+      </c>
+      <c r="M5" s="20">
+        <v>1</v>
+      </c>
+      <c r="N5" s="20">
+        <v>1</v>
+      </c>
+      <c r="O5" s="20">
+        <v>1</v>
+      </c>
+      <c r="P5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="20">
+        <v>1</v>
+      </c>
+      <c r="S5" s="20">
+        <v>0.98795180722891562</v>
+      </c>
+      <c r="T5" s="20">
+        <v>0.85245901639344257</v>
+      </c>
+      <c r="U5" s="20">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="V5" s="20">
+        <v>1</v>
+      </c>
+      <c r="W5" s="20">
+        <v>0.88732394366197187</v>
+      </c>
+      <c r="X5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="20">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="AB5" s="20">
+        <v>0.93684210526315792</v>
+      </c>
+      <c r="AC5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A6" s="17">
         <v>2025</v>
       </c>
@@ -12223,16 +12624,95 @@
         <v>8</v>
       </c>
       <c r="C6" s="20">
-        <v>0.96446384039900246</v>
+        <v>0.96508728179551118</v>
       </c>
       <c r="D6" s="20">
         <v>0.93925233644859818</v>
       </c>
       <c r="E6" s="20">
-        <v>0.96446384039900246</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.99465240641711228</v>
+      </c>
+      <c r="F6" s="20">
+        <v>0.79605263157894735</v>
+      </c>
+      <c r="G6" s="20">
+        <v>1</v>
+      </c>
+      <c r="H6" s="20">
+        <v>1</v>
+      </c>
+      <c r="I6" s="20">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0.99659863945578231</v>
+      </c>
+      <c r="K6" s="20">
+        <v>0.98222222222222222</v>
+      </c>
+      <c r="L6" s="20">
+        <v>1</v>
+      </c>
+      <c r="M6" s="20">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20">
+        <v>1</v>
+      </c>
+      <c r="O6" s="20">
+        <v>1</v>
+      </c>
+      <c r="P6" s="20">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="20">
+        <v>1</v>
+      </c>
+      <c r="S6" s="20">
+        <v>0.99137931034482762</v>
+      </c>
+      <c r="T6" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U6" s="20">
+        <v>0.85526315789473684</v>
+      </c>
+      <c r="V6" s="20">
+        <v>1</v>
+      </c>
+      <c r="W6" s="20">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="X6" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20">
+        <v>0.98717948717948723</v>
+      </c>
+      <c r="AB6" s="20">
+        <v>0.97959183673469385</v>
+      </c>
+      <c r="AC6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A7" s="17">
         <v>2025</v>
       </c>
@@ -12240,16 +12720,91 @@
         <v>9</v>
       </c>
       <c r="C7" s="20">
-        <v>0.94014598540145988</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="D7" s="20">
-        <v>0.91644562334217505</v>
+        <v>0.92819148936170215</v>
       </c>
       <c r="E7" s="20">
-        <v>0.94014598540145988</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.97077922077922074</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0.82666666666666666</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20">
+        <v>0.98952879581151831</v>
+      </c>
+      <c r="I7" s="20">
+        <v>0.8404907975460123</v>
+      </c>
+      <c r="J7" s="20">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20">
+        <v>0.89772727272727271</v>
+      </c>
+      <c r="L7" s="20">
+        <v>1</v>
+      </c>
+      <c r="M7" s="20">
+        <v>1</v>
+      </c>
+      <c r="N7" s="20">
+        <v>1</v>
+      </c>
+      <c r="O7" s="20">
+        <v>1</v>
+      </c>
+      <c r="P7" s="20">
+        <v>0.94202898550724634</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+      <c r="R7" s="20">
+        <v>1</v>
+      </c>
+      <c r="S7" s="20">
+        <v>1</v>
+      </c>
+      <c r="T7" s="20">
+        <v>0.72839506172839508</v>
+      </c>
+      <c r="U7" s="20">
+        <v>0.80487804878048785</v>
+      </c>
+      <c r="V7" s="20">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="W7" s="20">
+        <v>0.87654320987654322</v>
+      </c>
+      <c r="X7" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="AB7" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="AC7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A8" s="17">
         <v>2025</v>
       </c>
@@ -12257,16 +12812,91 @@
         <v>10</v>
       </c>
       <c r="C8" s="20">
-        <v>0.96103896103896103</v>
+        <v>0.97129909365558909</v>
       </c>
       <c r="D8" s="20">
-        <v>0.94759825327510916</v>
+        <v>0.96050775740479544</v>
       </c>
       <c r="E8" s="20">
-        <v>0.96103896103896103</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.98373983739837401</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0.91216216216216217</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20">
+        <v>0.99428571428571433</v>
+      </c>
+      <c r="I8" s="20">
+        <v>0.91034482758620694</v>
+      </c>
+      <c r="J8" s="20">
+        <v>0.99585062240663902</v>
+      </c>
+      <c r="K8" s="20">
+        <v>0.95408163265306123</v>
+      </c>
+      <c r="L8" s="20">
+        <v>1</v>
+      </c>
+      <c r="M8" s="20">
+        <v>0.99230769230769234</v>
+      </c>
+      <c r="N8" s="20">
+        <v>1</v>
+      </c>
+      <c r="O8" s="20">
+        <v>1</v>
+      </c>
+      <c r="P8" s="20">
+        <v>0.92537313432835822</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+      <c r="R8" s="20">
+        <v>1</v>
+      </c>
+      <c r="S8" s="20">
+        <v>0.98958333333333337</v>
+      </c>
+      <c r="T8" s="20">
+        <v>0.90123456790123457</v>
+      </c>
+      <c r="U8" s="20">
+        <v>0.90476190476190477</v>
+      </c>
+      <c r="V8" s="20">
+        <v>0.98979591836734693</v>
+      </c>
+      <c r="W8" s="20">
+        <v>0.91463414634146345</v>
+      </c>
+      <c r="X8" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20">
+        <v>0.98571428571428577</v>
+      </c>
+      <c r="AB8" s="20">
+        <v>0.93650793650793651</v>
+      </c>
+      <c r="AC8" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="20">
+        <v>0.99230769230769234</v>
+      </c>
+      <c r="AE8" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A9" s="17">
         <v>2025</v>
       </c>
@@ -12274,16 +12904,91 @@
         <v>11</v>
       </c>
       <c r="C9" s="20">
-        <v>0.96092592592592596</v>
+        <v>0.95263157894736838</v>
       </c>
       <c r="D9" s="20">
-        <v>0.93566945606694563</v>
+        <v>0.91898734177215191</v>
       </c>
       <c r="E9" s="20">
-        <v>0.96092592592592596</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.989041095890411</v>
+      </c>
+      <c r="F9" s="20">
+        <v>0.84482758620689657</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="I9" s="20">
+        <v>0.77519379844961245</v>
+      </c>
+      <c r="J9" s="20">
+        <v>0.99647887323943662</v>
+      </c>
+      <c r="K9" s="20">
+        <v>0.96019900497512434</v>
+      </c>
+      <c r="L9" s="20">
+        <v>1</v>
+      </c>
+      <c r="M9" s="20">
+        <v>1</v>
+      </c>
+      <c r="N9" s="20">
+        <v>1</v>
+      </c>
+      <c r="O9" s="20">
+        <v>1</v>
+      </c>
+      <c r="P9" s="20">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="R9" s="20">
+        <v>1</v>
+      </c>
+      <c r="S9" s="20">
+        <v>0.99173553719008267</v>
+      </c>
+      <c r="T9" s="20">
+        <v>0.72340425531914898</v>
+      </c>
+      <c r="U9" s="20">
+        <v>0.81355932203389836</v>
+      </c>
+      <c r="V9" s="20">
+        <v>0.96078431372549022</v>
+      </c>
+      <c r="W9" s="20">
+        <v>0.74285714285714288</v>
+      </c>
+      <c r="X9" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20">
+        <v>0.94915254237288138</v>
+      </c>
+      <c r="AB9" s="20">
+        <v>0.96478873239436624</v>
+      </c>
+      <c r="AC9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A10" s="17">
         <v>2025</v>
       </c>
@@ -12291,16 +12996,91 @@
         <v>12</v>
       </c>
       <c r="C10" s="20">
-        <v>0.88796366389099168</v>
+        <v>0.87736563209689633</v>
       </c>
       <c r="D10" s="20">
-        <v>0.8089887640449438</v>
+        <v>0.7921348314606742</v>
       </c>
       <c r="E10" s="20">
-        <v>0.88796366389099168</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.97701149425287359</v>
+      </c>
+      <c r="F10" s="20">
+        <v>0.65942028985507251</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20">
+        <v>0.95336787564766834</v>
+      </c>
+      <c r="I10" s="20">
+        <v>0.36879432624113473</v>
+      </c>
+      <c r="J10" s="20">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="K10" s="20">
+        <v>0.93220338983050843</v>
+      </c>
+      <c r="L10" s="20">
+        <v>0.97894736842105268</v>
+      </c>
+      <c r="M10" s="20">
+        <v>1</v>
+      </c>
+      <c r="N10" s="20">
+        <v>1</v>
+      </c>
+      <c r="O10" s="20">
+        <v>1</v>
+      </c>
+      <c r="P10" s="20">
+        <v>0.90625</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>0.97959183673469385</v>
+      </c>
+      <c r="R10" s="20">
+        <v>0.97560975609756095</v>
+      </c>
+      <c r="S10" s="20">
+        <v>0.99009900990099009</v>
+      </c>
+      <c r="T10" s="20">
+        <v>0.44594594594594594</v>
+      </c>
+      <c r="U10" s="20">
+        <v>0.45714285714285713</v>
+      </c>
+      <c r="V10" s="20">
+        <v>0.9263157894736842</v>
+      </c>
+      <c r="W10" s="20">
+        <v>0.28169014084507044</v>
+      </c>
+      <c r="X10" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20">
+        <v>0.92452830188679247</v>
+      </c>
+      <c r="AB10" s="20">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="AC10" s="20">
+        <v>0.97894736842105268</v>
+      </c>
+      <c r="AD10" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A11" s="17">
         <v>2025</v>
       </c>
@@ -12314,10 +13094,85 @@
         <v>0.95741758241758246</v>
       </c>
       <c r="E11" s="20">
-        <v>0.9748010610079576</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.99102564102564106</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0.91874999999999996</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20">
+        <v>0.98529411764705888</v>
+      </c>
+      <c r="I11" s="20">
+        <v>0.87704918032786883</v>
+      </c>
+      <c r="J11" s="20">
+        <v>1</v>
+      </c>
+      <c r="K11" s="20">
+        <v>0.98222222222222222</v>
+      </c>
+      <c r="L11" s="20">
+        <v>0.99186991869918695</v>
+      </c>
+      <c r="M11" s="20">
+        <v>0.9943820224719101</v>
+      </c>
+      <c r="N11" s="20">
+        <v>0.99530516431924887</v>
+      </c>
+      <c r="O11" s="20">
+        <v>1</v>
+      </c>
+      <c r="P11" s="20">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+      <c r="R11" s="20">
+        <v>1</v>
+      </c>
+      <c r="S11" s="20">
+        <v>1</v>
+      </c>
+      <c r="T11" s="20">
+        <v>0.87209302325581395</v>
+      </c>
+      <c r="U11" s="20">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="V11" s="20">
+        <v>0.97169811320754718</v>
+      </c>
+      <c r="W11" s="20">
+        <v>0.90140845070422537</v>
+      </c>
+      <c r="X11" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="20">
+        <v>0.97402597402597402</v>
+      </c>
+      <c r="AC11" s="20">
+        <v>0.99186991869918695</v>
+      </c>
+      <c r="AD11" s="20">
+        <v>0.9943820224719101</v>
+      </c>
+      <c r="AE11" s="20">
+        <v>0.99530516431924887</v>
+      </c>
+      <c r="AF11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A12" s="17">
         <v>2025</v>
       </c>
@@ -12325,16 +13180,91 @@
         <v>14</v>
       </c>
       <c r="C12" s="20">
-        <v>0.95245283018867921</v>
+        <v>0.89962264150943394</v>
       </c>
       <c r="D12" s="20">
-        <v>0.92094313453536758</v>
+        <v>0.82385575589459081</v>
       </c>
       <c r="E12" s="20">
-        <v>0.95245283018867921</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.99006622516556286</v>
+      </c>
+      <c r="F12" s="20">
+        <v>0.82822085889570551</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20">
+        <v>0.984375</v>
+      </c>
+      <c r="I12" s="20">
+        <v>0.8721804511278195</v>
+      </c>
+      <c r="J12" s="20">
+        <v>0.66094420600858372</v>
+      </c>
+      <c r="K12" s="20">
+        <v>0.9640718562874252</v>
+      </c>
+      <c r="L12" s="20">
+        <v>1</v>
+      </c>
+      <c r="M12" s="20">
+        <v>1</v>
+      </c>
+      <c r="N12" s="20">
+        <v>1</v>
+      </c>
+      <c r="O12" s="20">
+        <v>1</v>
+      </c>
+      <c r="P12" s="20">
+        <v>0.96202531645569622</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+      <c r="R12" s="20">
+        <v>1</v>
+      </c>
+      <c r="S12" s="20">
+        <v>0.44660194174757284</v>
+      </c>
+      <c r="T12" s="20">
+        <v>0.70238095238095233</v>
+      </c>
+      <c r="U12" s="20">
+        <v>0.9242424242424242</v>
+      </c>
+      <c r="V12" s="20">
+        <v>0.97115384615384615</v>
+      </c>
+      <c r="W12" s="20">
+        <v>0.82089552238805974</v>
+      </c>
+      <c r="X12" s="20">
+        <v>0.53191489361702127</v>
+      </c>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="AB12" s="20">
+        <v>0.96062992125984248</v>
+      </c>
+      <c r="AC12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A13" s="17">
         <v>2025</v>
       </c>
@@ -12342,16 +13272,91 @@
         <v>15</v>
       </c>
       <c r="C13" s="20">
-        <v>0.94237526352775824</v>
+        <v>0.9360505973295854</v>
       </c>
       <c r="D13" s="20">
-        <v>0.90527740189445194</v>
+        <v>0.89986468200270631</v>
       </c>
       <c r="E13" s="20">
-        <v>0.94237526352775824</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.97514619883040932</v>
+      </c>
+      <c r="F13" s="20">
+        <v>0.82738095238095233</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20">
+        <v>0.95431472081218272</v>
+      </c>
+      <c r="I13" s="20">
+        <v>0.83846153846153848</v>
+      </c>
+      <c r="J13" s="20">
+        <v>0.93852459016393441</v>
+      </c>
+      <c r="K13" s="20">
+        <v>0.92195121951219516</v>
+      </c>
+      <c r="L13" s="20">
+        <v>1</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0.99375000000000002</v>
+      </c>
+      <c r="N13" s="20">
+        <v>1</v>
+      </c>
+      <c r="O13" s="20">
+        <v>1</v>
+      </c>
+      <c r="P13" s="20">
+        <v>0.90666666666666662</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+      <c r="R13" s="20">
+        <v>1</v>
+      </c>
+      <c r="S13" s="20">
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="T13" s="20">
+        <v>0.76344086021505375</v>
+      </c>
+      <c r="U13" s="20">
+        <v>0.9107142857142857</v>
+      </c>
+      <c r="V13" s="20">
+        <v>0.91089108910891092</v>
+      </c>
+      <c r="W13" s="20">
+        <v>0.78378378378378377</v>
+      </c>
+      <c r="X13" s="20">
+        <v>0.83636363636363631</v>
+      </c>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20">
+        <v>0.91176470588235292</v>
+      </c>
+      <c r="AB13" s="20">
+        <v>0.92700729927007297</v>
+      </c>
+      <c r="AC13" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="20">
+        <v>0.99375000000000002</v>
+      </c>
+      <c r="AE13" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A14" s="17">
         <v>2026</v>
       </c>
@@ -12359,16 +13364,91 @@
         <v>4</v>
       </c>
       <c r="C14" s="20">
-        <v>0.89</v>
+        <v>0.88938053097345138</v>
       </c>
       <c r="D14" s="20">
-        <v>0.84</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="E14" s="20">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.90457256461232605</v>
+      </c>
+      <c r="F14" s="20">
+        <v>0.81203007518796988</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20">
+        <v>0.95930232558139539</v>
+      </c>
+      <c r="I14" s="20">
+        <v>0.81343283582089554</v>
+      </c>
+      <c r="J14" s="20">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="K14" s="20">
+        <v>0.80451127819548873</v>
+      </c>
+      <c r="L14" s="20">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M14" s="20">
+        <v>1</v>
+      </c>
+      <c r="N14" s="20">
+        <v>1</v>
+      </c>
+      <c r="O14" s="20">
+        <v>1</v>
+      </c>
+      <c r="P14" s="20">
+        <v>0.86440677966101698</v>
+      </c>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+      <c r="R14" s="20">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="S14" s="20">
+        <v>0.8904109589041096</v>
+      </c>
+      <c r="T14" s="20">
+        <v>0.77027027027027029</v>
+      </c>
+      <c r="U14" s="20">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="V14" s="20">
+        <v>0.92391304347826086</v>
+      </c>
+      <c r="W14" s="20">
+        <v>0.77464788732394363</v>
+      </c>
+      <c r="X14" s="20">
+        <v>0.81132075471698117</v>
+      </c>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20">
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="AB14" s="20">
+        <v>0.70512820512820518</v>
+      </c>
+      <c r="AC14" s="20">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AD14" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A15" s="17">
         <v>2026</v>
       </c>
@@ -12384,8 +13464,83 @@
       <c r="E15" s="20">
         <v>0.98250728862973757</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F15" s="20">
+        <v>0.72043010752688175</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20">
+        <v>0.97029702970297027</v>
+      </c>
+      <c r="I15" s="20">
+        <v>0.82795698924731187</v>
+      </c>
+      <c r="J15" s="20">
+        <v>0.90441176470588236</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="L15" s="20">
+        <v>1</v>
+      </c>
+      <c r="M15" s="20">
+        <v>1</v>
+      </c>
+      <c r="N15" s="20">
+        <v>1</v>
+      </c>
+      <c r="O15" s="20">
+        <v>1</v>
+      </c>
+      <c r="P15" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+      <c r="R15" s="20">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="S15" s="20">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="T15" s="20">
+        <v>0.69387755102040816</v>
+      </c>
+      <c r="U15" s="20">
+        <v>0.95918367346938771</v>
+      </c>
+      <c r="V15" s="20">
+        <v>0.9375</v>
+      </c>
+      <c r="W15" s="20">
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="X15" s="20">
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20">
+        <v>0.95081967213114749</v>
+      </c>
+      <c r="AB15" s="20">
+        <v>0.93181818181818177</v>
+      </c>
+      <c r="AC15" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A16" s="17">
         <v>2026</v>
       </c>
@@ -12393,16 +13548,91 @@
         <v>6</v>
       </c>
       <c r="C16" s="20">
-        <v>0.91644908616187992</v>
+        <v>0.84267241379310343</v>
       </c>
       <c r="D16" s="20">
-        <v>0.86288416075650121</v>
+        <v>0.75151515151515147</v>
       </c>
       <c r="E16" s="20">
-        <v>0.98250728862973757</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
+        <v>0.94688221709006926</v>
+      </c>
+      <c r="F16" s="20">
+        <v>0.55789473684210522</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="J16" s="20">
+        <v>0.74496644295302017</v>
+      </c>
+      <c r="K16" s="20">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="L16" s="20">
+        <v>1</v>
+      </c>
+      <c r="M16" s="20">
+        <v>1</v>
+      </c>
+      <c r="N16" s="20">
+        <v>0.94174757281553401</v>
+      </c>
+      <c r="O16" s="20">
+        <v>1</v>
+      </c>
+      <c r="P16" s="20">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>0.98701298701298701</v>
+      </c>
+      <c r="R16" s="20">
+        <v>0.67796610169491522</v>
+      </c>
+      <c r="S16" s="20">
+        <v>0.75555555555555554</v>
+      </c>
+      <c r="T16" s="20">
+        <v>0.48780487804878048</v>
+      </c>
+      <c r="U16" s="20">
+        <v>0.75438596491228072</v>
+      </c>
+      <c r="V16" s="20">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="W16" s="20">
+        <v>0.68627450980392157</v>
+      </c>
+      <c r="X16" s="20">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20">
+        <v>0.8783783783783784</v>
+      </c>
+      <c r="AB16" s="20">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="AC16" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="20">
+        <v>0.94174757281553401</v>
+      </c>
+      <c r="AF16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A17" s="17">
         <v>2026</v>
       </c>
@@ -12412,8 +13642,35 @@
       <c r="C17" s="14"/>
       <c r="D17" s="14"/>
       <c r="E17" s="14"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="14"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="17">
         <v>2026</v>
       </c>
@@ -12423,8 +13680,35 @@
       <c r="C18" s="14"/>
       <c r="D18" s="14"/>
       <c r="E18" s="14"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="14"/>
+      <c r="AF18" s="14"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="17">
         <v>2026</v>
       </c>
@@ -12434,8 +13718,35 @@
       <c r="C19" s="14"/>
       <c r="D19" s="14"/>
       <c r="E19" s="14"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="14"/>
+      <c r="AF19" s="14"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="17">
         <v>2026</v>
       </c>
@@ -12445,8 +13756,35 @@
       <c r="C20" s="14"/>
       <c r="D20" s="14"/>
       <c r="E20" s="14"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="14"/>
+      <c r="AE20" s="14"/>
+      <c r="AF20" s="14"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A21" s="17">
         <v>2026</v>
       </c>
@@ -12456,8 +13794,35 @@
       <c r="C21" s="14"/>
       <c r="D21" s="14"/>
       <c r="E21" s="14"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="14"/>
+      <c r="AF21" s="14"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A22" s="17">
         <v>2026</v>
       </c>
@@ -12467,8 +13832,35 @@
       <c r="C22" s="14"/>
       <c r="D22" s="14"/>
       <c r="E22" s="14"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="14"/>
+      <c r="AF22" s="14"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A23" s="17">
         <v>2026</v>
       </c>
@@ -12478,8 +13870,35 @@
       <c r="C23" s="14"/>
       <c r="D23" s="14"/>
       <c r="E23" s="14"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
+      <c r="AE23" s="14"/>
+      <c r="AF23" s="14"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A24" s="17">
         <v>2026</v>
       </c>
@@ -12489,8 +13908,35 @@
       <c r="C24" s="14"/>
       <c r="D24" s="14"/>
       <c r="E24" s="14"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="14"/>
+      <c r="AE24" s="14"/>
+      <c r="AF24" s="14"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A25" s="17">
         <v>2026</v>
       </c>
@@ -12500,8 +13946,35 @@
       <c r="C25" s="14"/>
       <c r="D25" s="14"/>
       <c r="E25" s="14"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="14"/>
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="14"/>
+      <c r="AE25" s="14"/>
+      <c r="AF25" s="14"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A26" s="17">
         <v>2027</v>
       </c>
@@ -12511,8 +13984,35 @@
       <c r="C26" s="14"/>
       <c r="D26" s="14"/>
       <c r="E26" s="14"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="14"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A27" s="17">
         <v>2027</v>
       </c>
@@ -12522,8 +14022,35 @@
       <c r="C27" s="14"/>
       <c r="D27" s="14"/>
       <c r="E27" s="14"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="14"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A28" s="17">
         <v>2027</v>
       </c>
@@ -12533,8 +14060,35 @@
       <c r="C28" s="14"/>
       <c r="D28" s="14"/>
       <c r="E28" s="14"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="14"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A29" s="17">
         <v>2027</v>
       </c>
@@ -12544,8 +14098,35 @@
       <c r="C29" s="14"/>
       <c r="D29" s="14"/>
       <c r="E29" s="14"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="14"/>
+      <c r="AF29" s="14"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A30" s="17">
         <v>2027</v>
       </c>
@@ -12555,8 +14136,35 @@
       <c r="C30" s="14"/>
       <c r="D30" s="14"/>
       <c r="E30" s="14"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="14"/>
+      <c r="AF30" s="14"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A31" s="17">
         <v>2027</v>
       </c>
@@ -12566,8 +14174,35 @@
       <c r="C31" s="14"/>
       <c r="D31" s="14"/>
       <c r="E31" s="14"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
+      <c r="AF31" s="14"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A32" s="17">
         <v>2027</v>
       </c>
@@ -12577,8 +14212,35 @@
       <c r="C32" s="14"/>
       <c r="D32" s="14"/>
       <c r="E32" s="14"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="14"/>
+      <c r="AF32" s="14"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="17">
         <v>2027</v>
       </c>
@@ -12588,8 +14250,35 @@
       <c r="C33" s="14"/>
       <c r="D33" s="14"/>
       <c r="E33" s="14"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
+      <c r="AF33" s="14"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A34" s="17">
         <v>2027</v>
       </c>
@@ -12599,8 +14288,35 @@
       <c r="C34" s="14"/>
       <c r="D34" s="14"/>
       <c r="E34" s="14"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="14"/>
+      <c r="AF34" s="14"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A35" s="17">
         <v>2027</v>
       </c>
@@ -12610,8 +14326,35 @@
       <c r="C35" s="14"/>
       <c r="D35" s="14"/>
       <c r="E35" s="14"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="14"/>
+      <c r="AF35" s="14"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A36" s="17">
         <v>2027</v>
       </c>
@@ -12621,8 +14364,35 @@
       <c r="C36" s="14"/>
       <c r="D36" s="14"/>
       <c r="E36" s="14"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="14"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="14"/>
+      <c r="AF36" s="14"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A37" s="17">
         <v>2027</v>
       </c>
@@ -12632,6 +14402,33 @@
       <c r="C37" s="14"/>
       <c r="D37" s="14"/>
       <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
+      <c r="AF37" s="14"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="6"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -19,7 +19,8 @@
     <sheet name="5.0E" sheetId="14" r:id="rId5"/>
     <sheet name="5.0F" sheetId="9" r:id="rId6"/>
     <sheet name="5.0G" sheetId="15" r:id="rId7"/>
-    <sheet name="5.3A" sheetId="16" r:id="rId8"/>
+    <sheet name="5.0I" sheetId="17" r:id="rId8"/>
+    <sheet name="5.3A" sheetId="16" r:id="rId9"/>
   </sheets>
   <definedNames>
     <definedName name="__A313546">#N/A</definedName>
@@ -30,16 +31,19 @@
     <definedName name="__xlnm._FilterDatabase" localSheetId="4">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase" localSheetId="6">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase" localSheetId="7">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase" localSheetId="8">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="4">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="6">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="7">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase_1" localSheetId="8">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="4">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="6">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="7">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase_3" localSheetId="8">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_4">#N/A</definedName>
     <definedName name="__xlnm.Database">#N/A</definedName>
@@ -7884,6 +7888,7 @@
     <definedName name="UILUI" localSheetId="4">#REF!</definedName>
     <definedName name="UILUI" localSheetId="6">#REF!</definedName>
     <definedName name="UILUI" localSheetId="7">#REF!</definedName>
+    <definedName name="UILUI" localSheetId="8">#REF!</definedName>
     <definedName name="UILUI">#REF!</definedName>
     <definedName name="unnn">"#REF!"</definedName>
     <definedName name="unnn_1">"#REF!"</definedName>
@@ -7969,7 +7974,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="46">
   <si>
     <t>Mes</t>
   </si>
@@ -14438,6 +14443,2320 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AF37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="32" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A1" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="12" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y1" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="AB1" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="AC1" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AD1" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AE1" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AF1" s="12" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A2" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="20">
+        <v>0.9839939024390244</v>
+      </c>
+      <c r="D2" s="20">
+        <v>0.98053892215568861</v>
+      </c>
+      <c r="E2" s="20">
+        <v>0.98757763975155277</v>
+      </c>
+      <c r="F2" s="20">
+        <v>0.93269230769230771</v>
+      </c>
+      <c r="G2" s="20">
+        <v>1</v>
+      </c>
+      <c r="H2" s="20">
+        <v>0.9939393939393939</v>
+      </c>
+      <c r="I2" s="20">
+        <v>0.9642857142857143</v>
+      </c>
+      <c r="J2" s="20">
+        <v>1</v>
+      </c>
+      <c r="K2" s="20">
+        <v>1</v>
+      </c>
+      <c r="L2" s="20">
+        <v>0.92792792792792789</v>
+      </c>
+      <c r="M2" s="20">
+        <v>1</v>
+      </c>
+      <c r="N2" s="20">
+        <v>1</v>
+      </c>
+      <c r="O2" s="20">
+        <v>1</v>
+      </c>
+      <c r="P2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q2" s="20">
+        <v>1</v>
+      </c>
+      <c r="R2" s="20">
+        <v>1</v>
+      </c>
+      <c r="S2" s="20">
+        <v>1</v>
+      </c>
+      <c r="T2" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="U2" s="20">
+        <v>0.98461538461538467</v>
+      </c>
+      <c r="V2" s="20">
+        <v>0.989247311827957</v>
+      </c>
+      <c r="W2" s="20">
+        <v>0.94666666666666666</v>
+      </c>
+      <c r="X2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y2" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z2" s="20"/>
+      <c r="AA2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC2" s="20">
+        <v>0.92792792792792789</v>
+      </c>
+      <c r="AD2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE2" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF2" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A3" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="20">
+        <v>0.9662921348314607</v>
+      </c>
+      <c r="D3" s="20">
+        <v>0.96610169491525422</v>
+      </c>
+      <c r="E3" s="20">
+        <v>0.96650717703349287</v>
+      </c>
+      <c r="F3" s="20">
+        <v>0.86086956521739133</v>
+      </c>
+      <c r="G3" s="20">
+        <v>1</v>
+      </c>
+      <c r="H3" s="20">
+        <v>1</v>
+      </c>
+      <c r="I3" s="20">
+        <v>0.94771241830065356</v>
+      </c>
+      <c r="J3" s="20">
+        <v>1</v>
+      </c>
+      <c r="K3" s="20">
+        <v>0.98843930635838151</v>
+      </c>
+      <c r="L3" s="20">
+        <v>0.79347826086956519</v>
+      </c>
+      <c r="M3" s="20">
+        <v>1</v>
+      </c>
+      <c r="N3" s="20">
+        <v>1</v>
+      </c>
+      <c r="O3" s="20">
+        <v>1</v>
+      </c>
+      <c r="P3" s="20">
+        <v>0.81132075471698117</v>
+      </c>
+      <c r="Q3" s="20">
+        <v>1</v>
+      </c>
+      <c r="R3" s="20">
+        <v>1</v>
+      </c>
+      <c r="S3" s="20">
+        <v>1</v>
+      </c>
+      <c r="T3" s="20">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="U3" s="20">
+        <v>0.91176470588235292</v>
+      </c>
+      <c r="V3" s="20">
+        <v>1</v>
+      </c>
+      <c r="W3" s="20">
+        <v>0.97647058823529409</v>
+      </c>
+      <c r="X3" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y3" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA3" s="20">
+        <v>0.96363636363636362</v>
+      </c>
+      <c r="AB3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AC3" s="20">
+        <v>0.79347826086956519</v>
+      </c>
+      <c r="AD3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE3" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF3" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A4" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="20">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="D4" s="20">
+        <v>0.93188010899182561</v>
+      </c>
+      <c r="E4" s="20">
+        <v>0.99534161490683226</v>
+      </c>
+      <c r="F4" s="20">
+        <v>0.75206611570247939</v>
+      </c>
+      <c r="G4" s="20">
+        <v>1</v>
+      </c>
+      <c r="H4" s="20">
+        <v>0.99444444444444446</v>
+      </c>
+      <c r="I4" s="20">
+        <v>0.89090909090909087</v>
+      </c>
+      <c r="J4" s="20">
+        <v>0.99601593625498008</v>
+      </c>
+      <c r="K4" s="20">
+        <v>0.9854368932038835</v>
+      </c>
+      <c r="L4" s="20">
+        <v>1</v>
+      </c>
+      <c r="M4" s="20">
+        <v>1</v>
+      </c>
+      <c r="N4" s="20">
+        <v>1</v>
+      </c>
+      <c r="O4" s="20">
+        <v>1</v>
+      </c>
+      <c r="P4" s="20">
+        <v>0.86885245901639341</v>
+      </c>
+      <c r="Q4" s="20">
+        <v>0.98913043478260865</v>
+      </c>
+      <c r="R4" s="20">
+        <v>0.98936170212765961</v>
+      </c>
+      <c r="S4" s="20">
+        <v>1</v>
+      </c>
+      <c r="T4" s="20">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="U4" s="20">
+        <v>0.86075949367088611</v>
+      </c>
+      <c r="V4" s="20">
+        <v>1</v>
+      </c>
+      <c r="W4" s="20">
+        <v>0.91860465116279066</v>
+      </c>
+      <c r="X4" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y4" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z4" s="20"/>
+      <c r="AA4" s="20">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="AB4" s="20">
+        <v>0.99206349206349209</v>
+      </c>
+      <c r="AC4" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD4" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE4" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF4" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A5" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="20">
+        <v>0.97153024911032027</v>
+      </c>
+      <c r="D5" s="20">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="E5" s="20">
+        <v>0.98601398601398604</v>
+      </c>
+      <c r="F5" s="20">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="G5" s="20">
+        <v>1</v>
+      </c>
+      <c r="H5" s="20">
+        <v>1</v>
+      </c>
+      <c r="I5" s="20">
+        <v>0.87610619469026552</v>
+      </c>
+      <c r="J5" s="20">
+        <v>0.9946236559139785</v>
+      </c>
+      <c r="K5" s="20">
+        <v>0.9526627218934911</v>
+      </c>
+      <c r="L5" s="20">
+        <v>1</v>
+      </c>
+      <c r="M5" s="20">
+        <v>1</v>
+      </c>
+      <c r="N5" s="20">
+        <v>1</v>
+      </c>
+      <c r="O5" s="20">
+        <v>1</v>
+      </c>
+      <c r="P5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Q5" s="20">
+        <v>1</v>
+      </c>
+      <c r="R5" s="20">
+        <v>1</v>
+      </c>
+      <c r="S5" s="20">
+        <v>0.98795180722891562</v>
+      </c>
+      <c r="T5" s="20">
+        <v>0.85245901639344257</v>
+      </c>
+      <c r="U5" s="20">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="V5" s="20">
+        <v>1</v>
+      </c>
+      <c r="W5" s="20">
+        <v>0.88732394366197187</v>
+      </c>
+      <c r="X5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y5" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AA5" s="20">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="AB5" s="20">
+        <v>0.93684210526315792</v>
+      </c>
+      <c r="AC5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE5" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF5" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A6" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="20">
+        <v>0.96508728179551118</v>
+      </c>
+      <c r="D6" s="20">
+        <v>0.93925233644859818</v>
+      </c>
+      <c r="E6" s="20">
+        <v>0.99465240641711228</v>
+      </c>
+      <c r="F6" s="20">
+        <v>0.79605263157894735</v>
+      </c>
+      <c r="G6" s="20">
+        <v>1</v>
+      </c>
+      <c r="H6" s="20">
+        <v>1</v>
+      </c>
+      <c r="I6" s="20">
+        <v>0.88571428571428568</v>
+      </c>
+      <c r="J6" s="20">
+        <v>0.99659863945578231</v>
+      </c>
+      <c r="K6" s="20">
+        <v>0.98222222222222222</v>
+      </c>
+      <c r="L6" s="20">
+        <v>1</v>
+      </c>
+      <c r="M6" s="20">
+        <v>1</v>
+      </c>
+      <c r="N6" s="20">
+        <v>1</v>
+      </c>
+      <c r="O6" s="20">
+        <v>1</v>
+      </c>
+      <c r="P6" s="20">
+        <v>0.91249999999999998</v>
+      </c>
+      <c r="Q6" s="20">
+        <v>1</v>
+      </c>
+      <c r="R6" s="20">
+        <v>1</v>
+      </c>
+      <c r="S6" s="20">
+        <v>0.99137931034482762</v>
+      </c>
+      <c r="T6" s="20">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="U6" s="20">
+        <v>0.85526315789473684</v>
+      </c>
+      <c r="V6" s="20">
+        <v>1</v>
+      </c>
+      <c r="W6" s="20">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="X6" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y6" s="20">
+        <v>1</v>
+      </c>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20">
+        <v>0.98717948717948723</v>
+      </c>
+      <c r="AB6" s="20">
+        <v>0.97959183673469385</v>
+      </c>
+      <c r="AC6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE6" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF6" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A7" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="20">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="D7" s="20">
+        <v>0.92819148936170215</v>
+      </c>
+      <c r="E7" s="20">
+        <v>0.97077922077922074</v>
+      </c>
+      <c r="F7" s="20">
+        <v>0.82666666666666666</v>
+      </c>
+      <c r="G7" s="20"/>
+      <c r="H7" s="20">
+        <v>0.98952879581151831</v>
+      </c>
+      <c r="I7" s="20">
+        <v>0.8404907975460123</v>
+      </c>
+      <c r="J7" s="20">
+        <v>1</v>
+      </c>
+      <c r="K7" s="20">
+        <v>0.89772727272727271</v>
+      </c>
+      <c r="L7" s="20">
+        <v>1</v>
+      </c>
+      <c r="M7" s="20">
+        <v>1</v>
+      </c>
+      <c r="N7" s="20">
+        <v>1</v>
+      </c>
+      <c r="O7" s="20">
+        <v>1</v>
+      </c>
+      <c r="P7" s="20">
+        <v>0.94202898550724634</v>
+      </c>
+      <c r="Q7" s="20">
+        <v>1</v>
+      </c>
+      <c r="R7" s="20">
+        <v>1</v>
+      </c>
+      <c r="S7" s="20">
+        <v>1</v>
+      </c>
+      <c r="T7" s="20">
+        <v>0.72839506172839508</v>
+      </c>
+      <c r="U7" s="20">
+        <v>0.80487804878048785</v>
+      </c>
+      <c r="V7" s="20">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="W7" s="20">
+        <v>0.87654320987654322</v>
+      </c>
+      <c r="X7" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y7" s="20"/>
+      <c r="Z7" s="20"/>
+      <c r="AA7" s="20">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="AB7" s="20">
+        <v>0.875</v>
+      </c>
+      <c r="AC7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE7" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF7" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A8" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="20">
+        <v>0.9773413897280967</v>
+      </c>
+      <c r="D8" s="20">
+        <v>0.97038081805359666</v>
+      </c>
+      <c r="E8" s="20">
+        <v>0.98536585365853657</v>
+      </c>
+      <c r="F8" s="20">
+        <v>0.92567567567567566</v>
+      </c>
+      <c r="G8" s="20"/>
+      <c r="H8" s="20">
+        <v>0.99428571428571433</v>
+      </c>
+      <c r="I8" s="20">
+        <v>0.93793103448275861</v>
+      </c>
+      <c r="J8" s="20">
+        <v>1</v>
+      </c>
+      <c r="K8" s="20">
+        <v>0.95408163265306123</v>
+      </c>
+      <c r="L8" s="20">
+        <v>1</v>
+      </c>
+      <c r="M8" s="20">
+        <v>1</v>
+      </c>
+      <c r="N8" s="20">
+        <v>1</v>
+      </c>
+      <c r="O8" s="20">
+        <v>1</v>
+      </c>
+      <c r="P8" s="20">
+        <v>0.92537313432835822</v>
+      </c>
+      <c r="Q8" s="20">
+        <v>1</v>
+      </c>
+      <c r="R8" s="20">
+        <v>1</v>
+      </c>
+      <c r="S8" s="20">
+        <v>1</v>
+      </c>
+      <c r="T8" s="20">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="U8" s="20">
+        <v>0.92063492063492058</v>
+      </c>
+      <c r="V8" s="20">
+        <v>0.98979591836734693</v>
+      </c>
+      <c r="W8" s="20">
+        <v>0.95121951219512191</v>
+      </c>
+      <c r="X8" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y8" s="20"/>
+      <c r="Z8" s="20"/>
+      <c r="AA8" s="20">
+        <v>0.98571428571428577</v>
+      </c>
+      <c r="AB8" s="20">
+        <v>0.93650793650793651</v>
+      </c>
+      <c r="AC8" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD8" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE8" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF8" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A9" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="20">
+        <v>0.96578947368421053</v>
+      </c>
+      <c r="D9" s="20">
+        <v>0.94050632911392407</v>
+      </c>
+      <c r="E9" s="20">
+        <v>0.99315068493150682</v>
+      </c>
+      <c r="F9" s="20">
+        <v>0.84482758620689657</v>
+      </c>
+      <c r="G9" s="20"/>
+      <c r="H9" s="20">
+        <v>0.99014778325123154</v>
+      </c>
+      <c r="I9" s="20">
+        <v>0.86821705426356588</v>
+      </c>
+      <c r="J9" s="20">
+        <v>0.99647887323943662</v>
+      </c>
+      <c r="K9" s="20">
+        <v>0.97512437810945274</v>
+      </c>
+      <c r="L9" s="20">
+        <v>1</v>
+      </c>
+      <c r="M9" s="20">
+        <v>1</v>
+      </c>
+      <c r="N9" s="20">
+        <v>1</v>
+      </c>
+      <c r="O9" s="20">
+        <v>1</v>
+      </c>
+      <c r="P9" s="20">
+        <v>0.98750000000000004</v>
+      </c>
+      <c r="Q9" s="20">
+        <v>0.99009900990099009</v>
+      </c>
+      <c r="R9" s="20">
+        <v>1</v>
+      </c>
+      <c r="S9" s="20">
+        <v>0.99173553719008267</v>
+      </c>
+      <c r="T9" s="20">
+        <v>0.72340425531914898</v>
+      </c>
+      <c r="U9" s="20">
+        <v>0.86440677966101698</v>
+      </c>
+      <c r="V9" s="20">
+        <v>0.99019607843137258</v>
+      </c>
+      <c r="W9" s="20">
+        <v>0.87142857142857144</v>
+      </c>
+      <c r="X9" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y9" s="20"/>
+      <c r="Z9" s="20"/>
+      <c r="AA9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB9" s="20">
+        <v>0.96478873239436624</v>
+      </c>
+      <c r="AC9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE9" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF9" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A10" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="20">
+        <v>0.88796366389099168</v>
+      </c>
+      <c r="D10" s="20">
+        <v>0.8089887640449438</v>
+      </c>
+      <c r="E10" s="20">
+        <v>0.98029556650246308</v>
+      </c>
+      <c r="F10" s="20">
+        <v>0.72463768115942029</v>
+      </c>
+      <c r="G10" s="20"/>
+      <c r="H10" s="20">
+        <v>0.95854922279792742</v>
+      </c>
+      <c r="I10" s="20">
+        <v>0.36879432624113473</v>
+      </c>
+      <c r="J10" s="20">
+        <v>0.99583333333333335</v>
+      </c>
+      <c r="K10" s="20">
+        <v>0.93220338983050843</v>
+      </c>
+      <c r="L10" s="20">
+        <v>1</v>
+      </c>
+      <c r="M10" s="20">
+        <v>1</v>
+      </c>
+      <c r="N10" s="20">
+        <v>1</v>
+      </c>
+      <c r="O10" s="20">
+        <v>1</v>
+      </c>
+      <c r="P10" s="20">
+        <v>0.90625</v>
+      </c>
+      <c r="Q10" s="20">
+        <v>0.98979591836734693</v>
+      </c>
+      <c r="R10" s="20">
+        <v>1</v>
+      </c>
+      <c r="S10" s="20">
+        <v>0.99009900990099009</v>
+      </c>
+      <c r="T10" s="20">
+        <v>0.56756756756756754</v>
+      </c>
+      <c r="U10" s="20">
+        <v>0.45714285714285713</v>
+      </c>
+      <c r="V10" s="20">
+        <v>0.9263157894736842</v>
+      </c>
+      <c r="W10" s="20">
+        <v>0.28169014084507044</v>
+      </c>
+      <c r="X10" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y10" s="20"/>
+      <c r="Z10" s="20"/>
+      <c r="AA10" s="20">
+        <v>0.92452830188679247</v>
+      </c>
+      <c r="AB10" s="20">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="AC10" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD10" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE10" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF10" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A11" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="20">
+        <v>0.9748010610079576</v>
+      </c>
+      <c r="D11" s="20">
+        <v>0.95741758241758246</v>
+      </c>
+      <c r="E11" s="20">
+        <v>0.99102564102564106</v>
+      </c>
+      <c r="F11" s="20">
+        <v>0.91874999999999996</v>
+      </c>
+      <c r="G11" s="20"/>
+      <c r="H11" s="20">
+        <v>0.98529411764705888</v>
+      </c>
+      <c r="I11" s="20">
+        <v>0.87704918032786883</v>
+      </c>
+      <c r="J11" s="20">
+        <v>1</v>
+      </c>
+      <c r="K11" s="20">
+        <v>0.98222222222222222</v>
+      </c>
+      <c r="L11" s="20">
+        <v>0.99186991869918695</v>
+      </c>
+      <c r="M11" s="20">
+        <v>0.9943820224719101</v>
+      </c>
+      <c r="N11" s="20">
+        <v>0.99530516431924887</v>
+      </c>
+      <c r="O11" s="20">
+        <v>1</v>
+      </c>
+      <c r="P11" s="20">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="Q11" s="20">
+        <v>1</v>
+      </c>
+      <c r="R11" s="20">
+        <v>1</v>
+      </c>
+      <c r="S11" s="20">
+        <v>1</v>
+      </c>
+      <c r="T11" s="20">
+        <v>0.87209302325581395</v>
+      </c>
+      <c r="U11" s="20">
+        <v>0.84313725490196079</v>
+      </c>
+      <c r="V11" s="20">
+        <v>0.97169811320754718</v>
+      </c>
+      <c r="W11" s="20">
+        <v>0.90140845070422537</v>
+      </c>
+      <c r="X11" s="20">
+        <v>1</v>
+      </c>
+      <c r="Y11" s="20"/>
+      <c r="Z11" s="20"/>
+      <c r="AA11" s="20">
+        <v>1</v>
+      </c>
+      <c r="AB11" s="20">
+        <v>0.97402597402597402</v>
+      </c>
+      <c r="AC11" s="20">
+        <v>0.99186991869918695</v>
+      </c>
+      <c r="AD11" s="20">
+        <v>0.9943820224719101</v>
+      </c>
+      <c r="AE11" s="20">
+        <v>0.99530516431924887</v>
+      </c>
+      <c r="AF11" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A12" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="20">
+        <v>0.95245283018867921</v>
+      </c>
+      <c r="D12" s="20">
+        <v>0.92094313453536758</v>
+      </c>
+      <c r="E12" s="20">
+        <v>0.99006622516556286</v>
+      </c>
+      <c r="F12" s="20">
+        <v>0.82822085889570551</v>
+      </c>
+      <c r="G12" s="20"/>
+      <c r="H12" s="20">
+        <v>0.984375</v>
+      </c>
+      <c r="I12" s="20">
+        <v>0.8721804511278195</v>
+      </c>
+      <c r="J12" s="20">
+        <v>0.96137339055793991</v>
+      </c>
+      <c r="K12" s="20">
+        <v>0.9640718562874252</v>
+      </c>
+      <c r="L12" s="20">
+        <v>1</v>
+      </c>
+      <c r="M12" s="20">
+        <v>1</v>
+      </c>
+      <c r="N12" s="20">
+        <v>1</v>
+      </c>
+      <c r="O12" s="20">
+        <v>1</v>
+      </c>
+      <c r="P12" s="20">
+        <v>0.96202531645569622</v>
+      </c>
+      <c r="Q12" s="20">
+        <v>1</v>
+      </c>
+      <c r="R12" s="20">
+        <v>1</v>
+      </c>
+      <c r="S12" s="20">
+        <v>0.95145631067961167</v>
+      </c>
+      <c r="T12" s="20">
+        <v>0.70238095238095233</v>
+      </c>
+      <c r="U12" s="20">
+        <v>0.9242424242424242</v>
+      </c>
+      <c r="V12" s="20">
+        <v>0.97115384615384615</v>
+      </c>
+      <c r="W12" s="20">
+        <v>0.82089552238805974</v>
+      </c>
+      <c r="X12" s="20">
+        <v>0.91489361702127658</v>
+      </c>
+      <c r="Y12" s="20"/>
+      <c r="Z12" s="20"/>
+      <c r="AA12" s="20">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="AB12" s="20">
+        <v>0.96062992125984248</v>
+      </c>
+      <c r="AC12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE12" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF12" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A13" s="17">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="20">
+        <v>0.94237526352775824</v>
+      </c>
+      <c r="D13" s="20">
+        <v>0.90527740189445194</v>
+      </c>
+      <c r="E13" s="20">
+        <v>0.98245614035087714</v>
+      </c>
+      <c r="F13" s="20">
+        <v>0.82738095238095233</v>
+      </c>
+      <c r="G13" s="20"/>
+      <c r="H13" s="20">
+        <v>0.95431472081218272</v>
+      </c>
+      <c r="I13" s="20">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="J13" s="20">
+        <v>0.95081967213114749</v>
+      </c>
+      <c r="K13" s="20">
+        <v>0.9463414634146341</v>
+      </c>
+      <c r="L13" s="20">
+        <v>1</v>
+      </c>
+      <c r="M13" s="20">
+        <v>0.99375000000000002</v>
+      </c>
+      <c r="N13" s="20">
+        <v>1</v>
+      </c>
+      <c r="O13" s="20">
+        <v>1</v>
+      </c>
+      <c r="P13" s="20">
+        <v>0.90666666666666662</v>
+      </c>
+      <c r="Q13" s="20">
+        <v>1</v>
+      </c>
+      <c r="R13" s="20">
+        <v>1</v>
+      </c>
+      <c r="S13" s="20">
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="T13" s="20">
+        <v>0.76344086021505375</v>
+      </c>
+      <c r="U13" s="20">
+        <v>0.9107142857142857</v>
+      </c>
+      <c r="V13" s="20">
+        <v>0.91089108910891092</v>
+      </c>
+      <c r="W13" s="20">
+        <v>0.79729729729729726</v>
+      </c>
+      <c r="X13" s="20">
+        <v>0.89090909090909087</v>
+      </c>
+      <c r="Y13" s="20"/>
+      <c r="Z13" s="20"/>
+      <c r="AA13" s="20">
+        <v>0.98529411764705888</v>
+      </c>
+      <c r="AB13" s="20">
+        <v>0.92700729927007297</v>
+      </c>
+      <c r="AC13" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD13" s="20">
+        <v>0.99375000000000002</v>
+      </c>
+      <c r="AE13" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF13" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A14" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="20">
+        <v>0.88938053097345138</v>
+      </c>
+      <c r="D14" s="20">
+        <v>0.8771929824561403</v>
+      </c>
+      <c r="E14" s="20">
+        <v>0.90457256461232605</v>
+      </c>
+      <c r="F14" s="20">
+        <v>0.81203007518796988</v>
+      </c>
+      <c r="G14" s="20"/>
+      <c r="H14" s="20">
+        <v>0.95930232558139539</v>
+      </c>
+      <c r="I14" s="20">
+        <v>0.81343283582089554</v>
+      </c>
+      <c r="J14" s="20">
+        <v>0.8936170212765957</v>
+      </c>
+      <c r="K14" s="20">
+        <v>0.80451127819548873</v>
+      </c>
+      <c r="L14" s="20">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="M14" s="20">
+        <v>1</v>
+      </c>
+      <c r="N14" s="20">
+        <v>1</v>
+      </c>
+      <c r="O14" s="20">
+        <v>1</v>
+      </c>
+      <c r="P14" s="20">
+        <v>0.86440677966101698</v>
+      </c>
+      <c r="Q14" s="20">
+        <v>1</v>
+      </c>
+      <c r="R14" s="20">
+        <v>0.967741935483871</v>
+      </c>
+      <c r="S14" s="20">
+        <v>0.8904109589041096</v>
+      </c>
+      <c r="T14" s="20">
+        <v>0.77027027027027029</v>
+      </c>
+      <c r="U14" s="20">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="V14" s="20">
+        <v>0.92391304347826086</v>
+      </c>
+      <c r="W14" s="20">
+        <v>0.77464788732394363</v>
+      </c>
+      <c r="X14" s="20">
+        <v>0.81132075471698117</v>
+      </c>
+      <c r="Y14" s="20"/>
+      <c r="Z14" s="20"/>
+      <c r="AA14" s="20">
+        <v>0.94545454545454544</v>
+      </c>
+      <c r="AB14" s="20">
+        <v>0.70512820512820518</v>
+      </c>
+      <c r="AC14" s="20">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="AD14" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE14" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF14" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A15" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="20">
+        <v>0.9177545691906005</v>
+      </c>
+      <c r="D15" s="20">
+        <v>0.86524822695035464</v>
+      </c>
+      <c r="E15" s="20">
+        <v>0.98250728862973757</v>
+      </c>
+      <c r="F15" s="20">
+        <v>0.72043010752688175</v>
+      </c>
+      <c r="G15" s="20"/>
+      <c r="H15" s="20">
+        <v>0.98019801980198018</v>
+      </c>
+      <c r="I15" s="20">
+        <v>0.82795698924731187</v>
+      </c>
+      <c r="J15" s="20">
+        <v>0.90441176470588236</v>
+      </c>
+      <c r="K15" s="20">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="L15" s="20">
+        <v>1</v>
+      </c>
+      <c r="M15" s="20">
+        <v>1</v>
+      </c>
+      <c r="N15" s="20">
+        <v>1</v>
+      </c>
+      <c r="O15" s="20">
+        <v>1</v>
+      </c>
+      <c r="P15" s="20">
+        <v>0.75</v>
+      </c>
+      <c r="Q15" s="20">
+        <v>1</v>
+      </c>
+      <c r="R15" s="20">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="S15" s="20">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="T15" s="20">
+        <v>0.69387755102040816</v>
+      </c>
+      <c r="U15" s="20">
+        <v>0.95918367346938771</v>
+      </c>
+      <c r="V15" s="20">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="W15" s="20">
+        <v>0.68181818181818177</v>
+      </c>
+      <c r="X15" s="20">
+        <v>0.88372093023255816</v>
+      </c>
+      <c r="Y15" s="20"/>
+      <c r="Z15" s="20"/>
+      <c r="AA15" s="20">
+        <v>0.95081967213114749</v>
+      </c>
+      <c r="AB15" s="20">
+        <v>0.93181818181818177</v>
+      </c>
+      <c r="AC15" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD15" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE15" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF15" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A16" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="20">
+        <v>0.89655172413793105</v>
+      </c>
+      <c r="D16" s="20">
+        <v>0.83030303030303032</v>
+      </c>
+      <c r="E16" s="20">
+        <v>0.97228637413394914</v>
+      </c>
+      <c r="F16" s="20">
+        <v>0.69473684210526321</v>
+      </c>
+      <c r="G16" s="20"/>
+      <c r="H16" s="20">
+        <v>0.95804195804195802</v>
+      </c>
+      <c r="I16" s="20">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="J16" s="20">
+        <v>0.87248322147651003</v>
+      </c>
+      <c r="K16" s="20">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="L16" s="20">
+        <v>1</v>
+      </c>
+      <c r="M16" s="20">
+        <v>1</v>
+      </c>
+      <c r="N16" s="20">
+        <v>1</v>
+      </c>
+      <c r="O16" s="20">
+        <v>1</v>
+      </c>
+      <c r="P16" s="20">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Q16" s="20">
+        <v>1</v>
+      </c>
+      <c r="R16" s="20">
+        <v>0.88135593220338981</v>
+      </c>
+      <c r="S16" s="20">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="T16" s="20">
+        <v>0.58536585365853655</v>
+      </c>
+      <c r="U16" s="20">
+        <v>0.75438596491228072</v>
+      </c>
+      <c r="V16" s="20">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="W16" s="20">
+        <v>0.68627450980392157</v>
+      </c>
+      <c r="X16" s="20">
+        <v>0.91111111111111109</v>
+      </c>
+      <c r="Y16" s="20"/>
+      <c r="Z16" s="20"/>
+      <c r="AA16" s="20">
+        <v>0.8783783783783784</v>
+      </c>
+      <c r="AB16" s="20">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="AC16" s="20">
+        <v>1</v>
+      </c>
+      <c r="AD16" s="20">
+        <v>1</v>
+      </c>
+      <c r="AE16" s="20">
+        <v>1</v>
+      </c>
+      <c r="AF16" s="20">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A17" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="14"/>
+      <c r="D17" s="14"/>
+      <c r="E17" s="14"/>
+      <c r="F17" s="14"/>
+      <c r="G17" s="14"/>
+      <c r="H17" s="14"/>
+      <c r="I17" s="14"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
+      <c r="O17" s="14"/>
+      <c r="P17" s="14"/>
+      <c r="Q17" s="14"/>
+      <c r="R17" s="14"/>
+      <c r="S17" s="14"/>
+      <c r="T17" s="14"/>
+      <c r="U17" s="14"/>
+      <c r="V17" s="14"/>
+      <c r="W17" s="14"/>
+      <c r="X17" s="14"/>
+      <c r="Y17" s="14"/>
+      <c r="Z17" s="14"/>
+      <c r="AA17" s="14"/>
+      <c r="AB17" s="14"/>
+      <c r="AC17" s="14"/>
+      <c r="AD17" s="14"/>
+      <c r="AE17" s="14"/>
+      <c r="AF17" s="14"/>
+    </row>
+    <row r="18" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A18" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="14"/>
+      <c r="D18" s="14"/>
+      <c r="E18" s="14"/>
+      <c r="F18" s="14"/>
+      <c r="G18" s="14"/>
+      <c r="H18" s="14"/>
+      <c r="I18" s="14"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
+      <c r="O18" s="14"/>
+      <c r="P18" s="14"/>
+      <c r="Q18" s="14"/>
+      <c r="R18" s="14"/>
+      <c r="S18" s="14"/>
+      <c r="T18" s="14"/>
+      <c r="U18" s="14"/>
+      <c r="V18" s="14"/>
+      <c r="W18" s="14"/>
+      <c r="X18" s="14"/>
+      <c r="Y18" s="14"/>
+      <c r="Z18" s="14"/>
+      <c r="AA18" s="14"/>
+      <c r="AB18" s="14"/>
+      <c r="AC18" s="14"/>
+      <c r="AD18" s="14"/>
+      <c r="AE18" s="14"/>
+      <c r="AF18" s="14"/>
+    </row>
+    <row r="19" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A19" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+      <c r="E19" s="14"/>
+      <c r="F19" s="14"/>
+      <c r="G19" s="14"/>
+      <c r="H19" s="14"/>
+      <c r="I19" s="14"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
+      <c r="O19" s="14"/>
+      <c r="P19" s="14"/>
+      <c r="Q19" s="14"/>
+      <c r="R19" s="14"/>
+      <c r="S19" s="14"/>
+      <c r="T19" s="14"/>
+      <c r="U19" s="14"/>
+      <c r="V19" s="14"/>
+      <c r="W19" s="14"/>
+      <c r="X19" s="14"/>
+      <c r="Y19" s="14"/>
+      <c r="Z19" s="14"/>
+      <c r="AA19" s="14"/>
+      <c r="AB19" s="14"/>
+      <c r="AC19" s="14"/>
+      <c r="AD19" s="14"/>
+      <c r="AE19" s="14"/>
+      <c r="AF19" s="14"/>
+    </row>
+    <row r="20" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A20" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+      <c r="E20" s="14"/>
+      <c r="F20" s="14"/>
+      <c r="G20" s="14"/>
+      <c r="H20" s="14"/>
+      <c r="I20" s="14"/>
+      <c r="J20" s="14"/>
+      <c r="K20" s="14"/>
+      <c r="L20" s="14"/>
+      <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
+      <c r="O20" s="14"/>
+      <c r="P20" s="14"/>
+      <c r="Q20" s="14"/>
+      <c r="R20" s="14"/>
+      <c r="S20" s="14"/>
+      <c r="T20" s="14"/>
+      <c r="U20" s="14"/>
+      <c r="V20" s="14"/>
+      <c r="W20" s="14"/>
+      <c r="X20" s="14"/>
+      <c r="Y20" s="14"/>
+      <c r="Z20" s="14"/>
+      <c r="AA20" s="14"/>
+      <c r="AB20" s="14"/>
+      <c r="AC20" s="14"/>
+      <c r="AD20" s="14"/>
+      <c r="AE20" s="14"/>
+      <c r="AF20" s="14"/>
+    </row>
+    <row r="21" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A21" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+      <c r="E21" s="14"/>
+      <c r="F21" s="14"/>
+      <c r="G21" s="14"/>
+      <c r="H21" s="14"/>
+      <c r="I21" s="14"/>
+      <c r="J21" s="14"/>
+      <c r="K21" s="14"/>
+      <c r="L21" s="14"/>
+      <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
+      <c r="O21" s="14"/>
+      <c r="P21" s="14"/>
+      <c r="Q21" s="14"/>
+      <c r="R21" s="14"/>
+      <c r="S21" s="14"/>
+      <c r="T21" s="14"/>
+      <c r="U21" s="14"/>
+      <c r="V21" s="14"/>
+      <c r="W21" s="14"/>
+      <c r="X21" s="14"/>
+      <c r="Y21" s="14"/>
+      <c r="Z21" s="14"/>
+      <c r="AA21" s="14"/>
+      <c r="AB21" s="14"/>
+      <c r="AC21" s="14"/>
+      <c r="AD21" s="14"/>
+      <c r="AE21" s="14"/>
+      <c r="AF21" s="14"/>
+    </row>
+    <row r="22" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A22" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+      <c r="E22" s="14"/>
+      <c r="F22" s="14"/>
+      <c r="G22" s="14"/>
+      <c r="H22" s="14"/>
+      <c r="I22" s="14"/>
+      <c r="J22" s="14"/>
+      <c r="K22" s="14"/>
+      <c r="L22" s="14"/>
+      <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
+      <c r="O22" s="14"/>
+      <c r="P22" s="14"/>
+      <c r="Q22" s="14"/>
+      <c r="R22" s="14"/>
+      <c r="S22" s="14"/>
+      <c r="T22" s="14"/>
+      <c r="U22" s="14"/>
+      <c r="V22" s="14"/>
+      <c r="W22" s="14"/>
+      <c r="X22" s="14"/>
+      <c r="Y22" s="14"/>
+      <c r="Z22" s="14"/>
+      <c r="AA22" s="14"/>
+      <c r="AB22" s="14"/>
+      <c r="AC22" s="14"/>
+      <c r="AD22" s="14"/>
+      <c r="AE22" s="14"/>
+      <c r="AF22" s="14"/>
+    </row>
+    <row r="23" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A23" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+      <c r="E23" s="14"/>
+      <c r="F23" s="14"/>
+      <c r="G23" s="14"/>
+      <c r="H23" s="14"/>
+      <c r="I23" s="14"/>
+      <c r="J23" s="14"/>
+      <c r="K23" s="14"/>
+      <c r="L23" s="14"/>
+      <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
+      <c r="O23" s="14"/>
+      <c r="P23" s="14"/>
+      <c r="Q23" s="14"/>
+      <c r="R23" s="14"/>
+      <c r="S23" s="14"/>
+      <c r="T23" s="14"/>
+      <c r="U23" s="14"/>
+      <c r="V23" s="14"/>
+      <c r="W23" s="14"/>
+      <c r="X23" s="14"/>
+      <c r="Y23" s="14"/>
+      <c r="Z23" s="14"/>
+      <c r="AA23" s="14"/>
+      <c r="AB23" s="14"/>
+      <c r="AC23" s="14"/>
+      <c r="AD23" s="14"/>
+      <c r="AE23" s="14"/>
+      <c r="AF23" s="14"/>
+    </row>
+    <row r="24" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A24" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+      <c r="E24" s="14"/>
+      <c r="F24" s="14"/>
+      <c r="G24" s="14"/>
+      <c r="H24" s="14"/>
+      <c r="I24" s="14"/>
+      <c r="J24" s="14"/>
+      <c r="K24" s="14"/>
+      <c r="L24" s="14"/>
+      <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
+      <c r="O24" s="14"/>
+      <c r="P24" s="14"/>
+      <c r="Q24" s="14"/>
+      <c r="R24" s="14"/>
+      <c r="S24" s="14"/>
+      <c r="T24" s="14"/>
+      <c r="U24" s="14"/>
+      <c r="V24" s="14"/>
+      <c r="W24" s="14"/>
+      <c r="X24" s="14"/>
+      <c r="Y24" s="14"/>
+      <c r="Z24" s="14"/>
+      <c r="AA24" s="14"/>
+      <c r="AB24" s="14"/>
+      <c r="AC24" s="14"/>
+      <c r="AD24" s="14"/>
+      <c r="AE24" s="14"/>
+      <c r="AF24" s="14"/>
+    </row>
+    <row r="25" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A25" s="17">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+      <c r="G25" s="14"/>
+      <c r="H25" s="14"/>
+      <c r="I25" s="14"/>
+      <c r="J25" s="14"/>
+      <c r="K25" s="14"/>
+      <c r="L25" s="14"/>
+      <c r="M25" s="14"/>
+      <c r="N25" s="14"/>
+      <c r="O25" s="14"/>
+      <c r="P25" s="14"/>
+      <c r="Q25" s="14"/>
+      <c r="R25" s="14"/>
+      <c r="S25" s="14"/>
+      <c r="T25" s="14"/>
+      <c r="U25" s="14"/>
+      <c r="V25" s="14"/>
+      <c r="W25" s="14"/>
+      <c r="X25" s="14"/>
+      <c r="Y25" s="14"/>
+      <c r="Z25" s="14"/>
+      <c r="AA25" s="14"/>
+      <c r="AB25" s="14"/>
+      <c r="AC25" s="14"/>
+      <c r="AD25" s="14"/>
+      <c r="AE25" s="14"/>
+      <c r="AF25" s="14"/>
+    </row>
+    <row r="26" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A26" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="14"/>
+      <c r="D26" s="14"/>
+      <c r="E26" s="14"/>
+      <c r="F26" s="14"/>
+      <c r="G26" s="14"/>
+      <c r="H26" s="14"/>
+      <c r="I26" s="14"/>
+      <c r="J26" s="14"/>
+      <c r="K26" s="14"/>
+      <c r="L26" s="14"/>
+      <c r="M26" s="14"/>
+      <c r="N26" s="14"/>
+      <c r="O26" s="14"/>
+      <c r="P26" s="14"/>
+      <c r="Q26" s="14"/>
+      <c r="R26" s="14"/>
+      <c r="S26" s="14"/>
+      <c r="T26" s="14"/>
+      <c r="U26" s="14"/>
+      <c r="V26" s="14"/>
+      <c r="W26" s="14"/>
+      <c r="X26" s="14"/>
+      <c r="Y26" s="14"/>
+      <c r="Z26" s="14"/>
+      <c r="AA26" s="14"/>
+      <c r="AB26" s="14"/>
+      <c r="AC26" s="14"/>
+      <c r="AD26" s="14"/>
+      <c r="AE26" s="14"/>
+      <c r="AF26" s="14"/>
+    </row>
+    <row r="27" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A27" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
+      <c r="I27" s="14"/>
+      <c r="J27" s="14"/>
+      <c r="K27" s="14"/>
+      <c r="L27" s="14"/>
+      <c r="M27" s="14"/>
+      <c r="N27" s="14"/>
+      <c r="O27" s="14"/>
+      <c r="P27" s="14"/>
+      <c r="Q27" s="14"/>
+      <c r="R27" s="14"/>
+      <c r="S27" s="14"/>
+      <c r="T27" s="14"/>
+      <c r="U27" s="14"/>
+      <c r="V27" s="14"/>
+      <c r="W27" s="14"/>
+      <c r="X27" s="14"/>
+      <c r="Y27" s="14"/>
+      <c r="Z27" s="14"/>
+      <c r="AA27" s="14"/>
+      <c r="AB27" s="14"/>
+      <c r="AC27" s="14"/>
+      <c r="AD27" s="14"/>
+      <c r="AE27" s="14"/>
+      <c r="AF27" s="14"/>
+    </row>
+    <row r="28" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A28" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+      <c r="G28" s="14"/>
+      <c r="H28" s="14"/>
+      <c r="I28" s="14"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
+      <c r="N28" s="14"/>
+      <c r="O28" s="14"/>
+      <c r="P28" s="14"/>
+      <c r="Q28" s="14"/>
+      <c r="R28" s="14"/>
+      <c r="S28" s="14"/>
+      <c r="T28" s="14"/>
+      <c r="U28" s="14"/>
+      <c r="V28" s="14"/>
+      <c r="W28" s="14"/>
+      <c r="X28" s="14"/>
+      <c r="Y28" s="14"/>
+      <c r="Z28" s="14"/>
+      <c r="AA28" s="14"/>
+      <c r="AB28" s="14"/>
+      <c r="AC28" s="14"/>
+      <c r="AD28" s="14"/>
+      <c r="AE28" s="14"/>
+      <c r="AF28" s="14"/>
+    </row>
+    <row r="29" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A29" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="14"/>
+      <c r="D29" s="14"/>
+      <c r="E29" s="14"/>
+      <c r="F29" s="14"/>
+      <c r="G29" s="14"/>
+      <c r="H29" s="14"/>
+      <c r="I29" s="14"/>
+      <c r="J29" s="14"/>
+      <c r="K29" s="14"/>
+      <c r="L29" s="14"/>
+      <c r="M29" s="14"/>
+      <c r="N29" s="14"/>
+      <c r="O29" s="14"/>
+      <c r="P29" s="14"/>
+      <c r="Q29" s="14"/>
+      <c r="R29" s="14"/>
+      <c r="S29" s="14"/>
+      <c r="T29" s="14"/>
+      <c r="U29" s="14"/>
+      <c r="V29" s="14"/>
+      <c r="W29" s="14"/>
+      <c r="X29" s="14"/>
+      <c r="Y29" s="14"/>
+      <c r="Z29" s="14"/>
+      <c r="AA29" s="14"/>
+      <c r="AB29" s="14"/>
+      <c r="AC29" s="14"/>
+      <c r="AD29" s="14"/>
+      <c r="AE29" s="14"/>
+      <c r="AF29" s="14"/>
+    </row>
+    <row r="30" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A30" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+      <c r="G30" s="14"/>
+      <c r="H30" s="14"/>
+      <c r="I30" s="14"/>
+      <c r="J30" s="14"/>
+      <c r="K30" s="14"/>
+      <c r="L30" s="14"/>
+      <c r="M30" s="14"/>
+      <c r="N30" s="14"/>
+      <c r="O30" s="14"/>
+      <c r="P30" s="14"/>
+      <c r="Q30" s="14"/>
+      <c r="R30" s="14"/>
+      <c r="S30" s="14"/>
+      <c r="T30" s="14"/>
+      <c r="U30" s="14"/>
+      <c r="V30" s="14"/>
+      <c r="W30" s="14"/>
+      <c r="X30" s="14"/>
+      <c r="Y30" s="14"/>
+      <c r="Z30" s="14"/>
+      <c r="AA30" s="14"/>
+      <c r="AB30" s="14"/>
+      <c r="AC30" s="14"/>
+      <c r="AD30" s="14"/>
+      <c r="AE30" s="14"/>
+      <c r="AF30" s="14"/>
+    </row>
+    <row r="31" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A31" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="14"/>
+      <c r="D31" s="14"/>
+      <c r="E31" s="14"/>
+      <c r="F31" s="14"/>
+      <c r="G31" s="14"/>
+      <c r="H31" s="14"/>
+      <c r="I31" s="14"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
+      <c r="N31" s="14"/>
+      <c r="O31" s="14"/>
+      <c r="P31" s="14"/>
+      <c r="Q31" s="14"/>
+      <c r="R31" s="14"/>
+      <c r="S31" s="14"/>
+      <c r="T31" s="14"/>
+      <c r="U31" s="14"/>
+      <c r="V31" s="14"/>
+      <c r="W31" s="14"/>
+      <c r="X31" s="14"/>
+      <c r="Y31" s="14"/>
+      <c r="Z31" s="14"/>
+      <c r="AA31" s="14"/>
+      <c r="AB31" s="14"/>
+      <c r="AC31" s="14"/>
+      <c r="AD31" s="14"/>
+      <c r="AE31" s="14"/>
+      <c r="AF31" s="14"/>
+    </row>
+    <row r="32" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A32" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="14"/>
+      <c r="D32" s="14"/>
+      <c r="E32" s="14"/>
+      <c r="F32" s="14"/>
+      <c r="G32" s="14"/>
+      <c r="H32" s="14"/>
+      <c r="I32" s="14"/>
+      <c r="J32" s="14"/>
+      <c r="K32" s="14"/>
+      <c r="L32" s="14"/>
+      <c r="M32" s="14"/>
+      <c r="N32" s="14"/>
+      <c r="O32" s="14"/>
+      <c r="P32" s="14"/>
+      <c r="Q32" s="14"/>
+      <c r="R32" s="14"/>
+      <c r="S32" s="14"/>
+      <c r="T32" s="14"/>
+      <c r="U32" s="14"/>
+      <c r="V32" s="14"/>
+      <c r="W32" s="14"/>
+      <c r="X32" s="14"/>
+      <c r="Y32" s="14"/>
+      <c r="Z32" s="14"/>
+      <c r="AA32" s="14"/>
+      <c r="AB32" s="14"/>
+      <c r="AC32" s="14"/>
+      <c r="AD32" s="14"/>
+      <c r="AE32" s="14"/>
+      <c r="AF32" s="14"/>
+    </row>
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A33" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="14"/>
+      <c r="D33" s="14"/>
+      <c r="E33" s="14"/>
+      <c r="F33" s="14"/>
+      <c r="G33" s="14"/>
+      <c r="H33" s="14"/>
+      <c r="I33" s="14"/>
+      <c r="J33" s="14"/>
+      <c r="K33" s="14"/>
+      <c r="L33" s="14"/>
+      <c r="M33" s="14"/>
+      <c r="N33" s="14"/>
+      <c r="O33" s="14"/>
+      <c r="P33" s="14"/>
+      <c r="Q33" s="14"/>
+      <c r="R33" s="14"/>
+      <c r="S33" s="14"/>
+      <c r="T33" s="14"/>
+      <c r="U33" s="14"/>
+      <c r="V33" s="14"/>
+      <c r="W33" s="14"/>
+      <c r="X33" s="14"/>
+      <c r="Y33" s="14"/>
+      <c r="Z33" s="14"/>
+      <c r="AA33" s="14"/>
+      <c r="AB33" s="14"/>
+      <c r="AC33" s="14"/>
+      <c r="AD33" s="14"/>
+      <c r="AE33" s="14"/>
+      <c r="AF33" s="14"/>
+    </row>
+    <row r="34" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A34" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="14"/>
+      <c r="D34" s="14"/>
+      <c r="E34" s="14"/>
+      <c r="F34" s="14"/>
+      <c r="G34" s="14"/>
+      <c r="H34" s="14"/>
+      <c r="I34" s="14"/>
+      <c r="J34" s="14"/>
+      <c r="K34" s="14"/>
+      <c r="L34" s="14"/>
+      <c r="M34" s="14"/>
+      <c r="N34" s="14"/>
+      <c r="O34" s="14"/>
+      <c r="P34" s="14"/>
+      <c r="Q34" s="14"/>
+      <c r="R34" s="14"/>
+      <c r="S34" s="14"/>
+      <c r="T34" s="14"/>
+      <c r="U34" s="14"/>
+      <c r="V34" s="14"/>
+      <c r="W34" s="14"/>
+      <c r="X34" s="14"/>
+      <c r="Y34" s="14"/>
+      <c r="Z34" s="14"/>
+      <c r="AA34" s="14"/>
+      <c r="AB34" s="14"/>
+      <c r="AC34" s="14"/>
+      <c r="AD34" s="14"/>
+      <c r="AE34" s="14"/>
+      <c r="AF34" s="14"/>
+    </row>
+    <row r="35" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A35" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="14"/>
+      <c r="D35" s="14"/>
+      <c r="E35" s="14"/>
+      <c r="F35" s="14"/>
+      <c r="G35" s="14"/>
+      <c r="H35" s="14"/>
+      <c r="I35" s="14"/>
+      <c r="J35" s="14"/>
+      <c r="K35" s="14"/>
+      <c r="L35" s="14"/>
+      <c r="M35" s="14"/>
+      <c r="N35" s="14"/>
+      <c r="O35" s="14"/>
+      <c r="P35" s="14"/>
+      <c r="Q35" s="14"/>
+      <c r="R35" s="14"/>
+      <c r="S35" s="14"/>
+      <c r="T35" s="14"/>
+      <c r="U35" s="14"/>
+      <c r="V35" s="14"/>
+      <c r="W35" s="14"/>
+      <c r="X35" s="14"/>
+      <c r="Y35" s="14"/>
+      <c r="Z35" s="14"/>
+      <c r="AA35" s="14"/>
+      <c r="AB35" s="14"/>
+      <c r="AC35" s="14"/>
+      <c r="AD35" s="14"/>
+      <c r="AE35" s="14"/>
+      <c r="AF35" s="14"/>
+    </row>
+    <row r="36" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A36" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+      <c r="G36" s="14"/>
+      <c r="H36" s="14"/>
+      <c r="I36" s="14"/>
+      <c r="J36" s="14"/>
+      <c r="K36" s="14"/>
+      <c r="L36" s="14"/>
+      <c r="M36" s="14"/>
+      <c r="N36" s="14"/>
+      <c r="O36" s="14"/>
+      <c r="P36" s="14"/>
+      <c r="Q36" s="14"/>
+      <c r="R36" s="14"/>
+      <c r="S36" s="14"/>
+      <c r="T36" s="14"/>
+      <c r="U36" s="14"/>
+      <c r="V36" s="14"/>
+      <c r="W36" s="14"/>
+      <c r="X36" s="14"/>
+      <c r="Y36" s="14"/>
+      <c r="Z36" s="14"/>
+      <c r="AA36" s="14"/>
+      <c r="AB36" s="14"/>
+      <c r="AC36" s="14"/>
+      <c r="AD36" s="14"/>
+      <c r="AE36" s="14"/>
+      <c r="AF36" s="14"/>
+    </row>
+    <row r="37" spans="1:32" x14ac:dyDescent="0.25">
+      <c r="A37" s="17">
+        <v>2027</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+      <c r="G37" s="14"/>
+      <c r="H37" s="14"/>
+      <c r="I37" s="14"/>
+      <c r="J37" s="14"/>
+      <c r="K37" s="14"/>
+      <c r="L37" s="14"/>
+      <c r="M37" s="14"/>
+      <c r="N37" s="14"/>
+      <c r="O37" s="14"/>
+      <c r="P37" s="14"/>
+      <c r="Q37" s="14"/>
+      <c r="R37" s="14"/>
+      <c r="S37" s="14"/>
+      <c r="T37" s="14"/>
+      <c r="U37" s="14"/>
+      <c r="V37" s="14"/>
+      <c r="W37" s="14"/>
+      <c r="X37" s="14"/>
+      <c r="Y37" s="14"/>
+      <c r="Z37" s="14"/>
+      <c r="AA37" s="14"/>
+      <c r="AB37" s="14"/>
+      <c r="AC37" s="14"/>
+      <c r="AD37" s="14"/>
+      <c r="AE37" s="14"/>
+      <c r="AF37" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -8236,7 +8236,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8313,6 +8313,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10048,16 +10049,16 @@
         <v>7</v>
       </c>
       <c r="C17" s="16">
-        <v>0.92826274848746759</v>
+        <v>0.9269662921348315</v>
       </c>
       <c r="D17" s="16">
-        <v>0.9084337349397591</v>
+        <v>0.90923694779116471</v>
       </c>
       <c r="E17" s="16">
-        <v>0.95135640785781106</v>
+        <v>0.94761459307764262</v>
       </c>
       <c r="F17" s="16">
-        <v>0.91289198606271782</v>
+        <v>0.91637630662020908</v>
       </c>
       <c r="G17" s="16" t="s">
         <v>47</v>
@@ -10066,19 +10067,19 @@
         <v>0.92567567567567566</v>
       </c>
       <c r="I17" s="16">
-        <v>0.87152777777777779</v>
+        <v>0.875</v>
       </c>
       <c r="J17" s="16">
-        <v>0.9197860962566845</v>
+        <v>0.91711229946524064</v>
       </c>
       <c r="K17" s="16">
-        <v>0.94385964912280707</v>
+        <v>0.94035087719298249</v>
       </c>
       <c r="L17" s="16">
-        <v>0.91304347826086962</v>
+        <v>0.90760869565217395</v>
       </c>
       <c r="M17" s="16">
-        <v>0.97124600638977632</v>
+        <v>0.96485623003194887</v>
       </c>
       <c r="N17" s="16">
         <v>0.95945945945945943</v>
@@ -10096,16 +10097,16 @@
         <v>0.96899224806201545</v>
       </c>
       <c r="S17" s="16">
-        <v>0.89387755102040822</v>
+        <v>0.88979591836734695</v>
       </c>
       <c r="T17" s="16">
-        <v>0.88888888888888884</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="U17" s="16">
         <v>0.8867924528301887</v>
       </c>
       <c r="V17" s="16">
-        <v>0.87152777777777779</v>
+        <v>0.875</v>
       </c>
       <c r="W17" s="16" t="s">
         <v>47</v>
@@ -10114,13 +10115,13 @@
         <v>47</v>
       </c>
       <c r="Y17" s="16">
-        <v>0.94385964912280707</v>
+        <v>0.94035087719298249</v>
       </c>
       <c r="Z17" s="16">
-        <v>0.91304347826086962</v>
+        <v>0.90760869565217395</v>
       </c>
       <c r="AA17" s="16">
-        <v>0.97124600638977632</v>
+        <v>0.96485623003194887</v>
       </c>
       <c r="AB17" s="16">
         <v>0.95945945945945943</v>
@@ -12278,64 +12279,64 @@
         <v>7</v>
       </c>
       <c r="C17" s="13">
-        <v>174197.53476424556</v>
+        <v>106718.46708921195</v>
       </c>
       <c r="D17" s="13">
-        <v>101742.77401326261</v>
+        <v>67973.526669520637</v>
       </c>
       <c r="E17" s="13">
-        <v>72816.573923106946</v>
+        <v>39172.444252725974</v>
       </c>
       <c r="F17" s="13">
-        <v>16308.124101526702</v>
+        <v>12890.12841315452</v>
       </c>
       <c r="G17" s="13" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="13">
-        <v>30420.094791240794</v>
+        <v>17320.151944690551</v>
       </c>
       <c r="I17" s="13">
-        <v>27574.656038247173</v>
+        <v>18971.617360254324</v>
       </c>
       <c r="J17" s="13">
-        <v>27558.355147092974</v>
+        <v>18927.698514328029</v>
       </c>
       <c r="K17" s="13">
-        <v>18947.777793680136</v>
+        <v>8545.3045055545117</v>
       </c>
       <c r="L17" s="13">
-        <v>15505.437185714323</v>
+        <v>8503.444153873681</v>
       </c>
       <c r="M17" s="13">
-        <v>24079.556102302624</v>
+        <v>13570.235039954079</v>
       </c>
       <c r="N17" s="13">
-        <v>12885.230822535108</v>
+        <v>7433.9524608384017</v>
       </c>
       <c r="O17" s="13">
-        <v>1530.3927063492085</v>
+        <v>1177.318736548777</v>
       </c>
       <c r="P17" s="13">
-        <v>9471.7326036363593</v>
+        <v>3804.0290038909734</v>
       </c>
       <c r="Q17" s="13">
-        <v>14328.155609774396</v>
+        <v>8452.1573946477729</v>
       </c>
       <c r="R17" s="13">
-        <v>10783.841378399995</v>
+        <v>8480.6059236960627</v>
       </c>
       <c r="S17" s="13">
-        <v>16667.085086757947</v>
+        <v>10273.348663930399</v>
       </c>
       <c r="T17" s="13">
-        <v>6643.9579499999891</v>
+        <v>9170.22637047219</v>
       </c>
       <c r="U17" s="13">
-        <v>16068.389457446767</v>
+        <v>8826.7150364999798</v>
       </c>
       <c r="V17" s="13">
-        <v>27574.656038247173</v>
+        <v>18971.617360254324</v>
       </c>
       <c r="W17" s="13" t="s">
         <v>47</v>
@@ -12344,19 +12345,19 @@
         <v>47</v>
       </c>
       <c r="Y17" s="13">
-        <v>18947.777793680136</v>
+        <v>8545.3045055545117</v>
       </c>
       <c r="Z17" s="13">
-        <v>15505.437185714323</v>
+        <v>8503.444153873681</v>
       </c>
       <c r="AA17" s="13">
-        <v>24079.556102302624</v>
+        <v>13570.235039954079</v>
       </c>
       <c r="AB17" s="13">
-        <v>12885.230822535108</v>
+        <v>7433.9524608384017</v>
       </c>
       <c r="AC17" s="13">
-        <v>1530.3927063492085</v>
+        <v>1177.318736548777</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
@@ -14448,79 +14449,79 @@
         <v>7</v>
       </c>
       <c r="C17" s="17">
-        <v>0.81459999999999999</v>
+        <v>0.81142216240466825</v>
       </c>
       <c r="D17" s="17">
-        <v>0.84409999999999996</v>
+        <v>0.83977586206896804</v>
       </c>
       <c r="E17" s="17">
-        <v>0.78190000000000004</v>
+        <v>0.78065481758653099</v>
       </c>
       <c r="F17" s="17">
-        <v>0.82705000000000006</v>
+        <v>0.82022786285835381</v>
       </c>
       <c r="G17" s="17"/>
       <c r="H17" s="17">
-        <v>0.83220000000000005</v>
+        <v>0.82980143045360411</v>
       </c>
       <c r="I17" s="17">
-        <v>0.82220000000000004</v>
+        <v>0.81879828326180282</v>
       </c>
       <c r="J17" s="17">
-        <v>0.8901</v>
+        <v>0.88437094211907707</v>
       </c>
       <c r="K17" s="17">
-        <v>0.77529999999999999</v>
+        <v>0.77528813559322018</v>
       </c>
       <c r="L17" s="17">
-        <v>0.7581</v>
+        <v>0.75805405405405424</v>
       </c>
       <c r="M17" s="17">
-        <v>0.73399999999999999</v>
+        <v>0.73558823529411743</v>
       </c>
       <c r="N17" s="17">
-        <v>0.88239999999999996</v>
+        <v>0.86882882882882828</v>
       </c>
       <c r="O17" s="17">
-        <v>0.7802</v>
+        <v>0.78032786885245886</v>
       </c>
       <c r="P17" s="17">
-        <v>0.84650000000000003</v>
+        <v>0.83955752212389323</v>
       </c>
       <c r="Q17" s="17">
-        <v>0.88200000000000001</v>
+        <v>0.87992753623188391</v>
       </c>
       <c r="R17" s="17">
-        <v>0.89139999999999997</v>
+        <v>0.89141732283464514</v>
       </c>
       <c r="S17" s="17">
-        <v>0.88880000000000003</v>
+        <v>0.87732456140350912</v>
       </c>
       <c r="T17" s="17">
-        <v>0.80759999999999998</v>
+        <v>0.80089820359281438</v>
       </c>
       <c r="U17" s="17">
-        <v>0.78239999999999998</v>
+        <v>0.77967532467532441</v>
       </c>
       <c r="V17" s="17">
-        <v>0.82220000000000004</v>
+        <v>0.81879828326180282</v>
       </c>
       <c r="W17" s="17"/>
       <c r="X17" s="17"/>
       <c r="Y17" s="17">
-        <v>0.77529999999999999</v>
+        <v>0.77528813559322018</v>
       </c>
       <c r="Z17" s="17">
-        <v>0.7581</v>
+        <v>0.75805405405405424</v>
       </c>
       <c r="AA17" s="17">
-        <v>0.73399999999999999</v>
+        <v>0.73558823529411743</v>
       </c>
       <c r="AB17" s="17">
-        <v>0.88239999999999996</v>
+        <v>0.86882882882882828</v>
       </c>
       <c r="AC17" s="17">
-        <v>0.7802</v>
+        <v>0.78032786885245886</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
@@ -16671,64 +16672,64 @@
         <v>7</v>
       </c>
       <c r="C17" s="12">
-        <v>198503.66118340264</v>
+        <v>121914.86296952383</v>
       </c>
       <c r="D17" s="12">
-        <v>109497.17829641039</v>
+        <v>73595.87803265595</v>
       </c>
       <c r="E17" s="12">
-        <v>88597.664918787283</v>
+        <v>47550.311589909572</v>
       </c>
       <c r="F17" s="12">
-        <v>18000.792938758219</v>
+        <v>14401.130224890472</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="12">
-        <v>33836.988464311369</v>
+        <v>19321.301176165209</v>
       </c>
       <c r="I17" s="12">
-        <v>29228.993797129824</v>
+        <v>20273.815333482802</v>
       </c>
       <c r="J17" s="12">
-        <v>28477.465340972874</v>
+        <v>19628.443542554684</v>
       </c>
       <c r="K17" s="12">
-        <v>23067.2551270474</v>
+        <v>10364.642793779909</v>
       </c>
       <c r="L17" s="12">
-        <v>18674.499802136968</v>
+        <v>10181.067980276332</v>
       </c>
       <c r="M17" s="12">
-        <v>31862.633106267014</v>
+        <v>17799.803195686392</v>
       </c>
       <c r="N17" s="12">
-        <v>14010.490253853015</v>
+        <v>8209.4145279893219</v>
       </c>
       <c r="O17" s="12">
-        <v>1901.1839271981569</v>
+        <v>1462.3257610074179</v>
       </c>
       <c r="P17" s="12">
-        <v>10610.532073242759</v>
+        <v>4296.6310085275336</v>
       </c>
       <c r="Q17" s="12">
-        <v>15770.765646258458</v>
+        <v>9325.0622792119721</v>
       </c>
       <c r="R17" s="12">
-        <v>11722.524904644373</v>
+        <v>9218.6243058400105</v>
       </c>
       <c r="S17" s="12">
-        <v>16762.301080107965</v>
+        <v>10419.386520430025</v>
       </c>
       <c r="T17" s="12">
-        <v>7312.7048043585801</v>
+        <v>10244.671978660323</v>
       </c>
       <c r="U17" s="12">
-        <v>18212.329371165601</v>
+        <v>10039.389512436437</v>
       </c>
       <c r="V17" s="12">
-        <v>29228.993797129824</v>
+        <v>20273.815333482802</v>
       </c>
       <c r="W17" s="12" t="s">
         <v>47</v>
@@ -16737,19 +16738,19 @@
         <v>47</v>
       </c>
       <c r="Y17" s="12">
-        <v>23067.2551270474</v>
+        <v>10364.642793779909</v>
       </c>
       <c r="Z17" s="12">
-        <v>18674.499802136968</v>
+        <v>10181.067980276332</v>
       </c>
       <c r="AA17" s="12">
-        <v>31862.633106267014</v>
+        <v>17799.803195686392</v>
       </c>
       <c r="AB17" s="12">
-        <v>14010.490253853015</v>
+        <v>8209.4145279893219</v>
       </c>
       <c r="AC17" s="12">
-        <v>1901.1839271981569</v>
+        <v>1462.3257610074179</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
@@ -18900,64 +18901,64 @@
         <v>7</v>
       </c>
       <c r="C17" s="12">
-        <v>6987.9465168539227</v>
+        <v>4275.0398331892757</v>
       </c>
       <c r="D17" s="12">
-        <v>7423.8207389558238</v>
+        <v>4964.1800738631546</v>
       </c>
       <c r="E17" s="12">
-        <v>6480.3100280635899</v>
+        <v>3472.4396464362549</v>
       </c>
       <c r="F17" s="12">
-        <v>5187.3016724738627</v>
+        <v>4115.7520094448628</v>
       </c>
       <c r="G17" s="12" t="s">
         <v>47</v>
       </c>
       <c r="H17" s="12">
-        <v>9513.2235810810544</v>
+        <v>5416.5011331779706</v>
       </c>
       <c r="I17" s="12">
-        <v>8344.4717708333828</v>
+        <v>5763.9462466050463</v>
       </c>
       <c r="J17" s="12">
-        <v>6777.48446524063</v>
+        <v>4641.3970877166303</v>
       </c>
       <c r="K17" s="12">
-        <v>6275.1027719297717</v>
+        <v>2819.5033640980109</v>
       </c>
       <c r="L17" s="12">
-        <v>7694.096902173932</v>
+        <v>4194.4564440480408</v>
       </c>
       <c r="M17" s="12">
-        <v>7471.9401597444057</v>
+        <v>4183.1711889129538</v>
       </c>
       <c r="N17" s="12">
-        <v>5568.8543243242784</v>
+        <v>3212.8720764519508</v>
       </c>
       <c r="O17" s="12">
-        <v>2282.0056923076954</v>
+        <v>1755.5285302384129</v>
       </c>
       <c r="P17" s="12">
-        <v>7742.9443103448239</v>
+        <v>3109.7145543103975</v>
       </c>
       <c r="Q17" s="12">
-        <v>10153.149854014569</v>
+        <v>5989.3277931064722</v>
       </c>
       <c r="R17" s="12">
-        <v>8100.3555813953444</v>
+        <v>6370.26465033356</v>
       </c>
       <c r="S17" s="12">
-        <v>6080.9523265305961</v>
+        <v>3731.0953914815946</v>
       </c>
       <c r="T17" s="12">
-        <v>3453.6493567251405</v>
+        <v>4798.2101661442666</v>
       </c>
       <c r="U17" s="12">
-        <v>8961.8405660377139</v>
+        <v>4922.9335079565572</v>
       </c>
       <c r="V17" s="12">
-        <v>8344.4717708333828</v>
+        <v>5763.9462466050463</v>
       </c>
       <c r="W17" s="12" t="s">
         <v>47</v>
@@ -18966,19 +18967,19 @@
         <v>47</v>
       </c>
       <c r="Y17" s="12">
-        <v>6275.1027719297717</v>
+        <v>2819.5033640980109</v>
       </c>
       <c r="Z17" s="12">
-        <v>7694.096902173932</v>
+        <v>4194.4564440480408</v>
       </c>
       <c r="AA17" s="12">
-        <v>7471.9401597444057</v>
+        <v>4183.1711889129538</v>
       </c>
       <c r="AB17" s="12">
-        <v>5568.8543243242784</v>
+        <v>3212.8720764519508</v>
       </c>
       <c r="AC17" s="12">
-        <v>2282.0056923076954</v>
+        <v>1755.5285302384129</v>
       </c>
     </row>
     <row r="18" spans="1:29" x14ac:dyDescent="0.25">
@@ -22756,166 +22757,166 @@
         <v>7</v>
       </c>
       <c r="C18" s="18">
-        <v>0.31323911162388229</v>
+        <v>0.34474226804123709</v>
       </c>
       <c r="D18" s="18">
-        <v>0.68676088837611771</v>
+        <v>0.65525773195876291</v>
       </c>
       <c r="E18" s="18">
-        <v>0.34938101788170561</v>
+        <v>0.38721079691516708</v>
       </c>
       <c r="F18" s="18">
-        <v>0.65061898211829439</v>
+        <v>0.61278920308483287</v>
       </c>
       <c r="G18" s="18">
-        <v>0.28713363139592646</v>
+        <v>0.31299543598366564</v>
       </c>
       <c r="H18" s="18">
-        <v>0.71286636860407349</v>
+        <v>0.68700456401633436</v>
       </c>
       <c r="I18" s="18">
-        <v>0.44785276073619634</v>
+        <v>0.45273631840796019</v>
       </c>
       <c r="J18" s="18">
-        <v>0.55214723926380371</v>
+        <v>0.54726368159203975</v>
       </c>
       <c r="K18" s="18"/>
       <c r="L18" s="18"/>
       <c r="M18" s="18">
-        <v>0.32105263157894737</v>
+        <v>0.41385767790262173</v>
       </c>
       <c r="N18" s="18">
-        <v>0.67894736842105263</v>
+        <v>0.58614232209737827</v>
       </c>
       <c r="O18" s="18">
-        <v>0.29065743944636679</v>
+        <v>0.28891509433962265</v>
       </c>
       <c r="P18" s="18">
-        <v>0.70934256055363321</v>
+        <v>0.71108490566037741</v>
       </c>
       <c r="Q18" s="18">
-        <v>0.33436055469953774</v>
+        <v>0.41348713398402842</v>
       </c>
       <c r="R18" s="18">
-        <v>0.66563944530046226</v>
+        <v>0.58651286601597163</v>
       </c>
       <c r="S18" s="18">
-        <v>0.24954462659380691</v>
+        <v>0.36779107725788901</v>
       </c>
       <c r="T18" s="18">
-        <v>0.75045537340619306</v>
+        <v>0.63220892274211093</v>
       </c>
       <c r="U18" s="18">
-        <v>0.42622950819672129</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="V18" s="18">
-        <v>0.57377049180327866</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="W18" s="18">
-        <v>0.30229419703103916</v>
+        <v>0.25868725868725867</v>
       </c>
       <c r="X18" s="18">
-        <v>0.6977058029689609</v>
+        <v>0.74131274131274127</v>
       </c>
       <c r="Y18" s="18">
-        <v>0.25257731958762886</v>
+        <v>0.24454148471615719</v>
       </c>
       <c r="Z18" s="18">
-        <v>0.74742268041237114</v>
+        <v>0.75545851528384278</v>
       </c>
       <c r="AA18" s="18">
-        <v>0.94736842105263153</v>
+        <v>0.94594594594594594</v>
       </c>
       <c r="AB18" s="18">
-        <v>5.2631578947368418E-2</v>
+        <v>5.4054054054054057E-2</v>
       </c>
       <c r="AC18" s="18">
-        <v>0.43965517241379309</v>
+        <v>0.41726618705035973</v>
       </c>
       <c r="AD18" s="18">
-        <v>0.56034482758620685</v>
+        <v>0.58273381294964033</v>
       </c>
       <c r="AE18" s="18">
-        <v>8.3333333333333329E-2</v>
+        <v>0.46400000000000002</v>
       </c>
       <c r="AF18" s="18">
-        <v>0.91666666666666663</v>
+        <v>0.53600000000000003</v>
       </c>
       <c r="AG18" s="18">
-        <v>0.4511627906976744</v>
+        <v>0.49209486166007904</v>
       </c>
       <c r="AH18" s="18">
-        <v>0.5488372093023256</v>
+        <v>0.5079051383399209</v>
       </c>
       <c r="AI18" s="18">
-        <v>0.25757575757575757</v>
+        <v>0.31487889273356401</v>
       </c>
       <c r="AJ18" s="18">
-        <v>0.74242424242424243</v>
+        <v>0.68512110726643594</v>
       </c>
       <c r="AK18" s="18">
-        <v>0.45238095238095238</v>
+        <v>0.48307692307692307</v>
       </c>
       <c r="AL18" s="18">
-        <v>0.54761904761904767</v>
+        <v>0.51692307692307693</v>
       </c>
       <c r="AM18" s="18">
-        <v>0.3253012048192771</v>
+        <v>0.26347305389221559</v>
       </c>
       <c r="AN18" s="18">
-        <v>0.67469879518072284</v>
+        <v>0.73652694610778446</v>
       </c>
       <c r="AO18" s="18">
-        <v>0.35542168674698793</v>
+        <v>0.36971830985915494</v>
       </c>
       <c r="AP18" s="18">
-        <v>0.64457831325301207</v>
+        <v>0.63028169014084512</v>
       </c>
       <c r="AQ18" s="18">
-        <v>0.27669902912621358</v>
+        <v>0.30544747081712065</v>
       </c>
       <c r="AR18" s="18">
-        <v>0.72330097087378642</v>
+        <v>0.69455252918287935</v>
       </c>
       <c r="AS18" s="18">
-        <v>0.2923728813559322</v>
+        <v>0.37951807228915663</v>
       </c>
       <c r="AT18" s="18">
-        <v>0.7076271186440678</v>
+        <v>0.62048192771084343</v>
       </c>
       <c r="AU18" s="18"/>
       <c r="AV18" s="18"/>
       <c r="AW18" s="18"/>
       <c r="AX18" s="18"/>
       <c r="AY18" s="18">
-        <v>0.24954462659380691</v>
+        <v>0.36779107725788901</v>
       </c>
       <c r="AZ18" s="18">
-        <v>0.75045537340619306</v>
+        <v>0.63220892274211093</v>
       </c>
       <c r="BA18" s="18">
-        <v>0.42622950819672129</v>
+        <v>0.68817204301075274</v>
       </c>
       <c r="BB18" s="18">
-        <v>0.57377049180327866</v>
+        <v>0.31182795698924731</v>
       </c>
       <c r="BC18" s="18">
-        <v>0.30229419703103916</v>
+        <v>0.25868725868725867</v>
       </c>
       <c r="BD18" s="18">
-        <v>0.6977058029689609</v>
+        <v>0.74131274131274127</v>
       </c>
       <c r="BE18" s="18">
-        <v>0.25257731958762886</v>
+        <v>0.24454148471615719</v>
       </c>
       <c r="BF18" s="18">
-        <v>0.74742268041237114</v>
+        <v>0.75545851528384278</v>
       </c>
       <c r="BG18" s="18">
-        <v>0.94736842105263153</v>
+        <v>0.94594594594594594</v>
       </c>
       <c r="BH18" s="18">
-        <v>5.2631578947368418E-2</v>
+        <v>5.4054054054054057E-2</v>
       </c>
     </row>
     <row r="19" spans="1:60" x14ac:dyDescent="0.25">
@@ -22992,63 +22993,63 @@
         <v>9</v>
       </c>
       <c r="C20" s="12"/>
-      <c r="D20" s="12"/>
+      <c r="D20" s="28"/>
       <c r="E20" s="12"/>
-      <c r="F20" s="12"/>
+      <c r="F20" s="28"/>
       <c r="G20" s="12"/>
-      <c r="H20" s="5"/>
+      <c r="H20" s="28"/>
       <c r="I20" s="5"/>
-      <c r="J20" s="5"/>
+      <c r="J20" s="28"/>
       <c r="K20" s="5"/>
       <c r="L20" s="5"/>
       <c r="M20" s="5"/>
-      <c r="N20" s="5"/>
+      <c r="N20" s="28"/>
       <c r="O20" s="5"/>
-      <c r="P20" s="5"/>
+      <c r="P20" s="28"/>
       <c r="Q20" s="5"/>
-      <c r="R20" s="5"/>
+      <c r="R20" s="28"/>
       <c r="S20" s="5"/>
-      <c r="T20" s="5"/>
+      <c r="T20" s="28"/>
       <c r="U20" s="5"/>
-      <c r="V20" s="5"/>
+      <c r="V20" s="28"/>
       <c r="W20" s="5"/>
-      <c r="X20" s="5"/>
+      <c r="X20" s="28"/>
       <c r="Y20" s="5"/>
-      <c r="Z20" s="5"/>
+      <c r="Z20" s="28"/>
       <c r="AA20" s="5"/>
-      <c r="AB20" s="5"/>
+      <c r="AB20" s="28"/>
       <c r="AC20" s="5"/>
-      <c r="AD20" s="5"/>
+      <c r="AD20" s="28"/>
       <c r="AE20" s="5"/>
-      <c r="AF20" s="5"/>
+      <c r="AF20" s="28"/>
       <c r="AG20" s="5"/>
-      <c r="AH20" s="5"/>
+      <c r="AH20" s="28"/>
       <c r="AI20" s="5"/>
-      <c r="AJ20" s="5"/>
+      <c r="AJ20" s="28"/>
       <c r="AK20" s="5"/>
-      <c r="AL20" s="5"/>
+      <c r="AL20" s="28"/>
       <c r="AM20" s="5"/>
-      <c r="AN20" s="5"/>
+      <c r="AN20" s="28"/>
       <c r="AO20" s="5"/>
-      <c r="AP20" s="5"/>
+      <c r="AP20" s="28"/>
       <c r="AQ20" s="5"/>
-      <c r="AR20" s="5"/>
+      <c r="AR20" s="28"/>
       <c r="AS20" s="5"/>
-      <c r="AT20" s="5"/>
+      <c r="AT20" s="28"/>
       <c r="AU20" s="5"/>
       <c r="AV20" s="5"/>
       <c r="AW20" s="5"/>
       <c r="AX20" s="5"/>
       <c r="AY20" s="5"/>
-      <c r="AZ20" s="5"/>
+      <c r="AZ20" s="28"/>
       <c r="BA20" s="5"/>
-      <c r="BB20" s="5"/>
+      <c r="BB20" s="28"/>
       <c r="BC20" s="5"/>
-      <c r="BD20" s="5"/>
+      <c r="BD20" s="28"/>
       <c r="BE20" s="5"/>
-      <c r="BF20" s="5"/>
+      <c r="BF20" s="28"/>
       <c r="BG20" s="5"/>
-      <c r="BH20" s="5"/>
+      <c r="BH20" s="28"/>
     </row>
     <row r="21" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A21" s="15">

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -25762,36 +25762,90 @@
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
+      <c r="C17" s="18">
+        <v>0.83295194508009152</v>
+      </c>
+      <c r="D17" s="18">
+        <v>0.71698113207547165</v>
+      </c>
+      <c r="E17" s="18">
+        <v>0.94222222222222218</v>
+      </c>
+      <c r="F17" s="18">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18">
+        <v>0.80392156862745101</v>
+      </c>
+      <c r="I17" s="18">
+        <v>0.73076923076923073</v>
+      </c>
+      <c r="J17" s="18">
+        <v>0.6619718309859155</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0.88405797101449279</v>
+      </c>
+      <c r="L17" s="18">
+        <v>1</v>
+      </c>
+      <c r="M17" s="18">
+        <v>1</v>
+      </c>
+      <c r="N17" s="18">
+        <v>1</v>
+      </c>
+      <c r="O17" s="18">
+        <v>0.58333333333333337</v>
+      </c>
+      <c r="P17" s="18">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="R17" s="18">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="S17" s="18">
+        <v>0.77272727272727271</v>
+      </c>
+      <c r="T17" s="18">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="U17" s="18">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="V17" s="18">
+        <v>0.70370370370370372</v>
+      </c>
+      <c r="W17" s="18">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="X17" s="18">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="AB17" s="18">
+        <v>0.82352941176470584</v>
+      </c>
+      <c r="AC17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="18">
+        <v>0.58333333333333337</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
@@ -28076,36 +28130,90 @@
       <c r="B17" s="8" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="12"/>
-      <c r="D17" s="12"/>
-      <c r="E17" s="12"/>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12"/>
-      <c r="H17" s="12"/>
-      <c r="I17" s="12"/>
-      <c r="J17" s="12"/>
-      <c r="K17" s="12"/>
-      <c r="L17" s="12"/>
-      <c r="M17" s="12"/>
-      <c r="N17" s="12"/>
-      <c r="O17" s="12"/>
-      <c r="P17" s="12"/>
-      <c r="Q17" s="12"/>
-      <c r="R17" s="12"/>
-      <c r="S17" s="12"/>
-      <c r="T17" s="12"/>
-      <c r="U17" s="12"/>
-      <c r="V17" s="12"/>
-      <c r="W17" s="12"/>
-      <c r="X17" s="12"/>
-      <c r="Y17" s="12"/>
-      <c r="Z17" s="12"/>
-      <c r="AA17" s="12"/>
-      <c r="AB17" s="12"/>
-      <c r="AC17" s="12"/>
-      <c r="AD17" s="12"/>
-      <c r="AE17" s="12"/>
-      <c r="AF17" s="12"/>
+      <c r="C17" s="18">
+        <v>0.93363844393592677</v>
+      </c>
+      <c r="D17" s="18">
+        <v>0.89622641509433965</v>
+      </c>
+      <c r="E17" s="18">
+        <v>0.96888888888888891</v>
+      </c>
+      <c r="F17" s="18">
+        <v>0.86842105263157898</v>
+      </c>
+      <c r="G17" s="18"/>
+      <c r="H17" s="18">
+        <v>0.92156862745098034</v>
+      </c>
+      <c r="I17" s="18">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="J17" s="18">
+        <v>0.90140845070422537</v>
+      </c>
+      <c r="K17" s="18">
+        <v>0.89855072463768115</v>
+      </c>
+      <c r="L17" s="18">
+        <v>1</v>
+      </c>
+      <c r="M17" s="18">
+        <v>1</v>
+      </c>
+      <c r="N17" s="18">
+        <v>1</v>
+      </c>
+      <c r="O17" s="18">
+        <v>1</v>
+      </c>
+      <c r="P17" s="18">
+        <v>1</v>
+      </c>
+      <c r="Q17" s="18">
+        <v>1</v>
+      </c>
+      <c r="R17" s="18">
+        <v>1</v>
+      </c>
+      <c r="S17" s="18">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="T17" s="18">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="U17" s="18">
+        <v>1</v>
+      </c>
+      <c r="V17" s="18">
+        <v>0.85185185185185186</v>
+      </c>
+      <c r="W17" s="18">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="X17" s="18">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="Y17" s="18"/>
+      <c r="Z17" s="18"/>
+      <c r="AA17" s="18">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="AB17" s="18">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="AC17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AD17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AE17" s="18">
+        <v>1</v>
+      </c>
+      <c r="AF17" s="18">
+        <v>1</v>
+      </c>
     </row>
     <row r="18" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A18" s="15">
@@ -35260,36 +35368,90 @@
       <c r="C67" s="21">
         <v>13</v>
       </c>
-      <c r="D67" s="22"/>
-      <c r="E67" s="22"/>
-      <c r="F67" s="22"/>
-      <c r="G67" s="22"/>
-      <c r="H67" s="22"/>
-      <c r="I67" s="22"/>
-      <c r="J67" s="22"/>
-      <c r="K67" s="22"/>
-      <c r="L67" s="22"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="22"/>
-      <c r="P67" s="22"/>
-      <c r="Q67" s="22"/>
-      <c r="R67" s="22"/>
-      <c r="S67" s="22"/>
-      <c r="T67" s="22"/>
-      <c r="U67" s="22"/>
-      <c r="V67" s="22"/>
-      <c r="W67" s="22"/>
-      <c r="X67" s="22"/>
-      <c r="Y67" s="22"/>
-      <c r="Z67" s="22"/>
-      <c r="AA67" s="22"/>
-      <c r="AB67" s="22"/>
-      <c r="AC67" s="22"/>
-      <c r="AD67" s="22"/>
-      <c r="AE67" s="22"/>
-      <c r="AF67" s="22"/>
-      <c r="AG67" s="22"/>
+      <c r="D67" s="25">
+        <v>0.75431034482758619</v>
+      </c>
+      <c r="E67" s="25">
+        <v>0.60169491525423724</v>
+      </c>
+      <c r="F67" s="25">
+        <v>0.91228070175438591</v>
+      </c>
+      <c r="G67" s="25">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="H67" s="25"/>
+      <c r="I67" s="25">
+        <v>0.70967741935483875</v>
+      </c>
+      <c r="J67" s="25">
+        <v>0.58620689655172409</v>
+      </c>
+      <c r="K67" s="25">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="L67" s="25">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="M67" s="25">
+        <v>1</v>
+      </c>
+      <c r="N67" s="25">
+        <v>1</v>
+      </c>
+      <c r="O67" s="25">
+        <v>1</v>
+      </c>
+      <c r="P67" s="25">
+        <v>0.16666666666666666</v>
+      </c>
+      <c r="Q67" s="25">
+        <v>0.75</v>
+      </c>
+      <c r="R67" s="25">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="S67" s="25">
+        <v>0.375</v>
+      </c>
+      <c r="T67" s="25">
+        <v>0.75</v>
+      </c>
+      <c r="U67" s="25">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="V67" s="25">
+        <v>0.5625</v>
+      </c>
+      <c r="W67" s="25">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="X67" s="25">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="Y67" s="25">
+        <v>0.33333333333333331</v>
+      </c>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="25"/>
+      <c r="AB67" s="25">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="AC67" s="25">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AD67" s="25">
+        <v>1</v>
+      </c>
+      <c r="AE67" s="25">
+        <v>1</v>
+      </c>
+      <c r="AF67" s="25">
+        <v>1</v>
+      </c>
+      <c r="AG67" s="25">
+        <v>0.16666666666666666</v>
+      </c>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A68" s="27">
@@ -35301,36 +35463,90 @@
       <c r="C68" s="21">
         <v>14</v>
       </c>
-      <c r="D68" s="22"/>
-      <c r="E68" s="22"/>
-      <c r="F68" s="22"/>
-      <c r="G68" s="22"/>
-      <c r="H68" s="22"/>
-      <c r="I68" s="22"/>
-      <c r="J68" s="22"/>
-      <c r="K68" s="22"/>
-      <c r="L68" s="22"/>
-      <c r="M68" s="22"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="22"/>
-      <c r="P68" s="22"/>
-      <c r="Q68" s="22"/>
-      <c r="R68" s="22"/>
-      <c r="S68" s="22"/>
-      <c r="T68" s="22"/>
-      <c r="U68" s="22"/>
-      <c r="V68" s="22"/>
-      <c r="W68" s="22"/>
-      <c r="X68" s="22"/>
-      <c r="Y68" s="22"/>
-      <c r="Z68" s="22"/>
-      <c r="AA68" s="22"/>
-      <c r="AB68" s="22"/>
-      <c r="AC68" s="22"/>
-      <c r="AD68" s="22"/>
-      <c r="AE68" s="22"/>
-      <c r="AF68" s="22"/>
-      <c r="AG68" s="22"/>
+      <c r="D68" s="25">
+        <v>0.92195121951219516</v>
+      </c>
+      <c r="E68" s="25">
+        <v>0.86170212765957444</v>
+      </c>
+      <c r="F68" s="25">
+        <v>0.97297297297297303</v>
+      </c>
+      <c r="G68" s="25">
+        <v>0.65</v>
+      </c>
+      <c r="H68" s="25"/>
+      <c r="I68" s="25">
+        <v>0.95</v>
+      </c>
+      <c r="J68" s="25">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="K68" s="25">
+        <v>0.90322580645161288</v>
+      </c>
+      <c r="L68" s="25">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="M68" s="25">
+        <v>1</v>
+      </c>
+      <c r="N68" s="25">
+        <v>1</v>
+      </c>
+      <c r="O68" s="25">
+        <v>1</v>
+      </c>
+      <c r="P68" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q68" s="25">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="R68" s="25">
+        <v>1</v>
+      </c>
+      <c r="S68" s="25">
+        <v>1</v>
+      </c>
+      <c r="T68" s="25">
+        <v>0.8</v>
+      </c>
+      <c r="U68" s="25">
+        <v>0.625</v>
+      </c>
+      <c r="V68" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="W68" s="25">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="X68" s="25">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Y68" s="25">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="25"/>
+      <c r="AB68" s="25">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="AC68" s="25">
+        <v>0.875</v>
+      </c>
+      <c r="AD68" s="25">
+        <v>1</v>
+      </c>
+      <c r="AE68" s="25">
+        <v>1</v>
+      </c>
+      <c r="AF68" s="25">
+        <v>1</v>
+      </c>
+      <c r="AG68" s="25">
+        <v>1</v>
+      </c>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A69" s="27">

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -36914,32 +36914,32 @@
         <v>7</v>
       </c>
       <c r="C17" s="18">
-        <v>0.97867104183757181</v>
+        <v>0.89632352941176474</v>
       </c>
       <c r="D17" s="18">
-        <v>0.96290050590219223</v>
+        <v>0.84957020057306587</v>
       </c>
       <c r="E17" s="18">
-        <v>0.99361022364217255</v>
+        <v>0.94561933534743203</v>
       </c>
       <c r="F17" s="18">
-        <v>0.95081967213114749</v>
+        <v>0.79220779220779225</v>
       </c>
       <c r="G17" s="18"/>
       <c r="H17" s="18">
-        <v>0.93902439024390238</v>
+        <v>0.93181818181818177</v>
       </c>
       <c r="I17" s="18">
-        <v>0.97619047619047616</v>
+        <v>0.81290322580645158</v>
       </c>
       <c r="J17" s="18">
-        <v>0.98342541436464093</v>
+        <v>0.84976525821596249</v>
       </c>
       <c r="K17" s="18">
-        <v>1</v>
+        <v>0.81725888324873097</v>
       </c>
       <c r="L17" s="18">
-        <v>0.96296296296296291</v>
+        <v>1</v>
       </c>
       <c r="M17" s="18">
         <v>1</v>
@@ -36951,42 +36951,42 @@
         <v>1</v>
       </c>
       <c r="P17" s="18">
-        <v>0.96666666666666667</v>
+        <v>0.7407407407407407</v>
       </c>
       <c r="Q17" s="18">
-        <v>0.96</v>
+        <v>1</v>
       </c>
       <c r="R17" s="18">
-        <v>1</v>
+        <v>0.83809523809523812</v>
       </c>
       <c r="S17" s="18">
-        <v>1</v>
+        <v>0.8771929824561403</v>
       </c>
       <c r="T17" s="18">
-        <v>0.93548387096774188</v>
+        <v>0.84931506849315064</v>
       </c>
       <c r="U17" s="18">
-        <v>0.98461538461538467</v>
+        <v>0.85526315789473684</v>
       </c>
       <c r="V17" s="18">
-        <v>0.90625</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="W17" s="18">
-        <v>0.96721311475409832</v>
+        <v>0.77215189873417722</v>
       </c>
       <c r="X17" s="18">
-        <v>0.93023255813953487</v>
+        <v>0.84313725490196079</v>
       </c>
       <c r="Y17" s="18"/>
       <c r="Z17" s="18"/>
       <c r="AA17" s="18">
-        <v>1</v>
+        <v>0.87878787878787878</v>
       </c>
       <c r="AB17" s="18">
-        <v>1</v>
+        <v>0.75510204081632648</v>
       </c>
       <c r="AC17" s="18">
-        <v>0.96296296296296291</v>
+        <v>1</v>
       </c>
       <c r="AD17" s="18">
         <v>1</v>
@@ -37006,26 +37006,26 @@
         <v>8</v>
       </c>
       <c r="C18" s="18">
-        <v>0.97508896797153022</v>
+        <v>0.9183006535947712</v>
       </c>
       <c r="D18" s="18">
-        <v>0.95302013422818788</v>
+        <v>0.85632183908045978</v>
       </c>
       <c r="E18" s="18">
         <v>1</v>
       </c>
       <c r="F18" s="18">
-        <v>1</v>
+        <v>0.54545454545454541</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18">
-        <v>0.9</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="I18" s="18">
-        <v>0.94444444444444442</v>
+        <v>0.94736842105263153</v>
       </c>
       <c r="J18" s="18">
-        <v>0.97959183673469385</v>
+        <v>0.98</v>
       </c>
       <c r="K18" s="18">
         <v>1</v>
@@ -37043,28 +37043,28 @@
         <v>1</v>
       </c>
       <c r="P18" s="18">
-        <v>1</v>
+        <v>0.54166666666666663</v>
       </c>
       <c r="Q18" s="18">
-        <v>0.86956521739130432</v>
+        <v>1</v>
       </c>
       <c r="R18" s="18">
         <v>1</v>
       </c>
       <c r="S18" s="18">
-        <v>0.92307692307692313</v>
+        <v>0.9285714285714286</v>
       </c>
       <c r="T18" s="18">
-        <v>1</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="U18" s="18">
         <v>1</v>
       </c>
       <c r="V18" s="18">
-        <v>0.94117647058823528</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="W18" s="18">
-        <v>0.88235294117647056</v>
+        <v>0.89473684210526316</v>
       </c>
       <c r="X18" s="18">
         <v>1</v>

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -21,9 +21,10 @@
     <sheet name="5.0G" sheetId="15" r:id="rId7"/>
     <sheet name="5.0I" sheetId="17" r:id="rId8"/>
     <sheet name="5.0J" sheetId="18" r:id="rId9"/>
-    <sheet name="5.3A" sheetId="16" r:id="rId10"/>
-    <sheet name="5.3G" sheetId="19" r:id="rId11"/>
-    <sheet name="5.3H" sheetId="20" r:id="rId12"/>
+    <sheet name="5.2E" sheetId="21" r:id="rId10"/>
+    <sheet name="5.3A" sheetId="16" r:id="rId11"/>
+    <sheet name="5.3G" sheetId="19" r:id="rId12"/>
+    <sheet name="5.3H" sheetId="20" r:id="rId13"/>
   </sheets>
   <definedNames>
     <definedName name="__A313546">#N/A</definedName>
@@ -38,6 +39,7 @@
     <definedName name="__xlnm._FilterDatabase" localSheetId="9">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase" localSheetId="10">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase" localSheetId="11">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase" localSheetId="12">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="4">#REF!</definedName>
@@ -47,6 +49,7 @@
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="9">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="10">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1" localSheetId="11">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase_1" localSheetId="12">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_1">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="4">#REF!</definedName>
@@ -56,6 +59,7 @@
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="9">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="10">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3" localSheetId="11">#REF!</definedName>
+    <definedName name="__xlnm._FilterDatabase_3" localSheetId="12">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_3">#REF!</definedName>
     <definedName name="__xlnm._FilterDatabase_4">#N/A</definedName>
     <definedName name="__xlnm.Database">#N/A</definedName>
@@ -7904,6 +7908,7 @@
     <definedName name="UILUI" localSheetId="9">#REF!</definedName>
     <definedName name="UILUI" localSheetId="10">#REF!</definedName>
     <definedName name="UILUI" localSheetId="11">#REF!</definedName>
+    <definedName name="UILUI" localSheetId="12">#REF!</definedName>
     <definedName name="UILUI">#REF!</definedName>
     <definedName name="unnn">"#REF!"</definedName>
     <definedName name="unnn_1">"#REF!"</definedName>
@@ -7979,7 +7984,7 @@
     <definedName name="ZXBB_2">"#REF!"</definedName>
     <definedName name="ZXBB_3">"#REF!"</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -7989,7 +7994,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="50">
   <si>
     <t>Mes</t>
   </si>
@@ -8251,7 +8256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8329,6 +8334,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -10907,6 +10915,2391 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:AE37"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="31" width="20.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A1" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="G1" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="H1" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="I1" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="J1" s="11" t="s">
+        <v>27</v>
+      </c>
+      <c r="K1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="L1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="M1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="N1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="O1" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="P1" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="Q1" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="R1" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="S1" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="T1" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="U1" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="V1" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="W1" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="X1" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y1" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="Z1" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="AA1" s="11" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB1" s="11" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC1" s="11" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD1" s="11" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE1" s="11" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A2" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="29">
+        <v>17906</v>
+      </c>
+      <c r="D2" s="29">
+        <v>10660</v>
+      </c>
+      <c r="E2" s="29">
+        <v>7246</v>
+      </c>
+      <c r="F2" s="29">
+        <v>3341</v>
+      </c>
+      <c r="G2" s="29">
+        <v>463</v>
+      </c>
+      <c r="H2" s="29">
+        <v>1775</v>
+      </c>
+      <c r="I2" s="29">
+        <v>3290</v>
+      </c>
+      <c r="J2" s="29">
+        <v>1791</v>
+      </c>
+      <c r="K2" s="29">
+        <v>1258</v>
+      </c>
+      <c r="L2" s="29">
+        <v>1879</v>
+      </c>
+      <c r="M2" s="29">
+        <v>2548</v>
+      </c>
+      <c r="N2" s="29">
+        <v>1461</v>
+      </c>
+      <c r="O2" s="29">
+        <v>100</v>
+      </c>
+      <c r="P2" s="29">
+        <v>1467</v>
+      </c>
+      <c r="Q2" s="29">
+        <v>660</v>
+      </c>
+      <c r="R2" s="29">
+        <v>673</v>
+      </c>
+      <c r="S2" s="29">
+        <v>1851</v>
+      </c>
+      <c r="T2" s="29">
+        <v>1874</v>
+      </c>
+      <c r="U2" s="29">
+        <v>249</v>
+      </c>
+      <c r="V2" s="29">
+        <v>1115</v>
+      </c>
+      <c r="W2" s="29">
+        <v>1542</v>
+      </c>
+      <c r="X2" s="29">
+        <v>766</v>
+      </c>
+      <c r="Y2" s="29">
+        <v>84</v>
+      </c>
+      <c r="Z2" s="29">
+        <v>379</v>
+      </c>
+      <c r="AA2" s="29">
+        <v>1258</v>
+      </c>
+      <c r="AB2" s="29">
+        <v>1879</v>
+      </c>
+      <c r="AC2" s="29">
+        <v>2548</v>
+      </c>
+      <c r="AD2" s="29">
+        <v>1461</v>
+      </c>
+      <c r="AE2" s="29">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="3" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A3" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C3" s="29">
+        <v>17492</v>
+      </c>
+      <c r="D3" s="29">
+        <v>10423</v>
+      </c>
+      <c r="E3" s="29">
+        <v>7069</v>
+      </c>
+      <c r="F3" s="29">
+        <v>3115</v>
+      </c>
+      <c r="G3" s="29">
+        <v>493</v>
+      </c>
+      <c r="H3" s="29">
+        <v>1755</v>
+      </c>
+      <c r="I3" s="29">
+        <v>3249</v>
+      </c>
+      <c r="J3" s="29">
+        <v>1811</v>
+      </c>
+      <c r="K3" s="29">
+        <v>990</v>
+      </c>
+      <c r="L3" s="29">
+        <v>1947</v>
+      </c>
+      <c r="M3" s="29">
+        <v>2642</v>
+      </c>
+      <c r="N3" s="29">
+        <v>1440</v>
+      </c>
+      <c r="O3" s="29">
+        <v>50</v>
+      </c>
+      <c r="P3" s="29">
+        <v>1542</v>
+      </c>
+      <c r="Q3" s="29">
+        <v>665</v>
+      </c>
+      <c r="R3" s="29">
+        <v>631</v>
+      </c>
+      <c r="S3" s="29">
+        <v>1847</v>
+      </c>
+      <c r="T3" s="29">
+        <v>1573</v>
+      </c>
+      <c r="U3" s="29">
+        <v>247</v>
+      </c>
+      <c r="V3" s="29">
+        <v>1090</v>
+      </c>
+      <c r="W3" s="29">
+        <v>1564</v>
+      </c>
+      <c r="X3" s="29">
+        <v>771</v>
+      </c>
+      <c r="Y3" s="29">
+        <v>86</v>
+      </c>
+      <c r="Z3" s="29">
+        <v>407</v>
+      </c>
+      <c r="AA3" s="29">
+        <v>990</v>
+      </c>
+      <c r="AB3" s="29">
+        <v>1947</v>
+      </c>
+      <c r="AC3" s="29">
+        <v>2642</v>
+      </c>
+      <c r="AD3" s="29">
+        <v>1440</v>
+      </c>
+      <c r="AE3" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A4" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C4" s="29">
+        <v>15756</v>
+      </c>
+      <c r="D4" s="29">
+        <v>9048</v>
+      </c>
+      <c r="E4" s="29">
+        <v>6708</v>
+      </c>
+      <c r="F4" s="29">
+        <v>2331</v>
+      </c>
+      <c r="G4" s="29">
+        <v>484</v>
+      </c>
+      <c r="H4" s="29">
+        <v>1492</v>
+      </c>
+      <c r="I4" s="29">
+        <v>2934</v>
+      </c>
+      <c r="J4" s="29">
+        <v>1807</v>
+      </c>
+      <c r="K4" s="29">
+        <v>973</v>
+      </c>
+      <c r="L4" s="29">
+        <v>1551</v>
+      </c>
+      <c r="M4" s="29">
+        <v>2781</v>
+      </c>
+      <c r="N4" s="29">
+        <v>1344</v>
+      </c>
+      <c r="O4" s="29">
+        <v>59</v>
+      </c>
+      <c r="P4" s="29">
+        <v>1041</v>
+      </c>
+      <c r="Q4" s="29">
+        <v>592</v>
+      </c>
+      <c r="R4" s="29">
+        <v>654</v>
+      </c>
+      <c r="S4" s="29">
+        <v>1590</v>
+      </c>
+      <c r="T4" s="29">
+        <v>1290</v>
+      </c>
+      <c r="U4" s="29">
+        <v>284</v>
+      </c>
+      <c r="V4" s="29">
+        <v>900</v>
+      </c>
+      <c r="W4" s="29">
+        <v>1523</v>
+      </c>
+      <c r="X4" s="29">
+        <v>690</v>
+      </c>
+      <c r="Y4" s="29">
+        <v>74</v>
+      </c>
+      <c r="Z4" s="29">
+        <v>410</v>
+      </c>
+      <c r="AA4" s="29">
+        <v>973</v>
+      </c>
+      <c r="AB4" s="29">
+        <v>1551</v>
+      </c>
+      <c r="AC4" s="29">
+        <v>2781</v>
+      </c>
+      <c r="AD4" s="29">
+        <v>1344</v>
+      </c>
+      <c r="AE4" s="29">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" s="29">
+        <v>14511</v>
+      </c>
+      <c r="D5" s="29">
+        <v>8819</v>
+      </c>
+      <c r="E5" s="29">
+        <v>5692</v>
+      </c>
+      <c r="F5" s="29">
+        <v>2109</v>
+      </c>
+      <c r="G5" s="29">
+        <v>594</v>
+      </c>
+      <c r="H5" s="29">
+        <v>1537</v>
+      </c>
+      <c r="I5" s="29">
+        <v>2867</v>
+      </c>
+      <c r="J5" s="29">
+        <v>1712</v>
+      </c>
+      <c r="K5" s="29">
+        <v>806</v>
+      </c>
+      <c r="L5" s="29">
+        <v>798</v>
+      </c>
+      <c r="M5" s="29">
+        <v>2578</v>
+      </c>
+      <c r="N5" s="29">
+        <v>1429</v>
+      </c>
+      <c r="O5" s="29">
+        <v>81</v>
+      </c>
+      <c r="P5" s="29">
+        <v>781</v>
+      </c>
+      <c r="Q5" s="29">
+        <v>611</v>
+      </c>
+      <c r="R5" s="29">
+        <v>548</v>
+      </c>
+      <c r="S5" s="29">
+        <v>1606</v>
+      </c>
+      <c r="T5" s="29">
+        <v>1328</v>
+      </c>
+      <c r="U5" s="29">
+        <v>886</v>
+      </c>
+      <c r="V5" s="29">
+        <v>926</v>
+      </c>
+      <c r="W5" s="29">
+        <v>826</v>
+      </c>
+      <c r="X5" s="29">
+        <v>713</v>
+      </c>
+      <c r="Y5" s="29">
+        <v>163</v>
+      </c>
+      <c r="Z5" s="29">
+        <v>431</v>
+      </c>
+      <c r="AA5" s="29">
+        <v>806</v>
+      </c>
+      <c r="AB5" s="29">
+        <v>798</v>
+      </c>
+      <c r="AC5" s="29">
+        <v>2578</v>
+      </c>
+      <c r="AD5" s="29">
+        <v>1429</v>
+      </c>
+      <c r="AE5" s="29">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="6" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A6" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="29">
+        <v>16424</v>
+      </c>
+      <c r="D6" s="29">
+        <v>9262</v>
+      </c>
+      <c r="E6" s="29">
+        <v>7162</v>
+      </c>
+      <c r="F6" s="29">
+        <v>2347</v>
+      </c>
+      <c r="G6" s="29">
+        <v>582</v>
+      </c>
+      <c r="H6" s="29">
+        <v>1419</v>
+      </c>
+      <c r="I6" s="29">
+        <v>2738</v>
+      </c>
+      <c r="J6" s="29">
+        <v>2176</v>
+      </c>
+      <c r="K6" s="29">
+        <v>1322</v>
+      </c>
+      <c r="L6" s="29">
+        <v>1856</v>
+      </c>
+      <c r="M6" s="29">
+        <v>2440</v>
+      </c>
+      <c r="N6" s="29">
+        <v>1510</v>
+      </c>
+      <c r="O6" s="29">
+        <v>34</v>
+      </c>
+      <c r="P6" s="29">
+        <v>838</v>
+      </c>
+      <c r="Q6" s="29">
+        <v>532</v>
+      </c>
+      <c r="R6" s="29">
+        <v>668</v>
+      </c>
+      <c r="S6" s="29">
+        <v>1325</v>
+      </c>
+      <c r="T6" s="29">
+        <v>1509</v>
+      </c>
+      <c r="U6" s="29">
+        <v>328</v>
+      </c>
+      <c r="V6" s="29">
+        <v>887</v>
+      </c>
+      <c r="W6" s="29">
+        <v>1848</v>
+      </c>
+      <c r="X6" s="29">
+        <v>745</v>
+      </c>
+      <c r="Y6" s="29">
+        <v>56</v>
+      </c>
+      <c r="Z6" s="29">
+        <v>526</v>
+      </c>
+      <c r="AA6" s="29">
+        <v>1322</v>
+      </c>
+      <c r="AB6" s="29">
+        <v>1856</v>
+      </c>
+      <c r="AC6" s="29">
+        <v>2440</v>
+      </c>
+      <c r="AD6" s="29">
+        <v>1510</v>
+      </c>
+      <c r="AE6" s="29">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A7" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="29">
+        <v>17314</v>
+      </c>
+      <c r="D7" s="29">
+        <v>10167</v>
+      </c>
+      <c r="E7" s="29">
+        <v>7147</v>
+      </c>
+      <c r="F7" s="29">
+        <v>2848</v>
+      </c>
+      <c r="G7" s="29">
+        <v>557</v>
+      </c>
+      <c r="H7" s="29">
+        <v>1457</v>
+      </c>
+      <c r="I7" s="29">
+        <v>2961</v>
+      </c>
+      <c r="J7" s="29">
+        <v>2344</v>
+      </c>
+      <c r="K7" s="29">
+        <v>1517</v>
+      </c>
+      <c r="L7" s="29">
+        <v>1997</v>
+      </c>
+      <c r="M7" s="29">
+        <v>2177</v>
+      </c>
+      <c r="N7" s="29">
+        <v>1406</v>
+      </c>
+      <c r="O7" s="29">
+        <v>50</v>
+      </c>
+      <c r="P7" s="29">
+        <v>1062</v>
+      </c>
+      <c r="Q7" s="29">
+        <v>470</v>
+      </c>
+      <c r="R7" s="29">
+        <v>685</v>
+      </c>
+      <c r="S7" s="29">
+        <v>1519</v>
+      </c>
+      <c r="T7" s="29">
+        <v>1786</v>
+      </c>
+      <c r="U7" s="29">
+        <v>366</v>
+      </c>
+      <c r="V7" s="29">
+        <v>987</v>
+      </c>
+      <c r="W7" s="29">
+        <v>1978</v>
+      </c>
+      <c r="X7" s="29">
+        <v>757</v>
+      </c>
+      <c r="Y7" s="29"/>
+      <c r="Z7" s="29">
+        <v>557</v>
+      </c>
+      <c r="AA7" s="29">
+        <v>1517</v>
+      </c>
+      <c r="AB7" s="29">
+        <v>1997</v>
+      </c>
+      <c r="AC7" s="29">
+        <v>2177</v>
+      </c>
+      <c r="AD7" s="29">
+        <v>1406</v>
+      </c>
+      <c r="AE7" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A8" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C8" s="29">
+        <v>22450</v>
+      </c>
+      <c r="D8" s="29">
+        <v>12518</v>
+      </c>
+      <c r="E8" s="29">
+        <v>9932</v>
+      </c>
+      <c r="F8" s="29">
+        <v>3654</v>
+      </c>
+      <c r="G8" s="29">
+        <v>2</v>
+      </c>
+      <c r="H8" s="29">
+        <v>1935</v>
+      </c>
+      <c r="I8" s="29">
+        <v>3859</v>
+      </c>
+      <c r="J8" s="29">
+        <v>3068</v>
+      </c>
+      <c r="K8" s="29">
+        <v>2476</v>
+      </c>
+      <c r="L8" s="29">
+        <v>2617</v>
+      </c>
+      <c r="M8" s="29">
+        <v>2480</v>
+      </c>
+      <c r="N8" s="29">
+        <v>1983</v>
+      </c>
+      <c r="O8" s="29">
+        <v>376</v>
+      </c>
+      <c r="P8" s="29">
+        <v>1479</v>
+      </c>
+      <c r="Q8" s="29">
+        <v>862</v>
+      </c>
+      <c r="R8" s="29">
+        <v>1284</v>
+      </c>
+      <c r="S8" s="29">
+        <v>1788</v>
+      </c>
+      <c r="T8" s="29">
+        <v>2175</v>
+      </c>
+      <c r="U8" s="29">
+        <v>572</v>
+      </c>
+      <c r="V8" s="29">
+        <v>1073</v>
+      </c>
+      <c r="W8" s="29">
+        <v>2496</v>
+      </c>
+      <c r="X8" s="29">
+        <v>787</v>
+      </c>
+      <c r="Y8" s="29">
+        <v>2</v>
+      </c>
+      <c r="Z8" s="29"/>
+      <c r="AA8" s="29">
+        <v>2476</v>
+      </c>
+      <c r="AB8" s="29">
+        <v>2617</v>
+      </c>
+      <c r="AC8" s="29">
+        <v>2480</v>
+      </c>
+      <c r="AD8" s="29">
+        <v>1983</v>
+      </c>
+      <c r="AE8" s="29">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="9" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A9" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="29">
+        <v>23069</v>
+      </c>
+      <c r="D9" s="29">
+        <v>13651</v>
+      </c>
+      <c r="E9" s="29">
+        <v>9418</v>
+      </c>
+      <c r="F9" s="29">
+        <v>4075</v>
+      </c>
+      <c r="G9" s="29">
+        <v>0</v>
+      </c>
+      <c r="H9" s="29">
+        <v>1942</v>
+      </c>
+      <c r="I9" s="29">
+        <v>4165</v>
+      </c>
+      <c r="J9" s="29">
+        <v>3469</v>
+      </c>
+      <c r="K9" s="29">
+        <v>2036</v>
+      </c>
+      <c r="L9" s="29">
+        <v>3106</v>
+      </c>
+      <c r="M9" s="29">
+        <v>2194</v>
+      </c>
+      <c r="N9" s="29">
+        <v>1843</v>
+      </c>
+      <c r="O9" s="29">
+        <v>239</v>
+      </c>
+      <c r="P9" s="29">
+        <v>1601</v>
+      </c>
+      <c r="Q9" s="29">
+        <v>907</v>
+      </c>
+      <c r="R9" s="29">
+        <v>1361</v>
+      </c>
+      <c r="S9" s="29">
+        <v>1942</v>
+      </c>
+      <c r="T9" s="29">
+        <v>2474</v>
+      </c>
+      <c r="U9" s="29">
+        <v>667</v>
+      </c>
+      <c r="V9" s="29">
+        <v>1035</v>
+      </c>
+      <c r="W9" s="29">
+        <v>2802</v>
+      </c>
+      <c r="X9" s="29">
+        <v>862</v>
+      </c>
+      <c r="Y9" s="29"/>
+      <c r="Z9" s="29"/>
+      <c r="AA9" s="29">
+        <v>2036</v>
+      </c>
+      <c r="AB9" s="29">
+        <v>3106</v>
+      </c>
+      <c r="AC9" s="29">
+        <v>2194</v>
+      </c>
+      <c r="AD9" s="29">
+        <v>1843</v>
+      </c>
+      <c r="AE9" s="29">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="10" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A10" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B10" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10" s="29">
+        <v>29199</v>
+      </c>
+      <c r="D10" s="29">
+        <v>16059</v>
+      </c>
+      <c r="E10" s="29">
+        <v>13140</v>
+      </c>
+      <c r="F10" s="29">
+        <v>4905</v>
+      </c>
+      <c r="G10" s="29">
+        <v>2</v>
+      </c>
+      <c r="H10" s="29">
+        <v>2531</v>
+      </c>
+      <c r="I10" s="29">
+        <v>4551</v>
+      </c>
+      <c r="J10" s="29">
+        <v>4070</v>
+      </c>
+      <c r="K10" s="29">
+        <v>3447</v>
+      </c>
+      <c r="L10" s="29">
+        <v>4074</v>
+      </c>
+      <c r="M10" s="29">
+        <v>3000</v>
+      </c>
+      <c r="N10" s="29">
+        <v>2145</v>
+      </c>
+      <c r="O10" s="29">
+        <v>474</v>
+      </c>
+      <c r="P10" s="29">
+        <v>1769</v>
+      </c>
+      <c r="Q10" s="29">
+        <v>1243</v>
+      </c>
+      <c r="R10" s="29">
+        <v>1450</v>
+      </c>
+      <c r="S10" s="29">
+        <v>2178</v>
+      </c>
+      <c r="T10" s="29">
+        <v>3136</v>
+      </c>
+      <c r="U10" s="29">
+        <v>771</v>
+      </c>
+      <c r="V10" s="29">
+        <v>1288</v>
+      </c>
+      <c r="W10" s="29">
+        <v>3299</v>
+      </c>
+      <c r="X10" s="29">
+        <v>923</v>
+      </c>
+      <c r="Y10" s="29">
+        <v>2</v>
+      </c>
+      <c r="Z10" s="29"/>
+      <c r="AA10" s="29">
+        <v>3447</v>
+      </c>
+      <c r="AB10" s="29">
+        <v>4074</v>
+      </c>
+      <c r="AC10" s="29">
+        <v>3000</v>
+      </c>
+      <c r="AD10" s="29">
+        <v>2145</v>
+      </c>
+      <c r="AE10" s="29">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="11" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A11" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C11" s="29">
+        <v>36000</v>
+      </c>
+      <c r="D11" s="29">
+        <v>19513</v>
+      </c>
+      <c r="E11" s="29">
+        <v>16487</v>
+      </c>
+      <c r="F11" s="29">
+        <v>5346</v>
+      </c>
+      <c r="G11" s="29">
+        <v>0</v>
+      </c>
+      <c r="H11" s="29">
+        <v>3262</v>
+      </c>
+      <c r="I11" s="29">
+        <v>5948</v>
+      </c>
+      <c r="J11" s="29">
+        <v>4957</v>
+      </c>
+      <c r="K11" s="29">
+        <v>4029</v>
+      </c>
+      <c r="L11" s="29">
+        <v>4945</v>
+      </c>
+      <c r="M11" s="29">
+        <v>3543</v>
+      </c>
+      <c r="N11" s="29">
+        <v>3285</v>
+      </c>
+      <c r="O11" s="29">
+        <v>685</v>
+      </c>
+      <c r="P11" s="29">
+        <v>1940</v>
+      </c>
+      <c r="Q11" s="29">
+        <v>1457</v>
+      </c>
+      <c r="R11" s="29">
+        <v>1678</v>
+      </c>
+      <c r="S11" s="29">
+        <v>3014</v>
+      </c>
+      <c r="T11" s="29">
+        <v>3406</v>
+      </c>
+      <c r="U11" s="29">
+        <v>939</v>
+      </c>
+      <c r="V11" s="29">
+        <v>1805</v>
+      </c>
+      <c r="W11" s="29">
+        <v>4018</v>
+      </c>
+      <c r="X11" s="29">
+        <v>1256</v>
+      </c>
+      <c r="Y11" s="29"/>
+      <c r="Z11" s="29"/>
+      <c r="AA11" s="29">
+        <v>4029</v>
+      </c>
+      <c r="AB11" s="29">
+        <v>4945</v>
+      </c>
+      <c r="AC11" s="29">
+        <v>3543</v>
+      </c>
+      <c r="AD11" s="29">
+        <v>3285</v>
+      </c>
+      <c r="AE11" s="29">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="12" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A12" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B12" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C12" s="29">
+        <v>38011</v>
+      </c>
+      <c r="D12" s="29">
+        <v>21294</v>
+      </c>
+      <c r="E12" s="29">
+        <v>16717</v>
+      </c>
+      <c r="F12" s="29">
+        <v>5661</v>
+      </c>
+      <c r="G12" s="29">
+        <v>0</v>
+      </c>
+      <c r="H12" s="29">
+        <v>3339</v>
+      </c>
+      <c r="I12" s="29">
+        <v>6840</v>
+      </c>
+      <c r="J12" s="29">
+        <v>5454</v>
+      </c>
+      <c r="K12" s="29">
+        <v>4254</v>
+      </c>
+      <c r="L12" s="29">
+        <v>4526</v>
+      </c>
+      <c r="M12" s="29">
+        <v>3550</v>
+      </c>
+      <c r="N12" s="29">
+        <v>3619</v>
+      </c>
+      <c r="O12" s="29">
+        <v>768</v>
+      </c>
+      <c r="P12" s="29">
+        <v>2191</v>
+      </c>
+      <c r="Q12" s="29">
+        <v>1370</v>
+      </c>
+      <c r="R12" s="29">
+        <v>1703</v>
+      </c>
+      <c r="S12" s="29">
+        <v>3618</v>
+      </c>
+      <c r="T12" s="29">
+        <v>3470</v>
+      </c>
+      <c r="U12" s="29">
+        <v>1257</v>
+      </c>
+      <c r="V12" s="29">
+        <v>1969</v>
+      </c>
+      <c r="W12" s="29">
+        <v>4197</v>
+      </c>
+      <c r="X12" s="29">
+        <v>1519</v>
+      </c>
+      <c r="Y12" s="29"/>
+      <c r="Z12" s="29"/>
+      <c r="AA12" s="29">
+        <v>4254</v>
+      </c>
+      <c r="AB12" s="29">
+        <v>4526</v>
+      </c>
+      <c r="AC12" s="29">
+        <v>3550</v>
+      </c>
+      <c r="AD12" s="29">
+        <v>3619</v>
+      </c>
+      <c r="AE12" s="29">
+        <v>768</v>
+      </c>
+    </row>
+    <row r="13" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>2025</v>
+      </c>
+      <c r="B13" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="29">
+        <v>48592</v>
+      </c>
+      <c r="D13" s="29">
+        <v>25831</v>
+      </c>
+      <c r="E13" s="29">
+        <v>22761</v>
+      </c>
+      <c r="F13" s="29">
+        <v>6539</v>
+      </c>
+      <c r="G13" s="29">
+        <v>0</v>
+      </c>
+      <c r="H13" s="29">
+        <v>4296</v>
+      </c>
+      <c r="I13" s="29">
+        <v>8318</v>
+      </c>
+      <c r="J13" s="29">
+        <v>6678</v>
+      </c>
+      <c r="K13" s="29">
+        <v>4652</v>
+      </c>
+      <c r="L13" s="29">
+        <v>6338</v>
+      </c>
+      <c r="M13" s="29">
+        <v>5963</v>
+      </c>
+      <c r="N13" s="29">
+        <v>4665</v>
+      </c>
+      <c r="O13" s="29">
+        <v>1143</v>
+      </c>
+      <c r="P13" s="29">
+        <v>2411</v>
+      </c>
+      <c r="Q13" s="29">
+        <v>1701</v>
+      </c>
+      <c r="R13" s="29">
+        <v>1480</v>
+      </c>
+      <c r="S13" s="29">
+        <v>4779</v>
+      </c>
+      <c r="T13" s="29">
+        <v>4128</v>
+      </c>
+      <c r="U13" s="29">
+        <v>1735</v>
+      </c>
+      <c r="V13" s="29">
+        <v>2595</v>
+      </c>
+      <c r="W13" s="29">
+        <v>4943</v>
+      </c>
+      <c r="X13" s="29">
+        <v>2059</v>
+      </c>
+      <c r="Y13" s="29"/>
+      <c r="Z13" s="29"/>
+      <c r="AA13" s="29">
+        <v>4652</v>
+      </c>
+      <c r="AB13" s="29">
+        <v>6338</v>
+      </c>
+      <c r="AC13" s="29">
+        <v>5963</v>
+      </c>
+      <c r="AD13" s="29">
+        <v>4665</v>
+      </c>
+      <c r="AE13" s="29">
+        <v>1143</v>
+      </c>
+    </row>
+    <row r="14" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A14" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B14" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C14" s="29">
+        <v>54991</v>
+      </c>
+      <c r="D14" s="29">
+        <v>30330</v>
+      </c>
+      <c r="E14" s="29">
+        <v>24661</v>
+      </c>
+      <c r="F14" s="29">
+        <v>7435</v>
+      </c>
+      <c r="G14" s="29">
+        <v>0</v>
+      </c>
+      <c r="H14" s="29">
+        <v>5629</v>
+      </c>
+      <c r="I14" s="29">
+        <v>9530</v>
+      </c>
+      <c r="J14" s="29">
+        <v>7736</v>
+      </c>
+      <c r="K14" s="29">
+        <v>5697</v>
+      </c>
+      <c r="L14" s="29">
+        <v>6673</v>
+      </c>
+      <c r="M14" s="29">
+        <v>6067</v>
+      </c>
+      <c r="N14" s="29">
+        <v>5141</v>
+      </c>
+      <c r="O14" s="29">
+        <v>1083</v>
+      </c>
+      <c r="P14" s="29">
+        <v>2829</v>
+      </c>
+      <c r="Q14" s="29">
+        <v>2213</v>
+      </c>
+      <c r="R14" s="29">
+        <v>2316</v>
+      </c>
+      <c r="S14" s="29">
+        <v>5053</v>
+      </c>
+      <c r="T14" s="29">
+        <v>4606</v>
+      </c>
+      <c r="U14" s="29">
+        <v>2223</v>
+      </c>
+      <c r="V14" s="29">
+        <v>3416</v>
+      </c>
+      <c r="W14" s="29">
+        <v>5513</v>
+      </c>
+      <c r="X14" s="29">
+        <v>2161</v>
+      </c>
+      <c r="Y14" s="29"/>
+      <c r="Z14" s="29"/>
+      <c r="AA14" s="29">
+        <v>5697</v>
+      </c>
+      <c r="AB14" s="29">
+        <v>6673</v>
+      </c>
+      <c r="AC14" s="29">
+        <v>6067</v>
+      </c>
+      <c r="AD14" s="29">
+        <v>5141</v>
+      </c>
+      <c r="AE14" s="29">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="15" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A15" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B15" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C15" s="29">
+        <v>58226</v>
+      </c>
+      <c r="D15" s="29">
+        <v>32787</v>
+      </c>
+      <c r="E15" s="29">
+        <v>25439</v>
+      </c>
+      <c r="F15" s="29">
+        <v>8123</v>
+      </c>
+      <c r="G15" s="29">
+        <v>0</v>
+      </c>
+      <c r="H15" s="29">
+        <v>6139</v>
+      </c>
+      <c r="I15" s="29">
+        <v>10178</v>
+      </c>
+      <c r="J15" s="29">
+        <v>8347</v>
+      </c>
+      <c r="K15" s="29">
+        <v>6217</v>
+      </c>
+      <c r="L15" s="29">
+        <v>6806</v>
+      </c>
+      <c r="M15" s="29">
+        <v>5995</v>
+      </c>
+      <c r="N15" s="29">
+        <v>5346</v>
+      </c>
+      <c r="O15" s="29">
+        <v>1075</v>
+      </c>
+      <c r="P15" s="29">
+        <v>3053</v>
+      </c>
+      <c r="Q15" s="29">
+        <v>2140</v>
+      </c>
+      <c r="R15" s="29">
+        <v>2555</v>
+      </c>
+      <c r="S15" s="29">
+        <v>5356</v>
+      </c>
+      <c r="T15" s="29">
+        <v>5070</v>
+      </c>
+      <c r="U15" s="29">
+        <v>2718</v>
+      </c>
+      <c r="V15" s="29">
+        <v>3999</v>
+      </c>
+      <c r="W15" s="29">
+        <v>5629</v>
+      </c>
+      <c r="X15" s="29">
+        <v>2267</v>
+      </c>
+      <c r="Y15" s="29"/>
+      <c r="Z15" s="29"/>
+      <c r="AA15" s="29">
+        <v>6217</v>
+      </c>
+      <c r="AB15" s="29">
+        <v>6806</v>
+      </c>
+      <c r="AC15" s="29">
+        <v>5995</v>
+      </c>
+      <c r="AD15" s="29">
+        <v>5346</v>
+      </c>
+      <c r="AE15" s="29">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="16" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A16" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C16" s="29">
+        <v>60922</v>
+      </c>
+      <c r="D16" s="29">
+        <v>35623</v>
+      </c>
+      <c r="E16" s="29">
+        <v>25299</v>
+      </c>
+      <c r="F16" s="29">
+        <v>8870</v>
+      </c>
+      <c r="G16" s="29">
+        <v>0</v>
+      </c>
+      <c r="H16" s="29">
+        <v>6570</v>
+      </c>
+      <c r="I16" s="29">
+        <v>11201</v>
+      </c>
+      <c r="J16" s="29">
+        <v>8982</v>
+      </c>
+      <c r="K16" s="29">
+        <v>6150</v>
+      </c>
+      <c r="L16" s="29">
+        <v>7198</v>
+      </c>
+      <c r="M16" s="29">
+        <v>5803</v>
+      </c>
+      <c r="N16" s="29">
+        <v>5012</v>
+      </c>
+      <c r="O16" s="29">
+        <v>1136</v>
+      </c>
+      <c r="P16" s="29">
+        <v>3412</v>
+      </c>
+      <c r="Q16" s="29">
+        <v>2073</v>
+      </c>
+      <c r="R16" s="29">
+        <v>2928</v>
+      </c>
+      <c r="S16" s="29">
+        <v>5803</v>
+      </c>
+      <c r="T16" s="29">
+        <v>5458</v>
+      </c>
+      <c r="U16" s="29">
+        <v>3247</v>
+      </c>
+      <c r="V16" s="29">
+        <v>4497</v>
+      </c>
+      <c r="W16" s="29">
+        <v>5735</v>
+      </c>
+      <c r="X16" s="29">
+        <v>2470</v>
+      </c>
+      <c r="Y16" s="29"/>
+      <c r="Z16" s="29"/>
+      <c r="AA16" s="29">
+        <v>6150</v>
+      </c>
+      <c r="AB16" s="29">
+        <v>7198</v>
+      </c>
+      <c r="AC16" s="29">
+        <v>5803</v>
+      </c>
+      <c r="AD16" s="29">
+        <v>5012</v>
+      </c>
+      <c r="AE16" s="29">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="17" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C17" s="29">
+        <v>19927</v>
+      </c>
+      <c r="D17" s="29">
+        <v>14877</v>
+      </c>
+      <c r="E17" s="29">
+        <v>5050</v>
+      </c>
+      <c r="F17" s="29">
+        <v>3514</v>
+      </c>
+      <c r="G17" s="29">
+        <v>0</v>
+      </c>
+      <c r="H17" s="29">
+        <v>3690</v>
+      </c>
+      <c r="I17" s="29">
+        <v>4210</v>
+      </c>
+      <c r="J17" s="29">
+        <v>3463</v>
+      </c>
+      <c r="K17" s="29">
+        <v>1616</v>
+      </c>
+      <c r="L17" s="29">
+        <v>1070</v>
+      </c>
+      <c r="M17" s="29">
+        <v>1072</v>
+      </c>
+      <c r="N17" s="29">
+        <v>1132</v>
+      </c>
+      <c r="O17" s="29">
+        <v>160</v>
+      </c>
+      <c r="P17" s="29">
+        <v>1262</v>
+      </c>
+      <c r="Q17" s="29">
+        <v>1374</v>
+      </c>
+      <c r="R17" s="29">
+        <v>1298</v>
+      </c>
+      <c r="S17" s="29">
+        <v>2009</v>
+      </c>
+      <c r="T17" s="29">
+        <v>2252</v>
+      </c>
+      <c r="U17" s="29">
+        <v>571</v>
+      </c>
+      <c r="V17" s="29">
+        <v>2316</v>
+      </c>
+      <c r="W17" s="29">
+        <v>2892</v>
+      </c>
+      <c r="X17" s="29">
+        <v>903</v>
+      </c>
+      <c r="Y17" s="29"/>
+      <c r="Z17" s="29"/>
+      <c r="AA17" s="29">
+        <v>1616</v>
+      </c>
+      <c r="AB17" s="29">
+        <v>1070</v>
+      </c>
+      <c r="AC17" s="29">
+        <v>1072</v>
+      </c>
+      <c r="AD17" s="29">
+        <v>1132</v>
+      </c>
+      <c r="AE17" s="29">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="18" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A18" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B18" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C18" s="29">
+        <v>34896</v>
+      </c>
+      <c r="D18" s="29">
+        <v>23288</v>
+      </c>
+      <c r="E18" s="29">
+        <v>11608</v>
+      </c>
+      <c r="F18" s="29">
+        <v>5379</v>
+      </c>
+      <c r="G18" s="29">
+        <v>0</v>
+      </c>
+      <c r="H18" s="29">
+        <v>5531</v>
+      </c>
+      <c r="I18" s="29">
+        <v>6754</v>
+      </c>
+      <c r="J18" s="29">
+        <v>5624</v>
+      </c>
+      <c r="K18" s="29">
+        <v>2879</v>
+      </c>
+      <c r="L18" s="29">
+        <v>2117</v>
+      </c>
+      <c r="M18" s="29">
+        <v>2781</v>
+      </c>
+      <c r="N18" s="29">
+        <v>3261</v>
+      </c>
+      <c r="O18" s="29">
+        <v>570</v>
+      </c>
+      <c r="P18" s="29">
+        <v>1980</v>
+      </c>
+      <c r="Q18" s="29">
+        <v>1846</v>
+      </c>
+      <c r="R18" s="29">
+        <v>1923</v>
+      </c>
+      <c r="S18" s="29">
+        <v>3447</v>
+      </c>
+      <c r="T18" s="29">
+        <v>3399</v>
+      </c>
+      <c r="U18" s="29">
+        <v>163</v>
+      </c>
+      <c r="V18" s="29">
+        <v>3685</v>
+      </c>
+      <c r="W18" s="29">
+        <v>5461</v>
+      </c>
+      <c r="X18" s="29">
+        <v>1384</v>
+      </c>
+      <c r="Y18" s="29"/>
+      <c r="Z18" s="29"/>
+      <c r="AA18" s="29">
+        <v>2879</v>
+      </c>
+      <c r="AB18" s="29">
+        <v>2117</v>
+      </c>
+      <c r="AC18" s="29">
+        <v>2781</v>
+      </c>
+      <c r="AD18" s="29">
+        <v>3261</v>
+      </c>
+      <c r="AE18" s="29">
+        <v>570</v>
+      </c>
+    </row>
+    <row r="19" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B19" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="12"/>
+      <c r="E19" s="12"/>
+      <c r="F19" s="12"/>
+      <c r="G19" s="12"/>
+      <c r="H19" s="12"/>
+      <c r="I19" s="12"/>
+      <c r="J19" s="12"/>
+      <c r="K19" s="12"/>
+      <c r="L19" s="12"/>
+      <c r="M19" s="12"/>
+      <c r="N19" s="12"/>
+      <c r="O19" s="12"/>
+      <c r="P19" s="12"/>
+      <c r="Q19" s="12"/>
+      <c r="R19" s="12"/>
+      <c r="S19" s="12"/>
+      <c r="T19" s="12"/>
+      <c r="U19" s="12"/>
+      <c r="V19" s="12"/>
+      <c r="W19" s="12"/>
+      <c r="X19" s="12"/>
+      <c r="Y19" s="12"/>
+      <c r="Z19" s="12"/>
+      <c r="AA19" s="12"/>
+      <c r="AB19" s="12"/>
+      <c r="AC19" s="12"/>
+      <c r="AD19" s="12"/>
+      <c r="AE19" s="12"/>
+    </row>
+    <row r="20" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A20" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B20" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="12"/>
+      <c r="D20" s="12"/>
+      <c r="E20" s="12"/>
+      <c r="F20" s="12"/>
+      <c r="G20" s="12"/>
+      <c r="H20" s="12"/>
+      <c r="I20" s="12"/>
+      <c r="J20" s="12"/>
+      <c r="K20" s="12"/>
+      <c r="L20" s="12"/>
+      <c r="M20" s="12"/>
+      <c r="N20" s="12"/>
+      <c r="O20" s="12"/>
+      <c r="P20" s="12"/>
+      <c r="Q20" s="12"/>
+      <c r="R20" s="12"/>
+      <c r="S20" s="12"/>
+      <c r="T20" s="12"/>
+      <c r="U20" s="12"/>
+      <c r="V20" s="12"/>
+      <c r="W20" s="12"/>
+      <c r="X20" s="12"/>
+      <c r="Y20" s="12"/>
+      <c r="Z20" s="12"/>
+      <c r="AA20" s="12"/>
+      <c r="AB20" s="12"/>
+      <c r="AC20" s="12"/>
+      <c r="AD20" s="12"/>
+      <c r="AE20" s="12"/>
+    </row>
+    <row r="21" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="12"/>
+      <c r="D21" s="12"/>
+      <c r="E21" s="12"/>
+      <c r="F21" s="12"/>
+      <c r="G21" s="12"/>
+      <c r="H21" s="12"/>
+      <c r="I21" s="12"/>
+      <c r="J21" s="12"/>
+      <c r="K21" s="12"/>
+      <c r="L21" s="12"/>
+      <c r="M21" s="12"/>
+      <c r="N21" s="12"/>
+      <c r="O21" s="12"/>
+      <c r="P21" s="12"/>
+      <c r="Q21" s="12"/>
+      <c r="R21" s="12"/>
+      <c r="S21" s="12"/>
+      <c r="T21" s="12"/>
+      <c r="U21" s="12"/>
+      <c r="V21" s="12"/>
+      <c r="W21" s="12"/>
+      <c r="X21" s="12"/>
+      <c r="Y21" s="12"/>
+      <c r="Z21" s="12"/>
+      <c r="AA21" s="12"/>
+      <c r="AB21" s="12"/>
+      <c r="AC21" s="12"/>
+      <c r="AD21" s="12"/>
+      <c r="AE21" s="12"/>
+    </row>
+    <row r="22" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A22" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B22" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C22" s="12"/>
+      <c r="D22" s="12"/>
+      <c r="E22" s="12"/>
+      <c r="F22" s="12"/>
+      <c r="G22" s="12"/>
+      <c r="H22" s="12"/>
+      <c r="I22" s="12"/>
+      <c r="J22" s="12"/>
+      <c r="K22" s="12"/>
+      <c r="L22" s="12"/>
+      <c r="M22" s="12"/>
+      <c r="N22" s="12"/>
+      <c r="O22" s="12"/>
+      <c r="P22" s="12"/>
+      <c r="Q22" s="12"/>
+      <c r="R22" s="12"/>
+      <c r="S22" s="12"/>
+      <c r="T22" s="12"/>
+      <c r="U22" s="12"/>
+      <c r="V22" s="12"/>
+      <c r="W22" s="12"/>
+      <c r="X22" s="12"/>
+      <c r="Y22" s="12"/>
+      <c r="Z22" s="12"/>
+      <c r="AA22" s="12"/>
+      <c r="AB22" s="12"/>
+      <c r="AC22" s="12"/>
+      <c r="AD22" s="12"/>
+      <c r="AE22" s="12"/>
+    </row>
+    <row r="23" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C23" s="12"/>
+      <c r="D23" s="12"/>
+      <c r="E23" s="12"/>
+      <c r="F23" s="12"/>
+      <c r="G23" s="12"/>
+      <c r="H23" s="12"/>
+      <c r="I23" s="12"/>
+      <c r="J23" s="12"/>
+      <c r="K23" s="12"/>
+      <c r="L23" s="12"/>
+      <c r="M23" s="12"/>
+      <c r="N23" s="12"/>
+      <c r="O23" s="12"/>
+      <c r="P23" s="12"/>
+      <c r="Q23" s="12"/>
+      <c r="R23" s="12"/>
+      <c r="S23" s="12"/>
+      <c r="T23" s="12"/>
+      <c r="U23" s="12"/>
+      <c r="V23" s="12"/>
+      <c r="W23" s="12"/>
+      <c r="X23" s="12"/>
+      <c r="Y23" s="12"/>
+      <c r="Z23" s="12"/>
+      <c r="AA23" s="12"/>
+      <c r="AB23" s="12"/>
+      <c r="AC23" s="12"/>
+      <c r="AD23" s="12"/>
+      <c r="AE23" s="12"/>
+    </row>
+    <row r="24" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A24" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B24" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C24" s="12"/>
+      <c r="D24" s="12"/>
+      <c r="E24" s="12"/>
+      <c r="F24" s="12"/>
+      <c r="G24" s="12"/>
+      <c r="H24" s="12"/>
+      <c r="I24" s="12"/>
+      <c r="J24" s="12"/>
+      <c r="K24" s="12"/>
+      <c r="L24" s="12"/>
+      <c r="M24" s="12"/>
+      <c r="N24" s="12"/>
+      <c r="O24" s="12"/>
+      <c r="P24" s="12"/>
+      <c r="Q24" s="12"/>
+      <c r="R24" s="12"/>
+      <c r="S24" s="12"/>
+      <c r="T24" s="12"/>
+      <c r="U24" s="12"/>
+      <c r="V24" s="12"/>
+      <c r="W24" s="12"/>
+      <c r="X24" s="12"/>
+      <c r="Y24" s="12"/>
+      <c r="Z24" s="12"/>
+      <c r="AA24" s="12"/>
+      <c r="AB24" s="12"/>
+      <c r="AC24" s="12"/>
+      <c r="AD24" s="12"/>
+      <c r="AE24" s="12"/>
+    </row>
+    <row r="25" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>2026</v>
+      </c>
+      <c r="B25" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C25" s="12"/>
+      <c r="D25" s="12"/>
+      <c r="E25" s="12"/>
+      <c r="F25" s="12"/>
+      <c r="G25" s="12"/>
+      <c r="H25" s="12"/>
+      <c r="I25" s="12"/>
+      <c r="J25" s="12"/>
+      <c r="K25" s="12"/>
+      <c r="L25" s="12"/>
+      <c r="M25" s="12"/>
+      <c r="N25" s="12"/>
+      <c r="O25" s="12"/>
+      <c r="P25" s="12"/>
+      <c r="Q25" s="12"/>
+      <c r="R25" s="12"/>
+      <c r="S25" s="12"/>
+      <c r="T25" s="12"/>
+      <c r="U25" s="12"/>
+      <c r="V25" s="12"/>
+      <c r="W25" s="12"/>
+      <c r="X25" s="12"/>
+      <c r="Y25" s="12"/>
+      <c r="Z25" s="12"/>
+      <c r="AA25" s="12"/>
+      <c r="AB25" s="12"/>
+      <c r="AC25" s="12"/>
+      <c r="AD25" s="12"/>
+      <c r="AE25" s="12"/>
+    </row>
+    <row r="26" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A26" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B26" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C26" s="12"/>
+      <c r="D26" s="12"/>
+      <c r="E26" s="12"/>
+      <c r="F26" s="12"/>
+      <c r="G26" s="12"/>
+      <c r="H26" s="12"/>
+      <c r="I26" s="12"/>
+      <c r="J26" s="12"/>
+      <c r="K26" s="12"/>
+      <c r="L26" s="12"/>
+      <c r="M26" s="12"/>
+      <c r="N26" s="12"/>
+      <c r="O26" s="12"/>
+      <c r="P26" s="12"/>
+      <c r="Q26" s="12"/>
+      <c r="R26" s="12"/>
+      <c r="S26" s="12"/>
+      <c r="T26" s="12"/>
+      <c r="U26" s="12"/>
+      <c r="V26" s="12"/>
+      <c r="W26" s="12"/>
+      <c r="X26" s="12"/>
+      <c r="Y26" s="12"/>
+      <c r="Z26" s="12"/>
+      <c r="AA26" s="12"/>
+      <c r="AB26" s="12"/>
+      <c r="AC26" s="12"/>
+      <c r="AD26" s="12"/>
+      <c r="AE26" s="12"/>
+    </row>
+    <row r="27" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A27" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B27" s="8" t="s">
+        <v>5</v>
+      </c>
+      <c r="C27" s="12"/>
+      <c r="D27" s="12"/>
+      <c r="E27" s="12"/>
+      <c r="F27" s="12"/>
+      <c r="G27" s="12"/>
+      <c r="H27" s="12"/>
+      <c r="I27" s="12"/>
+      <c r="J27" s="12"/>
+      <c r="K27" s="12"/>
+      <c r="L27" s="12"/>
+      <c r="M27" s="12"/>
+      <c r="N27" s="12"/>
+      <c r="O27" s="12"/>
+      <c r="P27" s="12"/>
+      <c r="Q27" s="12"/>
+      <c r="R27" s="12"/>
+      <c r="S27" s="12"/>
+      <c r="T27" s="12"/>
+      <c r="U27" s="12"/>
+      <c r="V27" s="12"/>
+      <c r="W27" s="12"/>
+      <c r="X27" s="12"/>
+      <c r="Y27" s="12"/>
+      <c r="Z27" s="12"/>
+      <c r="AA27" s="12"/>
+      <c r="AB27" s="12"/>
+      <c r="AC27" s="12"/>
+      <c r="AD27" s="12"/>
+      <c r="AE27" s="12"/>
+    </row>
+    <row r="28" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B28" s="8" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="12"/>
+      <c r="D28" s="12"/>
+      <c r="E28" s="12"/>
+      <c r="F28" s="12"/>
+      <c r="G28" s="12"/>
+      <c r="H28" s="12"/>
+      <c r="I28" s="12"/>
+      <c r="J28" s="12"/>
+      <c r="K28" s="12"/>
+      <c r="L28" s="12"/>
+      <c r="M28" s="12"/>
+      <c r="N28" s="12"/>
+      <c r="O28" s="12"/>
+      <c r="P28" s="12"/>
+      <c r="Q28" s="12"/>
+      <c r="R28" s="12"/>
+      <c r="S28" s="12"/>
+      <c r="T28" s="12"/>
+      <c r="U28" s="12"/>
+      <c r="V28" s="12"/>
+      <c r="W28" s="12"/>
+      <c r="X28" s="12"/>
+      <c r="Y28" s="12"/>
+      <c r="Z28" s="12"/>
+      <c r="AA28" s="12"/>
+      <c r="AB28" s="12"/>
+      <c r="AC28" s="12"/>
+      <c r="AD28" s="12"/>
+      <c r="AE28" s="12"/>
+    </row>
+    <row r="29" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A29" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B29" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="12"/>
+      <c r="D29" s="12"/>
+      <c r="E29" s="12"/>
+      <c r="F29" s="12"/>
+      <c r="G29" s="12"/>
+      <c r="H29" s="12"/>
+      <c r="I29" s="12"/>
+      <c r="J29" s="12"/>
+      <c r="K29" s="12"/>
+      <c r="L29" s="12"/>
+      <c r="M29" s="12"/>
+      <c r="N29" s="12"/>
+      <c r="O29" s="12"/>
+      <c r="P29" s="12"/>
+      <c r="Q29" s="12"/>
+      <c r="R29" s="12"/>
+      <c r="S29" s="12"/>
+      <c r="T29" s="12"/>
+      <c r="U29" s="12"/>
+      <c r="V29" s="12"/>
+      <c r="W29" s="12"/>
+      <c r="X29" s="12"/>
+      <c r="Y29" s="12"/>
+      <c r="Z29" s="12"/>
+      <c r="AA29" s="12"/>
+      <c r="AB29" s="12"/>
+      <c r="AC29" s="12"/>
+      <c r="AD29" s="12"/>
+      <c r="AE29" s="12"/>
+    </row>
+    <row r="30" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B30" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="12"/>
+      <c r="D30" s="12"/>
+      <c r="E30" s="12"/>
+      <c r="F30" s="12"/>
+      <c r="G30" s="12"/>
+      <c r="H30" s="12"/>
+      <c r="I30" s="12"/>
+      <c r="J30" s="12"/>
+      <c r="K30" s="12"/>
+      <c r="L30" s="12"/>
+      <c r="M30" s="12"/>
+      <c r="N30" s="12"/>
+      <c r="O30" s="12"/>
+      <c r="P30" s="12"/>
+      <c r="Q30" s="12"/>
+      <c r="R30" s="12"/>
+      <c r="S30" s="12"/>
+      <c r="T30" s="12"/>
+      <c r="U30" s="12"/>
+      <c r="V30" s="12"/>
+      <c r="W30" s="12"/>
+      <c r="X30" s="12"/>
+      <c r="Y30" s="12"/>
+      <c r="Z30" s="12"/>
+      <c r="AA30" s="12"/>
+      <c r="AB30" s="12"/>
+      <c r="AC30" s="12"/>
+      <c r="AD30" s="12"/>
+      <c r="AE30" s="12"/>
+    </row>
+    <row r="31" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A31" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B31" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C31" s="12"/>
+      <c r="D31" s="12"/>
+      <c r="E31" s="12"/>
+      <c r="F31" s="12"/>
+      <c r="G31" s="12"/>
+      <c r="H31" s="12"/>
+      <c r="I31" s="12"/>
+      <c r="J31" s="12"/>
+      <c r="K31" s="12"/>
+      <c r="L31" s="12"/>
+      <c r="M31" s="12"/>
+      <c r="N31" s="12"/>
+      <c r="O31" s="12"/>
+      <c r="P31" s="12"/>
+      <c r="Q31" s="12"/>
+      <c r="R31" s="12"/>
+      <c r="S31" s="12"/>
+      <c r="T31" s="12"/>
+      <c r="U31" s="12"/>
+      <c r="V31" s="12"/>
+      <c r="W31" s="12"/>
+      <c r="X31" s="12"/>
+      <c r="Y31" s="12"/>
+      <c r="Z31" s="12"/>
+      <c r="AA31" s="12"/>
+      <c r="AB31" s="12"/>
+      <c r="AC31" s="12"/>
+      <c r="AD31" s="12"/>
+      <c r="AE31" s="12"/>
+    </row>
+    <row r="32" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B32" s="8" t="s">
+        <v>10</v>
+      </c>
+      <c r="C32" s="12"/>
+      <c r="D32" s="12"/>
+      <c r="E32" s="12"/>
+      <c r="F32" s="12"/>
+      <c r="G32" s="12"/>
+      <c r="H32" s="12"/>
+      <c r="I32" s="12"/>
+      <c r="J32" s="12"/>
+      <c r="K32" s="12"/>
+      <c r="L32" s="12"/>
+      <c r="M32" s="12"/>
+      <c r="N32" s="12"/>
+      <c r="O32" s="12"/>
+      <c r="P32" s="12"/>
+      <c r="Q32" s="12"/>
+      <c r="R32" s="12"/>
+      <c r="S32" s="12"/>
+      <c r="T32" s="12"/>
+      <c r="U32" s="12"/>
+      <c r="V32" s="12"/>
+      <c r="W32" s="12"/>
+      <c r="X32" s="12"/>
+      <c r="Y32" s="12"/>
+      <c r="Z32" s="12"/>
+      <c r="AA32" s="12"/>
+      <c r="AB32" s="12"/>
+      <c r="AC32" s="12"/>
+      <c r="AD32" s="12"/>
+      <c r="AE32" s="12"/>
+    </row>
+    <row r="33" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A33" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B33" s="8" t="s">
+        <v>11</v>
+      </c>
+      <c r="C33" s="12"/>
+      <c r="D33" s="12"/>
+      <c r="E33" s="12"/>
+      <c r="F33" s="12"/>
+      <c r="G33" s="12"/>
+      <c r="H33" s="12"/>
+      <c r="I33" s="12"/>
+      <c r="J33" s="12"/>
+      <c r="K33" s="12"/>
+      <c r="L33" s="12"/>
+      <c r="M33" s="12"/>
+      <c r="N33" s="12"/>
+      <c r="O33" s="12"/>
+      <c r="P33" s="12"/>
+      <c r="Q33" s="12"/>
+      <c r="R33" s="12"/>
+      <c r="S33" s="12"/>
+      <c r="T33" s="12"/>
+      <c r="U33" s="12"/>
+      <c r="V33" s="12"/>
+      <c r="W33" s="12"/>
+      <c r="X33" s="12"/>
+      <c r="Y33" s="12"/>
+      <c r="Z33" s="12"/>
+      <c r="AA33" s="12"/>
+      <c r="AB33" s="12"/>
+      <c r="AC33" s="12"/>
+      <c r="AD33" s="12"/>
+      <c r="AE33" s="12"/>
+    </row>
+    <row r="34" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A34" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B34" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="C34" s="12"/>
+      <c r="D34" s="12"/>
+      <c r="E34" s="12"/>
+      <c r="F34" s="12"/>
+      <c r="G34" s="12"/>
+      <c r="H34" s="12"/>
+      <c r="I34" s="12"/>
+      <c r="J34" s="12"/>
+      <c r="K34" s="12"/>
+      <c r="L34" s="12"/>
+      <c r="M34" s="12"/>
+      <c r="N34" s="12"/>
+      <c r="O34" s="12"/>
+      <c r="P34" s="12"/>
+      <c r="Q34" s="12"/>
+      <c r="R34" s="12"/>
+      <c r="S34" s="12"/>
+      <c r="T34" s="12"/>
+      <c r="U34" s="12"/>
+      <c r="V34" s="12"/>
+      <c r="W34" s="12"/>
+      <c r="X34" s="12"/>
+      <c r="Y34" s="12"/>
+      <c r="Z34" s="12"/>
+      <c r="AA34" s="12"/>
+      <c r="AB34" s="12"/>
+      <c r="AC34" s="12"/>
+      <c r="AD34" s="12"/>
+      <c r="AE34" s="12"/>
+    </row>
+    <row r="35" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A35" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="C35" s="12"/>
+      <c r="D35" s="12"/>
+      <c r="E35" s="12"/>
+      <c r="F35" s="12"/>
+      <c r="G35" s="12"/>
+      <c r="H35" s="12"/>
+      <c r="I35" s="12"/>
+      <c r="J35" s="12"/>
+      <c r="K35" s="12"/>
+      <c r="L35" s="12"/>
+      <c r="M35" s="12"/>
+      <c r="N35" s="12"/>
+      <c r="O35" s="12"/>
+      <c r="P35" s="12"/>
+      <c r="Q35" s="12"/>
+      <c r="R35" s="12"/>
+      <c r="S35" s="12"/>
+      <c r="T35" s="12"/>
+      <c r="U35" s="12"/>
+      <c r="V35" s="12"/>
+      <c r="W35" s="12"/>
+      <c r="X35" s="12"/>
+      <c r="Y35" s="12"/>
+      <c r="Z35" s="12"/>
+      <c r="AA35" s="12"/>
+      <c r="AB35" s="12"/>
+      <c r="AC35" s="12"/>
+      <c r="AD35" s="12"/>
+      <c r="AE35" s="12"/>
+    </row>
+    <row r="36" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B36" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="12"/>
+      <c r="D36" s="12"/>
+      <c r="E36" s="12"/>
+      <c r="F36" s="12"/>
+      <c r="G36" s="12"/>
+      <c r="H36" s="12"/>
+      <c r="I36" s="12"/>
+      <c r="J36" s="12"/>
+      <c r="K36" s="12"/>
+      <c r="L36" s="12"/>
+      <c r="M36" s="12"/>
+      <c r="N36" s="12"/>
+      <c r="O36" s="12"/>
+      <c r="P36" s="12"/>
+      <c r="Q36" s="12"/>
+      <c r="R36" s="12"/>
+      <c r="S36" s="12"/>
+      <c r="T36" s="12"/>
+      <c r="U36" s="12"/>
+      <c r="V36" s="12"/>
+      <c r="W36" s="12"/>
+      <c r="X36" s="12"/>
+      <c r="Y36" s="12"/>
+      <c r="Z36" s="12"/>
+      <c r="AA36" s="12"/>
+      <c r="AB36" s="12"/>
+      <c r="AC36" s="12"/>
+      <c r="AD36" s="12"/>
+      <c r="AE36" s="12"/>
+    </row>
+    <row r="37" spans="1:31" x14ac:dyDescent="0.25">
+      <c r="A37" s="15">
+        <v>2027</v>
+      </c>
+      <c r="B37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="C37" s="12"/>
+      <c r="D37" s="12"/>
+      <c r="E37" s="12"/>
+      <c r="F37" s="12"/>
+      <c r="G37" s="12"/>
+      <c r="H37" s="12"/>
+      <c r="I37" s="12"/>
+      <c r="J37" s="12"/>
+      <c r="K37" s="12"/>
+      <c r="L37" s="12"/>
+      <c r="M37" s="12"/>
+      <c r="N37" s="12"/>
+      <c r="O37" s="12"/>
+      <c r="P37" s="12"/>
+      <c r="Q37" s="12"/>
+      <c r="R37" s="12"/>
+      <c r="S37" s="12"/>
+      <c r="T37" s="12"/>
+      <c r="U37" s="12"/>
+      <c r="V37" s="12"/>
+      <c r="W37" s="12"/>
+      <c r="X37" s="12"/>
+      <c r="Y37" s="12"/>
+      <c r="Z37" s="12"/>
+      <c r="AA37" s="12"/>
+      <c r="AB37" s="12"/>
+      <c r="AC37" s="12"/>
+      <c r="AD37" s="12"/>
+      <c r="AE37" s="12"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -19261,7 +21654,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -27985,7 +30378,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG107"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="9"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="12"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -7984,7 +7984,7 @@
     <definedName name="ZXBB_2">"#REF!"</definedName>
     <definedName name="ZXBB_3">"#REF!"</definedName>
   </definedNames>
-  <calcPr calcId="162913" calcMode="manual"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -30500,94 +30500,36 @@
       <c r="C2" s="21">
         <v>1</v>
       </c>
-      <c r="D2" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E2" s="24">
-        <v>0.97435897435897434</v>
-      </c>
-      <c r="F2" s="24">
-        <v>0.98765432098765427</v>
-      </c>
-      <c r="G2" s="24">
-        <v>0.93333333333333335</v>
-      </c>
-      <c r="H2" s="24">
-        <v>1</v>
-      </c>
-      <c r="I2" s="24">
-        <v>0.96666666666666667</v>
-      </c>
-      <c r="J2" s="24">
-        <v>0.96969696969696972</v>
-      </c>
-      <c r="K2" s="24">
-        <v>1</v>
-      </c>
-      <c r="L2" s="24">
-        <v>1</v>
-      </c>
-      <c r="M2" s="24">
-        <v>0.95</v>
-      </c>
-      <c r="N2" s="24">
-        <v>1</v>
-      </c>
-      <c r="O2" s="24">
-        <v>1</v>
-      </c>
-      <c r="P2" s="24">
-        <v>1</v>
-      </c>
-      <c r="Q2" s="24">
-        <v>1</v>
-      </c>
-      <c r="R2" s="24">
-        <v>1</v>
-      </c>
-      <c r="S2" s="24">
-        <v>1</v>
-      </c>
-      <c r="T2" s="24">
-        <v>1</v>
-      </c>
-      <c r="U2" s="24">
-        <v>0.9</v>
-      </c>
-      <c r="V2" s="24">
-        <v>1</v>
-      </c>
-      <c r="W2" s="24">
-        <v>0.95238095238095233</v>
-      </c>
-      <c r="X2" s="24">
-        <v>0.9375</v>
-      </c>
-      <c r="Y2" s="24">
-        <v>1</v>
-      </c>
-      <c r="Z2" s="24">
-        <v>1</v>
-      </c>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
+      <c r="L2" s="24"/>
+      <c r="M2" s="24"/>
+      <c r="N2" s="24"/>
+      <c r="O2" s="24"/>
+      <c r="P2" s="24"/>
+      <c r="Q2" s="24"/>
+      <c r="R2" s="24"/>
+      <c r="S2" s="24"/>
+      <c r="T2" s="24"/>
+      <c r="U2" s="24"/>
+      <c r="V2" s="24"/>
+      <c r="W2" s="24"/>
+      <c r="X2" s="24"/>
+      <c r="Y2" s="24"/>
+      <c r="Z2" s="24"/>
       <c r="AA2" s="24"/>
-      <c r="AB2" s="24">
-        <v>1</v>
-      </c>
-      <c r="AC2" s="24">
-        <v>1</v>
-      </c>
-      <c r="AD2" s="24">
-        <v>0.95</v>
-      </c>
-      <c r="AE2" s="24">
-        <v>1</v>
-      </c>
-      <c r="AF2" s="24">
-        <v>1</v>
-      </c>
-      <c r="AG2" s="24">
-        <v>1</v>
-      </c>
+      <c r="AB2" s="24"/>
+      <c r="AC2" s="24"/>
+      <c r="AD2" s="24"/>
+      <c r="AE2" s="24"/>
+      <c r="AF2" s="24"/>
+      <c r="AG2" s="24"/>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A3" s="26">
@@ -30599,96 +30541,36 @@
       <c r="C3" s="21">
         <v>2</v>
       </c>
-      <c r="D3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF3" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG3" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="24"/>
+      <c r="Q3" s="24"/>
+      <c r="R3" s="24"/>
+      <c r="S3" s="24"/>
+      <c r="T3" s="24"/>
+      <c r="U3" s="24"/>
+      <c r="V3" s="24"/>
+      <c r="W3" s="24"/>
+      <c r="X3" s="24"/>
+      <c r="Y3" s="24"/>
+      <c r="Z3" s="24"/>
+      <c r="AA3" s="24"/>
+      <c r="AB3" s="24"/>
+      <c r="AC3" s="24"/>
+      <c r="AD3" s="24"/>
+      <c r="AE3" s="24"/>
+      <c r="AF3" s="24"/>
+      <c r="AG3" s="24"/>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A4" s="26">
@@ -30700,96 +30582,36 @@
       <c r="C4" s="21">
         <v>3</v>
       </c>
-      <c r="D4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF4" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG4" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D4" s="24"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="24"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="24"/>
+      <c r="M4" s="24"/>
+      <c r="N4" s="24"/>
+      <c r="O4" s="24"/>
+      <c r="P4" s="24"/>
+      <c r="Q4" s="24"/>
+      <c r="R4" s="24"/>
+      <c r="S4" s="24"/>
+      <c r="T4" s="24"/>
+      <c r="U4" s="24"/>
+      <c r="V4" s="24"/>
+      <c r="W4" s="24"/>
+      <c r="X4" s="24"/>
+      <c r="Y4" s="24"/>
+      <c r="Z4" s="24"/>
+      <c r="AA4" s="24"/>
+      <c r="AB4" s="24"/>
+      <c r="AC4" s="24"/>
+      <c r="AD4" s="24"/>
+      <c r="AE4" s="24"/>
+      <c r="AF4" s="24"/>
+      <c r="AG4" s="24"/>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A5" s="26">
@@ -30801,96 +30623,36 @@
       <c r="C5" s="21">
         <v>4</v>
       </c>
-      <c r="D5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF5" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG5" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D5" s="24"/>
+      <c r="E5" s="24"/>
+      <c r="F5" s="24"/>
+      <c r="G5" s="24"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="24"/>
+      <c r="AC5" s="24"/>
+      <c r="AD5" s="24"/>
+      <c r="AE5" s="24"/>
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A6" s="26">
@@ -30902,96 +30664,36 @@
       <c r="C6" s="21">
         <v>5</v>
       </c>
-      <c r="D6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF6" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG6" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D6" s="24"/>
+      <c r="E6" s="24"/>
+      <c r="F6" s="24"/>
+      <c r="G6" s="24"/>
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24"/>
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="24"/>
+      <c r="AC6" s="24"/>
+      <c r="AD6" s="24"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A7" s="26">
@@ -31003,96 +30705,36 @@
       <c r="C7" s="21">
         <v>6</v>
       </c>
-      <c r="D7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF7" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG7" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D7" s="24"/>
+      <c r="E7" s="24"/>
+      <c r="F7" s="24"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
+      <c r="I7" s="24"/>
+      <c r="J7" s="24"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="24"/>
+      <c r="M7" s="24"/>
+      <c r="N7" s="24"/>
+      <c r="O7" s="24"/>
+      <c r="P7" s="24"/>
+      <c r="Q7" s="24"/>
+      <c r="R7" s="24"/>
+      <c r="S7" s="24"/>
+      <c r="T7" s="24"/>
+      <c r="U7" s="24"/>
+      <c r="V7" s="24"/>
+      <c r="W7" s="24"/>
+      <c r="X7" s="24"/>
+      <c r="Y7" s="24"/>
+      <c r="Z7" s="24"/>
+      <c r="AA7" s="24"/>
+      <c r="AB7" s="24"/>
+      <c r="AC7" s="24"/>
+      <c r="AD7" s="24"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A8" s="26">
@@ -31104,96 +30746,36 @@
       <c r="C8" s="21">
         <v>7</v>
       </c>
-      <c r="D8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF8" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG8" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D8" s="24"/>
+      <c r="E8" s="24"/>
+      <c r="F8" s="24"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
+      <c r="I8" s="24"/>
+      <c r="J8" s="24"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="24"/>
+      <c r="M8" s="24"/>
+      <c r="N8" s="24"/>
+      <c r="O8" s="24"/>
+      <c r="P8" s="24"/>
+      <c r="Q8" s="24"/>
+      <c r="R8" s="24"/>
+      <c r="S8" s="24"/>
+      <c r="T8" s="24"/>
+      <c r="U8" s="24"/>
+      <c r="V8" s="24"/>
+      <c r="W8" s="24"/>
+      <c r="X8" s="24"/>
+      <c r="Y8" s="24"/>
+      <c r="Z8" s="24"/>
+      <c r="AA8" s="24"/>
+      <c r="AB8" s="24"/>
+      <c r="AC8" s="24"/>
+      <c r="AD8" s="24"/>
+      <c r="AE8" s="24"/>
+      <c r="AF8" s="24"/>
+      <c r="AG8" s="24"/>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A9" s="26">
@@ -31205,96 +30787,36 @@
       <c r="C9" s="21">
         <v>8</v>
       </c>
-      <c r="D9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF9" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG9" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D9" s="24"/>
+      <c r="E9" s="24"/>
+      <c r="F9" s="24"/>
+      <c r="G9" s="24"/>
+      <c r="H9" s="24"/>
+      <c r="I9" s="24"/>
+      <c r="J9" s="24"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="24"/>
+      <c r="M9" s="24"/>
+      <c r="N9" s="24"/>
+      <c r="O9" s="24"/>
+      <c r="P9" s="24"/>
+      <c r="Q9" s="24"/>
+      <c r="R9" s="24"/>
+      <c r="S9" s="24"/>
+      <c r="T9" s="24"/>
+      <c r="U9" s="24"/>
+      <c r="V9" s="24"/>
+      <c r="W9" s="24"/>
+      <c r="X9" s="24"/>
+      <c r="Y9" s="24"/>
+      <c r="Z9" s="24"/>
+      <c r="AA9" s="24"/>
+      <c r="AB9" s="24"/>
+      <c r="AC9" s="24"/>
+      <c r="AD9" s="24"/>
+      <c r="AE9" s="24"/>
+      <c r="AF9" s="24"/>
+      <c r="AG9" s="24"/>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A10" s="26">
@@ -31306,96 +30828,36 @@
       <c r="C10" s="21">
         <v>9</v>
       </c>
-      <c r="D10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF10" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG10" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D10" s="24"/>
+      <c r="E10" s="24"/>
+      <c r="F10" s="24"/>
+      <c r="G10" s="24"/>
+      <c r="H10" s="24"/>
+      <c r="I10" s="24"/>
+      <c r="J10" s="24"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="24"/>
+      <c r="M10" s="24"/>
+      <c r="N10" s="24"/>
+      <c r="O10" s="24"/>
+      <c r="P10" s="24"/>
+      <c r="Q10" s="24"/>
+      <c r="R10" s="24"/>
+      <c r="S10" s="24"/>
+      <c r="T10" s="24"/>
+      <c r="U10" s="24"/>
+      <c r="V10" s="24"/>
+      <c r="W10" s="24"/>
+      <c r="X10" s="24"/>
+      <c r="Y10" s="24"/>
+      <c r="Z10" s="24"/>
+      <c r="AA10" s="24"/>
+      <c r="AB10" s="24"/>
+      <c r="AC10" s="24"/>
+      <c r="AD10" s="24"/>
+      <c r="AE10" s="24"/>
+      <c r="AF10" s="24"/>
+      <c r="AG10" s="24"/>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A11" s="26">
@@ -31407,96 +30869,36 @@
       <c r="C11" s="21">
         <v>10</v>
       </c>
-      <c r="D11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF11" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG11" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D11" s="24"/>
+      <c r="E11" s="24"/>
+      <c r="F11" s="24"/>
+      <c r="G11" s="24"/>
+      <c r="H11" s="24"/>
+      <c r="I11" s="24"/>
+      <c r="J11" s="24"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="24"/>
+      <c r="M11" s="24"/>
+      <c r="N11" s="24"/>
+      <c r="O11" s="24"/>
+      <c r="P11" s="24"/>
+      <c r="Q11" s="24"/>
+      <c r="R11" s="24"/>
+      <c r="S11" s="24"/>
+      <c r="T11" s="24"/>
+      <c r="U11" s="24"/>
+      <c r="V11" s="24"/>
+      <c r="W11" s="24"/>
+      <c r="X11" s="24"/>
+      <c r="Y11" s="24"/>
+      <c r="Z11" s="24"/>
+      <c r="AA11" s="24"/>
+      <c r="AB11" s="24"/>
+      <c r="AC11" s="24"/>
+      <c r="AD11" s="24"/>
+      <c r="AE11" s="24"/>
+      <c r="AF11" s="24"/>
+      <c r="AG11" s="24"/>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A12" s="26">
@@ -31508,96 +30910,36 @@
       <c r="C12" s="21">
         <v>11</v>
       </c>
-      <c r="D12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF12" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG12" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D12" s="24"/>
+      <c r="E12" s="24"/>
+      <c r="F12" s="24"/>
+      <c r="G12" s="24"/>
+      <c r="H12" s="24"/>
+      <c r="I12" s="24"/>
+      <c r="J12" s="24"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="24"/>
+      <c r="M12" s="24"/>
+      <c r="N12" s="24"/>
+      <c r="O12" s="24"/>
+      <c r="P12" s="24"/>
+      <c r="Q12" s="24"/>
+      <c r="R12" s="24"/>
+      <c r="S12" s="24"/>
+      <c r="T12" s="24"/>
+      <c r="U12" s="24"/>
+      <c r="V12" s="24"/>
+      <c r="W12" s="24"/>
+      <c r="X12" s="24"/>
+      <c r="Y12" s="24"/>
+      <c r="Z12" s="24"/>
+      <c r="AA12" s="24"/>
+      <c r="AB12" s="24"/>
+      <c r="AC12" s="24"/>
+      <c r="AD12" s="24"/>
+      <c r="AE12" s="24"/>
+      <c r="AF12" s="24"/>
+      <c r="AG12" s="24"/>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A13" s="26">
@@ -31609,96 +30951,36 @@
       <c r="C13" s="21">
         <v>12</v>
       </c>
-      <c r="D13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF13" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG13" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D13" s="24"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="24"/>
+      <c r="J13" s="24"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="24"/>
+      <c r="M13" s="24"/>
+      <c r="N13" s="24"/>
+      <c r="O13" s="24"/>
+      <c r="P13" s="24"/>
+      <c r="Q13" s="24"/>
+      <c r="R13" s="24"/>
+      <c r="S13" s="24"/>
+      <c r="T13" s="24"/>
+      <c r="U13" s="24"/>
+      <c r="V13" s="24"/>
+      <c r="W13" s="24"/>
+      <c r="X13" s="24"/>
+      <c r="Y13" s="24"/>
+      <c r="Z13" s="24"/>
+      <c r="AA13" s="24"/>
+      <c r="AB13" s="24"/>
+      <c r="AC13" s="24"/>
+      <c r="AD13" s="24"/>
+      <c r="AE13" s="24"/>
+      <c r="AF13" s="24"/>
+      <c r="AG13" s="24"/>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A14" s="26">
@@ -31710,96 +30992,36 @@
       <c r="C14" s="21">
         <v>13</v>
       </c>
-      <c r="D14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF14" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG14" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D14" s="24"/>
+      <c r="E14" s="24"/>
+      <c r="F14" s="24"/>
+      <c r="G14" s="24"/>
+      <c r="H14" s="24"/>
+      <c r="I14" s="24"/>
+      <c r="J14" s="24"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="24"/>
+      <c r="M14" s="24"/>
+      <c r="N14" s="24"/>
+      <c r="O14" s="24"/>
+      <c r="P14" s="24"/>
+      <c r="Q14" s="24"/>
+      <c r="R14" s="24"/>
+      <c r="S14" s="24"/>
+      <c r="T14" s="24"/>
+      <c r="U14" s="24"/>
+      <c r="V14" s="24"/>
+      <c r="W14" s="24"/>
+      <c r="X14" s="24"/>
+      <c r="Y14" s="24"/>
+      <c r="Z14" s="24"/>
+      <c r="AA14" s="24"/>
+      <c r="AB14" s="24"/>
+      <c r="AC14" s="24"/>
+      <c r="AD14" s="24"/>
+      <c r="AE14" s="24"/>
+      <c r="AF14" s="24"/>
+      <c r="AG14" s="24"/>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A15" s="26">
@@ -31811,96 +31033,36 @@
       <c r="C15" s="21">
         <v>14</v>
       </c>
-      <c r="D15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF15" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG15" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D15" s="24"/>
+      <c r="E15" s="24"/>
+      <c r="F15" s="24"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
+      <c r="I15" s="24"/>
+      <c r="J15" s="24"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="24"/>
+      <c r="M15" s="24"/>
+      <c r="N15" s="24"/>
+      <c r="O15" s="24"/>
+      <c r="P15" s="24"/>
+      <c r="Q15" s="24"/>
+      <c r="R15" s="24"/>
+      <c r="S15" s="24"/>
+      <c r="T15" s="24"/>
+      <c r="U15" s="24"/>
+      <c r="V15" s="24"/>
+      <c r="W15" s="24"/>
+      <c r="X15" s="24"/>
+      <c r="Y15" s="24"/>
+      <c r="Z15" s="24"/>
+      <c r="AA15" s="24"/>
+      <c r="AB15" s="24"/>
+      <c r="AC15" s="24"/>
+      <c r="AD15" s="24"/>
+      <c r="AE15" s="24"/>
+      <c r="AF15" s="24"/>
+      <c r="AG15" s="24"/>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A16" s="26">
@@ -31912,96 +31074,36 @@
       <c r="C16" s="21">
         <v>15</v>
       </c>
-      <c r="D16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF16" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG16" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D16" s="24"/>
+      <c r="E16" s="24"/>
+      <c r="F16" s="24"/>
+      <c r="G16" s="24"/>
+      <c r="H16" s="24"/>
+      <c r="I16" s="24"/>
+      <c r="J16" s="24"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="24"/>
+      <c r="M16" s="24"/>
+      <c r="N16" s="24"/>
+      <c r="O16" s="24"/>
+      <c r="P16" s="24"/>
+      <c r="Q16" s="24"/>
+      <c r="R16" s="24"/>
+      <c r="S16" s="24"/>
+      <c r="T16" s="24"/>
+      <c r="U16" s="24"/>
+      <c r="V16" s="24"/>
+      <c r="W16" s="24"/>
+      <c r="X16" s="24"/>
+      <c r="Y16" s="24"/>
+      <c r="Z16" s="24"/>
+      <c r="AA16" s="24"/>
+      <c r="AB16" s="24"/>
+      <c r="AC16" s="24"/>
+      <c r="AD16" s="24"/>
+      <c r="AE16" s="24"/>
+      <c r="AF16" s="24"/>
+      <c r="AG16" s="24"/>
     </row>
     <row r="17" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A17" s="26">
@@ -32013,96 +31115,36 @@
       <c r="C17" s="21">
         <v>16</v>
       </c>
-      <c r="D17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF17" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG17" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D17" s="24"/>
+      <c r="E17" s="24"/>
+      <c r="F17" s="24"/>
+      <c r="G17" s="24"/>
+      <c r="H17" s="24"/>
+      <c r="I17" s="24"/>
+      <c r="J17" s="24"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="24"/>
+      <c r="M17" s="24"/>
+      <c r="N17" s="24"/>
+      <c r="O17" s="24"/>
+      <c r="P17" s="24"/>
+      <c r="Q17" s="24"/>
+      <c r="R17" s="24"/>
+      <c r="S17" s="24"/>
+      <c r="T17" s="24"/>
+      <c r="U17" s="24"/>
+      <c r="V17" s="24"/>
+      <c r="W17" s="24"/>
+      <c r="X17" s="24"/>
+      <c r="Y17" s="24"/>
+      <c r="Z17" s="24"/>
+      <c r="AA17" s="24"/>
+      <c r="AB17" s="24"/>
+      <c r="AC17" s="24"/>
+      <c r="AD17" s="24"/>
+      <c r="AE17" s="24"/>
+      <c r="AF17" s="24"/>
+      <c r="AG17" s="24"/>
     </row>
     <row r="18" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A18" s="26">
@@ -32114,96 +31156,36 @@
       <c r="C18" s="21">
         <v>17</v>
       </c>
-      <c r="D18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF18" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG18" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="24"/>
+      <c r="I18" s="24"/>
+      <c r="J18" s="24"/>
+      <c r="K18" s="24"/>
+      <c r="L18" s="24"/>
+      <c r="M18" s="24"/>
+      <c r="N18" s="24"/>
+      <c r="O18" s="24"/>
+      <c r="P18" s="24"/>
+      <c r="Q18" s="24"/>
+      <c r="R18" s="24"/>
+      <c r="S18" s="24"/>
+      <c r="T18" s="24"/>
+      <c r="U18" s="24"/>
+      <c r="V18" s="24"/>
+      <c r="W18" s="24"/>
+      <c r="X18" s="24"/>
+      <c r="Y18" s="24"/>
+      <c r="Z18" s="24"/>
+      <c r="AA18" s="24"/>
+      <c r="AB18" s="24"/>
+      <c r="AC18" s="24"/>
+      <c r="AD18" s="24"/>
+      <c r="AE18" s="24"/>
+      <c r="AF18" s="24"/>
+      <c r="AG18" s="24"/>
     </row>
     <row r="19" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A19" s="26">
@@ -32215,96 +31197,36 @@
       <c r="C19" s="21">
         <v>18</v>
       </c>
-      <c r="D19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF19" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG19" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D19" s="24"/>
+      <c r="E19" s="24"/>
+      <c r="F19" s="24"/>
+      <c r="G19" s="24"/>
+      <c r="H19" s="24"/>
+      <c r="I19" s="24"/>
+      <c r="J19" s="24"/>
+      <c r="K19" s="24"/>
+      <c r="L19" s="24"/>
+      <c r="M19" s="24"/>
+      <c r="N19" s="24"/>
+      <c r="O19" s="24"/>
+      <c r="P19" s="24"/>
+      <c r="Q19" s="24"/>
+      <c r="R19" s="24"/>
+      <c r="S19" s="24"/>
+      <c r="T19" s="24"/>
+      <c r="U19" s="24"/>
+      <c r="V19" s="24"/>
+      <c r="W19" s="24"/>
+      <c r="X19" s="24"/>
+      <c r="Y19" s="24"/>
+      <c r="Z19" s="24"/>
+      <c r="AA19" s="24"/>
+      <c r="AB19" s="24"/>
+      <c r="AC19" s="24"/>
+      <c r="AD19" s="24"/>
+      <c r="AE19" s="24"/>
+      <c r="AF19" s="24"/>
+      <c r="AG19" s="24"/>
     </row>
     <row r="20" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A20" s="26">
@@ -32316,96 +31238,36 @@
       <c r="C20" s="21">
         <v>19</v>
       </c>
-      <c r="D20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF20" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG20" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D20" s="24"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="24"/>
+      <c r="J20" s="24"/>
+      <c r="K20" s="24"/>
+      <c r="L20" s="24"/>
+      <c r="M20" s="24"/>
+      <c r="N20" s="24"/>
+      <c r="O20" s="24"/>
+      <c r="P20" s="24"/>
+      <c r="Q20" s="24"/>
+      <c r="R20" s="24"/>
+      <c r="S20" s="24"/>
+      <c r="T20" s="24"/>
+      <c r="U20" s="24"/>
+      <c r="V20" s="24"/>
+      <c r="W20" s="24"/>
+      <c r="X20" s="24"/>
+      <c r="Y20" s="24"/>
+      <c r="Z20" s="24"/>
+      <c r="AA20" s="24"/>
+      <c r="AB20" s="24"/>
+      <c r="AC20" s="24"/>
+      <c r="AD20" s="24"/>
+      <c r="AE20" s="24"/>
+      <c r="AF20" s="24"/>
+      <c r="AG20" s="24"/>
     </row>
     <row r="21" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A21" s="26">
@@ -32417,96 +31279,36 @@
       <c r="C21" s="21">
         <v>20</v>
       </c>
-      <c r="D21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF21" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG21" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D21" s="24"/>
+      <c r="E21" s="24"/>
+      <c r="F21" s="24"/>
+      <c r="G21" s="24"/>
+      <c r="H21" s="24"/>
+      <c r="I21" s="24"/>
+      <c r="J21" s="24"/>
+      <c r="K21" s="24"/>
+      <c r="L21" s="24"/>
+      <c r="M21" s="24"/>
+      <c r="N21" s="24"/>
+      <c r="O21" s="24"/>
+      <c r="P21" s="24"/>
+      <c r="Q21" s="24"/>
+      <c r="R21" s="24"/>
+      <c r="S21" s="24"/>
+      <c r="T21" s="24"/>
+      <c r="U21" s="24"/>
+      <c r="V21" s="24"/>
+      <c r="W21" s="24"/>
+      <c r="X21" s="24"/>
+      <c r="Y21" s="24"/>
+      <c r="Z21" s="24"/>
+      <c r="AA21" s="24"/>
+      <c r="AB21" s="24"/>
+      <c r="AC21" s="24"/>
+      <c r="AD21" s="24"/>
+      <c r="AE21" s="24"/>
+      <c r="AF21" s="24"/>
+      <c r="AG21" s="24"/>
     </row>
     <row r="22" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A22" s="26">
@@ -32518,96 +31320,36 @@
       <c r="C22" s="21">
         <v>21</v>
       </c>
-      <c r="D22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF22" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG22" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D22" s="24"/>
+      <c r="E22" s="24"/>
+      <c r="F22" s="24"/>
+      <c r="G22" s="24"/>
+      <c r="H22" s="24"/>
+      <c r="I22" s="24"/>
+      <c r="J22" s="24"/>
+      <c r="K22" s="24"/>
+      <c r="L22" s="24"/>
+      <c r="M22" s="24"/>
+      <c r="N22" s="24"/>
+      <c r="O22" s="24"/>
+      <c r="P22" s="24"/>
+      <c r="Q22" s="24"/>
+      <c r="R22" s="24"/>
+      <c r="S22" s="24"/>
+      <c r="T22" s="24"/>
+      <c r="U22" s="24"/>
+      <c r="V22" s="24"/>
+      <c r="W22" s="24"/>
+      <c r="X22" s="24"/>
+      <c r="Y22" s="24"/>
+      <c r="Z22" s="24"/>
+      <c r="AA22" s="24"/>
+      <c r="AB22" s="24"/>
+      <c r="AC22" s="24"/>
+      <c r="AD22" s="24"/>
+      <c r="AE22" s="24"/>
+      <c r="AF22" s="24"/>
+      <c r="AG22" s="24"/>
     </row>
     <row r="23" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A23" s="26">
@@ -32619,96 +31361,36 @@
       <c r="C23" s="21">
         <v>22</v>
       </c>
-      <c r="D23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF23" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG23" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D23" s="24"/>
+      <c r="E23" s="24"/>
+      <c r="F23" s="24"/>
+      <c r="G23" s="24"/>
+      <c r="H23" s="24"/>
+      <c r="I23" s="24"/>
+      <c r="J23" s="24"/>
+      <c r="K23" s="24"/>
+      <c r="L23" s="24"/>
+      <c r="M23" s="24"/>
+      <c r="N23" s="24"/>
+      <c r="O23" s="24"/>
+      <c r="P23" s="24"/>
+      <c r="Q23" s="24"/>
+      <c r="R23" s="24"/>
+      <c r="S23" s="24"/>
+      <c r="T23" s="24"/>
+      <c r="U23" s="24"/>
+      <c r="V23" s="24"/>
+      <c r="W23" s="24"/>
+      <c r="X23" s="24"/>
+      <c r="Y23" s="24"/>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
+      <c r="AB23" s="24"/>
+      <c r="AC23" s="24"/>
+      <c r="AD23" s="24"/>
+      <c r="AE23" s="24"/>
+      <c r="AF23" s="24"/>
+      <c r="AG23" s="24"/>
     </row>
     <row r="24" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A24" s="26">
@@ -32720,96 +31402,36 @@
       <c r="C24" s="21">
         <v>23</v>
       </c>
-      <c r="D24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF24" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG24" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D24" s="24"/>
+      <c r="E24" s="24"/>
+      <c r="F24" s="24"/>
+      <c r="G24" s="24"/>
+      <c r="H24" s="24"/>
+      <c r="I24" s="24"/>
+      <c r="J24" s="24"/>
+      <c r="K24" s="24"/>
+      <c r="L24" s="24"/>
+      <c r="M24" s="24"/>
+      <c r="N24" s="24"/>
+      <c r="O24" s="24"/>
+      <c r="P24" s="24"/>
+      <c r="Q24" s="24"/>
+      <c r="R24" s="24"/>
+      <c r="S24" s="24"/>
+      <c r="T24" s="24"/>
+      <c r="U24" s="24"/>
+      <c r="V24" s="24"/>
+      <c r="W24" s="24"/>
+      <c r="X24" s="24"/>
+      <c r="Y24" s="24"/>
+      <c r="Z24" s="24"/>
+      <c r="AA24" s="24"/>
+      <c r="AB24" s="24"/>
+      <c r="AC24" s="24"/>
+      <c r="AD24" s="24"/>
+      <c r="AE24" s="24"/>
+      <c r="AF24" s="24"/>
+      <c r="AG24" s="24"/>
     </row>
     <row r="25" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A25" s="26">
@@ -32821,96 +31443,36 @@
       <c r="C25" s="21">
         <v>24</v>
       </c>
-      <c r="D25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF25" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG25" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D25" s="24"/>
+      <c r="E25" s="24"/>
+      <c r="F25" s="24"/>
+      <c r="G25" s="24"/>
+      <c r="H25" s="24"/>
+      <c r="I25" s="24"/>
+      <c r="J25" s="24"/>
+      <c r="K25" s="24"/>
+      <c r="L25" s="24"/>
+      <c r="M25" s="24"/>
+      <c r="N25" s="24"/>
+      <c r="O25" s="24"/>
+      <c r="P25" s="24"/>
+      <c r="Q25" s="24"/>
+      <c r="R25" s="24"/>
+      <c r="S25" s="24"/>
+      <c r="T25" s="24"/>
+      <c r="U25" s="24"/>
+      <c r="V25" s="24"/>
+      <c r="W25" s="24"/>
+      <c r="X25" s="24"/>
+      <c r="Y25" s="24"/>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
+      <c r="AB25" s="24"/>
+      <c r="AC25" s="24"/>
+      <c r="AD25" s="24"/>
+      <c r="AE25" s="24"/>
+      <c r="AF25" s="24"/>
+      <c r="AG25" s="24"/>
     </row>
     <row r="26" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A26" s="26">
@@ -32922,96 +31484,36 @@
       <c r="C26" s="21">
         <v>25</v>
       </c>
-      <c r="D26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF26" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG26" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D26" s="24"/>
+      <c r="E26" s="24"/>
+      <c r="F26" s="24"/>
+      <c r="G26" s="24"/>
+      <c r="H26" s="24"/>
+      <c r="I26" s="24"/>
+      <c r="J26" s="24"/>
+      <c r="K26" s="24"/>
+      <c r="L26" s="24"/>
+      <c r="M26" s="24"/>
+      <c r="N26" s="24"/>
+      <c r="O26" s="24"/>
+      <c r="P26" s="24"/>
+      <c r="Q26" s="24"/>
+      <c r="R26" s="24"/>
+      <c r="S26" s="24"/>
+      <c r="T26" s="24"/>
+      <c r="U26" s="24"/>
+      <c r="V26" s="24"/>
+      <c r="W26" s="24"/>
+      <c r="X26" s="24"/>
+      <c r="Y26" s="24"/>
+      <c r="Z26" s="24"/>
+      <c r="AA26" s="24"/>
+      <c r="AB26" s="24"/>
+      <c r="AC26" s="24"/>
+      <c r="AD26" s="24"/>
+      <c r="AE26" s="24"/>
+      <c r="AF26" s="24"/>
+      <c r="AG26" s="24"/>
     </row>
     <row r="27" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A27" s="26">
@@ -33023,96 +31525,36 @@
       <c r="C27" s="21">
         <v>26</v>
       </c>
-      <c r="D27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF27" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG27" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D27" s="24"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="24"/>
+      <c r="J27" s="24"/>
+      <c r="K27" s="24"/>
+      <c r="L27" s="24"/>
+      <c r="M27" s="24"/>
+      <c r="N27" s="24"/>
+      <c r="O27" s="24"/>
+      <c r="P27" s="24"/>
+      <c r="Q27" s="24"/>
+      <c r="R27" s="24"/>
+      <c r="S27" s="24"/>
+      <c r="T27" s="24"/>
+      <c r="U27" s="24"/>
+      <c r="V27" s="24"/>
+      <c r="W27" s="24"/>
+      <c r="X27" s="24"/>
+      <c r="Y27" s="24"/>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
+      <c r="AB27" s="24"/>
+      <c r="AC27" s="24"/>
+      <c r="AD27" s="24"/>
+      <c r="AE27" s="24"/>
+      <c r="AF27" s="24"/>
+      <c r="AG27" s="24"/>
     </row>
     <row r="28" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A28" s="26">
@@ -33124,96 +31566,36 @@
       <c r="C28" s="21">
         <v>27</v>
       </c>
-      <c r="D28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF28" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG28" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D28" s="24"/>
+      <c r="E28" s="24"/>
+      <c r="F28" s="24"/>
+      <c r="G28" s="24"/>
+      <c r="H28" s="24"/>
+      <c r="I28" s="24"/>
+      <c r="J28" s="24"/>
+      <c r="K28" s="24"/>
+      <c r="L28" s="24"/>
+      <c r="M28" s="24"/>
+      <c r="N28" s="24"/>
+      <c r="O28" s="24"/>
+      <c r="P28" s="24"/>
+      <c r="Q28" s="24"/>
+      <c r="R28" s="24"/>
+      <c r="S28" s="24"/>
+      <c r="T28" s="24"/>
+      <c r="U28" s="24"/>
+      <c r="V28" s="24"/>
+      <c r="W28" s="24"/>
+      <c r="X28" s="24"/>
+      <c r="Y28" s="24"/>
+      <c r="Z28" s="24"/>
+      <c r="AA28" s="24"/>
+      <c r="AB28" s="24"/>
+      <c r="AC28" s="24"/>
+      <c r="AD28" s="24"/>
+      <c r="AE28" s="24"/>
+      <c r="AF28" s="24"/>
+      <c r="AG28" s="24"/>
     </row>
     <row r="29" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A29" s="26">
@@ -33225,96 +31607,36 @@
       <c r="C29" s="21">
         <v>28</v>
       </c>
-      <c r="D29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF29" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG29" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D29" s="24"/>
+      <c r="E29" s="24"/>
+      <c r="F29" s="24"/>
+      <c r="G29" s="24"/>
+      <c r="H29" s="24"/>
+      <c r="I29" s="24"/>
+      <c r="J29" s="24"/>
+      <c r="K29" s="24"/>
+      <c r="L29" s="24"/>
+      <c r="M29" s="24"/>
+      <c r="N29" s="24"/>
+      <c r="O29" s="24"/>
+      <c r="P29" s="24"/>
+      <c r="Q29" s="24"/>
+      <c r="R29" s="24"/>
+      <c r="S29" s="24"/>
+      <c r="T29" s="24"/>
+      <c r="U29" s="24"/>
+      <c r="V29" s="24"/>
+      <c r="W29" s="24"/>
+      <c r="X29" s="24"/>
+      <c r="Y29" s="24"/>
+      <c r="Z29" s="24"/>
+      <c r="AA29" s="24"/>
+      <c r="AB29" s="24"/>
+      <c r="AC29" s="24"/>
+      <c r="AD29" s="24"/>
+      <c r="AE29" s="24"/>
+      <c r="AF29" s="24"/>
+      <c r="AG29" s="24"/>
     </row>
     <row r="30" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A30" s="26">
@@ -33326,96 +31648,36 @@
       <c r="C30" s="21">
         <v>29</v>
       </c>
-      <c r="D30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF30" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG30" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D30" s="24"/>
+      <c r="E30" s="24"/>
+      <c r="F30" s="24"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="24"/>
+      <c r="I30" s="24"/>
+      <c r="J30" s="24"/>
+      <c r="K30" s="24"/>
+      <c r="L30" s="24"/>
+      <c r="M30" s="24"/>
+      <c r="N30" s="24"/>
+      <c r="O30" s="24"/>
+      <c r="P30" s="24"/>
+      <c r="Q30" s="24"/>
+      <c r="R30" s="24"/>
+      <c r="S30" s="24"/>
+      <c r="T30" s="24"/>
+      <c r="U30" s="24"/>
+      <c r="V30" s="24"/>
+      <c r="W30" s="24"/>
+      <c r="X30" s="24"/>
+      <c r="Y30" s="24"/>
+      <c r="Z30" s="24"/>
+      <c r="AA30" s="24"/>
+      <c r="AB30" s="24"/>
+      <c r="AC30" s="24"/>
+      <c r="AD30" s="24"/>
+      <c r="AE30" s="24"/>
+      <c r="AF30" s="24"/>
+      <c r="AG30" s="24"/>
     </row>
     <row r="31" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A31" s="26">
@@ -33427,96 +31689,36 @@
       <c r="C31" s="21">
         <v>30</v>
       </c>
-      <c r="D31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF31" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG31" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D31" s="24"/>
+      <c r="E31" s="24"/>
+      <c r="F31" s="24"/>
+      <c r="G31" s="24"/>
+      <c r="H31" s="24"/>
+      <c r="I31" s="24"/>
+      <c r="J31" s="24"/>
+      <c r="K31" s="24"/>
+      <c r="L31" s="24"/>
+      <c r="M31" s="24"/>
+      <c r="N31" s="24"/>
+      <c r="O31" s="24"/>
+      <c r="P31" s="24"/>
+      <c r="Q31" s="24"/>
+      <c r="R31" s="24"/>
+      <c r="S31" s="24"/>
+      <c r="T31" s="24"/>
+      <c r="U31" s="24"/>
+      <c r="V31" s="24"/>
+      <c r="W31" s="24"/>
+      <c r="X31" s="24"/>
+      <c r="Y31" s="24"/>
+      <c r="Z31" s="24"/>
+      <c r="AA31" s="24"/>
+      <c r="AB31" s="24"/>
+      <c r="AC31" s="24"/>
+      <c r="AD31" s="24"/>
+      <c r="AE31" s="24"/>
+      <c r="AF31" s="24"/>
+      <c r="AG31" s="24"/>
     </row>
     <row r="32" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A32" s="26">
@@ -33528,96 +31730,36 @@
       <c r="C32" s="21">
         <v>31</v>
       </c>
-      <c r="D32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF32" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG32" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D32" s="24"/>
+      <c r="E32" s="24"/>
+      <c r="F32" s="24"/>
+      <c r="G32" s="24"/>
+      <c r="H32" s="24"/>
+      <c r="I32" s="24"/>
+      <c r="J32" s="24"/>
+      <c r="K32" s="24"/>
+      <c r="L32" s="24"/>
+      <c r="M32" s="24"/>
+      <c r="N32" s="24"/>
+      <c r="O32" s="24"/>
+      <c r="P32" s="24"/>
+      <c r="Q32" s="24"/>
+      <c r="R32" s="24"/>
+      <c r="S32" s="24"/>
+      <c r="T32" s="24"/>
+      <c r="U32" s="24"/>
+      <c r="V32" s="24"/>
+      <c r="W32" s="24"/>
+      <c r="X32" s="24"/>
+      <c r="Y32" s="24"/>
+      <c r="Z32" s="24"/>
+      <c r="AA32" s="24"/>
+      <c r="AB32" s="24"/>
+      <c r="AC32" s="24"/>
+      <c r="AD32" s="24"/>
+      <c r="AE32" s="24"/>
+      <c r="AF32" s="24"/>
+      <c r="AG32" s="24"/>
     </row>
     <row r="33" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A33" s="26">
@@ -33629,96 +31771,36 @@
       <c r="C33" s="21">
         <v>32</v>
       </c>
-      <c r="D33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF33" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG33" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D33" s="24"/>
+      <c r="E33" s="24"/>
+      <c r="F33" s="24"/>
+      <c r="G33" s="24"/>
+      <c r="H33" s="24"/>
+      <c r="I33" s="24"/>
+      <c r="J33" s="24"/>
+      <c r="K33" s="24"/>
+      <c r="L33" s="24"/>
+      <c r="M33" s="24"/>
+      <c r="N33" s="24"/>
+      <c r="O33" s="24"/>
+      <c r="P33" s="24"/>
+      <c r="Q33" s="24"/>
+      <c r="R33" s="24"/>
+      <c r="S33" s="24"/>
+      <c r="T33" s="24"/>
+      <c r="U33" s="24"/>
+      <c r="V33" s="24"/>
+      <c r="W33" s="24"/>
+      <c r="X33" s="24"/>
+      <c r="Y33" s="24"/>
+      <c r="Z33" s="24"/>
+      <c r="AA33" s="24"/>
+      <c r="AB33" s="24"/>
+      <c r="AC33" s="24"/>
+      <c r="AD33" s="24"/>
+      <c r="AE33" s="24"/>
+      <c r="AF33" s="24"/>
+      <c r="AG33" s="24"/>
     </row>
     <row r="34" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A34" s="26">
@@ -33730,96 +31812,36 @@
       <c r="C34" s="21">
         <v>33</v>
       </c>
-      <c r="D34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF34" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG34" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D34" s="24"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="24"/>
+      <c r="J34" s="24"/>
+      <c r="K34" s="24"/>
+      <c r="L34" s="24"/>
+      <c r="M34" s="24"/>
+      <c r="N34" s="24"/>
+      <c r="O34" s="24"/>
+      <c r="P34" s="24"/>
+      <c r="Q34" s="24"/>
+      <c r="R34" s="24"/>
+      <c r="S34" s="24"/>
+      <c r="T34" s="24"/>
+      <c r="U34" s="24"/>
+      <c r="V34" s="24"/>
+      <c r="W34" s="24"/>
+      <c r="X34" s="24"/>
+      <c r="Y34" s="24"/>
+      <c r="Z34" s="24"/>
+      <c r="AA34" s="24"/>
+      <c r="AB34" s="24"/>
+      <c r="AC34" s="24"/>
+      <c r="AD34" s="24"/>
+      <c r="AE34" s="24"/>
+      <c r="AF34" s="24"/>
+      <c r="AG34" s="24"/>
     </row>
     <row r="35" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A35" s="26">
@@ -33831,96 +31853,36 @@
       <c r="C35" s="21">
         <v>34</v>
       </c>
-      <c r="D35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF35" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG35" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D35" s="24"/>
+      <c r="E35" s="24"/>
+      <c r="F35" s="24"/>
+      <c r="G35" s="24"/>
+      <c r="H35" s="24"/>
+      <c r="I35" s="24"/>
+      <c r="J35" s="24"/>
+      <c r="K35" s="24"/>
+      <c r="L35" s="24"/>
+      <c r="M35" s="24"/>
+      <c r="N35" s="24"/>
+      <c r="O35" s="24"/>
+      <c r="P35" s="24"/>
+      <c r="Q35" s="24"/>
+      <c r="R35" s="24"/>
+      <c r="S35" s="24"/>
+      <c r="T35" s="24"/>
+      <c r="U35" s="24"/>
+      <c r="V35" s="24"/>
+      <c r="W35" s="24"/>
+      <c r="X35" s="24"/>
+      <c r="Y35" s="24"/>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="24"/>
+      <c r="AB35" s="24"/>
+      <c r="AC35" s="24"/>
+      <c r="AD35" s="24"/>
+      <c r="AE35" s="24"/>
+      <c r="AF35" s="24"/>
+      <c r="AG35" s="24"/>
     </row>
     <row r="36" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A36" s="26">
@@ -33932,96 +31894,36 @@
       <c r="C36" s="21">
         <v>35</v>
       </c>
-      <c r="D36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF36" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG36" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D36" s="24"/>
+      <c r="E36" s="24"/>
+      <c r="F36" s="24"/>
+      <c r="G36" s="24"/>
+      <c r="H36" s="24"/>
+      <c r="I36" s="24"/>
+      <c r="J36" s="24"/>
+      <c r="K36" s="24"/>
+      <c r="L36" s="24"/>
+      <c r="M36" s="24"/>
+      <c r="N36" s="24"/>
+      <c r="O36" s="24"/>
+      <c r="P36" s="24"/>
+      <c r="Q36" s="24"/>
+      <c r="R36" s="24"/>
+      <c r="S36" s="24"/>
+      <c r="T36" s="24"/>
+      <c r="U36" s="24"/>
+      <c r="V36" s="24"/>
+      <c r="W36" s="24"/>
+      <c r="X36" s="24"/>
+      <c r="Y36" s="24"/>
+      <c r="Z36" s="24"/>
+      <c r="AA36" s="24"/>
+      <c r="AB36" s="24"/>
+      <c r="AC36" s="24"/>
+      <c r="AD36" s="24"/>
+      <c r="AE36" s="24"/>
+      <c r="AF36" s="24"/>
+      <c r="AG36" s="24"/>
     </row>
     <row r="37" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A37" s="26">
@@ -34033,96 +31935,36 @@
       <c r="C37" s="21">
         <v>36</v>
       </c>
-      <c r="D37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF37" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG37" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="24"/>
+      <c r="I37" s="24"/>
+      <c r="J37" s="24"/>
+      <c r="K37" s="24"/>
+      <c r="L37" s="24"/>
+      <c r="M37" s="24"/>
+      <c r="N37" s="24"/>
+      <c r="O37" s="24"/>
+      <c r="P37" s="24"/>
+      <c r="Q37" s="24"/>
+      <c r="R37" s="24"/>
+      <c r="S37" s="24"/>
+      <c r="T37" s="24"/>
+      <c r="U37" s="24"/>
+      <c r="V37" s="24"/>
+      <c r="W37" s="24"/>
+      <c r="X37" s="24"/>
+      <c r="Y37" s="24"/>
+      <c r="Z37" s="24"/>
+      <c r="AA37" s="24"/>
+      <c r="AB37" s="24"/>
+      <c r="AC37" s="24"/>
+      <c r="AD37" s="24"/>
+      <c r="AE37" s="24"/>
+      <c r="AF37" s="24"/>
+      <c r="AG37" s="24"/>
     </row>
     <row r="38" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A38" s="26">
@@ -34134,96 +31976,36 @@
       <c r="C38" s="21">
         <v>37</v>
       </c>
-      <c r="D38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF38" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG38" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D38" s="24"/>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
+      <c r="G38" s="24"/>
+      <c r="H38" s="24"/>
+      <c r="I38" s="24"/>
+      <c r="J38" s="24"/>
+      <c r="K38" s="24"/>
+      <c r="L38" s="24"/>
+      <c r="M38" s="24"/>
+      <c r="N38" s="24"/>
+      <c r="O38" s="24"/>
+      <c r="P38" s="24"/>
+      <c r="Q38" s="24"/>
+      <c r="R38" s="24"/>
+      <c r="S38" s="24"/>
+      <c r="T38" s="24"/>
+      <c r="U38" s="24"/>
+      <c r="V38" s="24"/>
+      <c r="W38" s="24"/>
+      <c r="X38" s="24"/>
+      <c r="Y38" s="24"/>
+      <c r="Z38" s="24"/>
+      <c r="AA38" s="24"/>
+      <c r="AB38" s="24"/>
+      <c r="AC38" s="24"/>
+      <c r="AD38" s="24"/>
+      <c r="AE38" s="24"/>
+      <c r="AF38" s="24"/>
+      <c r="AG38" s="24"/>
     </row>
     <row r="39" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A39" s="26">
@@ -34235,96 +32017,36 @@
       <c r="C39" s="21">
         <v>38</v>
       </c>
-      <c r="D39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF39" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG39" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D39" s="24"/>
+      <c r="E39" s="24"/>
+      <c r="F39" s="24"/>
+      <c r="G39" s="24"/>
+      <c r="H39" s="24"/>
+      <c r="I39" s="24"/>
+      <c r="J39" s="24"/>
+      <c r="K39" s="24"/>
+      <c r="L39" s="24"/>
+      <c r="M39" s="24"/>
+      <c r="N39" s="24"/>
+      <c r="O39" s="24"/>
+      <c r="P39" s="24"/>
+      <c r="Q39" s="24"/>
+      <c r="R39" s="24"/>
+      <c r="S39" s="24"/>
+      <c r="T39" s="24"/>
+      <c r="U39" s="24"/>
+      <c r="V39" s="24"/>
+      <c r="W39" s="24"/>
+      <c r="X39" s="24"/>
+      <c r="Y39" s="24"/>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
+      <c r="AB39" s="24"/>
+      <c r="AC39" s="24"/>
+      <c r="AD39" s="24"/>
+      <c r="AE39" s="24"/>
+      <c r="AF39" s="24"/>
+      <c r="AG39" s="24"/>
     </row>
     <row r="40" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A40" s="26">
@@ -34336,96 +32058,36 @@
       <c r="C40" s="21">
         <v>39</v>
       </c>
-      <c r="D40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF40" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG40" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D40" s="24"/>
+      <c r="E40" s="24"/>
+      <c r="F40" s="24"/>
+      <c r="G40" s="24"/>
+      <c r="H40" s="24"/>
+      <c r="I40" s="24"/>
+      <c r="J40" s="24"/>
+      <c r="K40" s="24"/>
+      <c r="L40" s="24"/>
+      <c r="M40" s="24"/>
+      <c r="N40" s="24"/>
+      <c r="O40" s="24"/>
+      <c r="P40" s="24"/>
+      <c r="Q40" s="24"/>
+      <c r="R40" s="24"/>
+      <c r="S40" s="24"/>
+      <c r="T40" s="24"/>
+      <c r="U40" s="24"/>
+      <c r="V40" s="24"/>
+      <c r="W40" s="24"/>
+      <c r="X40" s="24"/>
+      <c r="Y40" s="24"/>
+      <c r="Z40" s="24"/>
+      <c r="AA40" s="24"/>
+      <c r="AB40" s="24"/>
+      <c r="AC40" s="24"/>
+      <c r="AD40" s="24"/>
+      <c r="AE40" s="24"/>
+      <c r="AF40" s="24"/>
+      <c r="AG40" s="24"/>
     </row>
     <row r="41" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A41" s="26">
@@ -34437,96 +32099,36 @@
       <c r="C41" s="21">
         <v>40</v>
       </c>
-      <c r="D41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF41" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG41" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D41" s="24"/>
+      <c r="E41" s="24"/>
+      <c r="F41" s="24"/>
+      <c r="G41" s="24"/>
+      <c r="H41" s="24"/>
+      <c r="I41" s="24"/>
+      <c r="J41" s="24"/>
+      <c r="K41" s="24"/>
+      <c r="L41" s="24"/>
+      <c r="M41" s="24"/>
+      <c r="N41" s="24"/>
+      <c r="O41" s="24"/>
+      <c r="P41" s="24"/>
+      <c r="Q41" s="24"/>
+      <c r="R41" s="24"/>
+      <c r="S41" s="24"/>
+      <c r="T41" s="24"/>
+      <c r="U41" s="24"/>
+      <c r="V41" s="24"/>
+      <c r="W41" s="24"/>
+      <c r="X41" s="24"/>
+      <c r="Y41" s="24"/>
+      <c r="Z41" s="24"/>
+      <c r="AA41" s="24"/>
+      <c r="AB41" s="24"/>
+      <c r="AC41" s="24"/>
+      <c r="AD41" s="24"/>
+      <c r="AE41" s="24"/>
+      <c r="AF41" s="24"/>
+      <c r="AG41" s="24"/>
     </row>
     <row r="42" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A42" s="26">
@@ -34538,96 +32140,36 @@
       <c r="C42" s="21">
         <v>41</v>
       </c>
-      <c r="D42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF42" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG42" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D42" s="24"/>
+      <c r="E42" s="24"/>
+      <c r="F42" s="24"/>
+      <c r="G42" s="24"/>
+      <c r="H42" s="24"/>
+      <c r="I42" s="24"/>
+      <c r="J42" s="24"/>
+      <c r="K42" s="24"/>
+      <c r="L42" s="24"/>
+      <c r="M42" s="24"/>
+      <c r="N42" s="24"/>
+      <c r="O42" s="24"/>
+      <c r="P42" s="24"/>
+      <c r="Q42" s="24"/>
+      <c r="R42" s="24"/>
+      <c r="S42" s="24"/>
+      <c r="T42" s="24"/>
+      <c r="U42" s="24"/>
+      <c r="V42" s="24"/>
+      <c r="W42" s="24"/>
+      <c r="X42" s="24"/>
+      <c r="Y42" s="24"/>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
+      <c r="AB42" s="24"/>
+      <c r="AC42" s="24"/>
+      <c r="AD42" s="24"/>
+      <c r="AE42" s="24"/>
+      <c r="AF42" s="24"/>
+      <c r="AG42" s="24"/>
     </row>
     <row r="43" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A43" s="26">
@@ -34639,96 +32181,36 @@
       <c r="C43" s="21">
         <v>42</v>
       </c>
-      <c r="D43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF43" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG43" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D43" s="24"/>
+      <c r="E43" s="24"/>
+      <c r="F43" s="24"/>
+      <c r="G43" s="24"/>
+      <c r="H43" s="24"/>
+      <c r="I43" s="24"/>
+      <c r="J43" s="24"/>
+      <c r="K43" s="24"/>
+      <c r="L43" s="24"/>
+      <c r="M43" s="24"/>
+      <c r="N43" s="24"/>
+      <c r="O43" s="24"/>
+      <c r="P43" s="24"/>
+      <c r="Q43" s="24"/>
+      <c r="R43" s="24"/>
+      <c r="S43" s="24"/>
+      <c r="T43" s="24"/>
+      <c r="U43" s="24"/>
+      <c r="V43" s="24"/>
+      <c r="W43" s="24"/>
+      <c r="X43" s="24"/>
+      <c r="Y43" s="24"/>
+      <c r="Z43" s="24"/>
+      <c r="AA43" s="24"/>
+      <c r="AB43" s="24"/>
+      <c r="AC43" s="24"/>
+      <c r="AD43" s="24"/>
+      <c r="AE43" s="24"/>
+      <c r="AF43" s="24"/>
+      <c r="AG43" s="24"/>
     </row>
     <row r="44" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A44" s="26">
@@ -34740,96 +32222,36 @@
       <c r="C44" s="21">
         <v>43</v>
       </c>
-      <c r="D44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF44" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG44" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D44" s="24"/>
+      <c r="E44" s="24"/>
+      <c r="F44" s="24"/>
+      <c r="G44" s="24"/>
+      <c r="H44" s="24"/>
+      <c r="I44" s="24"/>
+      <c r="J44" s="24"/>
+      <c r="K44" s="24"/>
+      <c r="L44" s="24"/>
+      <c r="M44" s="24"/>
+      <c r="N44" s="24"/>
+      <c r="O44" s="24"/>
+      <c r="P44" s="24"/>
+      <c r="Q44" s="24"/>
+      <c r="R44" s="24"/>
+      <c r="S44" s="24"/>
+      <c r="T44" s="24"/>
+      <c r="U44" s="24"/>
+      <c r="V44" s="24"/>
+      <c r="W44" s="24"/>
+      <c r="X44" s="24"/>
+      <c r="Y44" s="24"/>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
+      <c r="AB44" s="24"/>
+      <c r="AC44" s="24"/>
+      <c r="AD44" s="24"/>
+      <c r="AE44" s="24"/>
+      <c r="AF44" s="24"/>
+      <c r="AG44" s="24"/>
     </row>
     <row r="45" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A45" s="26">
@@ -34841,96 +32263,36 @@
       <c r="C45" s="21">
         <v>44</v>
       </c>
-      <c r="D45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF45" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG45" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D45" s="24"/>
+      <c r="E45" s="24"/>
+      <c r="F45" s="24"/>
+      <c r="G45" s="24"/>
+      <c r="H45" s="24"/>
+      <c r="I45" s="24"/>
+      <c r="J45" s="24"/>
+      <c r="K45" s="24"/>
+      <c r="L45" s="24"/>
+      <c r="M45" s="24"/>
+      <c r="N45" s="24"/>
+      <c r="O45" s="24"/>
+      <c r="P45" s="24"/>
+      <c r="Q45" s="24"/>
+      <c r="R45" s="24"/>
+      <c r="S45" s="24"/>
+      <c r="T45" s="24"/>
+      <c r="U45" s="24"/>
+      <c r="V45" s="24"/>
+      <c r="W45" s="24"/>
+      <c r="X45" s="24"/>
+      <c r="Y45" s="24"/>
+      <c r="Z45" s="24"/>
+      <c r="AA45" s="24"/>
+      <c r="AB45" s="24"/>
+      <c r="AC45" s="24"/>
+      <c r="AD45" s="24"/>
+      <c r="AE45" s="24"/>
+      <c r="AF45" s="24"/>
+      <c r="AG45" s="24"/>
     </row>
     <row r="46" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A46" s="26">
@@ -34942,96 +32304,36 @@
       <c r="C46" s="21">
         <v>45</v>
       </c>
-      <c r="D46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF46" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG46" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D46" s="24"/>
+      <c r="E46" s="24"/>
+      <c r="F46" s="24"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="24"/>
+      <c r="I46" s="24"/>
+      <c r="J46" s="24"/>
+      <c r="K46" s="24"/>
+      <c r="L46" s="24"/>
+      <c r="M46" s="24"/>
+      <c r="N46" s="24"/>
+      <c r="O46" s="24"/>
+      <c r="P46" s="24"/>
+      <c r="Q46" s="24"/>
+      <c r="R46" s="24"/>
+      <c r="S46" s="24"/>
+      <c r="T46" s="24"/>
+      <c r="U46" s="24"/>
+      <c r="V46" s="24"/>
+      <c r="W46" s="24"/>
+      <c r="X46" s="24"/>
+      <c r="Y46" s="24"/>
+      <c r="Z46" s="24"/>
+      <c r="AA46" s="24"/>
+      <c r="AB46" s="24"/>
+      <c r="AC46" s="24"/>
+      <c r="AD46" s="24"/>
+      <c r="AE46" s="24"/>
+      <c r="AF46" s="24"/>
+      <c r="AG46" s="24"/>
     </row>
     <row r="47" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A47" s="26">
@@ -35043,96 +32345,36 @@
       <c r="C47" s="21">
         <v>46</v>
       </c>
-      <c r="D47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF47" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG47" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D47" s="24"/>
+      <c r="E47" s="24"/>
+      <c r="F47" s="24"/>
+      <c r="G47" s="24"/>
+      <c r="H47" s="24"/>
+      <c r="I47" s="24"/>
+      <c r="J47" s="24"/>
+      <c r="K47" s="24"/>
+      <c r="L47" s="24"/>
+      <c r="M47" s="24"/>
+      <c r="N47" s="24"/>
+      <c r="O47" s="24"/>
+      <c r="P47" s="24"/>
+      <c r="Q47" s="24"/>
+      <c r="R47" s="24"/>
+      <c r="S47" s="24"/>
+      <c r="T47" s="24"/>
+      <c r="U47" s="24"/>
+      <c r="V47" s="24"/>
+      <c r="W47" s="24"/>
+      <c r="X47" s="24"/>
+      <c r="Y47" s="24"/>
+      <c r="Z47" s="24"/>
+      <c r="AA47" s="24"/>
+      <c r="AB47" s="24"/>
+      <c r="AC47" s="24"/>
+      <c r="AD47" s="24"/>
+      <c r="AE47" s="24"/>
+      <c r="AF47" s="24"/>
+      <c r="AG47" s="24"/>
     </row>
     <row r="48" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A48" s="26">
@@ -35144,96 +32386,36 @@
       <c r="C48" s="21">
         <v>47</v>
       </c>
-      <c r="D48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF48" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG48" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D48" s="24"/>
+      <c r="E48" s="24"/>
+      <c r="F48" s="24"/>
+      <c r="G48" s="24"/>
+      <c r="H48" s="24"/>
+      <c r="I48" s="24"/>
+      <c r="J48" s="24"/>
+      <c r="K48" s="24"/>
+      <c r="L48" s="24"/>
+      <c r="M48" s="24"/>
+      <c r="N48" s="24"/>
+      <c r="O48" s="24"/>
+      <c r="P48" s="24"/>
+      <c r="Q48" s="24"/>
+      <c r="R48" s="24"/>
+      <c r="S48" s="24"/>
+      <c r="T48" s="24"/>
+      <c r="U48" s="24"/>
+      <c r="V48" s="24"/>
+      <c r="W48" s="24"/>
+      <c r="X48" s="24"/>
+      <c r="Y48" s="24"/>
+      <c r="Z48" s="24"/>
+      <c r="AA48" s="24"/>
+      <c r="AB48" s="24"/>
+      <c r="AC48" s="24"/>
+      <c r="AD48" s="24"/>
+      <c r="AE48" s="24"/>
+      <c r="AF48" s="24"/>
+      <c r="AG48" s="24"/>
     </row>
     <row r="49" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A49" s="26">
@@ -35245,96 +32427,36 @@
       <c r="C49" s="21">
         <v>48</v>
       </c>
-      <c r="D49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF49" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG49" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D49" s="24"/>
+      <c r="E49" s="24"/>
+      <c r="F49" s="24"/>
+      <c r="G49" s="24"/>
+      <c r="H49" s="24"/>
+      <c r="I49" s="24"/>
+      <c r="J49" s="24"/>
+      <c r="K49" s="24"/>
+      <c r="L49" s="24"/>
+      <c r="M49" s="24"/>
+      <c r="N49" s="24"/>
+      <c r="O49" s="24"/>
+      <c r="P49" s="24"/>
+      <c r="Q49" s="24"/>
+      <c r="R49" s="24"/>
+      <c r="S49" s="24"/>
+      <c r="T49" s="24"/>
+      <c r="U49" s="24"/>
+      <c r="V49" s="24"/>
+      <c r="W49" s="24"/>
+      <c r="X49" s="24"/>
+      <c r="Y49" s="24"/>
+      <c r="Z49" s="24"/>
+      <c r="AA49" s="24"/>
+      <c r="AB49" s="24"/>
+      <c r="AC49" s="24"/>
+      <c r="AD49" s="24"/>
+      <c r="AE49" s="24"/>
+      <c r="AF49" s="24"/>
+      <c r="AG49" s="24"/>
     </row>
     <row r="50" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A50" s="26">
@@ -35346,96 +32468,36 @@
       <c r="C50" s="21">
         <v>49</v>
       </c>
-      <c r="D50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF50" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG50" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D50" s="24"/>
+      <c r="E50" s="24"/>
+      <c r="F50" s="24"/>
+      <c r="G50" s="24"/>
+      <c r="H50" s="24"/>
+      <c r="I50" s="24"/>
+      <c r="J50" s="24"/>
+      <c r="K50" s="24"/>
+      <c r="L50" s="24"/>
+      <c r="M50" s="24"/>
+      <c r="N50" s="24"/>
+      <c r="O50" s="24"/>
+      <c r="P50" s="24"/>
+      <c r="Q50" s="24"/>
+      <c r="R50" s="24"/>
+      <c r="S50" s="24"/>
+      <c r="T50" s="24"/>
+      <c r="U50" s="24"/>
+      <c r="V50" s="24"/>
+      <c r="W50" s="24"/>
+      <c r="X50" s="24"/>
+      <c r="Y50" s="24"/>
+      <c r="Z50" s="24"/>
+      <c r="AA50" s="24"/>
+      <c r="AB50" s="24"/>
+      <c r="AC50" s="24"/>
+      <c r="AD50" s="24"/>
+      <c r="AE50" s="24"/>
+      <c r="AF50" s="24"/>
+      <c r="AG50" s="24"/>
     </row>
     <row r="51" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A51" s="26">
@@ -35447,96 +32509,36 @@
       <c r="C51" s="21">
         <v>50</v>
       </c>
-      <c r="D51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF51" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG51" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D51" s="24"/>
+      <c r="E51" s="24"/>
+      <c r="F51" s="24"/>
+      <c r="G51" s="24"/>
+      <c r="H51" s="24"/>
+      <c r="I51" s="24"/>
+      <c r="J51" s="24"/>
+      <c r="K51" s="24"/>
+      <c r="L51" s="24"/>
+      <c r="M51" s="24"/>
+      <c r="N51" s="24"/>
+      <c r="O51" s="24"/>
+      <c r="P51" s="24"/>
+      <c r="Q51" s="24"/>
+      <c r="R51" s="24"/>
+      <c r="S51" s="24"/>
+      <c r="T51" s="24"/>
+      <c r="U51" s="24"/>
+      <c r="V51" s="24"/>
+      <c r="W51" s="24"/>
+      <c r="X51" s="24"/>
+      <c r="Y51" s="24"/>
+      <c r="Z51" s="24"/>
+      <c r="AA51" s="24"/>
+      <c r="AB51" s="24"/>
+      <c r="AC51" s="24"/>
+      <c r="AD51" s="24"/>
+      <c r="AE51" s="24"/>
+      <c r="AF51" s="24"/>
+      <c r="AG51" s="24"/>
     </row>
     <row r="52" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A52" s="26">
@@ -35548,96 +32550,36 @@
       <c r="C52" s="21">
         <v>51</v>
       </c>
-      <c r="D52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF52" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG52" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D52" s="24"/>
+      <c r="E52" s="24"/>
+      <c r="F52" s="24"/>
+      <c r="G52" s="24"/>
+      <c r="H52" s="24"/>
+      <c r="I52" s="24"/>
+      <c r="J52" s="24"/>
+      <c r="K52" s="24"/>
+      <c r="L52" s="24"/>
+      <c r="M52" s="24"/>
+      <c r="N52" s="24"/>
+      <c r="O52" s="24"/>
+      <c r="P52" s="24"/>
+      <c r="Q52" s="24"/>
+      <c r="R52" s="24"/>
+      <c r="S52" s="24"/>
+      <c r="T52" s="24"/>
+      <c r="U52" s="24"/>
+      <c r="V52" s="24"/>
+      <c r="W52" s="24"/>
+      <c r="X52" s="24"/>
+      <c r="Y52" s="24"/>
+      <c r="Z52" s="24"/>
+      <c r="AA52" s="24"/>
+      <c r="AB52" s="24"/>
+      <c r="AC52" s="24"/>
+      <c r="AD52" s="24"/>
+      <c r="AE52" s="24"/>
+      <c r="AF52" s="24"/>
+      <c r="AG52" s="24"/>
     </row>
     <row r="53" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A53" s="26">
@@ -35649,96 +32591,36 @@
       <c r="C53" s="21">
         <v>52</v>
       </c>
-      <c r="D53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF53" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG53" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D53" s="24"/>
+      <c r="E53" s="24"/>
+      <c r="F53" s="24"/>
+      <c r="G53" s="24"/>
+      <c r="H53" s="24"/>
+      <c r="I53" s="24"/>
+      <c r="J53" s="24"/>
+      <c r="K53" s="24"/>
+      <c r="L53" s="24"/>
+      <c r="M53" s="24"/>
+      <c r="N53" s="24"/>
+      <c r="O53" s="24"/>
+      <c r="P53" s="24"/>
+      <c r="Q53" s="24"/>
+      <c r="R53" s="24"/>
+      <c r="S53" s="24"/>
+      <c r="T53" s="24"/>
+      <c r="U53" s="24"/>
+      <c r="V53" s="24"/>
+      <c r="W53" s="24"/>
+      <c r="X53" s="24"/>
+      <c r="Y53" s="24"/>
+      <c r="Z53" s="24"/>
+      <c r="AA53" s="24"/>
+      <c r="AB53" s="24"/>
+      <c r="AC53" s="24"/>
+      <c r="AD53" s="24"/>
+      <c r="AE53" s="24"/>
+      <c r="AF53" s="24"/>
+      <c r="AG53" s="24"/>
     </row>
     <row r="54" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A54" s="26">
@@ -35750,96 +32632,36 @@
       <c r="C54" s="21">
         <v>53</v>
       </c>
-      <c r="D54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="E54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="F54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="G54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="H54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="I54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="J54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="K54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="L54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="M54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="N54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="O54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="P54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Q54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="R54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="S54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="T54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="U54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="V54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="W54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="X54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Y54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="Z54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AA54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AB54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AC54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AD54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AE54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AF54" s="24">
-        <v>0.99</v>
-      </c>
-      <c r="AG54" s="24">
-        <v>0.99</v>
-      </c>
+      <c r="D54" s="24"/>
+      <c r="E54" s="24"/>
+      <c r="F54" s="24"/>
+      <c r="G54" s="24"/>
+      <c r="H54" s="24"/>
+      <c r="I54" s="24"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="24"/>
+      <c r="N54" s="24"/>
+      <c r="O54" s="24"/>
+      <c r="P54" s="24"/>
+      <c r="Q54" s="24"/>
+      <c r="R54" s="24"/>
+      <c r="S54" s="24"/>
+      <c r="T54" s="24"/>
+      <c r="U54" s="24"/>
+      <c r="V54" s="24"/>
+      <c r="W54" s="24"/>
+      <c r="X54" s="24"/>
+      <c r="Y54" s="24"/>
+      <c r="Z54" s="24"/>
+      <c r="AA54" s="24"/>
+      <c r="AB54" s="24"/>
+      <c r="AC54" s="24"/>
+      <c r="AD54" s="24"/>
+      <c r="AE54" s="24"/>
+      <c r="AF54" s="24"/>
+      <c r="AG54" s="24"/>
     </row>
     <row r="55" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A55" s="26">
@@ -35851,95 +32673,89 @@
       <c r="C55" s="21">
         <v>1</v>
       </c>
-      <c r="D55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="E55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="F55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="G55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="H55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="I55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="J55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="K55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="L55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="M55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="N55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="O55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="P55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Q55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="R55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="S55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="T55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="U55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="V55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="W55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="X55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Y55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Z55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AA55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AB55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AC55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AD55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AE55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AF55" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AG55" s="24">
-        <v>0.65</v>
+      <c r="D55" s="25">
+        <v>0.95666666666666667</v>
+      </c>
+      <c r="E55" s="25">
+        <v>0.93442622950819676</v>
+      </c>
+      <c r="F55" s="25">
+        <v>0.98689384010484926</v>
+      </c>
+      <c r="G55" s="25">
+        <v>0.89583333333333337</v>
+      </c>
+      <c r="H55" s="25"/>
+      <c r="I55" s="25">
+        <v>1</v>
+      </c>
+      <c r="J55" s="25">
+        <v>0.87368421052631584</v>
+      </c>
+      <c r="K55" s="25">
+        <v>0.95497630331753558</v>
+      </c>
+      <c r="L55" s="25">
+        <v>1</v>
+      </c>
+      <c r="M55" s="25">
+        <v>0.90099009900990101</v>
+      </c>
+      <c r="N55" s="25">
+        <v>1</v>
+      </c>
+      <c r="O55" s="25">
+        <v>1</v>
+      </c>
+      <c r="P55" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q55" s="25">
+        <v>1</v>
+      </c>
+      <c r="R55" s="25">
+        <v>1</v>
+      </c>
+      <c r="S55" s="25">
+        <v>1</v>
+      </c>
+      <c r="T55" s="25">
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="U55" s="25">
+        <v>0.83552631578947367</v>
+      </c>
+      <c r="V55" s="25">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="W55" s="25">
+        <v>1</v>
+      </c>
+      <c r="X55" s="25">
+        <v>0.92561983471074383</v>
+      </c>
+      <c r="Y55" s="25">
+        <v>0.97499999999999998</v>
+      </c>
+      <c r="Z55" s="25"/>
+      <c r="AA55" s="25"/>
+      <c r="AB55" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC55" s="25">
+        <v>1</v>
+      </c>
+      <c r="AD55" s="25">
+        <v>0.90099009900990101</v>
+      </c>
+      <c r="AE55" s="25">
+        <v>1</v>
+      </c>
+      <c r="AF55" s="25">
+        <v>1</v>
+      </c>
+      <c r="AG55" s="25">
+        <v>1</v>
       </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
@@ -35952,95 +32768,89 @@
       <c r="C56" s="21">
         <v>2</v>
       </c>
-      <c r="D56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="E56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="F56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="G56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="H56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="I56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="J56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="K56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="L56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="M56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="N56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="O56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="P56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Q56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="R56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="S56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="T56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="U56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="V56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="W56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="X56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Y56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Z56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AA56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AB56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AC56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AD56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AE56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AF56" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AG56" s="24">
-        <v>0.65</v>
+      <c r="D56" s="25">
+        <v>0.88729703915950331</v>
+      </c>
+      <c r="E56" s="25">
+        <v>0.83796033994334274</v>
+      </c>
+      <c r="F56" s="25">
+        <v>0.95058139534883723</v>
+      </c>
+      <c r="G56" s="25">
+        <v>0.77506112469437649</v>
+      </c>
+      <c r="H56" s="25"/>
+      <c r="I56" s="25">
+        <v>0.9753363228699552</v>
+      </c>
+      <c r="J56" s="25">
+        <v>0.69543147208121825</v>
+      </c>
+      <c r="K56" s="25">
+        <v>0.87790697674418605</v>
+      </c>
+      <c r="L56" s="25">
+        <v>0.91238670694864044</v>
+      </c>
+      <c r="M56" s="25">
+        <v>0.81067961165048541</v>
+      </c>
+      <c r="N56" s="25">
+        <v>1</v>
+      </c>
+      <c r="O56" s="25">
+        <v>1</v>
+      </c>
+      <c r="P56" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q56" s="25">
+        <v>0.85253456221198154</v>
+      </c>
+      <c r="R56" s="25">
+        <v>1</v>
+      </c>
+      <c r="S56" s="25">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="T56" s="25">
+        <v>0.9</v>
+      </c>
+      <c r="U56" s="25">
+        <v>0.6875</v>
+      </c>
+      <c r="V56" s="25">
+        <v>0.78260869565217395</v>
+      </c>
+      <c r="W56" s="25">
+        <v>0.95154185022026427</v>
+      </c>
+      <c r="X56" s="25">
+        <v>0.59893048128342241</v>
+      </c>
+      <c r="Y56" s="25">
+        <v>0.75</v>
+      </c>
+      <c r="Z56" s="25"/>
+      <c r="AA56" s="25"/>
+      <c r="AB56" s="25">
+        <v>1</v>
+      </c>
+      <c r="AC56" s="25">
+        <v>1</v>
+      </c>
+      <c r="AD56" s="25">
+        <v>0.81067961165048541</v>
+      </c>
+      <c r="AE56" s="25">
+        <v>1</v>
+      </c>
+      <c r="AF56" s="25">
+        <v>1</v>
+      </c>
+      <c r="AG56" s="25">
+        <v>1</v>
       </c>
     </row>
     <row r="57" spans="1:33" x14ac:dyDescent="0.25">
@@ -36053,95 +32863,89 @@
       <c r="C57" s="21">
         <v>3</v>
       </c>
-      <c r="D57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="E57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="F57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="G57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="H57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="I57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="J57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="K57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="L57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="M57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="N57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="O57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="P57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Q57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="R57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="S57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="T57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="U57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="V57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="W57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="X57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Y57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="Z57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AA57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AB57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AC57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AD57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AE57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AF57" s="24">
-        <v>0.65</v>
-      </c>
-      <c r="AG57" s="24">
-        <v>0.65</v>
+      <c r="D57" s="25">
+        <v>0.85260770975056688</v>
+      </c>
+      <c r="E57" s="25">
+        <v>0.81595092024539873</v>
+      </c>
+      <c r="F57" s="25">
+        <v>0.87815305686190681</v>
+      </c>
+      <c r="G57" s="25">
+        <v>0.5662650602409639</v>
+      </c>
+      <c r="H57" s="25"/>
+      <c r="I57" s="25">
+        <v>0.97330595482546201</v>
+      </c>
+      <c r="J57" s="25">
+        <v>0.79002624671916011</v>
+      </c>
+      <c r="K57" s="25">
+        <v>0.85348837209302331</v>
+      </c>
+      <c r="L57" s="25">
+        <v>0.80538922155688619</v>
+      </c>
+      <c r="M57" s="25">
+        <v>0.57765667574931878</v>
+      </c>
+      <c r="N57" s="25">
+        <v>1</v>
+      </c>
+      <c r="O57" s="25">
+        <v>1</v>
+      </c>
+      <c r="P57" s="25">
+        <v>1</v>
+      </c>
+      <c r="Q57" s="25">
+        <v>0.70731707317073167</v>
+      </c>
+      <c r="R57" s="25">
+        <v>1</v>
+      </c>
+      <c r="S57" s="25">
+        <v>0.94936708860759489</v>
+      </c>
+      <c r="T57" s="25">
+        <v>0.82653061224489799</v>
+      </c>
+      <c r="U57" s="25">
+        <v>0.52</v>
+      </c>
+      <c r="V57" s="25">
+        <v>0.84</v>
+      </c>
+      <c r="W57" s="25">
+        <v>0.96036585365853655</v>
+      </c>
+      <c r="X57" s="25">
+        <v>0.765625</v>
+      </c>
+      <c r="Y57" s="25">
+        <v>0.7816091954022989</v>
+      </c>
+      <c r="Z57" s="25"/>
+      <c r="AA57" s="25"/>
+      <c r="AB57" s="25">
+        <v>0.99667774086378735</v>
+      </c>
+      <c r="AC57" s="25">
+        <v>0.99667774086378735</v>
+      </c>
+      <c r="AD57" s="25">
+        <v>0.57765667574931878</v>
+      </c>
+      <c r="AE57" s="25">
+        <v>1</v>
+      </c>
+      <c r="AF57" s="25">
+        <v>1</v>
+      </c>
+      <c r="AG57" s="25">
+        <v>1</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
@@ -36155,94 +32959,88 @@
         <v>4</v>
       </c>
       <c r="D58" s="25">
-        <v>0.65</v>
+        <v>0.9053384700055036</v>
       </c>
       <c r="E58" s="25">
-        <v>0.65</v>
+        <v>0.80897009966777411</v>
       </c>
       <c r="F58" s="25">
-        <v>0.65</v>
+        <v>0.95308641975308639</v>
       </c>
       <c r="G58" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H58" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.80612244897959184</v>
+      </c>
+      <c r="H58" s="25"/>
       <c r="I58" s="25">
-        <v>0.65</v>
+        <v>0.88947368421052631</v>
       </c>
       <c r="J58" s="25">
-        <v>0.65</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="K58" s="25">
-        <v>0.65</v>
+        <v>0.70434782608695656</v>
       </c>
       <c r="L58" s="25">
-        <v>0.65</v>
+        <v>0.77734375</v>
       </c>
       <c r="M58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q58" s="25">
-        <v>0.65</v>
+        <v>0.64814814814814814</v>
       </c>
       <c r="R58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T58" s="25">
-        <v>0.65</v>
+        <v>0.33783783783783783</v>
       </c>
       <c r="U58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="V58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W58" s="25">
-        <v>0.65</v>
+        <v>0.79207920792079212</v>
       </c>
       <c r="X58" s="25">
-        <v>0.65</v>
+        <v>0.81578947368421051</v>
       </c>
       <c r="Y58" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z58" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA58" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.80412371134020622</v>
+      </c>
+      <c r="Z58" s="25"/>
+      <c r="AA58" s="25"/>
       <c r="AB58" s="25">
-        <v>0.65</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AC58" s="25">
-        <v>0.65</v>
+        <v>0.76923076923076927</v>
       </c>
       <c r="AD58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG58" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
@@ -36256,94 +33054,88 @@
         <v>5</v>
       </c>
       <c r="D59" s="25">
-        <v>0.65</v>
+        <v>0.90735975295934124</v>
       </c>
       <c r="E59" s="25">
-        <v>0.65</v>
+        <v>0.84723523898781627</v>
       </c>
       <c r="F59" s="25">
-        <v>0.65</v>
+        <v>0.98059360730593603</v>
       </c>
       <c r="G59" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H59" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.60557768924302791</v>
+      </c>
+      <c r="H59" s="25"/>
       <c r="I59" s="25">
-        <v>0.65</v>
+        <v>0.92519685039370081</v>
       </c>
       <c r="J59" s="25">
-        <v>0.65</v>
+        <v>0.89855072463768115</v>
       </c>
       <c r="K59" s="25">
-        <v>0.65</v>
+        <v>0.93239436619718308</v>
       </c>
       <c r="L59" s="25">
-        <v>0.65</v>
+        <v>0.94158075601374569</v>
       </c>
       <c r="M59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q59" s="25">
-        <v>0.65</v>
+        <v>0.77272727272727271</v>
       </c>
       <c r="R59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T59" s="25">
-        <v>0.65</v>
+        <v>0.87037037037037035</v>
       </c>
       <c r="U59" s="25">
-        <v>0.65</v>
+        <v>0.47517730496453903</v>
       </c>
       <c r="V59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W59" s="25">
-        <v>0.65</v>
+        <v>0.86131386861313863</v>
       </c>
       <c r="X59" s="25">
-        <v>0.65</v>
+        <v>0.78350515463917525</v>
       </c>
       <c r="Y59" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z59" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA59" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.92805755395683454</v>
+      </c>
+      <c r="Z59" s="25"/>
+      <c r="AA59" s="25"/>
       <c r="AB59" s="25">
-        <v>0.65</v>
+        <v>0.9550561797752809</v>
       </c>
       <c r="AC59" s="25">
-        <v>0.65</v>
+        <v>0.9550561797752809</v>
       </c>
       <c r="AD59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG59" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
@@ -36357,94 +33149,88 @@
         <v>6</v>
       </c>
       <c r="D60" s="25">
-        <v>0.65</v>
+        <v>0.93688293370944997</v>
       </c>
       <c r="E60" s="25">
-        <v>0.65</v>
+        <v>0.89346246973365617</v>
       </c>
       <c r="F60" s="25">
-        <v>0.65</v>
+        <v>0.99746621621621623</v>
       </c>
       <c r="G60" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H60" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.65957446808510634</v>
+      </c>
+      <c r="H60" s="25"/>
       <c r="I60" s="25">
-        <v>0.65</v>
+        <v>0.9555555555555556</v>
       </c>
       <c r="J60" s="25">
-        <v>0.65</v>
+        <v>0.93800539083557954</v>
       </c>
       <c r="K60" s="25">
-        <v>0.65</v>
+        <v>0.98348623853211015</v>
       </c>
       <c r="L60" s="25">
-        <v>0.65</v>
+        <v>0.99022801302931596</v>
       </c>
       <c r="M60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q60" s="25">
-        <v>0.65</v>
+        <v>0.5901639344262295</v>
       </c>
       <c r="R60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S60" s="25">
-        <v>0.65</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="T60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="U60" s="25">
-        <v>0.65</v>
+        <v>0.72538860103626945</v>
       </c>
       <c r="V60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W60" s="25">
-        <v>0.65</v>
+        <v>0.9211822660098522</v>
       </c>
       <c r="X60" s="25">
-        <v>0.65</v>
+        <v>0.87222222222222223</v>
       </c>
       <c r="Y60" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z60" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA60" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.99397590361445787</v>
+      </c>
+      <c r="Z60" s="25"/>
+      <c r="AA60" s="25"/>
       <c r="AB60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AC60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AD60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG60" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
@@ -36458,94 +33244,88 @@
         <v>7</v>
       </c>
       <c r="D61" s="25">
-        <v>0.65</v>
+        <v>0.86409209060527292</v>
       </c>
       <c r="E61" s="25">
-        <v>0.65</v>
+        <v>0.78024852844996728</v>
       </c>
       <c r="F61" s="25">
-        <v>0.65</v>
+        <v>0.97422680412371132</v>
       </c>
       <c r="G61" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H61" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.58895705521472397</v>
+      </c>
+      <c r="H61" s="25"/>
       <c r="I61" s="25">
-        <v>0.65</v>
+        <v>0.96460176991150437</v>
       </c>
       <c r="J61" s="25">
-        <v>0.65</v>
+        <v>0.72222222222222221</v>
       </c>
       <c r="K61" s="25">
-        <v>0.65</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="L61" s="25">
-        <v>0.65</v>
+        <v>0.90384615384615385</v>
       </c>
       <c r="M61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q61" s="25">
-        <v>0.65</v>
+        <v>0.70714285714285718</v>
       </c>
       <c r="R61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S61" s="25">
-        <v>0.65</v>
+        <v>0.89729729729729735</v>
       </c>
       <c r="T61" s="25">
-        <v>0.65</v>
+        <v>0.76315789473684215</v>
       </c>
       <c r="U61" s="25">
-        <v>0.65</v>
+        <v>0.5</v>
       </c>
       <c r="V61" s="25">
-        <v>0.65</v>
+        <v>0.93888888888888888</v>
       </c>
       <c r="W61" s="25">
-        <v>0.65</v>
+        <v>0.93617021276595747</v>
       </c>
       <c r="X61" s="25">
-        <v>0.65</v>
+        <v>0.50555555555555554</v>
       </c>
       <c r="Y61" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z61" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA61" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.79041916167664672</v>
+      </c>
+      <c r="Z61" s="25"/>
+      <c r="AA61" s="25"/>
       <c r="AB61" s="25">
-        <v>0.65</v>
+        <v>0.90099009900990101</v>
       </c>
       <c r="AC61" s="25">
-        <v>0.65</v>
+        <v>0.90099009900990101</v>
       </c>
       <c r="AD61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG61" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
@@ -36559,94 +33339,88 @@
         <v>8</v>
       </c>
       <c r="D62" s="25">
-        <v>0.65</v>
+        <v>0.87221795855717577</v>
       </c>
       <c r="E62" s="25">
-        <v>0.65</v>
+        <v>0.76339969372128635</v>
       </c>
       <c r="F62" s="25">
-        <v>0.65</v>
+        <v>0.98153846153846158</v>
       </c>
       <c r="G62" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H62" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.47546012269938648</v>
+      </c>
+      <c r="H62" s="25"/>
       <c r="I62" s="25">
-        <v>0.65</v>
+        <v>0.96616541353383456</v>
       </c>
       <c r="J62" s="25">
-        <v>0.65</v>
+        <v>0.78498293515358364</v>
       </c>
       <c r="K62" s="25">
-        <v>0.65</v>
+        <v>0.84323040380047509</v>
       </c>
       <c r="L62" s="25">
-        <v>0.65</v>
+        <v>0.93548387096774188</v>
       </c>
       <c r="M62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q62" s="25">
-        <v>0.65</v>
+        <v>0.44230769230769229</v>
       </c>
       <c r="R62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T62" s="25">
-        <v>0.65</v>
+        <v>0.72</v>
       </c>
       <c r="U62" s="25">
-        <v>0.65</v>
+        <v>0.50588235294117645</v>
       </c>
       <c r="V62" s="25">
-        <v>0.65</v>
+        <v>0.8828125</v>
       </c>
       <c r="W62" s="25">
-        <v>0.65</v>
+        <v>0.94478527607361962</v>
       </c>
       <c r="X62" s="25">
-        <v>0.65</v>
+        <v>0.70909090909090911</v>
       </c>
       <c r="Y62" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z62" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA62" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.85833333333333328</v>
+      </c>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
       <c r="AB62" s="25">
-        <v>0.65</v>
+        <v>0.95437262357414454</v>
       </c>
       <c r="AC62" s="25">
-        <v>0.65</v>
+        <v>0.95437262357414454</v>
       </c>
       <c r="AD62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG62" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
@@ -36660,94 +33434,88 @@
         <v>9</v>
       </c>
       <c r="D63" s="25">
-        <v>0.65</v>
+        <v>0.87090558766859349</v>
       </c>
       <c r="E63" s="25">
-        <v>0.65</v>
+        <v>0.81019978969505779</v>
       </c>
       <c r="F63" s="25">
-        <v>0.65</v>
+        <v>0.93760831889081453</v>
       </c>
       <c r="G63" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H63" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.48614609571788414</v>
+      </c>
+      <c r="H63" s="25"/>
       <c r="I63" s="25">
-        <v>0.65</v>
+        <v>0.95668549905838041</v>
       </c>
       <c r="J63" s="25">
-        <v>0.65</v>
+        <v>0.80281690140845074</v>
       </c>
       <c r="K63" s="25">
-        <v>0.65</v>
+        <v>0.8966074313408724</v>
       </c>
       <c r="L63" s="25">
-        <v>0.65</v>
+        <v>0.78137651821862353</v>
       </c>
       <c r="M63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q63" s="25">
-        <v>0.65</v>
+        <v>0.43684210526315792</v>
       </c>
       <c r="R63" s="25">
-        <v>0.65</v>
+        <v>0.97549019607843135</v>
       </c>
       <c r="S63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T63" s="25">
-        <v>0.65</v>
+        <v>0.69953051643192488</v>
       </c>
       <c r="U63" s="25">
-        <v>0.65</v>
+        <v>0.53140096618357491</v>
       </c>
       <c r="V63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W63" s="25">
-        <v>0.65</v>
+        <v>0.94495412844036697</v>
       </c>
       <c r="X63" s="25">
-        <v>0.65</v>
+        <v>0.6428571428571429</v>
       </c>
       <c r="Y63" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z63" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA63" s="25">
-        <v>0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z63" s="25"/>
+      <c r="AA63" s="25"/>
       <c r="AB63" s="25">
-        <v>0.65</v>
+        <v>0.96577946768060841</v>
       </c>
       <c r="AC63" s="25">
-        <v>0.65</v>
+        <v>0.96577946768060841</v>
       </c>
       <c r="AD63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG63" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
@@ -36761,94 +33529,88 @@
         <v>10</v>
       </c>
       <c r="D64" s="25">
-        <v>0.65</v>
+        <v>0.93643358982937441</v>
       </c>
       <c r="E64" s="25">
-        <v>0.65</v>
+        <v>0.94061433447098974</v>
       </c>
       <c r="F64" s="25">
-        <v>0.65</v>
+        <v>0.9324146981627297</v>
       </c>
       <c r="G64" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H64" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.82704402515723274</v>
+      </c>
+      <c r="H64" s="25"/>
       <c r="I64" s="25">
-        <v>0.65</v>
+        <v>0.96675900277008309</v>
       </c>
       <c r="J64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="K64" s="25">
-        <v>0.65</v>
+        <v>0.95975855130784704</v>
       </c>
       <c r="L64" s="25">
-        <v>0.65</v>
+        <v>0.78315789473684205</v>
       </c>
       <c r="M64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q64" s="25">
-        <v>0.65</v>
+        <v>0.62328767123287676</v>
       </c>
       <c r="R64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S64" s="25">
-        <v>0.65</v>
+        <v>0.89690721649484539</v>
       </c>
       <c r="T64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="U64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="V64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W64" s="25">
-        <v>0.65</v>
+        <v>0.9452054794520548</v>
       </c>
       <c r="X64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Y64" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z64" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA64" s="25">
-        <v>0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z64" s="25"/>
+      <c r="AA64" s="25"/>
       <c r="AB64" s="25">
-        <v>0.65</v>
+        <v>0.69918699186991873</v>
       </c>
       <c r="AC64" s="25">
-        <v>0.65</v>
+        <v>0.69918699186991873</v>
       </c>
       <c r="AD64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG64" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
@@ -36862,94 +33624,88 @@
         <v>11</v>
       </c>
       <c r="D65" s="25">
-        <v>0.65</v>
+        <v>0.92770167427701677</v>
       </c>
       <c r="E65" s="25">
-        <v>0.65</v>
+        <v>0.90863668807994291</v>
       </c>
       <c r="F65" s="25">
-        <v>0.65</v>
+        <v>0.94947025264873675</v>
       </c>
       <c r="G65" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H65" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.83809523809523812</v>
+      </c>
+      <c r="H65" s="25"/>
       <c r="I65" s="25">
-        <v>0.65</v>
+        <v>0.96107784431137722</v>
       </c>
       <c r="J65" s="25">
-        <v>0.65</v>
+        <v>0.79203539823008851</v>
       </c>
       <c r="K65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="L65" s="25">
-        <v>0.65</v>
+        <v>0.80064308681672025</v>
       </c>
       <c r="M65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q65" s="25">
-        <v>0.65</v>
+        <v>0.66502463054187189</v>
       </c>
       <c r="R65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="U65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="V65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W65" s="25">
-        <v>0.65</v>
+        <v>0.93229166666666663</v>
       </c>
       <c r="X65" s="25">
-        <v>0.65</v>
+        <v>0.61157024793388426</v>
       </c>
       <c r="Y65" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z65" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA65" s="25">
-        <v>0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z65" s="25"/>
+      <c r="AA65" s="25"/>
       <c r="AB65" s="25">
-        <v>0.65</v>
+        <v>0.80519480519480524</v>
       </c>
       <c r="AC65" s="25">
-        <v>0.65</v>
+        <v>0.80519480519480524</v>
       </c>
       <c r="AD65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG65" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
@@ -36963,94 +33719,88 @@
         <v>12</v>
       </c>
       <c r="D66" s="25">
-        <v>0.65</v>
+        <v>0.90578455143747838</v>
       </c>
       <c r="E66" s="25">
-        <v>0.65</v>
+        <v>0.82450592885375495</v>
       </c>
       <c r="F66" s="25">
-        <v>0.65</v>
+        <v>0.96917385943279899</v>
       </c>
       <c r="G66" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H66" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.69152542372881354</v>
+      </c>
+      <c r="H66" s="25"/>
       <c r="I66" s="25">
-        <v>0.65</v>
+        <v>0.87573964497041423</v>
       </c>
       <c r="J66" s="25">
-        <v>0.65</v>
+        <v>0.73015873015873012</v>
       </c>
       <c r="K66" s="25">
-        <v>0.65</v>
+        <v>0.91422121896162534</v>
       </c>
       <c r="L66" s="25">
-        <v>0.65</v>
+        <v>0.88290398126463698</v>
       </c>
       <c r="M66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q66" s="25">
-        <v>0.65</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="R66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S66" s="25">
-        <v>0.65</v>
+        <v>0.93714285714285717</v>
       </c>
       <c r="T66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="U66" s="25">
-        <v>0.65</v>
+        <v>0.27272727272727271</v>
       </c>
       <c r="V66" s="25">
-        <v>0.65</v>
+        <v>0.94545454545454544</v>
       </c>
       <c r="W66" s="25">
-        <v>0.65</v>
+        <v>0.81578947368421051</v>
       </c>
       <c r="X66" s="25">
-        <v>0.65</v>
+        <v>0.64179104477611937</v>
       </c>
       <c r="Y66" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z66" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA66" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.75</v>
+      </c>
+      <c r="Z66" s="25"/>
+      <c r="AA66" s="25"/>
       <c r="AB66" s="25">
-        <v>0.65</v>
+        <v>0.82014388489208634</v>
       </c>
       <c r="AC66" s="25">
-        <v>0.65</v>
+        <v>0.82014388489208634</v>
       </c>
       <c r="AD66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG66" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
@@ -37064,94 +33814,88 @@
         <v>13</v>
       </c>
       <c r="D67" s="25">
-        <v>0.65</v>
+        <v>0.92393579902302858</v>
       </c>
       <c r="E67" s="25">
-        <v>0.65</v>
+        <v>0.87702037947997191</v>
       </c>
       <c r="F67" s="25">
-        <v>0.65</v>
+        <v>0.97020097020097018</v>
       </c>
       <c r="G67" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H67" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.93442622950819676</v>
+      </c>
+      <c r="H67" s="25"/>
       <c r="I67" s="25">
-        <v>0.65</v>
+        <v>0.89572192513368987</v>
       </c>
       <c r="J67" s="25">
-        <v>0.65</v>
+        <v>0.797583081570997</v>
       </c>
       <c r="K67" s="25">
-        <v>0.65</v>
+        <v>0.8934579439252337</v>
       </c>
       <c r="L67" s="25">
-        <v>0.65</v>
+        <v>0.89613526570048307</v>
       </c>
       <c r="M67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="R67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T67" s="25">
-        <v>0.65</v>
+        <v>0.80113636363636365</v>
       </c>
       <c r="U67" s="25">
-        <v>0.65</v>
+        <v>0.67567567567567566</v>
       </c>
       <c r="V67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W67" s="25">
-        <v>0.65</v>
+        <v>0.84146341463414631</v>
       </c>
       <c r="X67" s="25">
-        <v>0.65</v>
+        <v>0.63586956521739135</v>
       </c>
       <c r="Y67" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z67" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA67" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.86585365853658536</v>
+      </c>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="25"/>
       <c r="AB67" s="25">
-        <v>0.65</v>
+        <v>0.94396551724137934</v>
       </c>
       <c r="AC67" s="25">
-        <v>0.65</v>
+        <v>0.94396551724137934</v>
       </c>
       <c r="AD67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG67" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
@@ -37165,94 +33909,88 @@
         <v>14</v>
       </c>
       <c r="D68" s="25">
-        <v>0.65</v>
+        <v>0.97525977238990602</v>
       </c>
       <c r="E68" s="25">
-        <v>0.65</v>
+        <v>0.96332863187588147</v>
       </c>
       <c r="F68" s="25">
-        <v>0.65</v>
+        <v>0.98170731707317072</v>
       </c>
       <c r="G68" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H68" s="25">
-        <v>0.65</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H68" s="25"/>
       <c r="I68" s="25">
-        <v>0.65</v>
+        <v>0.98224852071005919</v>
       </c>
       <c r="J68" s="25">
-        <v>0.65</v>
+        <v>0.94666666666666666</v>
       </c>
       <c r="K68" s="25">
-        <v>0.65</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="L68" s="25">
-        <v>0.65</v>
+        <v>0.92920353982300885</v>
       </c>
       <c r="M68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="R68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="T68" s="25">
-        <v>0.65</v>
+        <v>0.92727272727272725</v>
       </c>
       <c r="U68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="V68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W68" s="25">
-        <v>0.65</v>
+        <v>0.97</v>
       </c>
       <c r="X68" s="25">
-        <v>0.65</v>
+        <v>0.9</v>
       </c>
       <c r="Y68" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z68" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA68" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="25"/>
       <c r="AB68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AC68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AD68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG68" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
@@ -37266,94 +34004,88 @@
         <v>15</v>
       </c>
       <c r="D69" s="25">
-        <v>0.65</v>
+        <v>0.89869753979739508</v>
       </c>
       <c r="E69" s="25">
-        <v>0.65</v>
+        <v>0.84487179487179487</v>
       </c>
       <c r="F69" s="25">
-        <v>0.65</v>
+        <v>0.96843853820598003</v>
       </c>
       <c r="G69" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H69" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.87362637362637363</v>
+      </c>
+      <c r="H69" s="25"/>
       <c r="I69" s="25">
-        <v>0.65</v>
+        <v>0.86413043478260865</v>
       </c>
       <c r="J69" s="25">
-        <v>0.65</v>
+        <v>0.86206896551724133</v>
       </c>
       <c r="K69" s="25">
-        <v>0.65</v>
+        <v>0.80297397769516732</v>
       </c>
       <c r="L69" s="25">
-        <v>0.65</v>
+        <v>0.89617486338797814</v>
       </c>
       <c r="M69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q69" s="25">
-        <v>0.65</v>
+        <v>0.71604938271604934</v>
       </c>
       <c r="R69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S69" s="25">
-        <v>0.65</v>
+        <v>0.82278481012658233</v>
       </c>
       <c r="T69" s="25">
-        <v>0.65</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="U69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="V69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="W69" s="25">
-        <v>0.65</v>
+        <v>0.71264367816091956</v>
       </c>
       <c r="X69" s="25">
-        <v>0.65</v>
+        <v>0.76744186046511631</v>
       </c>
       <c r="Y69" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z69" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA69" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="Z69" s="25"/>
+      <c r="AA69" s="25"/>
       <c r="AB69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AC69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AD69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG69" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
@@ -37367,94 +34099,88 @@
         <v>16</v>
       </c>
       <c r="D70" s="25">
-        <v>0.65</v>
+        <v>0.93723849372384938</v>
       </c>
       <c r="E70" s="25">
-        <v>0.65</v>
+        <v>0.91706730769230771</v>
       </c>
       <c r="F70" s="25">
-        <v>0.65</v>
+        <v>0.96511627906976749</v>
       </c>
       <c r="G70" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H70" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.90638297872340423</v>
+      </c>
+      <c r="H70" s="25"/>
       <c r="I70" s="25">
-        <v>0.65</v>
+        <v>0.94811320754716977</v>
       </c>
       <c r="J70" s="25">
-        <v>0.65</v>
+        <v>0.8984375</v>
       </c>
       <c r="K70" s="25">
-        <v>0.65</v>
+        <v>0.91050583657587547</v>
       </c>
       <c r="L70" s="25">
-        <v>0.65</v>
+        <v>0.88586956521739135</v>
       </c>
       <c r="M70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q70" s="25">
-        <v>0.65</v>
+        <v>0.80701754385964908</v>
       </c>
       <c r="R70" s="25">
-        <v>0.65</v>
+        <v>0.95454545454545459</v>
       </c>
       <c r="S70" s="25">
-        <v>0.65</v>
+        <v>0.87142857142857144</v>
       </c>
       <c r="T70" s="25">
-        <v>0.65</v>
+        <v>0.93442622950819676</v>
       </c>
       <c r="U70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="V70" s="25">
-        <v>0.65</v>
+        <v>0.84482758620689657</v>
       </c>
       <c r="W70" s="25">
-        <v>0.65</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="X70" s="25">
-        <v>0.65</v>
+        <v>0.94285714285714284</v>
       </c>
       <c r="Y70" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z70" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA70" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.9821428571428571</v>
+      </c>
+      <c r="Z70" s="25"/>
+      <c r="AA70" s="25"/>
       <c r="AB70" s="25">
-        <v>0.65</v>
+        <v>0.96385542168674698</v>
       </c>
       <c r="AC70" s="25">
-        <v>0.65</v>
+        <v>0.96385542168674698</v>
       </c>
       <c r="AD70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG70" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
@@ -37468,94 +34194,88 @@
         <v>17</v>
       </c>
       <c r="D71" s="25">
-        <v>0.65</v>
+        <v>0.84453360080240725</v>
       </c>
       <c r="E71" s="25">
-        <v>0.65</v>
+        <v>0.83024691358024694</v>
       </c>
       <c r="F71" s="25">
-        <v>0.65</v>
+        <v>0.87106017191977081</v>
       </c>
       <c r="G71" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H71" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.90116279069767447</v>
+      </c>
+      <c r="H71" s="25"/>
       <c r="I71" s="25">
-        <v>0.65</v>
+        <v>0.88513513513513509</v>
       </c>
       <c r="J71" s="25">
-        <v>0.65</v>
+        <v>0.66206896551724137</v>
       </c>
       <c r="K71" s="25">
-        <v>0.65</v>
+        <v>0.85245901639344257</v>
       </c>
       <c r="L71" s="25">
-        <v>0.65</v>
+        <v>0.54081632653061229</v>
       </c>
       <c r="M71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="N71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="O71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="P71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="Q71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="R71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="S71" s="25">
-        <v>0.65</v>
+        <v>0.77173913043478259</v>
       </c>
       <c r="T71" s="25">
-        <v>0.65</v>
+        <v>0.98148148148148151</v>
       </c>
       <c r="U71" s="25">
-        <v>0.65</v>
+        <v>0.82474226804123707</v>
       </c>
       <c r="V71" s="25">
-        <v>0.65</v>
+        <v>0.93333333333333335</v>
       </c>
       <c r="W71" s="25">
-        <v>0.65</v>
+        <v>0.79761904761904767</v>
       </c>
       <c r="X71" s="25">
-        <v>0.65</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="Y71" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z71" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA71" s="25">
-        <v>0.65</v>
-      </c>
+        <v>0.86486486486486491</v>
+      </c>
+      <c r="Z71" s="25"/>
+      <c r="AA71" s="25"/>
       <c r="AB71" s="25">
-        <v>0.65</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="AC71" s="25">
-        <v>0.65</v>
+        <v>0.46666666666666667</v>
       </c>
       <c r="AD71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AE71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AF71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
       <c r="AG71" s="25">
-        <v>0.65</v>
+        <v>1</v>
       </c>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
@@ -37568,96 +34288,36 @@
       <c r="C72" s="21">
         <v>18</v>
       </c>
-      <c r="D72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="E72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="F72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="G72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="H72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="I72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="J72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="K72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="L72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="M72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="N72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="O72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="P72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Q72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="R72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="S72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="T72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="U72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="V72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="W72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="X72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Y72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="Z72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AA72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AB72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AC72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AD72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AE72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AF72" s="25">
-        <v>0.65</v>
-      </c>
-      <c r="AG72" s="25">
-        <v>0.65</v>
-      </c>
+      <c r="D72" s="25"/>
+      <c r="E72" s="25"/>
+      <c r="F72" s="25"/>
+      <c r="G72" s="25"/>
+      <c r="H72" s="25"/>
+      <c r="I72" s="25"/>
+      <c r="J72" s="25"/>
+      <c r="K72" s="25"/>
+      <c r="L72" s="25"/>
+      <c r="M72" s="25"/>
+      <c r="N72" s="25"/>
+      <c r="O72" s="25"/>
+      <c r="P72" s="25"/>
+      <c r="Q72" s="25"/>
+      <c r="R72" s="25"/>
+      <c r="S72" s="25"/>
+      <c r="T72" s="25"/>
+      <c r="U72" s="25"/>
+      <c r="V72" s="25"/>
+      <c r="W72" s="25"/>
+      <c r="X72" s="25"/>
+      <c r="Y72" s="25"/>
+      <c r="Z72" s="25"/>
+      <c r="AA72" s="25"/>
+      <c r="AB72" s="25"/>
+      <c r="AC72" s="25"/>
+      <c r="AD72" s="25"/>
+      <c r="AE72" s="25"/>
+      <c r="AF72" s="25"/>
+      <c r="AG72" s="25"/>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="26">

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565" activeTab="12"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="27030" windowHeight="11565"/>
   </bookViews>
   <sheets>
     <sheet name="5.0A" sheetId="11" r:id="rId1"/>
@@ -7984,7 +7984,7 @@
     <definedName name="ZXBB_2">"#REF!"</definedName>
     <definedName name="ZXBB_3">"#REF!"</definedName>
   </definedNames>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="162913" calcMode="manual"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -7994,7 +7994,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1437" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1268" uniqueCount="50">
   <si>
     <t>Mes</t>
   </si>
@@ -11024,91 +11024,91 @@
         <v>4</v>
       </c>
       <c r="C2" s="29">
-        <v>17906</v>
+        <v>2803</v>
       </c>
       <c r="D2" s="29">
-        <v>10660</v>
+        <v>2183</v>
       </c>
       <c r="E2" s="29">
-        <v>7246</v>
+        <v>620</v>
       </c>
       <c r="F2" s="29">
-        <v>3341</v>
+        <v>644</v>
       </c>
       <c r="G2" s="29">
-        <v>463</v>
+        <v>93</v>
       </c>
       <c r="H2" s="29">
-        <v>1775</v>
+        <v>432</v>
       </c>
       <c r="I2" s="29">
-        <v>3290</v>
+        <v>555</v>
       </c>
       <c r="J2" s="29">
-        <v>1791</v>
+        <v>459</v>
       </c>
       <c r="K2" s="29">
-        <v>1258</v>
+        <v>177</v>
       </c>
       <c r="L2" s="29">
-        <v>1879</v>
+        <v>124</v>
       </c>
       <c r="M2" s="29">
-        <v>2548</v>
+        <v>140</v>
       </c>
       <c r="N2" s="29">
-        <v>1461</v>
+        <v>171</v>
       </c>
       <c r="O2" s="29">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="P2" s="29">
-        <v>1467</v>
+        <v>261</v>
       </c>
       <c r="Q2" s="29">
-        <v>660</v>
+        <v>186</v>
       </c>
       <c r="R2" s="29">
-        <v>673</v>
+        <v>233</v>
       </c>
       <c r="S2" s="29">
-        <v>1851</v>
+        <v>187</v>
       </c>
       <c r="T2" s="29">
-        <v>1874</v>
+        <v>383</v>
       </c>
       <c r="U2" s="29">
-        <v>249</v>
+        <v>51</v>
       </c>
       <c r="V2" s="29">
-        <v>1115</v>
+        <v>246</v>
       </c>
       <c r="W2" s="29">
-        <v>1542</v>
+        <v>408</v>
       </c>
       <c r="X2" s="29">
-        <v>766</v>
+        <v>135</v>
       </c>
       <c r="Y2" s="29">
+        <v>9</v>
+      </c>
+      <c r="Z2" s="29">
         <v>84</v>
       </c>
-      <c r="Z2" s="29">
-        <v>379</v>
-      </c>
       <c r="AA2" s="29">
-        <v>1258</v>
+        <v>177</v>
       </c>
       <c r="AB2" s="29">
-        <v>1879</v>
+        <v>124</v>
       </c>
       <c r="AC2" s="29">
-        <v>2548</v>
+        <v>140</v>
       </c>
       <c r="AD2" s="29">
-        <v>1461</v>
+        <v>171</v>
       </c>
       <c r="AE2" s="29">
-        <v>100</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:31" x14ac:dyDescent="0.25">
@@ -11119,91 +11119,91 @@
         <v>5</v>
       </c>
       <c r="C3" s="29">
-        <v>17492</v>
+        <v>2577</v>
       </c>
       <c r="D3" s="29">
-        <v>10423</v>
+        <v>2018</v>
       </c>
       <c r="E3" s="29">
-        <v>7069</v>
+        <v>559</v>
       </c>
       <c r="F3" s="29">
-        <v>3115</v>
+        <v>636</v>
       </c>
       <c r="G3" s="29">
-        <v>493</v>
+        <v>100</v>
       </c>
       <c r="H3" s="29">
-        <v>1755</v>
+        <v>369</v>
       </c>
       <c r="I3" s="29">
-        <v>3249</v>
+        <v>520</v>
       </c>
       <c r="J3" s="29">
-        <v>1811</v>
+        <v>393</v>
       </c>
       <c r="K3" s="29">
-        <v>990</v>
+        <v>174</v>
       </c>
       <c r="L3" s="29">
-        <v>1947</v>
+        <v>111</v>
       </c>
       <c r="M3" s="29">
-        <v>2642</v>
+        <v>127</v>
       </c>
       <c r="N3" s="29">
-        <v>1440</v>
+        <v>137</v>
       </c>
       <c r="O3" s="29">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="P3" s="29">
-        <v>1542</v>
+        <v>266</v>
       </c>
       <c r="Q3" s="29">
-        <v>665</v>
+        <v>160</v>
       </c>
       <c r="R3" s="29">
-        <v>631</v>
+        <v>195</v>
       </c>
       <c r="S3" s="29">
-        <v>1847</v>
+        <v>197</v>
       </c>
       <c r="T3" s="29">
-        <v>1573</v>
+        <v>370</v>
       </c>
       <c r="U3" s="29">
-        <v>247</v>
+        <v>52</v>
       </c>
       <c r="V3" s="29">
-        <v>1090</v>
+        <v>209</v>
       </c>
       <c r="W3" s="29">
-        <v>1564</v>
+        <v>341</v>
       </c>
       <c r="X3" s="29">
-        <v>771</v>
+        <v>128</v>
       </c>
       <c r="Y3" s="29">
-        <v>86</v>
+        <v>10</v>
       </c>
       <c r="Z3" s="29">
-        <v>407</v>
+        <v>90</v>
       </c>
       <c r="AA3" s="29">
-        <v>990</v>
+        <v>174</v>
       </c>
       <c r="AB3" s="29">
-        <v>1947</v>
+        <v>111</v>
       </c>
       <c r="AC3" s="29">
-        <v>2642</v>
+        <v>127</v>
       </c>
       <c r="AD3" s="29">
-        <v>1440</v>
+        <v>137</v>
       </c>
       <c r="AE3" s="29">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:31" x14ac:dyDescent="0.25">
@@ -11214,91 +11214,91 @@
         <v>6</v>
       </c>
       <c r="C4" s="29">
-        <v>15756</v>
+        <v>1757</v>
       </c>
       <c r="D4" s="29">
-        <v>9048</v>
+        <v>1465</v>
       </c>
       <c r="E4" s="29">
-        <v>6708</v>
+        <v>292</v>
       </c>
       <c r="F4" s="29">
-        <v>2331</v>
+        <v>504</v>
       </c>
       <c r="G4" s="29">
-        <v>484</v>
+        <v>75</v>
       </c>
       <c r="H4" s="29">
-        <v>1492</v>
+        <v>232</v>
       </c>
       <c r="I4" s="29">
-        <v>2934</v>
+        <v>332</v>
       </c>
       <c r="J4" s="29">
-        <v>1807</v>
+        <v>322</v>
       </c>
       <c r="K4" s="29">
-        <v>973</v>
+        <v>88</v>
       </c>
       <c r="L4" s="29">
-        <v>1551</v>
+        <v>46</v>
       </c>
       <c r="M4" s="29">
-        <v>2781</v>
+        <v>98</v>
       </c>
       <c r="N4" s="29">
-        <v>1344</v>
+        <v>45</v>
       </c>
       <c r="O4" s="29">
-        <v>59</v>
+        <v>15</v>
       </c>
       <c r="P4" s="29">
-        <v>1041</v>
+        <v>182</v>
       </c>
       <c r="Q4" s="29">
-        <v>592</v>
+        <v>106</v>
       </c>
       <c r="R4" s="29">
-        <v>654</v>
+        <v>117</v>
       </c>
       <c r="S4" s="29">
-        <v>1590</v>
+        <v>132</v>
       </c>
       <c r="T4" s="29">
-        <v>1290</v>
+        <v>322</v>
       </c>
       <c r="U4" s="29">
-        <v>284</v>
+        <v>49</v>
       </c>
       <c r="V4" s="29">
-        <v>900</v>
+        <v>126</v>
       </c>
       <c r="W4" s="29">
-        <v>1523</v>
+        <v>273</v>
       </c>
       <c r="X4" s="29">
-        <v>690</v>
+        <v>83</v>
       </c>
       <c r="Y4" s="29">
-        <v>74</v>
+        <v>6</v>
       </c>
       <c r="Z4" s="29">
-        <v>410</v>
+        <v>69</v>
       </c>
       <c r="AA4" s="29">
-        <v>973</v>
+        <v>88</v>
       </c>
       <c r="AB4" s="29">
-        <v>1551</v>
+        <v>46</v>
       </c>
       <c r="AC4" s="29">
-        <v>2781</v>
+        <v>98</v>
       </c>
       <c r="AD4" s="29">
-        <v>1344</v>
+        <v>45</v>
       </c>
       <c r="AE4" s="29">
-        <v>59</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" spans="1:31" x14ac:dyDescent="0.25">
@@ -11309,91 +11309,91 @@
         <v>7</v>
       </c>
       <c r="C5" s="29">
-        <v>14511</v>
+        <v>1423</v>
       </c>
       <c r="D5" s="29">
-        <v>8819</v>
+        <v>1262</v>
       </c>
       <c r="E5" s="29">
-        <v>5692</v>
+        <v>161</v>
       </c>
       <c r="F5" s="29">
-        <v>2109</v>
+        <v>437</v>
       </c>
       <c r="G5" s="29">
-        <v>594</v>
+        <v>95</v>
       </c>
       <c r="H5" s="29">
-        <v>1537</v>
+        <v>196</v>
       </c>
       <c r="I5" s="29">
-        <v>2867</v>
+        <v>271</v>
       </c>
       <c r="J5" s="29">
-        <v>1712</v>
+        <v>263</v>
       </c>
       <c r="K5" s="29">
-        <v>806</v>
+        <v>50</v>
       </c>
       <c r="L5" s="29">
-        <v>798</v>
+        <v>15</v>
       </c>
       <c r="M5" s="29">
-        <v>2578</v>
+        <v>63</v>
       </c>
       <c r="N5" s="29">
-        <v>1429</v>
+        <v>26</v>
       </c>
       <c r="O5" s="29">
-        <v>81</v>
+        <v>7</v>
       </c>
       <c r="P5" s="29">
-        <v>781</v>
+        <v>148</v>
       </c>
       <c r="Q5" s="29">
-        <v>611</v>
+        <v>93</v>
       </c>
       <c r="R5" s="29">
-        <v>548</v>
+        <v>83</v>
       </c>
       <c r="S5" s="29">
-        <v>1606</v>
+        <v>156</v>
       </c>
       <c r="T5" s="29">
-        <v>1328</v>
+        <v>289</v>
       </c>
       <c r="U5" s="29">
-        <v>886</v>
+        <v>137</v>
       </c>
       <c r="V5" s="29">
-        <v>926</v>
+        <v>103</v>
       </c>
       <c r="W5" s="29">
-        <v>826</v>
+        <v>126</v>
       </c>
       <c r="X5" s="29">
-        <v>713</v>
+        <v>32</v>
       </c>
       <c r="Y5" s="29">
-        <v>163</v>
+        <v>25</v>
       </c>
       <c r="Z5" s="29">
-        <v>431</v>
+        <v>70</v>
       </c>
       <c r="AA5" s="29">
-        <v>806</v>
+        <v>50</v>
       </c>
       <c r="AB5" s="29">
-        <v>798</v>
+        <v>15</v>
       </c>
       <c r="AC5" s="29">
-        <v>2578</v>
+        <v>63</v>
       </c>
       <c r="AD5" s="29">
-        <v>1429</v>
+        <v>26</v>
       </c>
       <c r="AE5" s="29">
-        <v>81</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:31" x14ac:dyDescent="0.25">
@@ -11404,91 +11404,91 @@
         <v>8</v>
       </c>
       <c r="C6" s="29">
-        <v>16424</v>
+        <v>2391</v>
       </c>
       <c r="D6" s="29">
-        <v>9262</v>
+        <v>1733</v>
       </c>
       <c r="E6" s="29">
-        <v>7162</v>
+        <v>658</v>
       </c>
       <c r="F6" s="29">
-        <v>2347</v>
+        <v>533</v>
       </c>
       <c r="G6" s="29">
-        <v>582</v>
+        <v>101</v>
       </c>
       <c r="H6" s="29">
-        <v>1419</v>
+        <v>296</v>
       </c>
       <c r="I6" s="29">
-        <v>2738</v>
+        <v>398</v>
       </c>
       <c r="J6" s="29">
-        <v>2176</v>
+        <v>405</v>
       </c>
       <c r="K6" s="29">
-        <v>1322</v>
+        <v>234</v>
       </c>
       <c r="L6" s="29">
-        <v>1856</v>
+        <v>121</v>
       </c>
       <c r="M6" s="29">
-        <v>2440</v>
+        <v>184</v>
       </c>
       <c r="N6" s="29">
-        <v>1510</v>
+        <v>107</v>
       </c>
       <c r="O6" s="29">
-        <v>34</v>
+        <v>12</v>
       </c>
       <c r="P6" s="29">
-        <v>838</v>
+        <v>180</v>
       </c>
       <c r="Q6" s="29">
-        <v>532</v>
+        <v>110</v>
       </c>
       <c r="R6" s="29">
-        <v>668</v>
+        <v>145</v>
       </c>
       <c r="S6" s="29">
-        <v>1325</v>
+        <v>172</v>
       </c>
       <c r="T6" s="29">
-        <v>1509</v>
+        <v>353</v>
       </c>
       <c r="U6" s="29">
-        <v>328</v>
+        <v>58</v>
       </c>
       <c r="V6" s="29">
-        <v>887</v>
+        <v>186</v>
       </c>
       <c r="W6" s="29">
-        <v>1848</v>
+        <v>347</v>
       </c>
       <c r="X6" s="29">
-        <v>745</v>
+        <v>81</v>
       </c>
       <c r="Y6" s="29">
-        <v>56</v>
+        <v>10</v>
       </c>
       <c r="Z6" s="29">
-        <v>526</v>
+        <v>91</v>
       </c>
       <c r="AA6" s="29">
-        <v>1322</v>
+        <v>234</v>
       </c>
       <c r="AB6" s="29">
-        <v>1856</v>
+        <v>121</v>
       </c>
       <c r="AC6" s="29">
-        <v>2440</v>
+        <v>184</v>
       </c>
       <c r="AD6" s="29">
-        <v>1510</v>
+        <v>107</v>
       </c>
       <c r="AE6" s="29">
-        <v>34</v>
+        <v>12</v>
       </c>
     </row>
     <row r="7" spans="1:31" x14ac:dyDescent="0.25">
@@ -11499,89 +11499,89 @@
         <v>9</v>
       </c>
       <c r="C7" s="29">
-        <v>17314</v>
+        <v>2026</v>
       </c>
       <c r="D7" s="29">
-        <v>10167</v>
+        <v>1514</v>
       </c>
       <c r="E7" s="29">
-        <v>7147</v>
+        <v>512</v>
       </c>
       <c r="F7" s="29">
-        <v>2848</v>
+        <v>456</v>
       </c>
       <c r="G7" s="29">
-        <v>557</v>
+        <v>98</v>
       </c>
       <c r="H7" s="29">
-        <v>1457</v>
+        <v>267</v>
       </c>
       <c r="I7" s="29">
-        <v>2961</v>
+        <v>298</v>
       </c>
       <c r="J7" s="29">
-        <v>2344</v>
+        <v>395</v>
       </c>
       <c r="K7" s="29">
-        <v>1517</v>
+        <v>228</v>
       </c>
       <c r="L7" s="29">
-        <v>1997</v>
+        <v>72</v>
       </c>
       <c r="M7" s="29">
-        <v>2177</v>
+        <v>135</v>
       </c>
       <c r="N7" s="29">
-        <v>1406</v>
+        <v>64</v>
       </c>
       <c r="O7" s="29">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="P7" s="29">
-        <v>1062</v>
+        <v>143</v>
       </c>
       <c r="Q7" s="29">
-        <v>470</v>
+        <v>82</v>
       </c>
       <c r="R7" s="29">
-        <v>685</v>
+        <v>91</v>
       </c>
       <c r="S7" s="29">
-        <v>1519</v>
+        <v>132</v>
       </c>
       <c r="T7" s="29">
-        <v>1786</v>
+        <v>313</v>
       </c>
       <c r="U7" s="29">
-        <v>366</v>
+        <v>62</v>
       </c>
       <c r="V7" s="29">
-        <v>987</v>
+        <v>185</v>
       </c>
       <c r="W7" s="29">
-        <v>1978</v>
+        <v>333</v>
       </c>
       <c r="X7" s="29">
-        <v>757</v>
+        <v>75</v>
       </c>
       <c r="Y7" s="29"/>
       <c r="Z7" s="29">
-        <v>557</v>
+        <v>98</v>
       </c>
       <c r="AA7" s="29">
-        <v>1517</v>
+        <v>228</v>
       </c>
       <c r="AB7" s="29">
-        <v>1997</v>
+        <v>72</v>
       </c>
       <c r="AC7" s="29">
-        <v>2177</v>
+        <v>135</v>
       </c>
       <c r="AD7" s="29">
-        <v>1406</v>
+        <v>64</v>
       </c>
       <c r="AE7" s="29">
-        <v>50</v>
+        <v>13</v>
       </c>
     </row>
     <row r="8" spans="1:31" x14ac:dyDescent="0.25">
@@ -11592,89 +11592,87 @@
         <v>10</v>
       </c>
       <c r="C8" s="29">
-        <v>22450</v>
+        <v>1915</v>
       </c>
       <c r="D8" s="29">
-        <v>12518</v>
+        <v>1323</v>
       </c>
       <c r="E8" s="29">
-        <v>9932</v>
+        <v>592</v>
       </c>
       <c r="F8" s="29">
-        <v>3654</v>
+        <v>398</v>
       </c>
       <c r="G8" s="29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H8" s="29">
-        <v>1935</v>
+        <v>271</v>
       </c>
       <c r="I8" s="29">
-        <v>3859</v>
+        <v>254</v>
       </c>
       <c r="J8" s="29">
-        <v>3068</v>
+        <v>400</v>
       </c>
       <c r="K8" s="29">
-        <v>2476</v>
+        <v>277</v>
       </c>
       <c r="L8" s="29">
-        <v>2617</v>
+        <v>83</v>
       </c>
       <c r="M8" s="29">
-        <v>2480</v>
+        <v>125</v>
       </c>
       <c r="N8" s="29">
-        <v>1983</v>
+        <v>93</v>
       </c>
       <c r="O8" s="29">
-        <v>376</v>
+        <v>14</v>
       </c>
       <c r="P8" s="29">
-        <v>1479</v>
+        <v>126</v>
       </c>
       <c r="Q8" s="29">
-        <v>862</v>
+        <v>109</v>
       </c>
       <c r="R8" s="29">
-        <v>1284</v>
+        <v>87</v>
       </c>
       <c r="S8" s="29">
-        <v>1788</v>
+        <v>117</v>
       </c>
       <c r="T8" s="29">
-        <v>2175</v>
+        <v>272</v>
       </c>
       <c r="U8" s="29">
-        <v>572</v>
+        <v>51</v>
       </c>
       <c r="V8" s="29">
-        <v>1073</v>
+        <v>162</v>
       </c>
       <c r="W8" s="29">
-        <v>2496</v>
+        <v>349</v>
       </c>
       <c r="X8" s="29">
-        <v>787</v>
-      </c>
-      <c r="Y8" s="29">
-        <v>2</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="Y8" s="29"/>
       <c r="Z8" s="29"/>
       <c r="AA8" s="29">
-        <v>2476</v>
+        <v>277</v>
       </c>
       <c r="AB8" s="29">
-        <v>2617</v>
+        <v>83</v>
       </c>
       <c r="AC8" s="29">
-        <v>2480</v>
+        <v>125</v>
       </c>
       <c r="AD8" s="29">
-        <v>1983</v>
+        <v>93</v>
       </c>
       <c r="AE8" s="29">
-        <v>376</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9" spans="1:31" x14ac:dyDescent="0.25">
@@ -11685,87 +11683,87 @@
         <v>11</v>
       </c>
       <c r="C9" s="29">
-        <v>23069</v>
+        <v>1714</v>
       </c>
       <c r="D9" s="29">
-        <v>13651</v>
+        <v>1259</v>
       </c>
       <c r="E9" s="29">
-        <v>9418</v>
+        <v>455</v>
       </c>
       <c r="F9" s="29">
-        <v>4075</v>
+        <v>359</v>
       </c>
       <c r="G9" s="29">
         <v>0</v>
       </c>
       <c r="H9" s="29">
-        <v>1942</v>
+        <v>250</v>
       </c>
       <c r="I9" s="29">
-        <v>4165</v>
+        <v>188</v>
       </c>
       <c r="J9" s="29">
-        <v>3469</v>
+        <v>462</v>
       </c>
       <c r="K9" s="29">
-        <v>2036</v>
+        <v>222</v>
       </c>
       <c r="L9" s="29">
-        <v>3106</v>
+        <v>73</v>
       </c>
       <c r="M9" s="29">
-        <v>2194</v>
+        <v>96</v>
       </c>
       <c r="N9" s="29">
-        <v>1843</v>
+        <v>55</v>
       </c>
       <c r="O9" s="29">
-        <v>239</v>
+        <v>9</v>
       </c>
       <c r="P9" s="29">
-        <v>1601</v>
+        <v>109</v>
       </c>
       <c r="Q9" s="29">
-        <v>907</v>
+        <v>92</v>
       </c>
       <c r="R9" s="29">
-        <v>1361</v>
+        <v>71</v>
       </c>
       <c r="S9" s="29">
-        <v>1942</v>
+        <v>78</v>
       </c>
       <c r="T9" s="29">
-        <v>2474</v>
+        <v>250</v>
       </c>
       <c r="U9" s="29">
-        <v>667</v>
+        <v>58</v>
       </c>
       <c r="V9" s="29">
-        <v>1035</v>
+        <v>158</v>
       </c>
       <c r="W9" s="29">
-        <v>2802</v>
+        <v>404</v>
       </c>
       <c r="X9" s="29">
-        <v>862</v>
+        <v>39</v>
       </c>
       <c r="Y9" s="29"/>
       <c r="Z9" s="29"/>
       <c r="AA9" s="29">
-        <v>2036</v>
+        <v>222</v>
       </c>
       <c r="AB9" s="29">
-        <v>3106</v>
+        <v>73</v>
       </c>
       <c r="AC9" s="29">
-        <v>2194</v>
+        <v>96</v>
       </c>
       <c r="AD9" s="29">
-        <v>1843</v>
+        <v>55</v>
       </c>
       <c r="AE9" s="29">
-        <v>239</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:31" x14ac:dyDescent="0.25">
@@ -11776,89 +11774,87 @@
         <v>12</v>
       </c>
       <c r="C10" s="29">
-        <v>29199</v>
+        <v>1906</v>
       </c>
       <c r="D10" s="29">
-        <v>16059</v>
+        <v>1394</v>
       </c>
       <c r="E10" s="29">
-        <v>13140</v>
+        <v>512</v>
       </c>
       <c r="F10" s="29">
-        <v>4905</v>
+        <v>400</v>
       </c>
       <c r="G10" s="29">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H10" s="29">
-        <v>2531</v>
+        <v>239</v>
       </c>
       <c r="I10" s="29">
-        <v>4551</v>
+        <v>207</v>
       </c>
       <c r="J10" s="29">
-        <v>4070</v>
+        <v>548</v>
       </c>
       <c r="K10" s="29">
-        <v>3447</v>
+        <v>229</v>
       </c>
       <c r="L10" s="29">
-        <v>4074</v>
+        <v>97</v>
       </c>
       <c r="M10" s="29">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="N10" s="29">
-        <v>2145</v>
+        <v>74</v>
       </c>
       <c r="O10" s="29">
-        <v>474</v>
+        <v>20</v>
       </c>
       <c r="P10" s="29">
-        <v>1769</v>
+        <v>109</v>
       </c>
       <c r="Q10" s="29">
-        <v>1243</v>
+        <v>100</v>
       </c>
       <c r="R10" s="29">
-        <v>1450</v>
+        <v>63</v>
       </c>
       <c r="S10" s="29">
-        <v>2178</v>
+        <v>102</v>
       </c>
       <c r="T10" s="29">
-        <v>3136</v>
+        <v>291</v>
       </c>
       <c r="U10" s="29">
-        <v>771</v>
+        <v>60</v>
       </c>
       <c r="V10" s="29">
-        <v>1288</v>
+        <v>139</v>
       </c>
       <c r="W10" s="29">
-        <v>3299</v>
+        <v>488</v>
       </c>
       <c r="X10" s="29">
-        <v>923</v>
-      </c>
-      <c r="Y10" s="29">
-        <v>2</v>
-      </c>
+        <v>42</v>
+      </c>
+      <c r="Y10" s="29"/>
       <c r="Z10" s="29"/>
       <c r="AA10" s="29">
-        <v>3447</v>
+        <v>229</v>
       </c>
       <c r="AB10" s="29">
-        <v>4074</v>
+        <v>97</v>
       </c>
       <c r="AC10" s="29">
-        <v>3000</v>
+        <v>92</v>
       </c>
       <c r="AD10" s="29">
-        <v>2145</v>
+        <v>74</v>
       </c>
       <c r="AE10" s="29">
-        <v>474</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" spans="1:31" x14ac:dyDescent="0.25">
@@ -11869,87 +11865,87 @@
         <v>13</v>
       </c>
       <c r="C11" s="29">
-        <v>36000</v>
+        <v>9118</v>
       </c>
       <c r="D11" s="29">
-        <v>19513</v>
+        <v>5270</v>
       </c>
       <c r="E11" s="29">
-        <v>16487</v>
+        <v>3848</v>
       </c>
       <c r="F11" s="29">
-        <v>5346</v>
+        <v>1277</v>
       </c>
       <c r="G11" s="29">
         <v>0</v>
       </c>
       <c r="H11" s="29">
-        <v>3262</v>
+        <v>1022</v>
       </c>
       <c r="I11" s="29">
-        <v>5948</v>
+        <v>1467</v>
       </c>
       <c r="J11" s="29">
-        <v>4957</v>
+        <v>1504</v>
       </c>
       <c r="K11" s="29">
-        <v>4029</v>
+        <v>1182</v>
       </c>
       <c r="L11" s="29">
-        <v>4945</v>
+        <v>503</v>
       </c>
       <c r="M11" s="29">
-        <v>3543</v>
+        <v>853</v>
       </c>
       <c r="N11" s="29">
-        <v>3285</v>
+        <v>1176</v>
       </c>
       <c r="O11" s="29">
-        <v>685</v>
+        <v>134</v>
       </c>
       <c r="P11" s="29">
-        <v>1940</v>
+        <v>428</v>
       </c>
       <c r="Q11" s="29">
-        <v>1457</v>
+        <v>371</v>
       </c>
       <c r="R11" s="29">
-        <v>1678</v>
+        <v>482</v>
       </c>
       <c r="S11" s="29">
-        <v>3014</v>
+        <v>750</v>
       </c>
       <c r="T11" s="29">
-        <v>3406</v>
+        <v>849</v>
       </c>
       <c r="U11" s="29">
-        <v>939</v>
+        <v>74</v>
       </c>
       <c r="V11" s="29">
-        <v>1805</v>
+        <v>651</v>
       </c>
       <c r="W11" s="29">
-        <v>4018</v>
+        <v>1430</v>
       </c>
       <c r="X11" s="29">
-        <v>1256</v>
+        <v>235</v>
       </c>
       <c r="Y11" s="29"/>
       <c r="Z11" s="29"/>
       <c r="AA11" s="29">
-        <v>4029</v>
+        <v>1182</v>
       </c>
       <c r="AB11" s="29">
-        <v>4945</v>
+        <v>503</v>
       </c>
       <c r="AC11" s="29">
-        <v>3543</v>
+        <v>853</v>
       </c>
       <c r="AD11" s="29">
-        <v>3285</v>
+        <v>1176</v>
       </c>
       <c r="AE11" s="29">
-        <v>685</v>
+        <v>134</v>
       </c>
     </row>
     <row r="12" spans="1:31" x14ac:dyDescent="0.25">
@@ -11960,87 +11956,87 @@
         <v>14</v>
       </c>
       <c r="C12" s="29">
-        <v>38011</v>
+        <v>12756</v>
       </c>
       <c r="D12" s="29">
-        <v>21294</v>
+        <v>7302</v>
       </c>
       <c r="E12" s="29">
-        <v>16717</v>
+        <v>5454</v>
       </c>
       <c r="F12" s="29">
-        <v>5661</v>
+        <v>1766</v>
       </c>
       <c r="G12" s="29">
         <v>0</v>
       </c>
       <c r="H12" s="29">
-        <v>3339</v>
+        <v>1554</v>
       </c>
       <c r="I12" s="29">
-        <v>6840</v>
+        <v>2245</v>
       </c>
       <c r="J12" s="29">
-        <v>5454</v>
+        <v>1737</v>
       </c>
       <c r="K12" s="29">
-        <v>4254</v>
+        <v>1605</v>
       </c>
       <c r="L12" s="29">
-        <v>4526</v>
+        <v>759</v>
       </c>
       <c r="M12" s="29">
-        <v>3550</v>
+        <v>1185</v>
       </c>
       <c r="N12" s="29">
-        <v>3619</v>
+        <v>1639</v>
       </c>
       <c r="O12" s="29">
-        <v>768</v>
+        <v>266</v>
       </c>
       <c r="P12" s="29">
-        <v>2191</v>
+        <v>627</v>
       </c>
       <c r="Q12" s="29">
-        <v>1370</v>
+        <v>616</v>
       </c>
       <c r="R12" s="29">
-        <v>1703</v>
+        <v>602</v>
       </c>
       <c r="S12" s="29">
-        <v>3618</v>
+        <v>1191</v>
       </c>
       <c r="T12" s="29">
-        <v>3470</v>
+        <v>1139</v>
       </c>
       <c r="U12" s="29">
-        <v>1257</v>
+        <v>119</v>
       </c>
       <c r="V12" s="29">
-        <v>1969</v>
+        <v>938</v>
       </c>
       <c r="W12" s="29">
-        <v>4197</v>
+        <v>1618</v>
       </c>
       <c r="X12" s="29">
-        <v>1519</v>
+        <v>452</v>
       </c>
       <c r="Y12" s="29"/>
       <c r="Z12" s="29"/>
       <c r="AA12" s="29">
-        <v>4254</v>
+        <v>1605</v>
       </c>
       <c r="AB12" s="29">
-        <v>4526</v>
+        <v>759</v>
       </c>
       <c r="AC12" s="29">
-        <v>3550</v>
+        <v>1185</v>
       </c>
       <c r="AD12" s="29">
-        <v>3619</v>
+        <v>1639</v>
       </c>
       <c r="AE12" s="29">
-        <v>768</v>
+        <v>266</v>
       </c>
     </row>
     <row r="13" spans="1:31" x14ac:dyDescent="0.25">
@@ -12051,87 +12047,87 @@
         <v>15</v>
       </c>
       <c r="C13" s="29">
-        <v>48592</v>
+        <v>23744</v>
       </c>
       <c r="D13" s="29">
-        <v>25831</v>
+        <v>10789</v>
       </c>
       <c r="E13" s="29">
-        <v>22761</v>
+        <v>12955</v>
       </c>
       <c r="F13" s="29">
-        <v>6539</v>
+        <v>2564</v>
       </c>
       <c r="G13" s="29">
         <v>0</v>
       </c>
       <c r="H13" s="29">
-        <v>4296</v>
+        <v>2419</v>
       </c>
       <c r="I13" s="29">
-        <v>8318</v>
+        <v>3320</v>
       </c>
       <c r="J13" s="29">
-        <v>6678</v>
+        <v>2486</v>
       </c>
       <c r="K13" s="29">
-        <v>4652</v>
+        <v>3429</v>
       </c>
       <c r="L13" s="29">
-        <v>6338</v>
+        <v>2336</v>
       </c>
       <c r="M13" s="29">
-        <v>5963</v>
+        <v>3645</v>
       </c>
       <c r="N13" s="29">
-        <v>4665</v>
+        <v>2781</v>
       </c>
       <c r="O13" s="29">
-        <v>1143</v>
+        <v>764</v>
       </c>
       <c r="P13" s="29">
-        <v>2411</v>
+        <v>859</v>
       </c>
       <c r="Q13" s="29">
-        <v>1701</v>
+        <v>937</v>
       </c>
       <c r="R13" s="29">
-        <v>1480</v>
+        <v>759</v>
       </c>
       <c r="S13" s="29">
-        <v>4779</v>
+        <v>1840</v>
       </c>
       <c r="T13" s="29">
-        <v>4128</v>
+        <v>1705</v>
       </c>
       <c r="U13" s="29">
-        <v>1735</v>
+        <v>376</v>
       </c>
       <c r="V13" s="29">
-        <v>2595</v>
+        <v>1482</v>
       </c>
       <c r="W13" s="29">
-        <v>4943</v>
+        <v>2110</v>
       </c>
       <c r="X13" s="29">
-        <v>2059</v>
+        <v>721</v>
       </c>
       <c r="Y13" s="29"/>
       <c r="Z13" s="29"/>
       <c r="AA13" s="29">
-        <v>4652</v>
+        <v>3429</v>
       </c>
       <c r="AB13" s="29">
-        <v>6338</v>
+        <v>2336</v>
       </c>
       <c r="AC13" s="29">
-        <v>5963</v>
+        <v>3645</v>
       </c>
       <c r="AD13" s="29">
-        <v>4665</v>
+        <v>2781</v>
       </c>
       <c r="AE13" s="29">
-        <v>1143</v>
+        <v>764</v>
       </c>
     </row>
     <row r="14" spans="1:31" x14ac:dyDescent="0.25">
@@ -12142,87 +12138,87 @@
         <v>4</v>
       </c>
       <c r="C14" s="29">
-        <v>54991</v>
+        <v>27869</v>
       </c>
       <c r="D14" s="29">
-        <v>30330</v>
+        <v>14225</v>
       </c>
       <c r="E14" s="29">
-        <v>24661</v>
+        <v>13644</v>
       </c>
       <c r="F14" s="29">
-        <v>7435</v>
+        <v>3208</v>
       </c>
       <c r="G14" s="29">
         <v>0</v>
       </c>
       <c r="H14" s="29">
-        <v>5629</v>
+        <v>3220</v>
       </c>
       <c r="I14" s="29">
-        <v>9530</v>
+        <v>4547</v>
       </c>
       <c r="J14" s="29">
-        <v>7736</v>
+        <v>3250</v>
       </c>
       <c r="K14" s="29">
-        <v>5697</v>
+        <v>3662</v>
       </c>
       <c r="L14" s="29">
-        <v>6673</v>
+        <v>2374</v>
       </c>
       <c r="M14" s="29">
-        <v>6067</v>
+        <v>3720</v>
       </c>
       <c r="N14" s="29">
-        <v>5141</v>
+        <v>3171</v>
       </c>
       <c r="O14" s="29">
-        <v>1083</v>
+        <v>717</v>
       </c>
       <c r="P14" s="29">
-        <v>2829</v>
+        <v>1169</v>
       </c>
       <c r="Q14" s="29">
-        <v>2213</v>
+        <v>1179</v>
       </c>
       <c r="R14" s="29">
-        <v>2316</v>
+        <v>1375</v>
       </c>
       <c r="S14" s="29">
-        <v>5053</v>
+        <v>2232</v>
       </c>
       <c r="T14" s="29">
-        <v>4606</v>
+        <v>2039</v>
       </c>
       <c r="U14" s="29">
-        <v>2223</v>
+        <v>584</v>
       </c>
       <c r="V14" s="29">
-        <v>3416</v>
+        <v>2041</v>
       </c>
       <c r="W14" s="29">
-        <v>5513</v>
+        <v>2666</v>
       </c>
       <c r="X14" s="29">
-        <v>2161</v>
+        <v>940</v>
       </c>
       <c r="Y14" s="29"/>
       <c r="Z14" s="29"/>
       <c r="AA14" s="29">
-        <v>5697</v>
+        <v>3662</v>
       </c>
       <c r="AB14" s="29">
-        <v>6673</v>
+        <v>2374</v>
       </c>
       <c r="AC14" s="29">
-        <v>6067</v>
+        <v>3720</v>
       </c>
       <c r="AD14" s="29">
-        <v>5141</v>
+        <v>3171</v>
       </c>
       <c r="AE14" s="29">
-        <v>1083</v>
+        <v>717</v>
       </c>
     </row>
     <row r="15" spans="1:31" x14ac:dyDescent="0.25">
@@ -12233,87 +12229,87 @@
         <v>5</v>
       </c>
       <c r="C15" s="29">
-        <v>58226</v>
+        <v>27458</v>
       </c>
       <c r="D15" s="29">
-        <v>32787</v>
+        <v>14237</v>
       </c>
       <c r="E15" s="29">
-        <v>25439</v>
+        <v>13221</v>
       </c>
       <c r="F15" s="29">
-        <v>8123</v>
+        <v>3356</v>
       </c>
       <c r="G15" s="29">
         <v>0</v>
       </c>
       <c r="H15" s="29">
-        <v>6139</v>
+        <v>3335</v>
       </c>
       <c r="I15" s="29">
-        <v>10178</v>
+        <v>4389</v>
       </c>
       <c r="J15" s="29">
-        <v>8347</v>
+        <v>3157</v>
       </c>
       <c r="K15" s="29">
-        <v>6217</v>
+        <v>3329</v>
       </c>
       <c r="L15" s="29">
-        <v>6806</v>
+        <v>2328</v>
       </c>
       <c r="M15" s="29">
-        <v>5995</v>
+        <v>3603</v>
       </c>
       <c r="N15" s="29">
-        <v>5346</v>
+        <v>3299</v>
       </c>
       <c r="O15" s="29">
-        <v>1075</v>
+        <v>662</v>
       </c>
       <c r="P15" s="29">
-        <v>3053</v>
+        <v>1218</v>
       </c>
       <c r="Q15" s="29">
-        <v>2140</v>
+        <v>1119</v>
       </c>
       <c r="R15" s="29">
-        <v>2555</v>
+        <v>1330</v>
       </c>
       <c r="S15" s="29">
-        <v>5356</v>
+        <v>2200</v>
       </c>
       <c r="T15" s="29">
-        <v>5070</v>
+        <v>2138</v>
       </c>
       <c r="U15" s="29">
-        <v>2718</v>
+        <v>599</v>
       </c>
       <c r="V15" s="29">
-        <v>3999</v>
+        <v>2216</v>
       </c>
       <c r="W15" s="29">
-        <v>5629</v>
+        <v>2558</v>
       </c>
       <c r="X15" s="29">
-        <v>2267</v>
+        <v>859</v>
       </c>
       <c r="Y15" s="29"/>
       <c r="Z15" s="29"/>
       <c r="AA15" s="29">
-        <v>6217</v>
+        <v>3329</v>
       </c>
       <c r="AB15" s="29">
-        <v>6806</v>
+        <v>2328</v>
       </c>
       <c r="AC15" s="29">
-        <v>5995</v>
+        <v>3603</v>
       </c>
       <c r="AD15" s="29">
-        <v>5346</v>
+        <v>3299</v>
       </c>
       <c r="AE15" s="29">
-        <v>1075</v>
+        <v>662</v>
       </c>
     </row>
     <row r="16" spans="1:31" x14ac:dyDescent="0.25">
@@ -12324,87 +12320,87 @@
         <v>6</v>
       </c>
       <c r="C16" s="29">
-        <v>60922</v>
+        <v>26616</v>
       </c>
       <c r="D16" s="29">
-        <v>35623</v>
+        <v>14596</v>
       </c>
       <c r="E16" s="29">
-        <v>25299</v>
+        <v>12020</v>
       </c>
       <c r="F16" s="29">
-        <v>8870</v>
+        <v>3553</v>
       </c>
       <c r="G16" s="29">
         <v>0</v>
       </c>
       <c r="H16" s="29">
-        <v>6570</v>
+        <v>3262</v>
       </c>
       <c r="I16" s="29">
-        <v>11201</v>
+        <v>4483</v>
       </c>
       <c r="J16" s="29">
-        <v>8982</v>
+        <v>3298</v>
       </c>
       <c r="K16" s="29">
-        <v>6150</v>
+        <v>2846</v>
       </c>
       <c r="L16" s="29">
-        <v>7198</v>
+        <v>2295</v>
       </c>
       <c r="M16" s="29">
-        <v>5803</v>
+        <v>3256</v>
       </c>
       <c r="N16" s="29">
-        <v>5012</v>
+        <v>2965</v>
       </c>
       <c r="O16" s="29">
-        <v>1136</v>
+        <v>658</v>
       </c>
       <c r="P16" s="29">
-        <v>3412</v>
+        <v>1292</v>
       </c>
       <c r="Q16" s="29">
-        <v>2073</v>
+        <v>1018</v>
       </c>
       <c r="R16" s="29">
-        <v>2928</v>
+        <v>1320</v>
       </c>
       <c r="S16" s="29">
-        <v>5803</v>
+        <v>2307</v>
       </c>
       <c r="T16" s="29">
-        <v>5458</v>
+        <v>2261</v>
       </c>
       <c r="U16" s="29">
-        <v>3247</v>
+        <v>639</v>
       </c>
       <c r="V16" s="29">
-        <v>4497</v>
+        <v>2244</v>
       </c>
       <c r="W16" s="29">
-        <v>5735</v>
+        <v>2659</v>
       </c>
       <c r="X16" s="29">
-        <v>2470</v>
+        <v>856</v>
       </c>
       <c r="Y16" s="29"/>
       <c r="Z16" s="29"/>
       <c r="AA16" s="29">
-        <v>6150</v>
+        <v>2846</v>
       </c>
       <c r="AB16" s="29">
-        <v>7198</v>
+        <v>2295</v>
       </c>
       <c r="AC16" s="29">
-        <v>5803</v>
+        <v>3256</v>
       </c>
       <c r="AD16" s="29">
-        <v>5012</v>
+        <v>2965</v>
       </c>
       <c r="AE16" s="29">
-        <v>1136</v>
+        <v>658</v>
       </c>
     </row>
     <row r="17" spans="1:31" x14ac:dyDescent="0.25">
@@ -12415,87 +12411,87 @@
         <v>7</v>
       </c>
       <c r="C17" s="29">
-        <v>19927</v>
+        <v>8318</v>
       </c>
       <c r="D17" s="29">
-        <v>14877</v>
+        <v>5608</v>
       </c>
       <c r="E17" s="29">
-        <v>5050</v>
+        <v>2710</v>
       </c>
       <c r="F17" s="29">
-        <v>3514</v>
+        <v>1514</v>
       </c>
       <c r="G17" s="29">
         <v>0</v>
       </c>
       <c r="H17" s="29">
-        <v>3690</v>
+        <v>1186</v>
       </c>
       <c r="I17" s="29">
-        <v>4210</v>
+        <v>1590</v>
       </c>
       <c r="J17" s="29">
-        <v>3463</v>
+        <v>1318</v>
       </c>
       <c r="K17" s="29">
-        <v>1616</v>
+        <v>900</v>
       </c>
       <c r="L17" s="29">
-        <v>1070</v>
+        <v>523</v>
       </c>
       <c r="M17" s="29">
-        <v>1072</v>
+        <v>572</v>
       </c>
       <c r="N17" s="29">
-        <v>1132</v>
+        <v>598</v>
       </c>
       <c r="O17" s="29">
-        <v>160</v>
+        <v>117</v>
       </c>
       <c r="P17" s="29">
-        <v>1262</v>
+        <v>452</v>
       </c>
       <c r="Q17" s="29">
-        <v>1374</v>
+        <v>365</v>
       </c>
       <c r="R17" s="29">
-        <v>1298</v>
+        <v>432</v>
       </c>
       <c r="S17" s="29">
-        <v>2009</v>
+        <v>843</v>
       </c>
       <c r="T17" s="29">
-        <v>2252</v>
+        <v>1062</v>
       </c>
       <c r="U17" s="29">
-        <v>571</v>
+        <v>216</v>
       </c>
       <c r="V17" s="29">
-        <v>2316</v>
+        <v>821</v>
       </c>
       <c r="W17" s="29">
-        <v>2892</v>
+        <v>1102</v>
       </c>
       <c r="X17" s="29">
-        <v>903</v>
+        <v>315</v>
       </c>
       <c r="Y17" s="29"/>
       <c r="Z17" s="29"/>
       <c r="AA17" s="29">
-        <v>1616</v>
+        <v>900</v>
       </c>
       <c r="AB17" s="29">
-        <v>1070</v>
+        <v>523</v>
       </c>
       <c r="AC17" s="29">
-        <v>1072</v>
+        <v>572</v>
       </c>
       <c r="AD17" s="29">
-        <v>1132</v>
+        <v>598</v>
       </c>
       <c r="AE17" s="29">
-        <v>160</v>
+        <v>117</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
@@ -12506,87 +12502,87 @@
         <v>8</v>
       </c>
       <c r="C18" s="29">
-        <v>34896</v>
+        <v>22494</v>
       </c>
       <c r="D18" s="29">
-        <v>23288</v>
+        <v>13456</v>
       </c>
       <c r="E18" s="29">
-        <v>11608</v>
+        <v>9038</v>
       </c>
       <c r="F18" s="29">
-        <v>5379</v>
+        <v>3290</v>
       </c>
       <c r="G18" s="29">
         <v>0</v>
       </c>
       <c r="H18" s="29">
-        <v>5531</v>
+        <v>2961</v>
       </c>
       <c r="I18" s="29">
-        <v>6754</v>
+        <v>4108</v>
       </c>
       <c r="J18" s="29">
-        <v>5624</v>
+        <v>3097</v>
       </c>
       <c r="K18" s="29">
-        <v>2879</v>
+        <v>2066</v>
       </c>
       <c r="L18" s="29">
-        <v>2117</v>
+        <v>1660</v>
       </c>
       <c r="M18" s="29">
-        <v>2781</v>
+        <v>2364</v>
       </c>
       <c r="N18" s="29">
-        <v>3261</v>
+        <v>2435</v>
       </c>
       <c r="O18" s="29">
-        <v>570</v>
+        <v>513</v>
       </c>
       <c r="P18" s="29">
-        <v>1980</v>
+        <v>1155</v>
       </c>
       <c r="Q18" s="29">
-        <v>1846</v>
+        <v>1035</v>
       </c>
       <c r="R18" s="29">
-        <v>1923</v>
+        <v>1125</v>
       </c>
       <c r="S18" s="29">
-        <v>3447</v>
+        <v>2168</v>
       </c>
       <c r="T18" s="29">
-        <v>3399</v>
+        <v>2135</v>
       </c>
       <c r="U18" s="29">
-        <v>163</v>
+        <v>1347</v>
       </c>
       <c r="V18" s="29">
-        <v>3685</v>
+        <v>1926</v>
       </c>
       <c r="W18" s="29">
-        <v>5461</v>
+        <v>1750</v>
       </c>
       <c r="X18" s="29">
-        <v>1384</v>
+        <v>815</v>
       </c>
       <c r="Y18" s="29"/>
       <c r="Z18" s="29"/>
       <c r="AA18" s="29">
-        <v>2879</v>
+        <v>2066</v>
       </c>
       <c r="AB18" s="29">
-        <v>2117</v>
+        <v>1660</v>
       </c>
       <c r="AC18" s="29">
-        <v>2781</v>
+        <v>2364</v>
       </c>
       <c r="AD18" s="29">
-        <v>3261</v>
+        <v>2435</v>
       </c>
       <c r="AE18" s="29">
-        <v>570</v>
+        <v>513</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
@@ -15567,9 +15563,7 @@
       <c r="Y23" s="24">
         <v>1</v>
       </c>
-      <c r="Z23" s="24">
-        <v>1</v>
-      </c>
+      <c r="Z23" s="24"/>
       <c r="AA23" s="24"/>
       <c r="AB23" s="24">
         <v>0.94117647058823528</v>
@@ -19900,10 +19894,18 @@
       <c r="L69" s="25">
         <v>0.82222222222222219</v>
       </c>
-      <c r="M69" s="25"/>
-      <c r="N69" s="25"/>
-      <c r="O69" s="25"/>
-      <c r="P69" s="25"/>
+      <c r="M69" s="25">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N69" s="25">
+        <v>1</v>
+      </c>
+      <c r="O69" s="25">
+        <v>1</v>
+      </c>
+      <c r="P69" s="25">
+        <v>1</v>
+      </c>
       <c r="Q69" s="25">
         <v>0.66666666666666663</v>
       </c>
@@ -19987,10 +19989,18 @@
       <c r="L70" s="25">
         <v>0.89583333333333337</v>
       </c>
-      <c r="M70" s="25"/>
-      <c r="N70" s="25"/>
-      <c r="O70" s="25"/>
-      <c r="P70" s="25"/>
+      <c r="M70" s="25">
+        <v>1</v>
+      </c>
+      <c r="N70" s="25">
+        <v>1</v>
+      </c>
+      <c r="O70" s="25">
+        <v>1</v>
+      </c>
+      <c r="P70" s="25">
+        <v>1</v>
+      </c>
       <c r="Q70" s="25">
         <v>0.7142857142857143</v>
       </c>
@@ -20074,10 +20084,18 @@
       <c r="L71" s="25">
         <v>0.52631578947368418</v>
       </c>
-      <c r="M71" s="25"/>
-      <c r="N71" s="25"/>
-      <c r="O71" s="25"/>
-      <c r="P71" s="25"/>
+      <c r="M71" s="25">
+        <v>1</v>
+      </c>
+      <c r="N71" s="25">
+        <v>1</v>
+      </c>
+      <c r="O71" s="25">
+        <v>1</v>
+      </c>
+      <c r="P71" s="25">
+        <v>1</v>
+      </c>
       <c r="Q71" s="25">
         <v>0.66666666666666663</v>
       </c>
@@ -20161,10 +20179,18 @@
       <c r="L72" s="25">
         <v>1</v>
       </c>
-      <c r="M72" s="25"/>
-      <c r="N72" s="25"/>
-      <c r="O72" s="25"/>
-      <c r="P72" s="25"/>
+      <c r="M72" s="25">
+        <v>1</v>
+      </c>
+      <c r="N72" s="25">
+        <v>1</v>
+      </c>
+      <c r="O72" s="25">
+        <v>1</v>
+      </c>
+      <c r="P72" s="25">
+        <v>1</v>
+      </c>
       <c r="Q72" s="25">
         <v>0.54166666666666663</v>
       </c>
@@ -20223,36 +20249,90 @@
       <c r="C73" s="21">
         <v>19</v>
       </c>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
+      <c r="D73" s="22">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="E73" s="22">
+        <v>0.67039106145251393</v>
+      </c>
+      <c r="F73" s="22">
+        <v>0.77519379844961245</v>
+      </c>
+      <c r="G73" s="22">
+        <v>0.57777777777777772</v>
+      </c>
       <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-      <c r="X73" s="22"/>
-      <c r="Y73" s="22"/>
+      <c r="I73" s="22">
+        <v>0.68888888888888888</v>
+      </c>
+      <c r="J73" s="22">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="K73" s="22">
+        <v>0.73469387755102045</v>
+      </c>
+      <c r="L73" s="22">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="M73" s="22">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="N73" s="22">
+        <v>1</v>
+      </c>
+      <c r="O73" s="22">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="P73" s="22">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Q73" s="22">
+        <v>0.70833333333333337</v>
+      </c>
+      <c r="R73" s="22">
+        <v>0.65384615384615385</v>
+      </c>
+      <c r="S73" s="22">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="T73" s="22">
+        <v>0.6428571428571429</v>
+      </c>
+      <c r="U73" s="22">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="V73" s="22">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="W73" s="22">
+        <v>0.73684210526315785</v>
+      </c>
+      <c r="X73" s="22">
+        <v>0.61904761904761907</v>
+      </c>
+      <c r="Y73" s="22">
+        <v>0.5</v>
+      </c>
       <c r="Z73" s="22"/>
       <c r="AA73" s="22"/>
-      <c r="AB73" s="22"/>
-      <c r="AC73" s="22"/>
-      <c r="AD73" s="22"/>
-      <c r="AE73" s="22"/>
-      <c r="AF73" s="22"/>
-      <c r="AG73" s="22"/>
+      <c r="AB73" s="22">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="AC73" s="22">
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="AD73" s="22">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="AE73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="22">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="AG73" s="22">
+        <v>0.66666666666666663</v>
+      </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="27">
@@ -21845,9 +21925,7 @@
       <c r="Z2" s="24">
         <v>1</v>
       </c>
-      <c r="AA2" s="24">
-        <v>1</v>
-      </c>
+      <c r="AA2" s="24"/>
       <c r="AB2" s="24">
         <v>1</v>
       </c>
@@ -21946,9 +22024,7 @@
       <c r="Z3" s="24">
         <v>1</v>
       </c>
-      <c r="AA3" s="24">
-        <v>1</v>
-      </c>
+      <c r="AA3" s="24"/>
       <c r="AB3" s="24">
         <v>1</v>
       </c>
@@ -22047,9 +22123,7 @@
       <c r="Z4" s="24">
         <v>1</v>
       </c>
-      <c r="AA4" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA4" s="24"/>
       <c r="AB4" s="24">
         <v>1</v>
       </c>
@@ -22148,9 +22222,7 @@
       <c r="Z5" s="24">
         <v>1</v>
       </c>
-      <c r="AA5" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA5" s="24"/>
       <c r="AB5" s="24">
         <v>1</v>
       </c>
@@ -22249,9 +22321,7 @@
       <c r="Z6" s="24">
         <v>1</v>
       </c>
-      <c r="AA6" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA6" s="24"/>
       <c r="AB6" s="24">
         <v>1</v>
       </c>
@@ -22350,9 +22420,7 @@
       <c r="Z7" s="24">
         <v>1</v>
       </c>
-      <c r="AA7" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA7" s="24"/>
       <c r="AB7" s="24">
         <v>1</v>
       </c>
@@ -22451,8 +22519,8 @@
       <c r="Z8" s="24">
         <v>1</v>
       </c>
-      <c r="AA8" s="24" t="s">
-        <v>47</v>
+      <c r="AA8" s="24">
+        <v>1</v>
       </c>
       <c r="AB8" s="24">
         <v>1</v>
@@ -22552,9 +22620,7 @@
       <c r="Z9" s="24">
         <v>1</v>
       </c>
-      <c r="AA9" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA9" s="24"/>
       <c r="AB9" s="24">
         <v>1</v>
       </c>
@@ -22653,9 +22719,7 @@
       <c r="Z10" s="24">
         <v>1</v>
       </c>
-      <c r="AA10" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA10" s="24"/>
       <c r="AB10" s="24">
         <v>0.89473684210526316</v>
       </c>
@@ -22754,9 +22818,7 @@
       <c r="Z11" s="24">
         <v>1</v>
       </c>
-      <c r="AA11" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA11" s="24"/>
       <c r="AB11" s="24">
         <v>1</v>
       </c>
@@ -22855,9 +22917,7 @@
       <c r="Z12" s="24">
         <v>1</v>
       </c>
-      <c r="AA12" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA12" s="24"/>
       <c r="AB12" s="24">
         <v>1</v>
       </c>
@@ -22956,9 +23016,7 @@
       <c r="Z13" s="24">
         <v>1</v>
       </c>
-      <c r="AA13" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA13" s="24"/>
       <c r="AB13" s="24">
         <v>0.94736842105263153</v>
       </c>
@@ -23057,9 +23115,7 @@
       <c r="Z14" s="24">
         <v>1</v>
       </c>
-      <c r="AA14" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA14" s="24"/>
       <c r="AB14" s="24">
         <v>0.95652173913043481</v>
       </c>
@@ -23158,8 +23214,8 @@
       <c r="Z15" s="24">
         <v>1</v>
       </c>
-      <c r="AA15" s="24" t="s">
-        <v>47</v>
+      <c r="AA15" s="24">
+        <v>1</v>
       </c>
       <c r="AB15" s="24">
         <v>1</v>
@@ -23259,9 +23315,7 @@
       <c r="Z16" s="24">
         <v>1</v>
       </c>
-      <c r="AA16" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA16" s="24"/>
       <c r="AB16" s="24">
         <v>1</v>
       </c>
@@ -23360,9 +23414,7 @@
       <c r="Z17" s="24">
         <v>1</v>
       </c>
-      <c r="AA17" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA17" s="24"/>
       <c r="AB17" s="24">
         <v>0.95238095238095233</v>
       </c>
@@ -23461,9 +23513,7 @@
       <c r="Z18" s="24">
         <v>1</v>
       </c>
-      <c r="AA18" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA18" s="24"/>
       <c r="AB18" s="24">
         <v>0.94117647058823528</v>
       </c>
@@ -23562,9 +23612,7 @@
       <c r="Z19" s="24">
         <v>1</v>
       </c>
-      <c r="AA19" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA19" s="24"/>
       <c r="AB19" s="24">
         <v>1</v>
       </c>
@@ -23663,9 +23711,7 @@
       <c r="Z20" s="24">
         <v>1</v>
       </c>
-      <c r="AA20" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA20" s="24"/>
       <c r="AB20" s="24">
         <v>1</v>
       </c>
@@ -23764,9 +23810,7 @@
       <c r="Z21" s="24">
         <v>1</v>
       </c>
-      <c r="AA21" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA21" s="24"/>
       <c r="AB21" s="24">
         <v>1</v>
       </c>
@@ -23865,9 +23909,7 @@
       <c r="Z22" s="24">
         <v>1</v>
       </c>
-      <c r="AA22" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="AA22" s="24"/>
       <c r="AB22" s="24">
         <v>1</v>
       </c>
@@ -23909,9 +23951,7 @@
       <c r="G23" s="24">
         <v>0.63888888888888884</v>
       </c>
-      <c r="H23" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H23" s="24"/>
       <c r="I23" s="24">
         <v>1</v>
       </c>
@@ -23963,12 +24003,8 @@
       <c r="Y23" s="24">
         <v>1</v>
       </c>
-      <c r="Z23" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA23" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z23" s="24"/>
+      <c r="AA23" s="24"/>
       <c r="AB23" s="24">
         <v>0.94117647058823528</v>
       </c>
@@ -24010,9 +24046,7 @@
       <c r="G24" s="24">
         <v>0.90625</v>
       </c>
-      <c r="H24" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H24" s="24"/>
       <c r="I24" s="24">
         <v>1</v>
       </c>
@@ -24064,12 +24098,8 @@
       <c r="Y24" s="24">
         <v>1</v>
       </c>
-      <c r="Z24" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA24" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z24" s="24"/>
+      <c r="AA24" s="24"/>
       <c r="AB24" s="24">
         <v>1</v>
       </c>
@@ -24111,9 +24141,7 @@
       <c r="G25" s="24">
         <v>1</v>
       </c>
-      <c r="H25" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H25" s="24"/>
       <c r="I25" s="24">
         <v>1</v>
       </c>
@@ -24165,12 +24193,8 @@
       <c r="Y25" s="24">
         <v>1</v>
       </c>
-      <c r="Z25" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA25" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z25" s="24"/>
+      <c r="AA25" s="24"/>
       <c r="AB25" s="24">
         <v>1</v>
       </c>
@@ -24212,9 +24236,7 @@
       <c r="G26" s="24">
         <v>0.77083333333333337</v>
       </c>
-      <c r="H26" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H26" s="24"/>
       <c r="I26" s="24">
         <v>0.97872340425531912</v>
       </c>
@@ -24266,12 +24288,8 @@
       <c r="Y26" s="24">
         <v>1</v>
       </c>
-      <c r="Z26" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA26" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z26" s="24"/>
+      <c r="AA26" s="24"/>
       <c r="AB26" s="24">
         <v>0.92307692307692313</v>
       </c>
@@ -24313,9 +24331,7 @@
       <c r="G27" s="24">
         <v>0.69230769230769229</v>
       </c>
-      <c r="H27" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H27" s="24"/>
       <c r="I27" s="24">
         <v>0.97916666666666663</v>
       </c>
@@ -24367,12 +24383,8 @@
       <c r="Y27" s="24">
         <v>1</v>
       </c>
-      <c r="Z27" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA27" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z27" s="24"/>
+      <c r="AA27" s="24"/>
       <c r="AB27" s="24">
         <v>0.92307692307692313</v>
       </c>
@@ -24414,9 +24426,7 @@
       <c r="G28" s="24">
         <v>1</v>
       </c>
-      <c r="H28" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H28" s="24"/>
       <c r="I28" s="24">
         <v>0.97368421052631582</v>
       </c>
@@ -24468,12 +24478,8 @@
       <c r="Y28" s="24">
         <v>1</v>
       </c>
-      <c r="Z28" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA28" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z28" s="24"/>
+      <c r="AA28" s="24"/>
       <c r="AB28" s="24">
         <v>1</v>
       </c>
@@ -24515,9 +24521,7 @@
       <c r="G29" s="24">
         <v>1</v>
       </c>
-      <c r="H29" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H29" s="24"/>
       <c r="I29" s="24">
         <v>1</v>
       </c>
@@ -24569,12 +24573,8 @@
       <c r="Y29" s="24">
         <v>1</v>
       </c>
-      <c r="Z29" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA29" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z29" s="24"/>
+      <c r="AA29" s="24"/>
       <c r="AB29" s="24">
         <v>1</v>
       </c>
@@ -24616,9 +24616,7 @@
       <c r="G30" s="24">
         <v>0.8571428571428571</v>
       </c>
-      <c r="H30" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H30" s="24"/>
       <c r="I30" s="24">
         <v>1</v>
       </c>
@@ -24670,12 +24668,8 @@
       <c r="Y30" s="24">
         <v>1</v>
       </c>
-      <c r="Z30" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA30" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z30" s="24"/>
+      <c r="AA30" s="24"/>
       <c r="AB30" s="24">
         <v>0.94444444444444442</v>
       </c>
@@ -24717,9 +24711,7 @@
       <c r="G31" s="24">
         <v>0.87804878048780488</v>
       </c>
-      <c r="H31" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H31" s="24"/>
       <c r="I31" s="24">
         <v>1</v>
       </c>
@@ -24771,12 +24763,8 @@
       <c r="Y31" s="24">
         <v>1</v>
       </c>
-      <c r="Z31" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA31" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z31" s="24"/>
+      <c r="AA31" s="24"/>
       <c r="AB31" s="24">
         <v>1</v>
       </c>
@@ -24818,9 +24806,7 @@
       <c r="G32" s="24">
         <v>1</v>
       </c>
-      <c r="H32" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H32" s="24"/>
       <c r="I32" s="24">
         <v>0.97674418604651159</v>
       </c>
@@ -24872,12 +24858,8 @@
       <c r="Y32" s="24">
         <v>1</v>
       </c>
-      <c r="Z32" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA32" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z32" s="24"/>
+      <c r="AA32" s="24"/>
       <c r="AB32" s="24">
         <v>1</v>
       </c>
@@ -24919,9 +24901,7 @@
       <c r="G33" s="24">
         <v>0.92</v>
       </c>
-      <c r="H33" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H33" s="24"/>
       <c r="I33" s="24">
         <v>1</v>
       </c>
@@ -24973,12 +24953,8 @@
       <c r="Y33" s="24">
         <v>1</v>
       </c>
-      <c r="Z33" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA33" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z33" s="24"/>
+      <c r="AA33" s="24"/>
       <c r="AB33" s="24">
         <v>1</v>
       </c>
@@ -25020,9 +24996,7 @@
       <c r="G34" s="24">
         <v>0.96969696969696972</v>
       </c>
-      <c r="H34" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H34" s="24"/>
       <c r="I34" s="24">
         <v>0.97872340425531912</v>
       </c>
@@ -25074,12 +25048,8 @@
       <c r="Y34" s="24">
         <v>1</v>
       </c>
-      <c r="Z34" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA34" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z34" s="24"/>
+      <c r="AA34" s="24"/>
       <c r="AB34" s="24">
         <v>1</v>
       </c>
@@ -25121,9 +25091,7 @@
       <c r="G35" s="24">
         <v>0.94285714285714284</v>
       </c>
-      <c r="H35" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H35" s="24"/>
       <c r="I35" s="24">
         <v>1</v>
       </c>
@@ -25175,12 +25143,8 @@
       <c r="Y35" s="24">
         <v>1</v>
       </c>
-      <c r="Z35" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA35" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z35" s="24"/>
+      <c r="AA35" s="24"/>
       <c r="AB35" s="24">
         <v>1</v>
       </c>
@@ -25222,9 +25186,7 @@
       <c r="G36" s="24">
         <v>0.55102040816326525</v>
       </c>
-      <c r="H36" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H36" s="24"/>
       <c r="I36" s="24">
         <v>1</v>
       </c>
@@ -25276,12 +25238,8 @@
       <c r="Y36" s="24">
         <v>1</v>
       </c>
-      <c r="Z36" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA36" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z36" s="24"/>
+      <c r="AA36" s="24"/>
       <c r="AB36" s="24">
         <v>1</v>
       </c>
@@ -25323,9 +25281,7 @@
       <c r="G37" s="24">
         <v>0.90697674418604646</v>
       </c>
-      <c r="H37" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H37" s="24"/>
       <c r="I37" s="24">
         <v>0.90384615384615385</v>
       </c>
@@ -25377,12 +25333,8 @@
       <c r="Y37" s="24">
         <v>1</v>
       </c>
-      <c r="Z37" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA37" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z37" s="24"/>
+      <c r="AA37" s="24"/>
       <c r="AB37" s="24">
         <v>1</v>
       </c>
@@ -25424,9 +25376,7 @@
       <c r="G38" s="24">
         <v>0.76923076923076927</v>
       </c>
-      <c r="H38" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H38" s="24"/>
       <c r="I38" s="24">
         <v>0.97916666666666663</v>
       </c>
@@ -25478,12 +25428,8 @@
       <c r="Y38" s="24">
         <v>1</v>
       </c>
-      <c r="Z38" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA38" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z38" s="24"/>
+      <c r="AA38" s="24"/>
       <c r="AB38" s="24">
         <v>0.92307692307692313</v>
       </c>
@@ -25525,9 +25471,7 @@
       <c r="G39" s="24">
         <v>0.60606060606060608</v>
       </c>
-      <c r="H39" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H39" s="24"/>
       <c r="I39" s="24">
         <v>0.97619047619047616</v>
       </c>
@@ -25579,12 +25523,8 @@
       <c r="Y39" s="24">
         <v>1</v>
       </c>
-      <c r="Z39" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA39" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z39" s="24"/>
+      <c r="AA39" s="24"/>
       <c r="AB39" s="24">
         <v>0.88235294117647056</v>
       </c>
@@ -25626,9 +25566,7 @@
       <c r="G40" s="24">
         <v>0.58333333333333337</v>
       </c>
-      <c r="H40" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H40" s="24"/>
       <c r="I40" s="24">
         <v>0.98039215686274506</v>
       </c>
@@ -25680,12 +25618,8 @@
       <c r="Y40" s="24">
         <v>1</v>
       </c>
-      <c r="Z40" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA40" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z40" s="24"/>
+      <c r="AA40" s="24"/>
       <c r="AB40" s="24">
         <v>0.94117647058823528</v>
       </c>
@@ -25727,9 +25661,7 @@
       <c r="G41" s="24">
         <v>0.8928571428571429</v>
       </c>
-      <c r="H41" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H41" s="24"/>
       <c r="I41" s="24">
         <v>0.97619047619047616</v>
       </c>
@@ -25781,12 +25713,8 @@
       <c r="Y41" s="24">
         <v>1</v>
       </c>
-      <c r="Z41" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA41" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z41" s="24"/>
+      <c r="AA41" s="24"/>
       <c r="AB41" s="24">
         <v>1</v>
       </c>
@@ -25828,9 +25756,7 @@
       <c r="G42" s="24">
         <v>0.96551724137931039</v>
       </c>
-      <c r="H42" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H42" s="24"/>
       <c r="I42" s="24">
         <v>1</v>
       </c>
@@ -25882,12 +25808,8 @@
       <c r="Y42" s="24">
         <v>1</v>
       </c>
-      <c r="Z42" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA42" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z42" s="24"/>
+      <c r="AA42" s="24"/>
       <c r="AB42" s="24">
         <v>1</v>
       </c>
@@ -25929,9 +25851,7 @@
       <c r="G43" s="24">
         <v>0.9375</v>
       </c>
-      <c r="H43" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H43" s="24"/>
       <c r="I43" s="24">
         <v>1</v>
       </c>
@@ -25983,12 +25903,8 @@
       <c r="Y43" s="24">
         <v>1</v>
       </c>
-      <c r="Z43" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA43" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z43" s="24"/>
+      <c r="AA43" s="24"/>
       <c r="AB43" s="24">
         <v>1</v>
       </c>
@@ -26030,9 +25946,7 @@
       <c r="G44" s="24">
         <v>0.91666666666666663</v>
       </c>
-      <c r="H44" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H44" s="24"/>
       <c r="I44" s="24">
         <v>1</v>
       </c>
@@ -26084,12 +25998,8 @@
       <c r="Y44" s="24">
         <v>1</v>
       </c>
-      <c r="Z44" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA44" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z44" s="24"/>
+      <c r="AA44" s="24"/>
       <c r="AB44" s="24">
         <v>1</v>
       </c>
@@ -26131,9 +26041,7 @@
       <c r="G45" s="24">
         <v>0.88571428571428568</v>
       </c>
-      <c r="H45" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H45" s="24"/>
       <c r="I45" s="24">
         <v>0.95918367346938771</v>
       </c>
@@ -26185,12 +26093,8 @@
       <c r="Y45" s="24">
         <v>1</v>
       </c>
-      <c r="Z45" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA45" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z45" s="24"/>
+      <c r="AA45" s="24"/>
       <c r="AB45" s="24">
         <v>1</v>
       </c>
@@ -26232,9 +26136,7 @@
       <c r="G46" s="24">
         <v>0.97142857142857142</v>
       </c>
-      <c r="H46" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H46" s="24"/>
       <c r="I46" s="24">
         <v>0.97674418604651159</v>
       </c>
@@ -26286,12 +26188,8 @@
       <c r="Y46" s="24">
         <v>1</v>
       </c>
-      <c r="Z46" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA46" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z46" s="24"/>
+      <c r="AA46" s="24"/>
       <c r="AB46" s="24">
         <v>1</v>
       </c>
@@ -26333,9 +26231,7 @@
       <c r="G47" s="24">
         <v>0.86956521739130432</v>
       </c>
-      <c r="H47" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H47" s="24"/>
       <c r="I47" s="24">
         <v>1</v>
       </c>
@@ -26387,12 +26283,8 @@
       <c r="Y47" s="24">
         <v>0.8</v>
       </c>
-      <c r="Z47" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA47" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z47" s="24"/>
+      <c r="AA47" s="24"/>
       <c r="AB47" s="24">
         <v>0.94117647058823528</v>
       </c>
@@ -26434,9 +26326,7 @@
       <c r="G48" s="24">
         <v>0.69444444444444442</v>
       </c>
-      <c r="H48" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H48" s="24"/>
       <c r="I48" s="24">
         <v>0.97777777777777775</v>
       </c>
@@ -26488,12 +26378,8 @@
       <c r="Y48" s="24">
         <v>1</v>
       </c>
-      <c r="Z48" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA48" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z48" s="24"/>
+      <c r="AA48" s="24"/>
       <c r="AB48" s="24">
         <v>1</v>
       </c>
@@ -26535,9 +26421,7 @@
       <c r="G49" s="24">
         <v>0.78260869565217395</v>
       </c>
-      <c r="H49" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H49" s="24"/>
       <c r="I49" s="24">
         <v>0.97959183673469385</v>
       </c>
@@ -26589,12 +26473,8 @@
       <c r="Y49" s="24">
         <v>1</v>
       </c>
-      <c r="Z49" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA49" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z49" s="24"/>
+      <c r="AA49" s="24"/>
       <c r="AB49" s="24">
         <v>1</v>
       </c>
@@ -26636,9 +26516,7 @@
       <c r="G50" s="24">
         <v>0.95121951219512191</v>
       </c>
-      <c r="H50" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H50" s="24"/>
       <c r="I50" s="24">
         <v>1</v>
       </c>
@@ -26690,12 +26568,8 @@
       <c r="Y50" s="24">
         <v>1</v>
       </c>
-      <c r="Z50" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA50" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z50" s="24"/>
+      <c r="AA50" s="24"/>
       <c r="AB50" s="24">
         <v>1</v>
       </c>
@@ -26737,9 +26611,7 @@
       <c r="G51" s="24">
         <v>0.94871794871794868</v>
       </c>
-      <c r="H51" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H51" s="24"/>
       <c r="I51" s="24">
         <v>0.97916666666666663</v>
       </c>
@@ -26791,12 +26663,8 @@
       <c r="Y51" s="24">
         <v>0.91666666666666663</v>
       </c>
-      <c r="Z51" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA51" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z51" s="24"/>
+      <c r="AA51" s="24"/>
       <c r="AB51" s="24">
         <v>1</v>
       </c>
@@ -26838,9 +26706,7 @@
       <c r="G52" s="24">
         <v>0.76470588235294112</v>
       </c>
-      <c r="H52" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H52" s="24"/>
       <c r="I52" s="24">
         <v>0.97826086956521741</v>
       </c>
@@ -26892,12 +26758,8 @@
       <c r="Y52" s="24">
         <v>0.8125</v>
       </c>
-      <c r="Z52" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA52" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z52" s="24"/>
+      <c r="AA52" s="24"/>
       <c r="AB52" s="24">
         <v>1</v>
       </c>
@@ -26939,9 +26801,7 @@
       <c r="G53" s="24">
         <v>0.65714285714285714</v>
       </c>
-      <c r="H53" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H53" s="24"/>
       <c r="I53" s="24">
         <v>1</v>
       </c>
@@ -26993,12 +26853,8 @@
       <c r="Y53" s="24">
         <v>1</v>
       </c>
-      <c r="Z53" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA53" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z53" s="24"/>
+      <c r="AA53" s="24"/>
       <c r="AB53" s="24">
         <v>1</v>
       </c>
@@ -27040,9 +26896,7 @@
       <c r="G54" s="24">
         <v>0.73684210526315785</v>
       </c>
-      <c r="H54" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H54" s="24"/>
       <c r="I54" s="24">
         <v>0.78125</v>
       </c>
@@ -27094,12 +26948,8 @@
       <c r="Y54" s="24">
         <v>0.6</v>
       </c>
-      <c r="Z54" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA54" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z54" s="24"/>
+      <c r="AA54" s="24"/>
       <c r="AB54" s="24">
         <v>0.75</v>
       </c>
@@ -27141,9 +26991,7 @@
       <c r="G55" s="24">
         <v>0.87878787878787878</v>
       </c>
-      <c r="H55" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H55" s="24"/>
       <c r="I55" s="24">
         <v>1</v>
       </c>
@@ -27195,12 +27043,8 @@
       <c r="Y55" s="24">
         <v>0.94117647058823528</v>
       </c>
-      <c r="Z55" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA55" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z55" s="24"/>
+      <c r="AA55" s="24"/>
       <c r="AB55" s="24">
         <v>1</v>
       </c>
@@ -27242,9 +27086,7 @@
       <c r="G56" s="24">
         <v>0.7857142857142857</v>
       </c>
-      <c r="H56" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H56" s="24"/>
       <c r="I56" s="24">
         <v>0.98148148148148151</v>
       </c>
@@ -27296,12 +27138,8 @@
       <c r="Y56" s="24">
         <v>0.75</v>
       </c>
-      <c r="Z56" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA56" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z56" s="24"/>
+      <c r="AA56" s="24"/>
       <c r="AB56" s="24">
         <v>1</v>
       </c>
@@ -27343,9 +27181,7 @@
       <c r="G57" s="24">
         <v>0.69444444444444442</v>
       </c>
-      <c r="H57" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="H57" s="24"/>
       <c r="I57" s="24">
         <v>0.9</v>
       </c>
@@ -27397,12 +27233,8 @@
       <c r="Y57" s="24">
         <v>0.7142857142857143</v>
       </c>
-      <c r="Z57" s="24" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA57" s="24" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z57" s="24"/>
+      <c r="AA57" s="24"/>
       <c r="AB57" s="24">
         <v>0.94444444444444442</v>
       </c>
@@ -27444,9 +27276,7 @@
       <c r="G58" s="25">
         <v>0.95454545454545459</v>
       </c>
-      <c r="H58" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H58" s="25"/>
       <c r="I58" s="25">
         <v>0.95833333333333337</v>
       </c>
@@ -27498,12 +27328,8 @@
       <c r="Y58" s="25">
         <v>0.8</v>
       </c>
-      <c r="Z58" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA58" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z58" s="25"/>
+      <c r="AA58" s="25"/>
       <c r="AB58" s="25">
         <v>0.77777777777777779</v>
       </c>
@@ -27545,9 +27371,7 @@
       <c r="G59" s="25">
         <v>0.78260869565217395</v>
       </c>
-      <c r="H59" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H59" s="25"/>
       <c r="I59" s="25">
         <v>1</v>
       </c>
@@ -27599,12 +27423,8 @@
       <c r="Y59" s="25">
         <v>1</v>
       </c>
-      <c r="Z59" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA59" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z59" s="25"/>
+      <c r="AA59" s="25"/>
       <c r="AB59" s="25">
         <v>1</v>
       </c>
@@ -27646,9 +27466,7 @@
       <c r="G60" s="25">
         <v>1</v>
       </c>
-      <c r="H60" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H60" s="25"/>
       <c r="I60" s="25">
         <v>1</v>
       </c>
@@ -27700,12 +27518,8 @@
       <c r="Y60" s="25">
         <v>0.90909090909090906</v>
       </c>
-      <c r="Z60" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA60" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z60" s="25"/>
+      <c r="AA60" s="25"/>
       <c r="AB60" s="25">
         <v>1</v>
       </c>
@@ -27747,9 +27561,7 @@
       <c r="G61" s="25">
         <v>0.72413793103448276</v>
       </c>
-      <c r="H61" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H61" s="25"/>
       <c r="I61" s="25">
         <v>0.96551724137931039</v>
       </c>
@@ -27801,12 +27613,8 @@
       <c r="Y61" s="25">
         <v>0.75</v>
       </c>
-      <c r="Z61" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA61" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z61" s="25"/>
+      <c r="AA61" s="25"/>
       <c r="AB61" s="25">
         <v>0.89473684210526316</v>
       </c>
@@ -27848,9 +27656,7 @@
       <c r="G62" s="25">
         <v>0.45833333333333331</v>
       </c>
-      <c r="H62" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H62" s="25"/>
       <c r="I62" s="25">
         <v>0.95833333333333337</v>
       </c>
@@ -27902,12 +27708,8 @@
       <c r="Y62" s="25">
         <v>0.90909090909090906</v>
       </c>
-      <c r="Z62" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA62" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z62" s="25"/>
+      <c r="AA62" s="25"/>
       <c r="AB62" s="25">
         <v>0.94444444444444442</v>
       </c>
@@ -27949,9 +27751,7 @@
       <c r="G63" s="25">
         <v>0.94117647058823528</v>
       </c>
-      <c r="H63" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H63" s="25"/>
       <c r="I63" s="25">
         <v>0.97368421052631582</v>
       </c>
@@ -28003,12 +27803,8 @@
       <c r="Y63" s="25">
         <v>1</v>
       </c>
-      <c r="Z63" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA63" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z63" s="25"/>
+      <c r="AA63" s="25"/>
       <c r="AB63" s="25">
         <v>1</v>
       </c>
@@ -28050,9 +27846,7 @@
       <c r="G64" s="25">
         <v>0.66666666666666663</v>
       </c>
-      <c r="H64" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H64" s="25"/>
       <c r="I64" s="25">
         <v>0.95121951219512191</v>
       </c>
@@ -28104,12 +27898,8 @@
       <c r="Y64" s="25">
         <v>1</v>
       </c>
-      <c r="Z64" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA64" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z64" s="25"/>
+      <c r="AA64" s="25"/>
       <c r="AB64" s="25">
         <v>0.77777777777777779</v>
       </c>
@@ -28151,9 +27941,7 @@
       <c r="G65" s="25">
         <v>0.56666666666666665</v>
       </c>
-      <c r="H65" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H65" s="25"/>
       <c r="I65" s="25">
         <v>1</v>
       </c>
@@ -28205,12 +27993,8 @@
       <c r="Y65" s="25">
         <v>0.8</v>
       </c>
-      <c r="Z65" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA65" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z65" s="25"/>
+      <c r="AA65" s="25"/>
       <c r="AB65" s="25">
         <v>0.94444444444444442</v>
       </c>
@@ -28252,9 +28036,7 @@
       <c r="G66" s="25">
         <v>0.70833333333333337</v>
       </c>
-      <c r="H66" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H66" s="25"/>
       <c r="I66" s="25">
         <v>0.91176470588235292</v>
       </c>
@@ -28306,12 +28088,8 @@
       <c r="Y66" s="25">
         <v>0.81818181818181823</v>
       </c>
-      <c r="Z66" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA66" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z66" s="25"/>
+      <c r="AA66" s="25"/>
       <c r="AB66" s="25">
         <v>0.81818181818181823</v>
       </c>
@@ -28353,9 +28131,7 @@
       <c r="G67" s="25">
         <v>0.8666666666666667</v>
       </c>
-      <c r="H67" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H67" s="25"/>
       <c r="I67" s="25">
         <v>1</v>
       </c>
@@ -28407,12 +28183,8 @@
       <c r="Y67" s="25">
         <v>0.75</v>
       </c>
-      <c r="Z67" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA67" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z67" s="25"/>
+      <c r="AA67" s="25"/>
       <c r="AB67" s="25">
         <v>0.94444444444444442</v>
       </c>
@@ -28454,9 +28226,7 @@
       <c r="G68" s="25">
         <v>0.9</v>
       </c>
-      <c r="H68" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H68" s="25"/>
       <c r="I68" s="25">
         <v>1</v>
       </c>
@@ -28508,12 +28278,8 @@
       <c r="Y68" s="25">
         <v>0.88888888888888884</v>
       </c>
-      <c r="Z68" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA68" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z68" s="25"/>
+      <c r="AA68" s="25"/>
       <c r="AB68" s="25">
         <v>1</v>
       </c>
@@ -28555,9 +28321,7 @@
       <c r="G69" s="25">
         <v>0.84210526315789469</v>
       </c>
-      <c r="H69" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H69" s="25"/>
       <c r="I69" s="25">
         <v>0.85106382978723405</v>
       </c>
@@ -28609,12 +28373,8 @@
       <c r="Y69" s="25">
         <v>0.75</v>
       </c>
-      <c r="Z69" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA69" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z69" s="25"/>
+      <c r="AA69" s="25"/>
       <c r="AB69" s="25">
         <v>0.90909090909090906</v>
       </c>
@@ -28656,9 +28416,7 @@
       <c r="G70" s="25">
         <v>0.67500000000000004</v>
       </c>
-      <c r="H70" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H70" s="25"/>
       <c r="I70" s="25">
         <v>0.97959183673469385</v>
       </c>
@@ -28710,12 +28468,8 @@
       <c r="Y70" s="25">
         <v>0.91666666666666663</v>
       </c>
-      <c r="Z70" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA70" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z70" s="25"/>
+      <c r="AA70" s="25"/>
       <c r="AB70" s="25">
         <v>0.95833333333333337</v>
       </c>
@@ -28757,9 +28511,7 @@
       <c r="G71" s="25">
         <v>0.78048780487804881</v>
       </c>
-      <c r="H71" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H71" s="25"/>
       <c r="I71" s="25">
         <v>0.89743589743589747</v>
       </c>
@@ -28811,12 +28563,8 @@
       <c r="Y71" s="25">
         <v>0.9</v>
       </c>
-      <c r="Z71" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA71" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z71" s="25"/>
+      <c r="AA71" s="25"/>
       <c r="AB71" s="25">
         <v>0.52941176470588236</v>
       </c>
@@ -28858,9 +28606,7 @@
       <c r="G72" s="25">
         <v>0.54545454545454541</v>
       </c>
-      <c r="H72" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="H72" s="25"/>
       <c r="I72" s="25">
         <v>0.95238095238095233</v>
       </c>
@@ -28912,12 +28658,8 @@
       <c r="Y72" s="25">
         <v>1</v>
       </c>
-      <c r="Z72" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA72" s="25" t="s">
-        <v>47</v>
-      </c>
+      <c r="Z72" s="25"/>
+      <c r="AA72" s="25"/>
       <c r="AB72" s="25">
         <v>1</v>
       </c>
@@ -28933,9 +28675,7 @@
       <c r="AF72" s="25">
         <v>1</v>
       </c>
-      <c r="AG72" s="25">
-        <v>1</v>
-      </c>
+      <c r="AG72" s="25"/>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="27">
@@ -28947,35 +28687,87 @@
       <c r="C73" s="21">
         <v>19</v>
       </c>
-      <c r="D73" s="22"/>
-      <c r="E73" s="22"/>
-      <c r="F73" s="22"/>
-      <c r="G73" s="22"/>
+      <c r="D73" s="22">
+        <v>0.88636363636363635</v>
+      </c>
+      <c r="E73" s="22">
+        <v>0.83798882681564246</v>
+      </c>
+      <c r="F73" s="22">
+        <v>0.95348837209302328</v>
+      </c>
+      <c r="G73" s="22">
+        <v>0.84444444444444444</v>
+      </c>
       <c r="H73" s="22"/>
-      <c r="I73" s="22"/>
-      <c r="J73" s="22"/>
-      <c r="K73" s="22"/>
-      <c r="L73" s="22"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-      <c r="X73" s="22"/>
-      <c r="Y73" s="22"/>
+      <c r="I73" s="22">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="J73" s="22">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="K73" s="22">
+        <v>0.81632653061224492</v>
+      </c>
+      <c r="L73" s="22">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="M73" s="22">
+        <v>1</v>
+      </c>
+      <c r="N73" s="22">
+        <v>1</v>
+      </c>
+      <c r="O73" s="22">
+        <v>1</v>
+      </c>
+      <c r="P73" s="22">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="22">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="R73" s="22">
+        <v>0.80769230769230771</v>
+      </c>
+      <c r="S73" s="22">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="T73" s="22">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="U73" s="22">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="V73" s="22">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="W73" s="22">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="X73" s="22">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="Y73" s="22">
+        <v>0.66666666666666663</v>
+      </c>
       <c r="Z73" s="22"/>
       <c r="AA73" s="22"/>
-      <c r="AB73" s="22"/>
-      <c r="AC73" s="22"/>
-      <c r="AD73" s="22"/>
-      <c r="AE73" s="22"/>
-      <c r="AF73" s="22"/>
+      <c r="AB73" s="22">
+        <v>0.91304347826086951</v>
+      </c>
+      <c r="AC73" s="22">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="AD73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="22">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="22">
+        <v>1</v>
+      </c>
       <c r="AG73" s="22"/>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
@@ -32674,88 +32466,88 @@
         <v>1</v>
       </c>
       <c r="D55" s="25">
-        <v>0.95666666666666667</v>
+        <v>0.51777777777777778</v>
       </c>
       <c r="E55" s="25">
-        <v>0.93442622950819676</v>
+        <v>0.47830279652844743</v>
       </c>
       <c r="F55" s="25">
-        <v>0.98689384010484926</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="G55" s="25">
-        <v>0.89583333333333337</v>
+        <v>0.375</v>
       </c>
       <c r="H55" s="25"/>
       <c r="I55" s="25">
-        <v>1</v>
+        <v>0.56216216216216219</v>
       </c>
       <c r="J55" s="25">
-        <v>0.87368421052631584</v>
+        <v>0.54736842105263162</v>
       </c>
       <c r="K55" s="25">
-        <v>0.95497630331753558</v>
+        <v>0.46919431279620855</v>
       </c>
       <c r="L55" s="25">
-        <v>1</v>
+        <v>0.80392156862745101</v>
       </c>
       <c r="M55" s="25">
-        <v>0.90099009900990101</v>
+        <v>0.41584158415841582</v>
       </c>
       <c r="N55" s="25">
-        <v>1</v>
+        <v>0.66222222222222227</v>
       </c>
       <c r="O55" s="25">
-        <v>1</v>
+        <v>0.25766871165644173</v>
       </c>
       <c r="P55" s="25">
-        <v>1</v>
+        <v>0.55714285714285716</v>
       </c>
       <c r="Q55" s="25">
-        <v>1</v>
+        <v>0.30681818181818182</v>
       </c>
       <c r="R55" s="25">
-        <v>1</v>
+        <v>0.79365079365079361</v>
       </c>
       <c r="S55" s="25">
-        <v>1</v>
+        <v>0.58571428571428574</v>
       </c>
       <c r="T55" s="25">
-        <v>0.93103448275862066</v>
+        <v>0.40948275862068967</v>
       </c>
       <c r="U55" s="25">
-        <v>0.83552631578947367</v>
+        <v>0.41447368421052633</v>
       </c>
       <c r="V55" s="25">
-        <v>0.78260869565217395</v>
+        <v>0.62318840579710144</v>
       </c>
       <c r="W55" s="25">
-        <v>1</v>
+        <v>0.44262295081967212</v>
       </c>
       <c r="X55" s="25">
-        <v>0.92561983471074383</v>
+        <v>0.50413223140495866</v>
       </c>
       <c r="Y55" s="25">
-        <v>0.97499999999999998</v>
+        <v>0.51666666666666672</v>
       </c>
       <c r="Z55" s="25"/>
       <c r="AA55" s="25"/>
       <c r="AB55" s="25">
-        <v>1</v>
+        <v>0.9140625</v>
       </c>
       <c r="AC55" s="25">
-        <v>1</v>
+        <v>0.61842105263157898</v>
       </c>
       <c r="AD55" s="25">
-        <v>0.90099009900990101</v>
+        <v>0.41584158415841582</v>
       </c>
       <c r="AE55" s="25">
-        <v>1</v>
+        <v>0.66222222222222227</v>
       </c>
       <c r="AF55" s="25">
-        <v>1</v>
+        <v>0.25766871165644173</v>
       </c>
       <c r="AG55" s="25">
-        <v>1</v>
+        <v>0.55714285714285716</v>
       </c>
     </row>
     <row r="56" spans="1:33" x14ac:dyDescent="0.25">
@@ -32838,7 +32630,7 @@
         <v>1</v>
       </c>
       <c r="AC56" s="25">
-        <v>1</v>
+        <v>0.84895833333333337</v>
       </c>
       <c r="AD56" s="25">
         <v>0.81067961165048541</v>
@@ -32864,88 +32656,88 @@
         <v>3</v>
       </c>
       <c r="D57" s="25">
-        <v>0.85260770975056688</v>
+        <v>0.34920634920634919</v>
       </c>
       <c r="E57" s="25">
-        <v>0.81595092024539873</v>
+        <v>0.30736196319018405</v>
       </c>
       <c r="F57" s="25">
-        <v>0.87815305686190681</v>
+        <v>0.37836682342881572</v>
       </c>
       <c r="G57" s="25">
-        <v>0.5662650602409639</v>
+        <v>0.23795180722891565</v>
       </c>
       <c r="H57" s="25"/>
       <c r="I57" s="25">
-        <v>0.97330595482546201</v>
+        <v>0.29774127310061604</v>
       </c>
       <c r="J57" s="25">
-        <v>0.79002624671916011</v>
+        <v>0.40157480314960631</v>
       </c>
       <c r="K57" s="25">
-        <v>0.85348837209302331</v>
+        <v>0.28837209302325584</v>
       </c>
       <c r="L57" s="25">
-        <v>0.80538922155688619</v>
+        <v>0.4880239520958084</v>
       </c>
       <c r="M57" s="25">
-        <v>0.57765667574931878</v>
+        <v>0.2561307901907357</v>
       </c>
       <c r="N57" s="25">
-        <v>1</v>
+        <v>0.39512195121951221</v>
       </c>
       <c r="O57" s="25">
-        <v>1</v>
+        <v>0.33374384236453203</v>
       </c>
       <c r="P57" s="25">
-        <v>1</v>
+        <v>0.3902439024390244</v>
       </c>
       <c r="Q57" s="25">
-        <v>0.70731707317073167</v>
+        <v>0.26829268292682928</v>
       </c>
       <c r="R57" s="25">
-        <v>1</v>
+        <v>0.47169811320754718</v>
       </c>
       <c r="S57" s="25">
-        <v>0.94936708860759489</v>
+        <v>0.25949367088607594</v>
       </c>
       <c r="T57" s="25">
-        <v>0.82653061224489799</v>
+        <v>0.30612244897959184</v>
       </c>
       <c r="U57" s="25">
-        <v>0.52</v>
+        <v>0.22800000000000001</v>
       </c>
       <c r="V57" s="25">
-        <v>0.84</v>
+        <v>0.48799999999999999</v>
       </c>
       <c r="W57" s="25">
-        <v>0.96036585365853655</v>
+        <v>0.21341463414634146</v>
       </c>
       <c r="X57" s="25">
-        <v>0.765625</v>
+        <v>0.359375</v>
       </c>
       <c r="Y57" s="25">
-        <v>0.7816091954022989</v>
+        <v>0.3045977011494253</v>
       </c>
       <c r="Z57" s="25"/>
       <c r="AA57" s="25"/>
       <c r="AB57" s="25">
-        <v>0.99667774086378735</v>
+        <v>0.65780730897009965</v>
       </c>
       <c r="AC57" s="25">
-        <v>0.99667774086378735</v>
+        <v>0.34877384196185285</v>
       </c>
       <c r="AD57" s="25">
-        <v>0.57765667574931878</v>
+        <v>0.2561307901907357</v>
       </c>
       <c r="AE57" s="25">
-        <v>1</v>
+        <v>0.39512195121951221</v>
       </c>
       <c r="AF57" s="25">
-        <v>1</v>
+        <v>0.33374384236453203</v>
       </c>
       <c r="AG57" s="25">
-        <v>1</v>
+        <v>0.3902439024390244</v>
       </c>
     </row>
     <row r="58" spans="1:33" x14ac:dyDescent="0.25">
@@ -32959,88 +32751,88 @@
         <v>4</v>
       </c>
       <c r="D58" s="25">
-        <v>0.9053384700055036</v>
+        <v>8.5855806274078156E-2</v>
       </c>
       <c r="E58" s="25">
-        <v>0.80897009966777411</v>
+        <v>0.11960132890365449</v>
       </c>
       <c r="F58" s="25">
-        <v>0.95308641975308639</v>
+        <v>6.9135802469135796E-2</v>
       </c>
       <c r="G58" s="25">
-        <v>0.80612244897959184</v>
+        <v>0.20408163265306123</v>
       </c>
       <c r="H58" s="25"/>
       <c r="I58" s="25">
-        <v>0.88947368421052631</v>
+        <v>0.10526315789473684</v>
       </c>
       <c r="J58" s="25">
-        <v>0.91666666666666663</v>
+        <v>0.23809523809523808</v>
       </c>
       <c r="K58" s="25">
-        <v>0.70434782608695656</v>
+        <v>5.2173913043478258E-2</v>
       </c>
       <c r="L58" s="25">
-        <v>0.77734375</v>
+        <v>5.859375E-2</v>
       </c>
       <c r="M58" s="25">
-        <v>1</v>
+        <v>8.0536912751677847E-2</v>
       </c>
       <c r="N58" s="25">
-        <v>1</v>
+        <v>7.9470198675496692E-2</v>
       </c>
       <c r="O58" s="25">
-        <v>1</v>
+        <v>6.398104265402843E-2</v>
       </c>
       <c r="P58" s="25">
-        <v>1</v>
+        <v>6.9767441860465115E-2</v>
       </c>
       <c r="Q58" s="25">
-        <v>0.64814814814814814</v>
+        <v>0.18518518518518517</v>
       </c>
       <c r="R58" s="25">
-        <v>1</v>
+        <v>0.12359550561797752</v>
       </c>
       <c r="S58" s="25">
-        <v>1</v>
+        <v>0.11864406779661017</v>
       </c>
       <c r="T58" s="25">
-        <v>0.33783783783783783</v>
+        <v>1.3513513513513514E-2</v>
       </c>
       <c r="U58" s="25">
-        <v>1</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="V58" s="25">
-        <v>1</v>
+        <v>0.2391304347826087</v>
       </c>
       <c r="W58" s="25">
-        <v>0.79207920792079212</v>
+        <v>8.9108910891089105E-2</v>
       </c>
       <c r="X58" s="25">
-        <v>0.81578947368421051</v>
+        <v>0.23684210526315788</v>
       </c>
       <c r="Y58" s="25">
-        <v>0.80412371134020622</v>
+        <v>4.1237113402061855E-2</v>
       </c>
       <c r="Z58" s="25"/>
       <c r="AA58" s="25"/>
       <c r="AB58" s="25">
-        <v>0.76923076923076927</v>
+        <v>5.9829059829059832E-2</v>
       </c>
       <c r="AC58" s="25">
-        <v>0.76923076923076927</v>
+        <v>5.7553956834532377E-2</v>
       </c>
       <c r="AD58" s="25">
-        <v>1</v>
+        <v>8.0536912751677847E-2</v>
       </c>
       <c r="AE58" s="25">
-        <v>1</v>
+        <v>7.9470198675496692E-2</v>
       </c>
       <c r="AF58" s="25">
-        <v>1</v>
+        <v>6.398104265402843E-2</v>
       </c>
       <c r="AG58" s="25">
-        <v>1</v>
+        <v>6.9767441860465115E-2</v>
       </c>
     </row>
     <row r="59" spans="1:33" x14ac:dyDescent="0.25">
@@ -33054,88 +32846,88 @@
         <v>5</v>
       </c>
       <c r="D59" s="25">
-        <v>0.90735975295934124</v>
+        <v>0.28615542974781266</v>
       </c>
       <c r="E59" s="25">
-        <v>0.84723523898781627</v>
+        <v>0.23805060918462981</v>
       </c>
       <c r="F59" s="25">
-        <v>0.98059360730593603</v>
+        <v>0.34474885844748859</v>
       </c>
       <c r="G59" s="25">
-        <v>0.60557768924302791</v>
+        <v>0.12350597609561753</v>
       </c>
       <c r="H59" s="25"/>
       <c r="I59" s="25">
-        <v>0.92519685039370081</v>
+        <v>0.25590551181102361</v>
       </c>
       <c r="J59" s="25">
-        <v>0.89855072463768115</v>
+        <v>0.34299516908212563</v>
       </c>
       <c r="K59" s="25">
-        <v>0.93239436619718308</v>
+        <v>0.24507042253521127</v>
       </c>
       <c r="L59" s="25">
-        <v>0.94158075601374569</v>
+        <v>0.4329896907216495</v>
       </c>
       <c r="M59" s="25">
-        <v>1</v>
+        <v>0.22429906542056074</v>
       </c>
       <c r="N59" s="25">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="O59" s="25">
-        <v>1</v>
+        <v>0.30252100840336132</v>
       </c>
       <c r="P59" s="25">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="Q59" s="25">
-        <v>0.77272727272727271</v>
+        <v>0.16363636363636364</v>
       </c>
       <c r="R59" s="25">
-        <v>1</v>
+        <v>0.39316239316239315</v>
       </c>
       <c r="S59" s="25">
-        <v>1</v>
+        <v>0.17592592592592593</v>
       </c>
       <c r="T59" s="25">
-        <v>0.87037037037037035</v>
+        <v>0.14814814814814814</v>
       </c>
       <c r="U59" s="25">
-        <v>0.47517730496453903</v>
+        <v>9.2198581560283682E-2</v>
       </c>
       <c r="V59" s="25">
-        <v>1</v>
+        <v>0.36363636363636365</v>
       </c>
       <c r="W59" s="25">
-        <v>0.86131386861313863</v>
+        <v>0.13868613138686131</v>
       </c>
       <c r="X59" s="25">
-        <v>0.78350515463917525</v>
+        <v>0.31958762886597936</v>
       </c>
       <c r="Y59" s="25">
-        <v>0.92805755395683454</v>
+        <v>0.37410071942446044</v>
       </c>
       <c r="Z59" s="25"/>
       <c r="AA59" s="25"/>
       <c r="AB59" s="25">
-        <v>0.9550561797752809</v>
+        <v>0.4101123595505618</v>
       </c>
       <c r="AC59" s="25">
-        <v>0.9550561797752809</v>
+        <v>0.46902654867256638</v>
       </c>
       <c r="AD59" s="25">
-        <v>1</v>
+        <v>0.22429906542056074</v>
       </c>
       <c r="AE59" s="25">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
       <c r="AF59" s="25">
-        <v>1</v>
+        <v>0.30252100840336132</v>
       </c>
       <c r="AG59" s="25">
-        <v>1</v>
+        <v>0.33333333333333331</v>
       </c>
     </row>
     <row r="60" spans="1:33" x14ac:dyDescent="0.25">
@@ -33149,88 +32941,88 @@
         <v>6</v>
       </c>
       <c r="D60" s="25">
-        <v>0.93688293370944997</v>
+        <v>0.3578984485190409</v>
       </c>
       <c r="E60" s="25">
-        <v>0.89346246973365617</v>
+        <v>0.31658595641646486</v>
       </c>
       <c r="F60" s="25">
-        <v>0.99746621621621623</v>
+        <v>0.41554054054054052</v>
       </c>
       <c r="G60" s="25">
-        <v>0.65957446808510634</v>
+        <v>0.19414893617021275</v>
       </c>
       <c r="H60" s="25"/>
       <c r="I60" s="25">
-        <v>0.9555555555555556</v>
+        <v>0.35833333333333334</v>
       </c>
       <c r="J60" s="25">
-        <v>0.93800539083557954</v>
+        <v>0.39892183288409705</v>
       </c>
       <c r="K60" s="25">
-        <v>0.98348623853211015</v>
+        <v>0.31743119266055048</v>
       </c>
       <c r="L60" s="25">
-        <v>0.99022801302931596</v>
+        <v>0.45928338762214982</v>
       </c>
       <c r="M60" s="25">
-        <v>1</v>
+        <v>0.24096385542168675</v>
       </c>
       <c r="N60" s="25">
-        <v>1</v>
+        <v>0.5191740412979351</v>
       </c>
       <c r="O60" s="25">
-        <v>1</v>
+        <v>0.33559322033898303</v>
       </c>
       <c r="P60" s="25">
-        <v>1</v>
+        <v>0.46753246753246752</v>
       </c>
       <c r="Q60" s="25">
-        <v>0.5901639344262295</v>
+        <v>0.15846994535519127</v>
       </c>
       <c r="R60" s="25">
-        <v>1</v>
+        <v>0.46496815286624205</v>
       </c>
       <c r="S60" s="25">
-        <v>0.95454545454545459</v>
+        <v>0.38068181818181818</v>
       </c>
       <c r="T60" s="25">
-        <v>1</v>
+        <v>0.30541871921182268</v>
       </c>
       <c r="U60" s="25">
-        <v>0.72538860103626945</v>
+        <v>0.22797927461139897</v>
       </c>
       <c r="V60" s="25">
-        <v>1</v>
+        <v>0.37172774869109948</v>
       </c>
       <c r="W60" s="25">
-        <v>0.9211822660098522</v>
+        <v>0.27586206896551724</v>
       </c>
       <c r="X60" s="25">
-        <v>0.87222222222222223</v>
+        <v>0.42777777777777776</v>
       </c>
       <c r="Y60" s="25">
-        <v>0.99397590361445787</v>
+        <v>0.26506024096385544</v>
       </c>
       <c r="Z60" s="25"/>
       <c r="AA60" s="25"/>
       <c r="AB60" s="25">
-        <v>1</v>
+        <v>0.38364779874213839</v>
       </c>
       <c r="AC60" s="25">
-        <v>1</v>
+        <v>0.54054054054054057</v>
       </c>
       <c r="AD60" s="25">
-        <v>1</v>
+        <v>0.24096385542168675</v>
       </c>
       <c r="AE60" s="25">
-        <v>1</v>
+        <v>0.5191740412979351</v>
       </c>
       <c r="AF60" s="25">
-        <v>1</v>
+        <v>0.33559322033898303</v>
       </c>
       <c r="AG60" s="25">
-        <v>1</v>
+        <v>0.46753246753246752</v>
       </c>
     </row>
     <row r="61" spans="1:33" x14ac:dyDescent="0.25">
@@ -33244,88 +33036,88 @@
         <v>7</v>
       </c>
       <c r="D61" s="25">
-        <v>0.86409209060527292</v>
+        <v>0.30969179353880433</v>
       </c>
       <c r="E61" s="25">
-        <v>0.78024852844996728</v>
+        <v>0.26095487246566385</v>
       </c>
       <c r="F61" s="25">
-        <v>0.97422680412371132</v>
+        <v>0.37371134020618557</v>
       </c>
       <c r="G61" s="25">
-        <v>0.58895705521472397</v>
+        <v>0.16564417177914109</v>
       </c>
       <c r="H61" s="25"/>
       <c r="I61" s="25">
-        <v>0.96460176991150437</v>
+        <v>0.28613569321533922</v>
       </c>
       <c r="J61" s="25">
-        <v>0.72222222222222221</v>
+        <v>0.28888888888888886</v>
       </c>
       <c r="K61" s="25">
-        <v>0.8214285714285714</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="L61" s="25">
-        <v>0.90384615384615385</v>
+        <v>0.45192307692307693</v>
       </c>
       <c r="M61" s="25">
-        <v>1</v>
+        <v>0.25735294117647056</v>
       </c>
       <c r="N61" s="25">
-        <v>1</v>
+        <v>0.44262295081967212</v>
       </c>
       <c r="O61" s="25">
-        <v>1</v>
+        <v>0.27941176470588236</v>
       </c>
       <c r="P61" s="25">
-        <v>1</v>
+        <v>0.40845070422535212</v>
       </c>
       <c r="Q61" s="25">
-        <v>0.70714285714285718</v>
+        <v>0.21428571428571427</v>
       </c>
       <c r="R61" s="25">
-        <v>1</v>
+        <v>0.38410596026490068</v>
       </c>
       <c r="S61" s="25">
-        <v>0.89729729729729735</v>
+        <v>0.32432432432432434</v>
       </c>
       <c r="T61" s="25">
-        <v>0.76315789473684215</v>
+        <v>0.24342105263157895</v>
       </c>
       <c r="U61" s="25">
-        <v>0.5</v>
+        <v>0.12903225806451613</v>
       </c>
       <c r="V61" s="25">
-        <v>0.93888888888888888</v>
+        <v>0.29444444444444445</v>
       </c>
       <c r="W61" s="25">
-        <v>0.93617021276595747</v>
+        <v>0.20744680851063829</v>
       </c>
       <c r="X61" s="25">
-        <v>0.50555555555555554</v>
+        <v>0.28333333333333333</v>
       </c>
       <c r="Y61" s="25">
-        <v>0.79041916167664672</v>
+        <v>0.28143712574850299</v>
       </c>
       <c r="Z61" s="25"/>
       <c r="AA61" s="25"/>
       <c r="AB61" s="25">
-        <v>0.90099009900990101</v>
+        <v>0.46039603960396042</v>
       </c>
       <c r="AC61" s="25">
-        <v>0.90099009900990101</v>
+        <v>0.43636363636363634</v>
       </c>
       <c r="AD61" s="25">
-        <v>1</v>
+        <v>0.25735294117647056</v>
       </c>
       <c r="AE61" s="25">
-        <v>1</v>
+        <v>0.44262295081967212</v>
       </c>
       <c r="AF61" s="25">
-        <v>1</v>
+        <v>0.27941176470588236</v>
       </c>
       <c r="AG61" s="25">
-        <v>1</v>
+        <v>0.40845070422535212</v>
       </c>
     </row>
     <row r="62" spans="1:33" x14ac:dyDescent="0.25">
@@ -33339,88 +33131,88 @@
         <v>8</v>
       </c>
       <c r="D62" s="25">
-        <v>0.87221795855717577</v>
+        <v>0.27705295471987723</v>
       </c>
       <c r="E62" s="25">
-        <v>0.76339969372128635</v>
+        <v>0.20903522205206737</v>
       </c>
       <c r="F62" s="25">
-        <v>0.98153846153846158</v>
+        <v>0.3453846153846154</v>
       </c>
       <c r="G62" s="25">
-        <v>0.47546012269938648</v>
+        <v>8.8957055214723926E-2</v>
       </c>
       <c r="H62" s="25"/>
       <c r="I62" s="25">
-        <v>0.96616541353383456</v>
+        <v>0.27067669172932329</v>
       </c>
       <c r="J62" s="25">
-        <v>0.78498293515358364</v>
+        <v>0.28668941979522183</v>
       </c>
       <c r="K62" s="25">
-        <v>0.84323040380047509</v>
+        <v>0.20902612826603326</v>
       </c>
       <c r="L62" s="25">
-        <v>0.93548387096774188</v>
+        <v>0.35483870967741937</v>
       </c>
       <c r="M62" s="25">
-        <v>1</v>
+        <v>0.23170731707317074</v>
       </c>
       <c r="N62" s="25">
-        <v>1</v>
+        <v>0.43373493975903615</v>
       </c>
       <c r="O62" s="25">
-        <v>1</v>
+        <v>0.29829545454545453</v>
       </c>
       <c r="P62" s="25">
-        <v>1</v>
+        <v>0.375</v>
       </c>
       <c r="Q62" s="25">
-        <v>0.44230769230769229</v>
+        <v>8.3333333333333329E-2</v>
       </c>
       <c r="R62" s="25">
-        <v>1</v>
+        <v>0.37864077669902912</v>
       </c>
       <c r="S62" s="25">
-        <v>1</v>
+        <v>0.34126984126984128</v>
       </c>
       <c r="T62" s="25">
-        <v>0.72</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="U62" s="25">
-        <v>0.50588235294117645</v>
+        <v>9.4117647058823528E-2</v>
       </c>
       <c r="V62" s="25">
-        <v>0.8828125</v>
+        <v>0.34375</v>
       </c>
       <c r="W62" s="25">
-        <v>0.94478527607361962</v>
+        <v>0.20245398773006135</v>
       </c>
       <c r="X62" s="25">
-        <v>0.70909090909090911</v>
+        <v>0.24242424242424243</v>
       </c>
       <c r="Y62" s="25">
-        <v>0.85833333333333328</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="Z62" s="25"/>
       <c r="AA62" s="25"/>
       <c r="AB62" s="25">
-        <v>0.95437262357414454</v>
+        <v>0.35741444866920152</v>
       </c>
       <c r="AC62" s="25">
-        <v>0.95437262357414454</v>
+        <v>0.34862385321100919</v>
       </c>
       <c r="AD62" s="25">
-        <v>1</v>
+        <v>0.23170731707317074</v>
       </c>
       <c r="AE62" s="25">
-        <v>1</v>
+        <v>0.43373493975903615</v>
       </c>
       <c r="AF62" s="25">
-        <v>1</v>
+        <v>0.29829545454545453</v>
       </c>
       <c r="AG62" s="25">
-        <v>1</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="63" spans="1:33" x14ac:dyDescent="0.25">
@@ -33434,88 +33226,88 @@
         <v>9</v>
       </c>
       <c r="D63" s="25">
-        <v>0.87090558766859349</v>
+        <v>0.35177539223782001</v>
       </c>
       <c r="E63" s="25">
-        <v>0.81019978969505779</v>
+        <v>0.30231335436382756</v>
       </c>
       <c r="F63" s="25">
-        <v>0.93760831889081453</v>
+        <v>0.40612362796071633</v>
       </c>
       <c r="G63" s="25">
-        <v>0.48614609571788414</v>
+        <v>0.20151133501259447</v>
       </c>
       <c r="H63" s="25"/>
       <c r="I63" s="25">
-        <v>0.95668549905838041</v>
+        <v>0.34651600753295669</v>
       </c>
       <c r="J63" s="25">
-        <v>0.80281690140845074</v>
+        <v>0.36338028169014086</v>
       </c>
       <c r="K63" s="25">
-        <v>0.8966074313408724</v>
+        <v>0.2940226171243942</v>
       </c>
       <c r="L63" s="25">
-        <v>0.78137651821862353</v>
+        <v>0.49797570850202427</v>
       </c>
       <c r="M63" s="25">
-        <v>1</v>
+        <v>0.28363636363636363</v>
       </c>
       <c r="N63" s="25">
-        <v>1</v>
+        <v>0.40492170022371365</v>
       </c>
       <c r="O63" s="25">
-        <v>1</v>
+        <v>0.40497737556561086</v>
       </c>
       <c r="P63" s="25">
-        <v>1</v>
+        <v>0.26027397260273971</v>
       </c>
       <c r="Q63" s="25">
-        <v>0.43684210526315792</v>
+        <v>0.19473684210526315</v>
       </c>
       <c r="R63" s="25">
-        <v>0.97549019607843135</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="S63" s="25">
-        <v>1</v>
+        <v>0.21794871794871795</v>
       </c>
       <c r="T63" s="25">
-        <v>0.69953051643192488</v>
+        <v>0.28638497652582162</v>
       </c>
       <c r="U63" s="25">
-        <v>0.53140096618357491</v>
+        <v>0.20772946859903382</v>
       </c>
       <c r="V63" s="25">
-        <v>1</v>
+        <v>0.40251572327044027</v>
       </c>
       <c r="W63" s="25">
-        <v>0.94495412844036697</v>
+        <v>0.26911314984709478</v>
       </c>
       <c r="X63" s="25">
-        <v>0.6428571428571429</v>
+        <v>0.33163265306122447</v>
       </c>
       <c r="Y63" s="25">
-        <v>1</v>
+        <v>0.40697674418604651</v>
       </c>
       <c r="Z63" s="25"/>
       <c r="AA63" s="25"/>
       <c r="AB63" s="25">
-        <v>0.96577946768060841</v>
+        <v>0.57794676806083645</v>
       </c>
       <c r="AC63" s="25">
-        <v>0.96577946768060841</v>
+        <v>0.40692640692640691</v>
       </c>
       <c r="AD63" s="25">
-        <v>1</v>
+        <v>0.28363636363636363</v>
       </c>
       <c r="AE63" s="25">
-        <v>1</v>
+        <v>0.40492170022371365</v>
       </c>
       <c r="AF63" s="25">
-        <v>1</v>
+        <v>0.40497737556561086</v>
       </c>
       <c r="AG63" s="25">
-        <v>1</v>
+        <v>0.26027397260273971</v>
       </c>
     </row>
     <row r="64" spans="1:33" x14ac:dyDescent="0.25">
@@ -33529,88 +33321,88 @@
         <v>10</v>
       </c>
       <c r="D64" s="25">
-        <v>0.93643358982937441</v>
+        <v>0.25259284041485447</v>
       </c>
       <c r="E64" s="25">
-        <v>0.94061433447098974</v>
+        <v>0.21160409556313994</v>
       </c>
       <c r="F64" s="25">
-        <v>0.9324146981627297</v>
+        <v>0.29199475065616798</v>
       </c>
       <c r="G64" s="25">
-        <v>0.82704402515723274</v>
+        <v>6.6037735849056603E-2</v>
       </c>
       <c r="H64" s="25"/>
       <c r="I64" s="25">
-        <v>0.96675900277008309</v>
+        <v>0.23545706371191136</v>
       </c>
       <c r="J64" s="25">
-        <v>1</v>
+        <v>0.27681660899653981</v>
       </c>
       <c r="K64" s="25">
-        <v>0.95975855130784704</v>
+        <v>0.24949698189134809</v>
       </c>
       <c r="L64" s="25">
-        <v>0.78315789473684205</v>
+        <v>0.23157894736842105</v>
       </c>
       <c r="M64" s="25">
-        <v>1</v>
+        <v>0.16033755274261605</v>
       </c>
       <c r="N64" s="25">
-        <v>1</v>
+        <v>0.43717277486910994</v>
       </c>
       <c r="O64" s="25">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="P64" s="25">
-        <v>1</v>
+        <v>0.38356164383561642</v>
       </c>
       <c r="Q64" s="25">
-        <v>0.62328767123287676</v>
+        <v>7.5342465753424653E-2</v>
       </c>
       <c r="R64" s="25">
-        <v>1</v>
+        <v>0.27464788732394368</v>
       </c>
       <c r="S64" s="25">
-        <v>0.89690721649484539</v>
+        <v>0.26288659793814434</v>
       </c>
       <c r="T64" s="25">
-        <v>1</v>
+        <v>0.20108695652173914</v>
       </c>
       <c r="U64" s="25">
-        <v>1</v>
+        <v>5.8139534883720929E-2</v>
       </c>
       <c r="V64" s="25">
-        <v>1</v>
+        <v>0.23622047244094488</v>
       </c>
       <c r="W64" s="25">
-        <v>0.9452054794520548</v>
+        <v>0.21004566210045661</v>
       </c>
       <c r="X64" s="25">
-        <v>1</v>
+        <v>0.30864197530864196</v>
       </c>
       <c r="Y64" s="25">
-        <v>1</v>
+        <v>0.30252100840336132</v>
       </c>
       <c r="Z64" s="25"/>
       <c r="AA64" s="25"/>
       <c r="AB64" s="25">
-        <v>0.69918699186991873</v>
+        <v>0.2073170731707317</v>
       </c>
       <c r="AC64" s="25">
-        <v>0.69918699186991873</v>
+        <v>0.2576419213973799</v>
       </c>
       <c r="AD64" s="25">
-        <v>1</v>
+        <v>0.16033755274261605</v>
       </c>
       <c r="AE64" s="25">
-        <v>1</v>
+        <v>0.43717277486910994</v>
       </c>
       <c r="AF64" s="25">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="AG64" s="25">
-        <v>1</v>
+        <v>0.38356164383561642</v>
       </c>
     </row>
     <row r="65" spans="1:33" x14ac:dyDescent="0.25">
@@ -33624,88 +33416,88 @@
         <v>11</v>
       </c>
       <c r="D65" s="25">
-        <v>0.92770167427701677</v>
+        <v>0.2332572298325723</v>
       </c>
       <c r="E65" s="25">
-        <v>0.90863668807994291</v>
+        <v>0.21627408993576017</v>
       </c>
       <c r="F65" s="25">
-        <v>0.94947025264873675</v>
+        <v>0.25264873675631622</v>
       </c>
       <c r="G65" s="25">
-        <v>0.83809523809523812</v>
+        <v>0.14285714285714285</v>
       </c>
       <c r="H65" s="25"/>
       <c r="I65" s="25">
-        <v>0.96107784431137722</v>
+        <v>0.26347305389221559</v>
       </c>
       <c r="J65" s="25">
-        <v>0.79203539823008851</v>
+        <v>0.20796460176991149</v>
       </c>
       <c r="K65" s="25">
-        <v>1</v>
+        <v>0.25653206650831356</v>
       </c>
       <c r="L65" s="25">
-        <v>0.80064308681672025</v>
+        <v>0.18006430868167203</v>
       </c>
       <c r="M65" s="25">
-        <v>1</v>
+        <v>0.15957446808510639</v>
       </c>
       <c r="N65" s="25">
-        <v>1</v>
+        <v>0.36807817589576547</v>
       </c>
       <c r="O65" s="25">
-        <v>1</v>
+        <v>0.2344632768361582</v>
       </c>
       <c r="P65" s="25">
-        <v>1</v>
+        <v>0.41791044776119401</v>
       </c>
       <c r="Q65" s="25">
-        <v>0.66502463054187189</v>
+        <v>0.14778325123152711</v>
       </c>
       <c r="R65" s="25">
-        <v>1</v>
+        <v>0.23943661971830985</v>
       </c>
       <c r="S65" s="25">
-        <v>1</v>
+        <v>0.23125000000000001</v>
       </c>
       <c r="T65" s="25">
-        <v>1</v>
+        <v>0.29285714285714287</v>
       </c>
       <c r="U65" s="25">
-        <v>1</v>
+        <v>0.13824884792626729</v>
       </c>
       <c r="V65" s="25">
-        <v>1</v>
+        <v>0.22857142857142856</v>
       </c>
       <c r="W65" s="25">
-        <v>0.93229166666666663</v>
+        <v>0.28125</v>
       </c>
       <c r="X65" s="25">
-        <v>0.61157024793388426</v>
+        <v>0.19008264462809918</v>
       </c>
       <c r="Y65" s="25">
-        <v>1</v>
+        <v>0.24793388429752067</v>
       </c>
       <c r="Z65" s="25"/>
       <c r="AA65" s="25"/>
       <c r="AB65" s="25">
-        <v>0.80519480519480524</v>
+        <v>0.18614718614718614</v>
       </c>
       <c r="AC65" s="25">
-        <v>0.80519480519480524</v>
+        <v>0.16250000000000001</v>
       </c>
       <c r="AD65" s="25">
-        <v>1</v>
+        <v>0.15957446808510639</v>
       </c>
       <c r="AE65" s="25">
-        <v>1</v>
+        <v>0.36807817589576547</v>
       </c>
       <c r="AF65" s="25">
-        <v>1</v>
+        <v>0.2344632768361582</v>
       </c>
       <c r="AG65" s="25">
-        <v>1</v>
+        <v>0.41791044776119401</v>
       </c>
     </row>
     <row r="66" spans="1:33" x14ac:dyDescent="0.25">
@@ -33719,88 +33511,88 @@
         <v>12</v>
       </c>
       <c r="D66" s="25">
-        <v>0.90578455143747838</v>
+        <v>0.2396951853134742</v>
       </c>
       <c r="E66" s="25">
-        <v>0.82450592885375495</v>
+        <v>0.19446640316205532</v>
       </c>
       <c r="F66" s="25">
-        <v>0.96917385943279899</v>
+        <v>0.27496917385943281</v>
       </c>
       <c r="G66" s="25">
-        <v>0.69152542372881354</v>
+        <v>0.15593220338983052</v>
       </c>
       <c r="H66" s="25"/>
       <c r="I66" s="25">
-        <v>0.87573964497041423</v>
+        <v>0.21301775147928995</v>
       </c>
       <c r="J66" s="25">
-        <v>0.73015873015873012</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="K66" s="25">
-        <v>0.91422121896162534</v>
+        <v>0.1670428893905192</v>
       </c>
       <c r="L66" s="25">
-        <v>0.88290398126463698</v>
+        <v>0.17798594847775176</v>
       </c>
       <c r="M66" s="25">
-        <v>1</v>
+        <v>0.16935483870967741</v>
       </c>
       <c r="N66" s="25">
-        <v>1</v>
+        <v>0.40561224489795916</v>
       </c>
       <c r="O66" s="25">
-        <v>1</v>
+        <v>0.29158110882956878</v>
       </c>
       <c r="P66" s="25">
-        <v>1</v>
+        <v>0.39705882352941174</v>
       </c>
       <c r="Q66" s="25">
-        <v>0.86956521739130432</v>
+        <v>0.19806763285024154</v>
       </c>
       <c r="R66" s="25">
-        <v>1</v>
+        <v>0.30909090909090908</v>
       </c>
       <c r="S66" s="25">
-        <v>0.93714285714285717</v>
+        <v>0.18285714285714286</v>
       </c>
       <c r="T66" s="25">
-        <v>1</v>
+        <v>0.16875000000000001</v>
       </c>
       <c r="U66" s="25">
-        <v>0.27272727272727271</v>
+        <v>5.6818181818181816E-2</v>
       </c>
       <c r="V66" s="25">
-        <v>0.94545454545454544</v>
+        <v>0.47272727272727272</v>
       </c>
       <c r="W66" s="25">
-        <v>0.81578947368421051</v>
+        <v>0.16666666666666666</v>
       </c>
       <c r="X66" s="25">
-        <v>0.64179104477611937</v>
+        <v>0.20895522388059701</v>
       </c>
       <c r="Y66" s="25">
-        <v>0.75</v>
+        <v>0.1388888888888889</v>
       </c>
       <c r="Z66" s="25"/>
       <c r="AA66" s="25"/>
       <c r="AB66" s="25">
-        <v>0.82014388489208634</v>
+        <v>0.1223021582733813</v>
       </c>
       <c r="AC66" s="25">
-        <v>0.82014388489208634</v>
+        <v>0.28187919463087246</v>
       </c>
       <c r="AD66" s="25">
-        <v>1</v>
+        <v>0.16935483870967741</v>
       </c>
       <c r="AE66" s="25">
-        <v>1</v>
+        <v>0.40561224489795916</v>
       </c>
       <c r="AF66" s="25">
-        <v>1</v>
+        <v>0.29158110882956878</v>
       </c>
       <c r="AG66" s="25">
-        <v>1</v>
+        <v>0.39705882352941174</v>
       </c>
     </row>
     <row r="67" spans="1:33" x14ac:dyDescent="0.25">
@@ -33814,88 +33606,88 @@
         <v>13</v>
       </c>
       <c r="D67" s="25">
-        <v>0.92393579902302858</v>
+        <v>0.30600139567341245</v>
       </c>
       <c r="E67" s="25">
-        <v>0.87702037947997191</v>
+        <v>0.28460997891777934</v>
       </c>
       <c r="F67" s="25">
-        <v>0.97020097020097018</v>
+        <v>0.32709632709632708</v>
       </c>
       <c r="G67" s="25">
-        <v>0.93442622950819676</v>
+        <v>0.32786885245901637</v>
       </c>
       <c r="H67" s="25"/>
       <c r="I67" s="25">
-        <v>0.89572192513368987</v>
+        <v>0.22727272727272727</v>
       </c>
       <c r="J67" s="25">
-        <v>0.797583081570997</v>
+        <v>0.25075528700906347</v>
       </c>
       <c r="K67" s="25">
-        <v>0.8934579439252337</v>
+        <v>0.33084112149532713</v>
       </c>
       <c r="L67" s="25">
-        <v>0.89613526570048307</v>
+        <v>0.3188405797101449</v>
       </c>
       <c r="M67" s="25">
-        <v>1</v>
+        <v>0.24463519313304721</v>
       </c>
       <c r="N67" s="25">
-        <v>1</v>
+        <v>0.37467700258397935</v>
       </c>
       <c r="O67" s="25">
-        <v>1</v>
+        <v>0.3493975903614458</v>
       </c>
       <c r="P67" s="25">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
       <c r="Q67" s="25">
-        <v>1</v>
+        <v>0.31506849315068491</v>
       </c>
       <c r="R67" s="25">
-        <v>1</v>
+        <v>0.296875</v>
       </c>
       <c r="S67" s="25">
-        <v>1</v>
+        <v>0.41025641025641024</v>
       </c>
       <c r="T67" s="25">
-        <v>0.80113636363636365</v>
+        <v>0.28409090909090912</v>
       </c>
       <c r="U67" s="25">
-        <v>0.67567567567567566</v>
+        <v>0.3783783783783784</v>
       </c>
       <c r="V67" s="25">
-        <v>1</v>
+        <v>0.25850340136054423</v>
       </c>
       <c r="W67" s="25">
-        <v>0.84146341463414631</v>
+        <v>0.1910569105691057</v>
       </c>
       <c r="X67" s="25">
-        <v>0.63586956521739135</v>
+        <v>0.24456521739130435</v>
       </c>
       <c r="Y67" s="25">
-        <v>0.86585365853658536</v>
+        <v>0.28658536585365851</v>
       </c>
       <c r="Z67" s="25"/>
       <c r="AA67" s="25"/>
       <c r="AB67" s="25">
-        <v>0.94396551724137934</v>
+        <v>0.27586206896551724</v>
       </c>
       <c r="AC67" s="25">
-        <v>0.94396551724137934</v>
+        <v>0.37362637362637363</v>
       </c>
       <c r="AD67" s="25">
-        <v>1</v>
+        <v>0.24463519313304721</v>
       </c>
       <c r="AE67" s="25">
-        <v>1</v>
+        <v>0.37467700258397935</v>
       </c>
       <c r="AF67" s="25">
-        <v>1</v>
+        <v>0.3493975903614458</v>
       </c>
       <c r="AG67" s="25">
-        <v>1</v>
+        <v>0.2857142857142857</v>
       </c>
     </row>
     <row r="68" spans="1:33" x14ac:dyDescent="0.25">
@@ -33909,88 +33701,88 @@
         <v>14</v>
       </c>
       <c r="D68" s="25">
-        <v>0.97525977238990602</v>
+        <v>0.33250865907966354</v>
       </c>
       <c r="E68" s="25">
-        <v>0.96332863187588147</v>
+        <v>0.36671368124118475</v>
       </c>
       <c r="F68" s="25">
-        <v>0.98170731707317072</v>
+        <v>0.31402439024390244</v>
       </c>
       <c r="G68" s="25">
-        <v>1</v>
+        <v>0.34507042253521125</v>
       </c>
       <c r="H68" s="25"/>
       <c r="I68" s="25">
-        <v>0.98224852071005919</v>
+        <v>0.32544378698224852</v>
       </c>
       <c r="J68" s="25">
-        <v>0.94666666666666666</v>
+        <v>0.57333333333333336</v>
       </c>
       <c r="K68" s="25">
-        <v>0.94117647058823528</v>
+        <v>0.34984520123839008</v>
       </c>
       <c r="L68" s="25">
-        <v>0.92920353982300885</v>
+        <v>0.36873156342182889</v>
       </c>
       <c r="M68" s="25">
-        <v>1</v>
+        <v>0.22033898305084745</v>
       </c>
       <c r="N68" s="25">
-        <v>1</v>
+        <v>0.35882352941176471</v>
       </c>
       <c r="O68" s="25">
-        <v>1</v>
+        <v>0.30654761904761907</v>
       </c>
       <c r="P68" s="25">
-        <v>1</v>
+        <v>0.16393442622950818</v>
       </c>
       <c r="Q68" s="25">
-        <v>1</v>
+        <v>0.41772151898734178</v>
       </c>
       <c r="R68" s="25">
-        <v>1</v>
+        <v>0.36231884057971014</v>
       </c>
       <c r="S68" s="25">
-        <v>1</v>
+        <v>0.44736842105263158</v>
       </c>
       <c r="T68" s="25">
-        <v>0.92727272727272725</v>
+        <v>0.3</v>
       </c>
       <c r="U68" s="25">
-        <v>1</v>
+        <v>0.25396825396825395</v>
       </c>
       <c r="V68" s="25">
-        <v>1</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="W68" s="25">
-        <v>0.97</v>
+        <v>0.3</v>
       </c>
       <c r="X68" s="25">
-        <v>0.9</v>
+        <v>0.57499999999999996</v>
       </c>
       <c r="Y68" s="25">
-        <v>0.88888888888888884</v>
+        <v>0.29292929292929293</v>
       </c>
       <c r="Z68" s="25"/>
       <c r="AA68" s="25"/>
       <c r="AB68" s="25">
-        <v>1</v>
+        <v>0.33510638297872342</v>
       </c>
       <c r="AC68" s="25">
-        <v>1</v>
+        <v>0.41059602649006621</v>
       </c>
       <c r="AD68" s="25">
-        <v>1</v>
+        <v>0.22033898305084745</v>
       </c>
       <c r="AE68" s="25">
-        <v>1</v>
+        <v>0.35882352941176471</v>
       </c>
       <c r="AF68" s="25">
-        <v>1</v>
+        <v>0.30654761904761907</v>
       </c>
       <c r="AG68" s="25">
-        <v>1</v>
+        <v>0.16393442622950818</v>
       </c>
     </row>
     <row r="69" spans="1:33" x14ac:dyDescent="0.25">
@@ -34004,88 +33796,88 @@
         <v>15</v>
       </c>
       <c r="D69" s="25">
-        <v>0.89869753979739508</v>
+        <v>0.59044862518089725</v>
       </c>
       <c r="E69" s="25">
-        <v>0.84487179487179487</v>
+        <v>0.50384615384615383</v>
       </c>
       <c r="F69" s="25">
-        <v>0.96843853820598003</v>
+        <v>0.70265780730897009</v>
       </c>
       <c r="G69" s="25">
-        <v>0.87362637362637363</v>
+        <v>0.37362637362637363</v>
       </c>
       <c r="H69" s="25"/>
       <c r="I69" s="25">
-        <v>0.86413043478260865</v>
+        <v>0.5</v>
       </c>
       <c r="J69" s="25">
-        <v>0.86206896551724133</v>
+        <v>0.61379310344827587</v>
       </c>
       <c r="K69" s="25">
-        <v>0.80297397769516732</v>
+        <v>0.53531598513011147</v>
       </c>
       <c r="L69" s="25">
-        <v>0.89617486338797814</v>
+        <v>0.69945355191256831</v>
       </c>
       <c r="M69" s="25">
-        <v>1</v>
+        <v>0.69369369369369371</v>
       </c>
       <c r="N69" s="25">
-        <v>1</v>
+        <v>0.77049180327868849</v>
       </c>
       <c r="O69" s="25">
-        <v>1</v>
+        <v>0.71739130434782605</v>
       </c>
       <c r="P69" s="25">
-        <v>1</v>
+        <v>0.52083333333333337</v>
       </c>
       <c r="Q69" s="25">
-        <v>0.71604938271604934</v>
+        <v>0.46913580246913578</v>
       </c>
       <c r="R69" s="25">
-        <v>1</v>
+        <v>0.5670103092783505</v>
       </c>
       <c r="S69" s="25">
-        <v>0.82278481012658233</v>
+        <v>0.620253164556962</v>
       </c>
       <c r="T69" s="25">
-        <v>0.7592592592592593</v>
+        <v>0.37037037037037035</v>
       </c>
       <c r="U69" s="25">
-        <v>1</v>
+        <v>0.29702970297029702</v>
       </c>
       <c r="V69" s="25">
-        <v>1</v>
+        <v>0.69491525423728817</v>
       </c>
       <c r="W69" s="25">
-        <v>0.71264367816091956</v>
+        <v>0.42528735632183906</v>
       </c>
       <c r="X69" s="25">
-        <v>0.76744186046511631</v>
+        <v>0.55813953488372092</v>
       </c>
       <c r="Y69" s="25">
-        <v>0.78947368421052633</v>
+        <v>0.45614035087719296</v>
       </c>
       <c r="Z69" s="25"/>
       <c r="AA69" s="25"/>
       <c r="AB69" s="25">
-        <v>1</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="AC69" s="25">
-        <v>1</v>
+        <v>0.60227272727272729</v>
       </c>
       <c r="AD69" s="25">
-        <v>1</v>
+        <v>0.69369369369369371</v>
       </c>
       <c r="AE69" s="25">
-        <v>1</v>
+        <v>0.77049180327868849</v>
       </c>
       <c r="AF69" s="25">
-        <v>1</v>
+        <v>0.71739130434782605</v>
       </c>
       <c r="AG69" s="25">
-        <v>1</v>
+        <v>0.52083333333333337</v>
       </c>
     </row>
     <row r="70" spans="1:33" x14ac:dyDescent="0.25">
@@ -34099,88 +33891,88 @@
         <v>16</v>
       </c>
       <c r="D70" s="25">
-        <v>0.93723849372384938</v>
+        <v>0.6378340365682138</v>
       </c>
       <c r="E70" s="25">
-        <v>0.91706730769230771</v>
+        <v>0.54024390243902443</v>
       </c>
       <c r="F70" s="25">
-        <v>0.96511627906976749</v>
+        <v>0.77076411960132896</v>
       </c>
       <c r="G70" s="25">
-        <v>0.90638297872340423</v>
+        <v>0.4</v>
       </c>
       <c r="H70" s="25"/>
       <c r="I70" s="25">
-        <v>0.94811320754716977</v>
+        <v>0.59903381642512077</v>
       </c>
       <c r="J70" s="25">
-        <v>0.8984375</v>
+        <v>0.5</v>
       </c>
       <c r="K70" s="25">
-        <v>0.91050583657587547</v>
+        <v>0.64400000000000002</v>
       </c>
       <c r="L70" s="25">
-        <v>0.88586956521739135</v>
+        <v>0.69565217391304346</v>
       </c>
       <c r="M70" s="25">
-        <v>1</v>
+        <v>0.76237623762376239</v>
       </c>
       <c r="N70" s="25">
-        <v>1</v>
+        <v>0.93700787401574803</v>
       </c>
       <c r="O70" s="25">
-        <v>1</v>
+        <v>0.74375000000000002</v>
       </c>
       <c r="P70" s="25">
-        <v>1</v>
+        <v>0.7</v>
       </c>
       <c r="Q70" s="25">
-        <v>0.80701754385964908</v>
+        <v>0.42982456140350878</v>
       </c>
       <c r="R70" s="25">
-        <v>0.95454545454545459</v>
+        <v>0.76190476190476186</v>
       </c>
       <c r="S70" s="25">
-        <v>0.87142857142857144</v>
+        <v>0.6992481203007519</v>
       </c>
       <c r="T70" s="25">
-        <v>0.93442622950819676</v>
+        <v>0.54098360655737709</v>
       </c>
       <c r="U70" s="25">
-        <v>1</v>
+        <v>0.37190082644628097</v>
       </c>
       <c r="V70" s="25">
-        <v>0.84482758620689657</v>
+        <v>0.51724137931034486</v>
       </c>
       <c r="W70" s="25">
-        <v>0.94117647058823528</v>
+        <v>0.43137254901960786</v>
       </c>
       <c r="X70" s="25">
-        <v>0.94285714285714284</v>
+        <v>0.48571428571428571</v>
       </c>
       <c r="Y70" s="25">
-        <v>0.9821428571428571</v>
+        <v>0.625</v>
       </c>
       <c r="Z70" s="25"/>
       <c r="AA70" s="25"/>
       <c r="AB70" s="25">
-        <v>0.96385542168674698</v>
+        <v>0.72289156626506024</v>
       </c>
       <c r="AC70" s="25">
-        <v>0.96385542168674698</v>
+        <v>0.67326732673267331</v>
       </c>
       <c r="AD70" s="25">
-        <v>1</v>
+        <v>0.76237623762376239</v>
       </c>
       <c r="AE70" s="25">
-        <v>1</v>
+        <v>0.93700787401574803</v>
       </c>
       <c r="AF70" s="25">
-        <v>1</v>
+        <v>0.74375000000000002</v>
       </c>
       <c r="AG70" s="25">
-        <v>1</v>
+        <v>0.7</v>
       </c>
     </row>
     <row r="71" spans="1:33" x14ac:dyDescent="0.25">
@@ -34194,88 +33986,88 @@
         <v>17</v>
       </c>
       <c r="D71" s="25">
-        <v>0.84453360080240725</v>
+        <v>0.57973921765295888</v>
       </c>
       <c r="E71" s="25">
-        <v>0.83024691358024694</v>
+        <v>0.53703703703703709</v>
       </c>
       <c r="F71" s="25">
-        <v>0.87106017191977081</v>
+        <v>0.65902578796561606</v>
       </c>
       <c r="G71" s="25">
-        <v>0.90116279069767447</v>
+        <v>0.52906976744186052</v>
       </c>
       <c r="H71" s="25"/>
       <c r="I71" s="25">
-        <v>0.88513513513513509</v>
+        <v>0.63513513513513509</v>
       </c>
       <c r="J71" s="25">
-        <v>0.66206896551724137</v>
+        <v>0.46206896551724136</v>
       </c>
       <c r="K71" s="25">
-        <v>0.85245901639344257</v>
+        <v>0.52459016393442626</v>
       </c>
       <c r="L71" s="25">
-        <v>0.54081632653061229</v>
+        <v>0.5</v>
       </c>
       <c r="M71" s="25">
-        <v>1</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="N71" s="25">
-        <v>1</v>
+        <v>0.83132530120481929</v>
       </c>
       <c r="O71" s="25">
-        <v>1</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="P71" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q71" s="25">
-        <v>1</v>
+        <v>0.53333333333333333</v>
       </c>
       <c r="R71" s="25">
-        <v>1</v>
+        <v>0.703125</v>
       </c>
       <c r="S71" s="25">
-        <v>0.77173913043478259</v>
+        <v>0.43478260869565216</v>
       </c>
       <c r="T71" s="25">
-        <v>0.98148148148148151</v>
+        <v>0.64814814814814814</v>
       </c>
       <c r="U71" s="25">
-        <v>0.82474226804123707</v>
+        <v>0.52577319587628868</v>
       </c>
       <c r="V71" s="25">
-        <v>0.93333333333333335</v>
+        <v>0.65</v>
       </c>
       <c r="W71" s="25">
-        <v>0.79761904761904767</v>
+        <v>0.58333333333333337</v>
       </c>
       <c r="X71" s="25">
-        <v>0.47058823529411764</v>
+        <v>0.32941176470588235</v>
       </c>
       <c r="Y71" s="25">
-        <v>0.86486486486486491</v>
+        <v>0.56756756756756754</v>
       </c>
       <c r="Z71" s="25"/>
       <c r="AA71" s="25"/>
       <c r="AB71" s="25">
-        <v>0.46666666666666667</v>
+        <v>0.42222222222222222</v>
       </c>
       <c r="AC71" s="25">
-        <v>0.46666666666666667</v>
+        <v>0.56603773584905659</v>
       </c>
       <c r="AD71" s="25">
-        <v>1</v>
+        <v>0.55555555555555558</v>
       </c>
       <c r="AE71" s="25">
-        <v>1</v>
+        <v>0.83132530120481929</v>
       </c>
       <c r="AF71" s="25">
-        <v>1</v>
+        <v>0.7592592592592593</v>
       </c>
       <c r="AG71" s="25">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:33" x14ac:dyDescent="0.25">
@@ -34288,36 +34080,90 @@
       <c r="C72" s="21">
         <v>18</v>
       </c>
-      <c r="D72" s="25"/>
-      <c r="E72" s="25"/>
-      <c r="F72" s="25"/>
-      <c r="G72" s="25"/>
+      <c r="D72" s="25">
+        <v>0.38280450358239509</v>
+      </c>
+      <c r="E72" s="25">
+        <v>0.35859820700896494</v>
+      </c>
+      <c r="F72" s="25">
+        <v>0.4236588720770289</v>
+      </c>
+      <c r="G72" s="25">
+        <v>0.26453488372093026</v>
+      </c>
       <c r="H72" s="25"/>
-      <c r="I72" s="25"/>
-      <c r="J72" s="25"/>
-      <c r="K72" s="25"/>
-      <c r="L72" s="25"/>
-      <c r="M72" s="25"/>
-      <c r="N72" s="25"/>
-      <c r="O72" s="25"/>
-      <c r="P72" s="25"/>
-      <c r="Q72" s="25"/>
-      <c r="R72" s="25"/>
-      <c r="S72" s="25"/>
-      <c r="T72" s="25"/>
-      <c r="U72" s="25"/>
-      <c r="V72" s="25"/>
-      <c r="W72" s="25"/>
-      <c r="X72" s="25"/>
-      <c r="Y72" s="25"/>
+      <c r="I72" s="25">
+        <v>0.375</v>
+      </c>
+      <c r="J72" s="25">
+        <v>0.46183206106870228</v>
+      </c>
+      <c r="K72" s="25">
+        <v>0.36036036036036034</v>
+      </c>
+      <c r="L72" s="25">
+        <v>0.69402985074626866</v>
+      </c>
+      <c r="M72" s="25">
+        <v>0.47663551401869159</v>
+      </c>
+      <c r="N72" s="25">
+        <v>0.48484848484848486</v>
+      </c>
+      <c r="O72" s="25">
+        <v>0.28482972136222912</v>
+      </c>
+      <c r="P72" s="25">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="Q72" s="25">
+        <v>0.26737967914438504</v>
+      </c>
+      <c r="R72" s="25">
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="S72" s="25">
+        <v>0.39726027397260272</v>
+      </c>
+      <c r="T72" s="25">
+        <v>0.37037037037037035</v>
+      </c>
+      <c r="U72" s="25">
+        <v>0.26114649681528662</v>
+      </c>
+      <c r="V72" s="25">
+        <v>0.45967741935483869</v>
+      </c>
+      <c r="W72" s="25">
+        <v>0.36416184971098264</v>
+      </c>
+      <c r="X72" s="25">
+        <v>0.46376811594202899</v>
+      </c>
+      <c r="Y72" s="25">
+        <v>0.27848101265822783</v>
+      </c>
       <c r="Z72" s="25"/>
       <c r="AA72" s="25"/>
-      <c r="AB72" s="25"/>
-      <c r="AC72" s="25"/>
-      <c r="AD72" s="25"/>
-      <c r="AE72" s="25"/>
-      <c r="AF72" s="25"/>
-      <c r="AG72" s="25"/>
+      <c r="AB72" s="25">
+        <v>0.64935064935064934</v>
+      </c>
+      <c r="AC72" s="25">
+        <v>0.75438596491228072</v>
+      </c>
+      <c r="AD72" s="25">
+        <v>0.47663551401869159</v>
+      </c>
+      <c r="AE72" s="25">
+        <v>0.48484848484848486</v>
+      </c>
+      <c r="AF72" s="25">
+        <v>0.28482972136222912</v>
+      </c>
+      <c r="AG72" s="25">
+        <v>0.25806451612903225</v>
+      </c>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="26">
@@ -51093,88 +50939,88 @@
         <v>8</v>
       </c>
       <c r="C18" s="18">
-        <v>0.89542483660130723</v>
+        <v>0.80456026058631924</v>
       </c>
       <c r="D18" s="18">
-        <v>0.81609195402298851</v>
+        <v>0.74220963172804533</v>
       </c>
       <c r="E18" s="18">
-        <v>1</v>
+        <v>0.88888888888888884</v>
       </c>
       <c r="F18" s="18">
-        <v>0.54545454545454541</v>
+        <v>0.5617977528089888</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18">
-        <v>0.8571428571428571</v>
+        <v>0.77011494252873558</v>
       </c>
       <c r="I18" s="18">
-        <v>0.89473684210526316</v>
+        <v>0.78205128205128205</v>
       </c>
       <c r="J18" s="18">
-        <v>0.96</v>
+        <v>0.84848484848484851</v>
       </c>
       <c r="K18" s="18">
-        <v>1</v>
+        <v>0.8214285714285714</v>
       </c>
       <c r="L18" s="18">
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="M18" s="18">
         <v>1</v>
       </c>
       <c r="N18" s="18">
-        <v>1</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="O18" s="18">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="P18" s="18">
-        <v>0.54166666666666663</v>
+        <v>0.625</v>
       </c>
       <c r="Q18" s="18">
-        <v>0.86956521739130432</v>
+        <v>0.75510204081632648</v>
       </c>
       <c r="R18" s="18">
-        <v>1</v>
+        <v>0.95744680851063835</v>
       </c>
       <c r="S18" s="18">
-        <v>0.8571428571428571</v>
+        <v>0.75</v>
       </c>
       <c r="T18" s="18">
-        <v>0.55000000000000004</v>
+        <v>0.48780487804878048</v>
       </c>
       <c r="U18" s="18">
-        <v>1</v>
+        <v>0.86842105263157898</v>
       </c>
       <c r="V18" s="18">
-        <v>0.84210526315789469</v>
+        <v>0.78947368421052633</v>
       </c>
       <c r="W18" s="18">
-        <v>0.78947368421052633</v>
+        <v>0.7</v>
       </c>
       <c r="X18" s="18">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="Y18" s="18"/>
       <c r="Z18" s="18"/>
       <c r="AA18" s="18">
-        <v>1</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="AB18" s="18">
-        <v>1</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="AC18" s="18">
-        <v>1</v>
+        <v>0.91666666666666663</v>
       </c>
       <c r="AD18" s="18">
         <v>1</v>
       </c>
       <c r="AE18" s="18">
-        <v>1</v>
+        <v>0.86956521739130432</v>
       </c>
       <c r="AF18" s="18">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -53515,76 +53361,76 @@
         <v>8</v>
       </c>
       <c r="C18" s="18">
-        <v>0.9183006535947712</v>
+        <v>0.90228013029315957</v>
       </c>
       <c r="D18" s="18">
-        <v>0.85632183908045978</v>
+        <v>0.84702549575070818</v>
       </c>
       <c r="E18" s="18">
-        <v>1</v>
+        <v>0.97701149425287359</v>
       </c>
       <c r="F18" s="18">
-        <v>0.54545454545454541</v>
+        <v>0.6966292134831461</v>
       </c>
       <c r="G18" s="18"/>
       <c r="H18" s="18">
-        <v>0.95238095238095233</v>
+        <v>0.90804597701149425</v>
       </c>
       <c r="I18" s="18">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="J18" s="18">
+        <v>0.89898989898989901</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="L18" s="18">
+        <v>1</v>
+      </c>
+      <c r="M18" s="18">
+        <v>1</v>
+      </c>
+      <c r="N18" s="18">
+        <v>1</v>
+      </c>
+      <c r="O18" s="18">
+        <v>1</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.72916666666666663</v>
+      </c>
+      <c r="Q18" s="18">
+        <v>0.89795918367346939</v>
+      </c>
+      <c r="R18" s="18">
+        <v>0.95744680851063835</v>
+      </c>
+      <c r="S18" s="18">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="T18" s="18">
+        <v>0.65853658536585369</v>
+      </c>
+      <c r="U18" s="18">
         <v>0.94736842105263153</v>
       </c>
-      <c r="J18" s="18">
-        <v>0.98</v>
-      </c>
-      <c r="K18" s="18">
-        <v>1</v>
-      </c>
-      <c r="L18" s="18">
-        <v>1</v>
-      </c>
-      <c r="M18" s="18">
-        <v>1</v>
-      </c>
-      <c r="N18" s="18">
-        <v>1</v>
-      </c>
-      <c r="O18" s="18">
-        <v>1</v>
-      </c>
-      <c r="P18" s="18">
-        <v>0.54166666666666663</v>
-      </c>
-      <c r="Q18" s="18">
-        <v>1</v>
-      </c>
-      <c r="R18" s="18">
-        <v>1</v>
-      </c>
-      <c r="S18" s="18">
-        <v>0.9285714285714286</v>
-      </c>
-      <c r="T18" s="18">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="U18" s="18">
-        <v>1</v>
-      </c>
       <c r="V18" s="18">
-        <v>0.89473684210526316</v>
+        <v>0.92105263157894735</v>
       </c>
       <c r="W18" s="18">
-        <v>0.89473684210526316</v>
+        <v>0.82499999999999996</v>
       </c>
       <c r="X18" s="18">
-        <v>1</v>
+        <v>0.83333333333333337</v>
       </c>
       <c r="Y18" s="18"/>
       <c r="Z18" s="18"/>
       <c r="AA18" s="18">
-        <v>1</v>
+        <v>0.95238095238095233</v>
       </c>
       <c r="AB18" s="18">
-        <v>1</v>
+        <v>0.90476190476190477</v>
       </c>
       <c r="AC18" s="18">
         <v>1</v>
@@ -55264,36 +55110,90 @@
       <c r="B18" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="12"/>
-      <c r="D18" s="12"/>
-      <c r="E18" s="12"/>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12"/>
-      <c r="H18" s="12"/>
-      <c r="I18" s="12"/>
-      <c r="J18" s="12"/>
-      <c r="K18" s="12"/>
-      <c r="L18" s="12"/>
-      <c r="M18" s="12"/>
-      <c r="N18" s="12"/>
-      <c r="O18" s="12"/>
-      <c r="P18" s="12"/>
-      <c r="Q18" s="12"/>
-      <c r="R18" s="12"/>
-      <c r="S18" s="12"/>
-      <c r="T18" s="12"/>
-      <c r="U18" s="12"/>
-      <c r="V18" s="12"/>
-      <c r="W18" s="12"/>
-      <c r="X18" s="12"/>
-      <c r="Y18" s="12"/>
-      <c r="Z18" s="12"/>
-      <c r="AA18" s="12"/>
-      <c r="AB18" s="12"/>
-      <c r="AC18" s="12"/>
-      <c r="AD18" s="12"/>
-      <c r="AE18" s="12"/>
-      <c r="AF18" s="12"/>
+      <c r="C18" s="18">
+        <v>0.38280450358239509</v>
+      </c>
+      <c r="D18" s="18">
+        <v>0.35859820700896494</v>
+      </c>
+      <c r="E18" s="18">
+        <v>0.4236588720770289</v>
+      </c>
+      <c r="F18" s="18">
+        <v>0.26453488372093026</v>
+      </c>
+      <c r="G18" s="18"/>
+      <c r="H18" s="18">
+        <v>0.375</v>
+      </c>
+      <c r="I18" s="18">
+        <v>0.46183206106870228</v>
+      </c>
+      <c r="J18" s="18">
+        <v>0.36036036036036034</v>
+      </c>
+      <c r="K18" s="18">
+        <v>0.69402985074626866</v>
+      </c>
+      <c r="L18" s="18">
+        <v>0.47663551401869159</v>
+      </c>
+      <c r="M18" s="18">
+        <v>0.48484848484848486</v>
+      </c>
+      <c r="N18" s="18">
+        <v>0.28482972136222912</v>
+      </c>
+      <c r="O18" s="18">
+        <v>0.25806451612903225</v>
+      </c>
+      <c r="P18" s="18">
+        <v>0.26737967914438504</v>
+      </c>
+      <c r="Q18" s="18">
+        <v>0.39130434782608697</v>
+      </c>
+      <c r="R18" s="18">
+        <v>0.39726027397260272</v>
+      </c>
+      <c r="S18" s="18">
+        <v>0.37037037037037035</v>
+      </c>
+      <c r="T18" s="18">
+        <v>0.26114649681528662</v>
+      </c>
+      <c r="U18" s="18">
+        <v>0.45967741935483869</v>
+      </c>
+      <c r="V18" s="18">
+        <v>0.36416184971098264</v>
+      </c>
+      <c r="W18" s="18">
+        <v>0.46376811594202899</v>
+      </c>
+      <c r="X18" s="18">
+        <v>0.27848101265822783</v>
+      </c>
+      <c r="Y18" s="18"/>
+      <c r="Z18" s="18"/>
+      <c r="AA18" s="18">
+        <v>0.64935064935064934</v>
+      </c>
+      <c r="AB18" s="18">
+        <v>0.75438596491228072</v>
+      </c>
+      <c r="AC18" s="18">
+        <v>0.47663551401869159</v>
+      </c>
+      <c r="AD18" s="18">
+        <v>0.48484848484848486</v>
+      </c>
+      <c r="AE18" s="18">
+        <v>0.28482972136222912</v>
+      </c>
+      <c r="AF18" s="18">
+        <v>0.25806451612903225</v>
+      </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A19" s="15">

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -10158,64 +10158,64 @@
         <v>8</v>
       </c>
       <c r="C18" s="15">
-        <v>0.92254435309389871</v>
+        <v>0.91975033437360676</v>
       </c>
       <c r="D18" s="15">
-        <v>0.90453074433656955</v>
+        <v>0.89518900343642616</v>
       </c>
       <c r="E18" s="15">
-        <v>0.94325581395348834</v>
+        <v>0.94624652455977754</v>
       </c>
       <c r="F18" s="15">
-        <v>0.90647482014388492</v>
+        <v>0.9083665338645418</v>
       </c>
       <c r="G18" s="15" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="15">
-        <v>0.92491467576791808</v>
+        <v>0.92164179104477606</v>
       </c>
       <c r="I18" s="15">
-        <v>0.88541666666666663</v>
+        <v>0.87769784172661869</v>
       </c>
       <c r="J18" s="15">
-        <v>0.90185676392572944</v>
+        <v>0.88010899182561309</v>
       </c>
       <c r="K18" s="15">
-        <v>0.94718309859154926</v>
+        <v>0.94982078853046592</v>
       </c>
       <c r="L18" s="15">
-        <v>0.90760869565217395</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="M18" s="15">
-        <v>0.95454545454545459</v>
+        <v>0.95508982035928147</v>
       </c>
       <c r="N18" s="15">
-        <v>0.94339622641509435</v>
+        <v>0.95327102803738317</v>
       </c>
       <c r="O18" s="15">
         <v>0.96923076923076923</v>
       </c>
       <c r="P18" s="15">
-        <v>0.94594594594594594</v>
+        <v>0.94117647058823528</v>
       </c>
       <c r="Q18" s="15">
-        <v>0.97014925373134331</v>
+        <v>0.96638655462184875</v>
       </c>
       <c r="R18" s="15">
-        <v>0.953125</v>
+        <v>0.88524590163934425</v>
       </c>
       <c r="S18" s="15">
-        <v>0.87550200803212852</v>
+        <v>0.87755102040816324</v>
       </c>
       <c r="T18" s="15">
-        <v>0.88023952095808378</v>
+        <v>0.88590604026845643</v>
       </c>
       <c r="U18" s="15">
-        <v>0.8867924528301887</v>
+        <v>0.88590604026845643</v>
       </c>
       <c r="V18" s="15">
-        <v>0.88541666666666663</v>
+        <v>0.87769784172661869</v>
       </c>
       <c r="W18" s="15" t="s">
         <v>47</v>
@@ -10224,16 +10224,16 @@
         <v>47</v>
       </c>
       <c r="Y18" s="15">
-        <v>0.94718309859154926</v>
+        <v>0.94982078853046592</v>
       </c>
       <c r="Z18" s="15">
-        <v>0.90760869565217395</v>
+        <v>0.90909090909090906</v>
       </c>
       <c r="AA18" s="15">
-        <v>0.95454545454545459</v>
+        <v>0.95508982035928147</v>
       </c>
       <c r="AB18" s="15">
-        <v>0.94339622641509435</v>
+        <v>0.95327102803738317</v>
       </c>
       <c r="AC18" s="15">
         <v>0.96923076923076923</v>
@@ -12079,87 +12079,87 @@
         <v>8</v>
       </c>
       <c r="C18" s="28">
-        <v>22494</v>
+        <v>21697</v>
       </c>
       <c r="D18" s="28">
-        <v>13456</v>
+        <v>12713</v>
       </c>
       <c r="E18" s="28">
-        <v>9038</v>
+        <v>8984</v>
       </c>
       <c r="F18" s="28">
-        <v>3290</v>
+        <v>2982</v>
       </c>
       <c r="G18" s="28">
         <v>0</v>
       </c>
       <c r="H18" s="28">
-        <v>2961</v>
+        <v>2757</v>
       </c>
       <c r="I18" s="28">
-        <v>4108</v>
+        <v>3836</v>
       </c>
       <c r="J18" s="28">
-        <v>3097</v>
+        <v>3138</v>
       </c>
       <c r="K18" s="28">
-        <v>2066</v>
+        <v>2124</v>
       </c>
       <c r="L18" s="28">
-        <v>1660</v>
+        <v>1687</v>
       </c>
       <c r="M18" s="28">
-        <v>2364</v>
+        <v>2317</v>
       </c>
       <c r="N18" s="28">
-        <v>2435</v>
+        <v>2354</v>
       </c>
       <c r="O18" s="28">
-        <v>513</v>
+        <v>502</v>
       </c>
       <c r="P18" s="28">
-        <v>1155</v>
+        <v>1085</v>
       </c>
       <c r="Q18" s="28">
-        <v>1035</v>
+        <v>934</v>
       </c>
       <c r="R18" s="28">
-        <v>1125</v>
+        <v>995</v>
       </c>
       <c r="S18" s="28">
-        <v>2168</v>
+        <v>2097</v>
       </c>
       <c r="T18" s="28">
-        <v>2135</v>
+        <v>1897</v>
       </c>
       <c r="U18" s="28">
-        <v>1347</v>
+        <v>1393</v>
       </c>
       <c r="V18" s="28">
-        <v>1926</v>
+        <v>1823</v>
       </c>
       <c r="W18" s="28">
-        <v>1750</v>
+        <v>1745</v>
       </c>
       <c r="X18" s="28">
-        <v>815</v>
+        <v>744</v>
       </c>
       <c r="Y18" s="28"/>
       <c r="Z18" s="28"/>
       <c r="AA18" s="28">
-        <v>2066</v>
+        <v>2124</v>
       </c>
       <c r="AB18" s="28">
-        <v>1660</v>
+        <v>1687</v>
       </c>
       <c r="AC18" s="28">
-        <v>2364</v>
+        <v>2317</v>
       </c>
       <c r="AD18" s="28">
-        <v>2435</v>
+        <v>2354</v>
       </c>
       <c r="AE18" s="28">
-        <v>513</v>
+        <v>502</v>
       </c>
     </row>
     <row r="19" spans="1:31" x14ac:dyDescent="0.25">
@@ -19382,89 +19382,89 @@
       <c r="C73" s="20">
         <v>19</v>
       </c>
-      <c r="D73" s="21">
-        <v>0.7142857142857143</v>
-      </c>
-      <c r="E73" s="21">
-        <v>0.67039106145251393</v>
-      </c>
-      <c r="F73" s="21">
-        <v>0.77519379844961245</v>
-      </c>
-      <c r="G73" s="21">
-        <v>0.57777777777777772</v>
-      </c>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21">
-        <v>0.68888888888888888</v>
-      </c>
-      <c r="J73" s="21">
-        <v>0.67500000000000004</v>
-      </c>
-      <c r="K73" s="21">
-        <v>0.73469387755102045</v>
-      </c>
-      <c r="L73" s="21">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="M73" s="21">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="N73" s="21">
-        <v>1</v>
-      </c>
-      <c r="O73" s="21">
+      <c r="D73" s="24">
+        <v>0.89403973509933776</v>
+      </c>
+      <c r="E73" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="F73" s="24">
+        <v>0.94488188976377951</v>
+      </c>
+      <c r="G73" s="24">
+        <v>0.81818181818181823</v>
+      </c>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="J73" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="K73" s="24">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="L73" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="M73" s="24">
+        <v>1</v>
+      </c>
+      <c r="N73" s="24">
+        <v>1</v>
+      </c>
+      <c r="O73" s="24">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="P73" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="24">
+        <v>0.82608695652173914</v>
+      </c>
+      <c r="R73" s="24">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="S73" s="24">
+        <v>1</v>
+      </c>
+      <c r="T73" s="24">
+        <v>0.7857142857142857</v>
+      </c>
+      <c r="U73" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="V73" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="W73" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="X73" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Y73" s="24">
         <v>0.72727272727272729</v>
       </c>
-      <c r="P73" s="21">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="Q73" s="21">
-        <v>0.70833333333333337</v>
-      </c>
-      <c r="R73" s="21">
-        <v>0.65384615384615385</v>
-      </c>
-      <c r="S73" s="21">
-        <v>0.91304347826086951</v>
-      </c>
-      <c r="T73" s="21">
-        <v>0.6428571428571429</v>
-      </c>
-      <c r="U73" s="21">
-        <v>0.42857142857142855</v>
-      </c>
-      <c r="V73" s="21">
-        <v>0.73684210526315785</v>
-      </c>
-      <c r="W73" s="21">
-        <v>0.73684210526315785</v>
-      </c>
-      <c r="X73" s="21">
-        <v>0.61904761904761907</v>
-      </c>
-      <c r="Y73" s="21">
-        <v>0.5</v>
-      </c>
-      <c r="Z73" s="21"/>
-      <c r="AA73" s="21"/>
-      <c r="AB73" s="21">
-        <v>0.73913043478260865</v>
-      </c>
-      <c r="AC73" s="21">
-        <v>0.52631578947368418</v>
-      </c>
-      <c r="AD73" s="21">
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="AE73" s="21">
-        <v>1</v>
-      </c>
-      <c r="AF73" s="21">
-        <v>0.72727272727272729</v>
-      </c>
-      <c r="AG73" s="21">
-        <v>0.66666666666666663</v>
+      <c r="Z73" s="24"/>
+      <c r="AA73" s="24"/>
+      <c r="AB73" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="AC73" s="24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="AD73" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="24">
+        <v>0.96969696969696972</v>
+      </c>
+      <c r="AG73" s="24">
+        <v>1</v>
       </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
@@ -19477,36 +19477,90 @@
       <c r="C74" s="20">
         <v>20</v>
       </c>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
-      <c r="R74" s="21"/>
-      <c r="S74" s="21"/>
-      <c r="T74" s="21"/>
-      <c r="U74" s="21"/>
-      <c r="V74" s="21"/>
-      <c r="W74" s="21"/>
-      <c r="X74" s="21"/>
-      <c r="Y74" s="21"/>
-      <c r="Z74" s="21"/>
-      <c r="AA74" s="21"/>
-      <c r="AB74" s="21"/>
-      <c r="AC74" s="21"/>
-      <c r="AD74" s="21"/>
-      <c r="AE74" s="21"/>
-      <c r="AF74" s="21"/>
-      <c r="AG74" s="21"/>
+      <c r="D74" s="24">
+        <v>0.8682432432432432</v>
+      </c>
+      <c r="E74" s="24">
+        <v>0.8597560975609756</v>
+      </c>
+      <c r="F74" s="24">
+        <v>0.87878787878787878</v>
+      </c>
+      <c r="G74" s="24">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24">
+        <v>0.86111111111111116</v>
+      </c>
+      <c r="J74" s="24">
+        <v>0.7567567567567568</v>
+      </c>
+      <c r="K74" s="24">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="L74" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="M74" s="24">
+        <v>1</v>
+      </c>
+      <c r="N74" s="24">
+        <v>1</v>
+      </c>
+      <c r="O74" s="24">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="P74" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="24">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="R74" s="24">
+        <v>0.76470588235294112</v>
+      </c>
+      <c r="S74" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="T74" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U74" s="24">
+        <v>1</v>
+      </c>
+      <c r="V74" s="24">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="W74" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="X74" s="24">
+        <v>0.72222222222222221</v>
+      </c>
+      <c r="Y74" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z74" s="24"/>
+      <c r="AA74" s="24"/>
+      <c r="AB74" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AC74" s="24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="AD74" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE74" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF74" s="24">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="AG74" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="26">
@@ -19518,36 +19572,90 @@
       <c r="C75" s="20">
         <v>21</v>
       </c>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
-      <c r="P75" s="21"/>
-      <c r="Q75" s="21"/>
-      <c r="R75" s="21"/>
-      <c r="S75" s="21"/>
-      <c r="T75" s="21"/>
-      <c r="U75" s="21"/>
-      <c r="V75" s="21"/>
-      <c r="W75" s="21"/>
-      <c r="X75" s="21"/>
-      <c r="Y75" s="21"/>
-      <c r="Z75" s="21"/>
-      <c r="AA75" s="21"/>
-      <c r="AB75" s="21"/>
-      <c r="AC75" s="21"/>
-      <c r="AD75" s="21"/>
-      <c r="AE75" s="21"/>
-      <c r="AF75" s="21"/>
-      <c r="AG75" s="21"/>
+      <c r="D75" s="24">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="E75" s="24">
+        <v>0.92817679558011046</v>
+      </c>
+      <c r="F75" s="24">
+        <v>0.9007633587786259</v>
+      </c>
+      <c r="G75" s="24">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="H75" s="24"/>
+      <c r="I75" s="24">
+        <v>1</v>
+      </c>
+      <c r="J75" s="24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="K75" s="24">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="L75" s="24">
+        <v>0.69047619047619047</v>
+      </c>
+      <c r="M75" s="24">
+        <v>1</v>
+      </c>
+      <c r="N75" s="24">
+        <v>1</v>
+      </c>
+      <c r="O75" s="24">
+        <v>1</v>
+      </c>
+      <c r="P75" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="24">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="R75" s="24">
+        <v>1</v>
+      </c>
+      <c r="S75" s="24">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="T75" s="24">
+        <v>1</v>
+      </c>
+      <c r="U75" s="24">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="V75" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="W75" s="24">
+        <v>1</v>
+      </c>
+      <c r="X75" s="24">
+        <v>0.63636363636363635</v>
+      </c>
+      <c r="Y75" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="24"/>
+      <c r="AA75" s="24"/>
+      <c r="AB75" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AC75" s="24">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="AD75" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG75" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="26">
@@ -27728,10 +27836,10 @@
         <v>18</v>
       </c>
       <c r="D72" s="24">
-        <v>0.9183006535947712</v>
+        <v>0.91176470588235292</v>
       </c>
       <c r="E72" s="24">
-        <v>0.85632183908045978</v>
+        <v>0.84482758620689657</v>
       </c>
       <c r="F72" s="24">
         <v>1</v>
@@ -27744,10 +27852,10 @@
         <v>0.95238095238095233</v>
       </c>
       <c r="J72" s="24">
-        <v>0.94736842105263153</v>
+        <v>0.92105263157894735</v>
       </c>
       <c r="K72" s="24">
-        <v>0.98</v>
+        <v>0.96</v>
       </c>
       <c r="L72" s="24">
         <v>1</v>
@@ -27774,7 +27882,7 @@
         <v>1</v>
       </c>
       <c r="T72" s="24">
-        <v>0.9285714285714286</v>
+        <v>0.8571428571428571</v>
       </c>
       <c r="U72" s="24">
         <v>0.55000000000000004</v>
@@ -27786,7 +27894,7 @@
         <v>0.89473684210526316</v>
       </c>
       <c r="X72" s="24">
-        <v>0.89473684210526316</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="Y72" s="24">
         <v>1</v>
@@ -27808,7 +27916,9 @@
       <c r="AF72" s="24">
         <v>1</v>
       </c>
-      <c r="AG72" s="24"/>
+      <c r="AG72" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="73" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A73" s="26">
@@ -27820,88 +27930,90 @@
       <c r="C73" s="20">
         <v>19</v>
       </c>
-      <c r="D73" s="21">
-        <v>0.88636363636363635</v>
-      </c>
-      <c r="E73" s="21">
-        <v>0.83798882681564246</v>
-      </c>
-      <c r="F73" s="21">
-        <v>0.95348837209302328</v>
-      </c>
-      <c r="G73" s="21">
-        <v>0.84444444444444444</v>
-      </c>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21">
-        <v>0.8666666666666667</v>
-      </c>
-      <c r="J73" s="21">
-        <v>0.82499999999999996</v>
-      </c>
-      <c r="K73" s="21">
-        <v>0.81632653061224492</v>
-      </c>
-      <c r="L73" s="21">
-        <v>0.8571428571428571</v>
-      </c>
-      <c r="M73" s="21">
-        <v>1</v>
-      </c>
-      <c r="N73" s="21">
-        <v>1</v>
-      </c>
-      <c r="O73" s="21">
-        <v>1</v>
-      </c>
-      <c r="P73" s="21">
-        <v>1</v>
-      </c>
-      <c r="Q73" s="21">
-        <v>0.91666666666666663</v>
-      </c>
-      <c r="R73" s="21">
-        <v>0.80769230769230771</v>
-      </c>
-      <c r="S73" s="21">
+      <c r="D73" s="24">
+        <v>0.90397350993377479</v>
+      </c>
+      <c r="E73" s="24">
+        <v>0.86857142857142855</v>
+      </c>
+      <c r="F73" s="24">
+        <v>0.952755905511811</v>
+      </c>
+      <c r="G73" s="24">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24">
+        <v>0.88888888888888884</v>
+      </c>
+      <c r="J73" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="K73" s="24">
+        <v>0.86956521739130432</v>
+      </c>
+      <c r="L73" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="M73" s="24">
+        <v>1</v>
+      </c>
+      <c r="N73" s="24">
+        <v>1</v>
+      </c>
+      <c r="O73" s="24">
+        <v>1</v>
+      </c>
+      <c r="P73" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q73" s="24">
         <v>0.91304347826086951</v>
       </c>
-      <c r="T73" s="21">
+      <c r="R73" s="24">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="S73" s="24">
+        <v>1</v>
+      </c>
+      <c r="T73" s="24">
         <v>0.7857142857142857</v>
       </c>
-      <c r="U73" s="21">
+      <c r="U73" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="V73" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="W73" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="X73" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="Y73" s="24">
+        <v>0.72727272727272729</v>
+      </c>
+      <c r="Z73" s="24"/>
+      <c r="AA73" s="24"/>
+      <c r="AB73" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="AC73" s="24">
         <v>0.76190476190476186</v>
       </c>
-      <c r="V73" s="21">
-        <v>0.89473684210526316</v>
-      </c>
-      <c r="W73" s="21">
-        <v>0.94736842105263153</v>
-      </c>
-      <c r="X73" s="21">
-        <v>0.76190476190476186</v>
-      </c>
-      <c r="Y73" s="21">
-        <v>0.66666666666666663</v>
-      </c>
-      <c r="Z73" s="21"/>
-      <c r="AA73" s="21"/>
-      <c r="AB73" s="21">
-        <v>0.91304347826086951</v>
-      </c>
-      <c r="AC73" s="21">
-        <v>0.78947368421052633</v>
-      </c>
-      <c r="AD73" s="21">
-        <v>1</v>
-      </c>
-      <c r="AE73" s="21">
-        <v>1</v>
-      </c>
-      <c r="AF73" s="21">
-        <v>1</v>
-      </c>
-      <c r="AG73" s="21"/>
+      <c r="AD73" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE73" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF73" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG73" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="26">
@@ -27913,36 +28025,90 @@
       <c r="C74" s="20">
         <v>20</v>
       </c>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
-      <c r="R74" s="21"/>
-      <c r="S74" s="21"/>
-      <c r="T74" s="21"/>
-      <c r="U74" s="21"/>
-      <c r="V74" s="21"/>
-      <c r="W74" s="21"/>
-      <c r="X74" s="21"/>
-      <c r="Y74" s="21"/>
-      <c r="Z74" s="21"/>
-      <c r="AA74" s="21"/>
-      <c r="AB74" s="21"/>
-      <c r="AC74" s="21"/>
-      <c r="AD74" s="21"/>
-      <c r="AE74" s="21"/>
-      <c r="AF74" s="21"/>
-      <c r="AG74" s="21"/>
+      <c r="D74" s="24">
+        <v>0.90878378378378377</v>
+      </c>
+      <c r="E74" s="24">
+        <v>0.88414634146341464</v>
+      </c>
+      <c r="F74" s="24">
+        <v>0.93939393939393945</v>
+      </c>
+      <c r="G74" s="24">
+        <v>0.97826086956521741</v>
+      </c>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="J74" s="24">
+        <v>0.78378378378378377</v>
+      </c>
+      <c r="K74" s="24">
+        <v>0.82222222222222219</v>
+      </c>
+      <c r="L74" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="M74" s="24">
+        <v>1</v>
+      </c>
+      <c r="N74" s="24">
+        <v>1</v>
+      </c>
+      <c r="O74" s="24">
+        <v>1</v>
+      </c>
+      <c r="P74" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q74" s="24">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="R74" s="24">
+        <v>0.94117647058823528</v>
+      </c>
+      <c r="S74" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="T74" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="U74" s="24">
+        <v>1</v>
+      </c>
+      <c r="V74" s="24">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="W74" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="X74" s="24">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="Y74" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="Z74" s="24"/>
+      <c r="AA74" s="24"/>
+      <c r="AB74" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AC74" s="24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="AD74" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE74" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF74" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG74" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="26">
@@ -27954,36 +28120,90 @@
       <c r="C75" s="20">
         <v>21</v>
       </c>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
-      <c r="P75" s="21"/>
-      <c r="Q75" s="21"/>
-      <c r="R75" s="21"/>
-      <c r="S75" s="21"/>
-      <c r="T75" s="21"/>
-      <c r="U75" s="21"/>
-      <c r="V75" s="21"/>
-      <c r="W75" s="21"/>
-      <c r="X75" s="21"/>
-      <c r="Y75" s="21"/>
-      <c r="Z75" s="21"/>
-      <c r="AA75" s="21"/>
-      <c r="AB75" s="21"/>
-      <c r="AC75" s="21"/>
-      <c r="AD75" s="21"/>
-      <c r="AE75" s="21"/>
-      <c r="AF75" s="21"/>
-      <c r="AG75" s="21"/>
+      <c r="D75" s="24">
+        <v>0.9391025641025641</v>
+      </c>
+      <c r="E75" s="24">
+        <v>0.96685082872928174</v>
+      </c>
+      <c r="F75" s="24">
+        <v>0.9007633587786259</v>
+      </c>
+      <c r="G75" s="24">
+        <v>0.95652173913043481</v>
+      </c>
+      <c r="H75" s="24"/>
+      <c r="I75" s="24">
+        <v>1</v>
+      </c>
+      <c r="J75" s="24">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="K75" s="24">
+        <v>0.98039215686274506</v>
+      </c>
+      <c r="L75" s="24">
+        <v>0.69047619047619047</v>
+      </c>
+      <c r="M75" s="24">
+        <v>1</v>
+      </c>
+      <c r="N75" s="24">
+        <v>1</v>
+      </c>
+      <c r="O75" s="24">
+        <v>1</v>
+      </c>
+      <c r="P75" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q75" s="24">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="R75" s="24">
+        <v>1</v>
+      </c>
+      <c r="S75" s="24">
+        <v>0.96296296296296291</v>
+      </c>
+      <c r="T75" s="24">
+        <v>1</v>
+      </c>
+      <c r="U75" s="24">
+        <v>0.95454545454545459</v>
+      </c>
+      <c r="V75" s="24">
+        <v>1</v>
+      </c>
+      <c r="W75" s="24">
+        <v>1</v>
+      </c>
+      <c r="X75" s="24">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="Y75" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z75" s="24"/>
+      <c r="AA75" s="24"/>
+      <c r="AB75" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="AC75" s="24">
+        <v>0.6071428571428571</v>
+      </c>
+      <c r="AD75" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE75" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF75" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG75" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="26">
@@ -33308,36 +33528,90 @@
       <c r="C73" s="20">
         <v>19</v>
       </c>
-      <c r="D73" s="21"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="21"/>
-      <c r="H73" s="21"/>
-      <c r="I73" s="21"/>
-      <c r="J73" s="21"/>
-      <c r="K73" s="21"/>
-      <c r="L73" s="21"/>
-      <c r="M73" s="21"/>
-      <c r="N73" s="21"/>
-      <c r="O73" s="21"/>
-      <c r="P73" s="21"/>
-      <c r="Q73" s="21"/>
-      <c r="R73" s="21"/>
-      <c r="S73" s="21"/>
-      <c r="T73" s="21"/>
-      <c r="U73" s="21"/>
-      <c r="V73" s="21"/>
-      <c r="W73" s="21"/>
-      <c r="X73" s="21"/>
-      <c r="Y73" s="21"/>
-      <c r="Z73" s="21"/>
-      <c r="AA73" s="21"/>
-      <c r="AB73" s="21"/>
-      <c r="AC73" s="21"/>
-      <c r="AD73" s="21"/>
-      <c r="AE73" s="21"/>
-      <c r="AF73" s="21"/>
-      <c r="AG73" s="21"/>
+      <c r="D73" s="24">
+        <v>0.3829301688726609</v>
+      </c>
+      <c r="E73" s="24">
+        <v>0.3491475166790215</v>
+      </c>
+      <c r="F73" s="24">
+        <v>0.43705463182897863</v>
+      </c>
+      <c r="G73" s="24">
+        <v>0.37575757575757573</v>
+      </c>
+      <c r="H73" s="24"/>
+      <c r="I73" s="24">
+        <v>0.33798882681564246</v>
+      </c>
+      <c r="J73" s="24">
+        <v>0.36082474226804123</v>
+      </c>
+      <c r="K73" s="24">
+        <v>0.32702702702702702</v>
+      </c>
+      <c r="L73" s="24">
+        <v>0.44578313253012047</v>
+      </c>
+      <c r="M73" s="24">
+        <v>0.52755905511811019</v>
+      </c>
+      <c r="N73" s="24">
+        <v>0.58288770053475936</v>
+      </c>
+      <c r="O73" s="24">
+        <v>0.32075471698113206</v>
+      </c>
+      <c r="P73" s="24">
+        <v>0.36363636363636365</v>
+      </c>
+      <c r="Q73" s="24">
+        <v>0.33862433862433861</v>
+      </c>
+      <c r="R73" s="24">
+        <v>0.35365853658536583</v>
+      </c>
+      <c r="S73" s="24">
+        <v>0.39860139860139859</v>
+      </c>
+      <c r="T73" s="24">
+        <v>0.23312883435582821</v>
+      </c>
+      <c r="U73" s="24">
+        <v>0.42553191489361702</v>
+      </c>
+      <c r="V73" s="24">
+        <v>0.3902439024390244</v>
+      </c>
+      <c r="W73" s="24">
+        <v>0.32474226804123713</v>
+      </c>
+      <c r="X73" s="24">
+        <v>0.3392857142857143</v>
+      </c>
+      <c r="Y73" s="24">
+        <v>0.40625</v>
+      </c>
+      <c r="Z73" s="24"/>
+      <c r="AA73" s="24"/>
+      <c r="AB73" s="24">
+        <v>0.70454545454545459</v>
+      </c>
+      <c r="AC73" s="24">
+        <v>0.15384615384615385</v>
+      </c>
+      <c r="AD73" s="24">
+        <v>0.52755905511811019</v>
+      </c>
+      <c r="AE73" s="24">
+        <v>0.58288770053475936</v>
+      </c>
+      <c r="AF73" s="24">
+        <v>0.32075471698113206</v>
+      </c>
+      <c r="AG73" s="24">
+        <v>0.36363636363636365</v>
+      </c>
     </row>
     <row r="74" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A74" s="25">
@@ -33349,36 +33623,90 @@
       <c r="C74" s="20">
         <v>20</v>
       </c>
-      <c r="D74" s="21"/>
-      <c r="E74" s="21"/>
-      <c r="F74" s="21"/>
-      <c r="G74" s="21"/>
-      <c r="H74" s="21"/>
-      <c r="I74" s="21"/>
-      <c r="J74" s="21"/>
-      <c r="K74" s="21"/>
-      <c r="L74" s="21"/>
-      <c r="M74" s="21"/>
-      <c r="N74" s="21"/>
-      <c r="O74" s="21"/>
-      <c r="P74" s="21"/>
-      <c r="Q74" s="21"/>
-      <c r="R74" s="21"/>
-      <c r="S74" s="21"/>
-      <c r="T74" s="21"/>
-      <c r="U74" s="21"/>
-      <c r="V74" s="21"/>
-      <c r="W74" s="21"/>
-      <c r="X74" s="21"/>
-      <c r="Y74" s="21"/>
-      <c r="Z74" s="21"/>
-      <c r="AA74" s="21"/>
-      <c r="AB74" s="21"/>
-      <c r="AC74" s="21"/>
-      <c r="AD74" s="21"/>
-      <c r="AE74" s="21"/>
-      <c r="AF74" s="21"/>
-      <c r="AG74" s="21"/>
+      <c r="D74" s="24">
+        <v>0.46</v>
+      </c>
+      <c r="E74" s="24">
+        <v>0.44631410256410259</v>
+      </c>
+      <c r="F74" s="24">
+        <v>0.48129675810473815</v>
+      </c>
+      <c r="G74" s="24">
+        <v>0.58900523560209428</v>
+      </c>
+      <c r="H74" s="24"/>
+      <c r="I74" s="24">
+        <v>0.33457249070631973</v>
+      </c>
+      <c r="J74" s="24">
+        <v>0.34728033472803349</v>
+      </c>
+      <c r="K74" s="24">
+        <v>0.44413407821229051</v>
+      </c>
+      <c r="L74" s="24">
+        <v>0.60194174757281549</v>
+      </c>
+      <c r="M74" s="24">
+        <v>0.33043478260869563</v>
+      </c>
+      <c r="N74" s="24">
+        <v>0.63120567375886527</v>
+      </c>
+      <c r="O74" s="24">
+        <v>0.39802631578947367</v>
+      </c>
+      <c r="P74" s="24">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="Q74" s="24">
+        <v>0.48936170212765956</v>
+      </c>
+      <c r="R74" s="24">
+        <v>0.2857142857142857</v>
+      </c>
+      <c r="S74" s="24">
+        <v>0.41984732824427479</v>
+      </c>
+      <c r="T74" s="24">
+        <v>0.48148148148148145</v>
+      </c>
+      <c r="U74" s="24">
+        <v>0.68556701030927836</v>
+      </c>
+      <c r="V74" s="24">
+        <v>0.30476190476190479</v>
+      </c>
+      <c r="W74" s="24">
+        <v>0.3595505617977528</v>
+      </c>
+      <c r="X74" s="24">
+        <v>0.38059701492537312</v>
+      </c>
+      <c r="Y74" s="24">
+        <v>0.42391304347826086</v>
+      </c>
+      <c r="Z74" s="24"/>
+      <c r="AA74" s="24"/>
+      <c r="AB74" s="24">
+        <v>0.69473684210526321</v>
+      </c>
+      <c r="AC74" s="24">
+        <v>0.52252252252252251</v>
+      </c>
+      <c r="AD74" s="24">
+        <v>0.33043478260869563</v>
+      </c>
+      <c r="AE74" s="24">
+        <v>0.63120567375886527</v>
+      </c>
+      <c r="AF74" s="24">
+        <v>0.39802631578947367</v>
+      </c>
+      <c r="AG74" s="24">
+        <v>0.3888888888888889</v>
+      </c>
     </row>
     <row r="75" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A75" s="25">
@@ -33390,36 +33718,90 @@
       <c r="C75" s="20">
         <v>21</v>
       </c>
-      <c r="D75" s="21"/>
-      <c r="E75" s="21"/>
-      <c r="F75" s="21"/>
-      <c r="G75" s="21"/>
-      <c r="H75" s="21"/>
-      <c r="I75" s="21"/>
-      <c r="J75" s="21"/>
-      <c r="K75" s="21"/>
-      <c r="L75" s="21"/>
-      <c r="M75" s="21"/>
-      <c r="N75" s="21"/>
-      <c r="O75" s="21"/>
-      <c r="P75" s="21"/>
-      <c r="Q75" s="21"/>
-      <c r="R75" s="21"/>
-      <c r="S75" s="21"/>
-      <c r="T75" s="21"/>
-      <c r="U75" s="21"/>
-      <c r="V75" s="21"/>
-      <c r="W75" s="21"/>
-      <c r="X75" s="21"/>
-      <c r="Y75" s="21"/>
-      <c r="Z75" s="21"/>
-      <c r="AA75" s="21"/>
-      <c r="AB75" s="21"/>
-      <c r="AC75" s="21"/>
-      <c r="AD75" s="21"/>
-      <c r="AE75" s="21"/>
-      <c r="AF75" s="21"/>
-      <c r="AG75" s="21"/>
+      <c r="D75" s="24">
+        <v>0.32771084337349399</v>
+      </c>
+      <c r="E75" s="24">
+        <v>0.34123770965876227</v>
+      </c>
+      <c r="F75" s="24">
+        <v>0.30782312925170069</v>
+      </c>
+      <c r="G75" s="24">
+        <v>0.42535787321063395</v>
+      </c>
+      <c r="H75" s="24"/>
+      <c r="I75" s="24">
+        <v>0.40673575129533679</v>
+      </c>
+      <c r="J75" s="24">
+        <v>0.25255102040816324</v>
+      </c>
+      <c r="K75" s="24">
+        <v>0.27272727272727271</v>
+      </c>
+      <c r="L75" s="24">
+        <v>0.18688524590163935</v>
+      </c>
+      <c r="M75" s="24">
+        <v>0.11931818181818182</v>
+      </c>
+      <c r="N75" s="24">
+        <v>0.41532258064516131</v>
+      </c>
+      <c r="O75" s="24">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="P75" s="24">
+        <v>0.23636363636363636</v>
+      </c>
+      <c r="Q75" s="24">
+        <v>0.30241935483870969</v>
+      </c>
+      <c r="R75" s="24">
+        <v>0.46103896103896103</v>
+      </c>
+      <c r="S75" s="24">
+        <v>0.35449735449735448</v>
+      </c>
+      <c r="T75" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="U75" s="24">
+        <v>0.55186721991701249</v>
+      </c>
+      <c r="V75" s="24">
+        <v>0.29064039408866993</v>
+      </c>
+      <c r="W75" s="24">
+        <v>0.37068965517241381</v>
+      </c>
+      <c r="X75" s="24">
+        <v>0.21164021164021163</v>
+      </c>
+      <c r="Y75" s="24">
+        <v>0.15841584158415842</v>
+      </c>
+      <c r="Z75" s="24"/>
+      <c r="AA75" s="24"/>
+      <c r="AB75" s="24">
+        <v>0.24242424242424243</v>
+      </c>
+      <c r="AC75" s="24">
+        <v>0.14450867052023122</v>
+      </c>
+      <c r="AD75" s="24">
+        <v>0.11931818181818182</v>
+      </c>
+      <c r="AE75" s="24">
+        <v>0.41532258064516131</v>
+      </c>
+      <c r="AF75" s="24">
+        <v>0.42857142857142855</v>
+      </c>
+      <c r="AG75" s="24">
+        <v>0.23636363636363636</v>
+      </c>
     </row>
     <row r="76" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A76" s="25">
@@ -36271,64 +36653,64 @@
         <v>8</v>
       </c>
       <c r="C18" s="12">
-        <v>40622.810138414607</v>
+        <v>205966.23629282569</v>
       </c>
       <c r="D18" s="12">
-        <v>23573.359925581379</v>
+        <v>141409.40998387698</v>
       </c>
       <c r="E18" s="12">
-        <v>17125.275096153833</v>
+        <v>66419.653091184999</v>
       </c>
       <c r="F18" s="12">
-        <v>3817.8981071428584</v>
+        <v>30728.684797806971</v>
       </c>
       <c r="G18" s="12" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="12">
-        <v>8383.4350380073702</v>
+        <v>42148.434866396674</v>
       </c>
       <c r="I18" s="12">
-        <v>4624.0056847058813</v>
+        <v>31111.770363114712</v>
       </c>
       <c r="J18" s="12">
-        <v>6668.316677941174</v>
+        <v>36953.090471826617</v>
       </c>
       <c r="K18" s="12">
-        <v>3811.1750572490632</v>
+        <v>14423.442153962189</v>
       </c>
       <c r="L18" s="12">
-        <v>4838.6704766467055</v>
+        <v>15434.956459999994</v>
       </c>
       <c r="M18" s="12">
-        <v>4220.658514285713</v>
+        <v>20247.232655799351</v>
       </c>
       <c r="N18" s="12">
-        <v>3857.7079259999996</v>
+        <v>14463.765597058806</v>
       </c>
       <c r="O18" s="12">
-        <v>499.21836507936524</v>
+        <v>2055.3284761904761</v>
       </c>
       <c r="P18" s="12">
-        <v>2377.7793114285728</v>
+        <v>16692.552131250006</v>
       </c>
       <c r="Q18" s="12">
-        <v>3616.0314369230741</v>
+        <v>18733.400018260858</v>
       </c>
       <c r="R18" s="12">
-        <v>1779.4479213114755</v>
+        <v>14352.634422222227</v>
       </c>
       <c r="S18" s="12">
-        <v>4931.8335770642179</v>
+        <v>22582.318223255799</v>
       </c>
       <c r="T18" s="12">
-        <v>1376.418317006802</v>
+        <v>13773.77627575752</v>
       </c>
       <c r="U18" s="12">
-        <v>4787.8980999999922</v>
+        <v>23413.378120454468</v>
       </c>
       <c r="V18" s="12">
-        <v>4624.0056847058813</v>
+        <v>31111.770363114712</v>
       </c>
       <c r="W18" s="12" t="s">
         <v>47</v>
@@ -36337,19 +36719,19 @@
         <v>47</v>
       </c>
       <c r="Y18" s="12">
-        <v>3811.1750572490632</v>
+        <v>14423.442153962189</v>
       </c>
       <c r="Z18" s="12">
-        <v>4838.6704766467055</v>
+        <v>15434.956459999994</v>
       </c>
       <c r="AA18" s="12">
-        <v>4220.658514285713</v>
+        <v>20247.232655799351</v>
       </c>
       <c r="AB18" s="12">
-        <v>3857.7079259999996</v>
+        <v>14463.765597058806</v>
       </c>
       <c r="AC18" s="12">
-        <v>499.21836507936524</v>
+        <v>2055.3284761904761</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
@@ -38069,79 +38451,79 @@
         <v>8</v>
       </c>
       <c r="C18" s="16">
-        <v>0.81459999999999999</v>
+        <v>0.81499999999999995</v>
       </c>
       <c r="D18" s="16">
-        <v>0.84450000000000003</v>
+        <v>0.84519999999999995</v>
       </c>
       <c r="E18" s="16">
-        <v>0.78139999999999998</v>
+        <v>0.78200000000000003</v>
       </c>
       <c r="F18" s="16">
-        <v>0.82705000000000006</v>
+        <v>0.83650000000000002</v>
       </c>
       <c r="G18" s="16"/>
       <c r="H18" s="16">
-        <v>0.83319999999999994</v>
+        <v>0.83499999999999996</v>
       </c>
       <c r="I18" s="16">
-        <v>0.82220000000000004</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="J18" s="16">
-        <v>0.89005000000000001</v>
+        <v>0.88324999999999998</v>
       </c>
       <c r="K18" s="16">
-        <v>0.77539999999999998</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="L18" s="16">
         <v>0.75700000000000001</v>
       </c>
       <c r="M18" s="16">
-        <v>0.73529999999999995</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="N18" s="16">
-        <v>0.88239999999999996</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="O18" s="16">
-        <v>0.77080000000000004</v>
+        <v>0.77100000000000002</v>
       </c>
       <c r="P18" s="16">
-        <v>0.84650000000000003</v>
+        <v>0.86299999999999999</v>
       </c>
       <c r="Q18" s="16">
-        <v>0.8841</v>
+        <v>0.88500000000000001</v>
       </c>
       <c r="R18" s="16">
-        <v>0.89029999999999998</v>
+        <v>0.88400000000000001</v>
       </c>
       <c r="S18" s="16">
-        <v>0.88980000000000004</v>
+        <v>0.88249999999999995</v>
       </c>
       <c r="T18" s="16">
-        <v>0.80759999999999998</v>
+        <v>0.81</v>
       </c>
       <c r="U18" s="16">
-        <v>0.7823</v>
+        <v>0.78500000000000003</v>
       </c>
       <c r="V18" s="16">
-        <v>0.82220000000000004</v>
+        <v>0.82399999999999995</v>
       </c>
       <c r="W18" s="16"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="16">
-        <v>0.77539999999999998</v>
+        <v>0.77600000000000002</v>
       </c>
       <c r="Z18" s="16">
         <v>0.75700000000000001</v>
       </c>
       <c r="AA18" s="16">
-        <v>0.73529999999999995</v>
+        <v>0.73799999999999999</v>
       </c>
       <c r="AB18" s="16">
-        <v>0.88239999999999996</v>
+        <v>0.88200000000000001</v>
       </c>
       <c r="AC18" s="16">
-        <v>0.77080000000000004</v>
+        <v>0.77100000000000002</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
@@ -39926,82 +40308,82 @@
         <v>8</v>
       </c>
       <c r="C18" s="11">
-        <v>46005.823839921402</v>
+        <v>149773.01088499746</v>
       </c>
       <c r="D18" s="11">
-        <v>25249.057193605666</v>
+        <v>80370.033120204462</v>
       </c>
       <c r="E18" s="11">
-        <v>20672.530458152021</v>
-      </c>
-      <c r="F18" s="11">
-        <v>4184.5456743848627</v>
-      </c>
-      <c r="G18" s="11" t="s">
+        <v>33368.689659294621</v>
+      </c>
+      <c r="F18" s="11" t="s">
         <v>47</v>
       </c>
+      <c r="G18" s="11">
+        <v>46521.867065868166</v>
+      </c>
       <c r="H18" s="11">
-        <v>9306.2435189630232</v>
+        <v>33139.239927184426</v>
       </c>
       <c r="I18" s="11">
-        <v>4979.5325954755517</v>
+        <v>36821.678120577395</v>
       </c>
       <c r="J18" s="11">
-        <v>6756.773776754113</v>
+        <v>17654.233505154545</v>
       </c>
       <c r="K18" s="11">
-        <v>4655.5076089760041</v>
+        <v>18536.035138705407</v>
       </c>
       <c r="L18" s="11">
-        <v>5801.3466314398929</v>
+        <v>26203.151490514876</v>
       </c>
       <c r="M18" s="11">
-        <v>5479.1383108935106</v>
+        <v>15632.526870748279</v>
       </c>
       <c r="N18" s="11">
-        <v>4124.3734134179513</v>
+        <v>2583.7712062256805</v>
       </c>
       <c r="O18" s="11">
-        <v>627.73456149455126</v>
+        <v>18204.678215527238</v>
       </c>
       <c r="P18" s="11">
-        <v>2657.1183697578276</v>
+        <v>20456.164858757049</v>
       </c>
       <c r="Q18" s="11">
-        <v>3967.9789616559183</v>
+        <v>14372.862895927605</v>
       </c>
       <c r="R18" s="11">
-        <v>1905.0166236100192</v>
+        <v>22455.678640226615</v>
       </c>
       <c r="S18" s="11">
-        <v>4852.5850752978167</v>
+        <v>15064.532839506111</v>
       </c>
       <c r="T18" s="11">
-        <v>1500.2201584943032</v>
+        <v>26422.997579617746</v>
       </c>
       <c r="U18" s="11">
-        <v>5427.4215773999658</v>
-      </c>
-      <c r="V18" s="11">
-        <v>4979.5325954755517</v>
+        <v>33139.239927184426</v>
+      </c>
+      <c r="V18" s="11" t="s">
+        <v>47</v>
       </c>
       <c r="W18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="X18" s="11" t="s">
-        <v>47</v>
+      <c r="X18" s="11">
+        <v>17654.233505154545</v>
       </c>
       <c r="Y18" s="11">
-        <v>4655.5076089760041</v>
+        <v>18536.035138705407</v>
       </c>
       <c r="Z18" s="11">
-        <v>5801.3466314398929</v>
+        <v>26203.151490514876</v>
       </c>
       <c r="AA18" s="11">
-        <v>5479.1383108935106</v>
+        <v>15632.526870748279</v>
       </c>
       <c r="AB18" s="11">
-        <v>4124.3734134179513</v>
+        <v>2583.7712062256805</v>
       </c>
       <c r="AC18" s="11">
         <v>627.73456149455126</v>
@@ -41789,64 +42171,64 @@
         <v>8</v>
       </c>
       <c r="C18" s="11">
-        <v>1621.650545218519</v>
+        <v>8445.7206732055165</v>
       </c>
       <c r="D18" s="11">
-        <v>1725.1479611650473</v>
+        <v>10875.270515463904</v>
       </c>
       <c r="E18" s="11">
-        <v>1502.6525860465106</v>
+        <v>5824.7790454124088</v>
       </c>
       <c r="F18" s="11">
-        <v>1244.9023381294967</v>
+        <v>11120.680836653368</v>
       </c>
       <c r="G18" s="11" t="s">
         <v>47</v>
       </c>
       <c r="H18" s="11">
-        <v>2646.4034470989727</v>
+        <v>14494.68619402982</v>
       </c>
       <c r="I18" s="11">
-        <v>1421.5873958333329</v>
+        <v>9822.5660791366772</v>
       </c>
       <c r="J18" s="11">
-        <v>1595.1900530503974</v>
+        <v>8861.7839782016308</v>
       </c>
       <c r="K18" s="11">
-        <v>1271.0847183098567</v>
+        <v>4910.2814336917309</v>
       </c>
       <c r="L18" s="11">
-        <v>2386.7496739130429</v>
+        <v>7503.6249197860934</v>
       </c>
       <c r="M18" s="11">
-        <v>1220.8516363636359</v>
+        <v>5789.7981437125682</v>
       </c>
       <c r="N18" s="11">
-        <v>1716.6731603773583</v>
+        <v>6442.9386448598052</v>
       </c>
       <c r="O18" s="11">
-        <v>744.39661538461564</v>
+        <v>3064.7501538461534</v>
       </c>
       <c r="P18" s="11">
-        <v>2026.351981981983</v>
+        <v>15402.585588235299</v>
       </c>
       <c r="Q18" s="11">
-        <v>2617.9777611940276</v>
+        <v>15213.198235294109</v>
       </c>
       <c r="R18" s="11">
-        <v>1325.028359375</v>
+        <v>10414.435081967216</v>
       </c>
       <c r="S18" s="11">
-        <v>1734.0683534136538</v>
+        <v>8088.6271020408112</v>
       </c>
       <c r="T18" s="11">
-        <v>725.49568862275419</v>
+        <v>8189.4440268456046</v>
       </c>
       <c r="U18" s="11">
-        <v>2670.3596855345872</v>
+        <v>13920.841006711364</v>
       </c>
       <c r="V18" s="11">
-        <v>1421.5873958333329</v>
+        <v>9822.5660791366772</v>
       </c>
       <c r="W18" s="11" t="s">
         <v>47</v>
@@ -41855,19 +42237,19 @@
         <v>47</v>
       </c>
       <c r="Y18" s="11">
-        <v>1271.0847183098567</v>
+        <v>4910.2814336917309</v>
       </c>
       <c r="Z18" s="11">
-        <v>2386.7496739130429</v>
+        <v>7503.6249197860934</v>
       </c>
       <c r="AA18" s="11">
-        <v>1220.8516363636359</v>
+        <v>5789.7981437125682</v>
       </c>
       <c r="AB18" s="11">
-        <v>1716.6731603773583</v>
+        <v>6442.9386448598052</v>
       </c>
       <c r="AC18" s="11">
-        <v>744.39661538461564</v>
+        <v>3064.7501538461534</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">
@@ -45360,166 +45742,166 @@
         <v>8</v>
       </c>
       <c r="C19" s="17">
-        <v>0.44038277511961721</v>
+        <v>0.44448400688386447</v>
       </c>
       <c r="D19" s="17">
-        <v>0.55961722488038279</v>
+        <v>0.55551599311613553</v>
       </c>
       <c r="E19" s="17">
-        <v>0.60653247246486897</v>
+        <v>0.58079599826011308</v>
       </c>
       <c r="F19" s="17">
-        <v>0.39346752753513103</v>
+        <v>0.41920400173988692</v>
       </c>
       <c r="G19" s="17">
-        <v>0.27160493827160492</v>
+        <v>0.28073154800783801</v>
       </c>
       <c r="H19" s="17">
-        <v>0.72839506172839508</v>
+        <v>0.71926845199216194</v>
       </c>
       <c r="I19" s="17">
-        <v>0.69035532994923854</v>
+        <v>0.60472103004291844</v>
       </c>
       <c r="J19" s="17">
-        <v>0.30964467005076141</v>
+        <v>0.39527896995708156</v>
       </c>
       <c r="K19" s="17"/>
       <c r="L19" s="17"/>
       <c r="M19" s="17">
-        <v>0.50805270863836016</v>
+        <v>0.57183098591549297</v>
       </c>
       <c r="N19" s="17">
-        <v>0.49194729136163984</v>
+        <v>0.42816901408450703</v>
       </c>
       <c r="O19" s="17">
-        <v>0.57873485868102292</v>
+        <v>0.49693829486575603</v>
       </c>
       <c r="P19" s="17">
-        <v>0.42126514131897713</v>
+        <v>0.50306170513424397</v>
       </c>
       <c r="Q19" s="17">
-        <v>0.67404674046740465</v>
+        <v>0.63490241102181399</v>
       </c>
       <c r="R19" s="17">
-        <v>0.32595325953259535</v>
+        <v>0.36509758897818601</v>
       </c>
       <c r="S19" s="17">
-        <v>0.36923076923076925</v>
+        <v>0.38507718696397941</v>
       </c>
       <c r="T19" s="17">
-        <v>0.63076923076923075</v>
+        <v>0.61492281303602059</v>
       </c>
       <c r="U19" s="17">
-        <v>0.38421052631578945</v>
+        <v>0.37851662404092073</v>
       </c>
       <c r="V19" s="17">
-        <v>0.61578947368421055</v>
+        <v>0.62148337595907932</v>
       </c>
       <c r="W19" s="17">
-        <v>0.22844344904815231</v>
+        <v>0.23154246100519932</v>
       </c>
       <c r="X19" s="17">
-        <v>0.77155655095184772</v>
+        <v>0.76845753899480074</v>
       </c>
       <c r="Y19" s="17">
-        <v>0.21269095182138661</v>
+        <v>0.24184683034078416</v>
       </c>
       <c r="Z19" s="17">
-        <v>0.78730904817861336</v>
+        <v>0.75815316965921586</v>
       </c>
       <c r="AA19" s="17">
-        <v>0.38461538461538464</v>
+        <v>0.81720430107526887</v>
       </c>
       <c r="AB19" s="17">
-        <v>0.61538461538461542</v>
+        <v>0.18279569892473119</v>
       </c>
       <c r="AC19" s="17">
-        <v>0.70403587443946192</v>
+        <v>0.63594994311717856</v>
       </c>
       <c r="AD19" s="17">
-        <v>0.29596412556053814</v>
+        <v>0.36405005688282138</v>
       </c>
       <c r="AE19" s="17">
-        <v>0.39359267734553777</v>
+        <v>0.41905642923219244</v>
       </c>
       <c r="AF19" s="17">
-        <v>0.60640732265446229</v>
+        <v>0.58094357076780756</v>
       </c>
       <c r="AG19" s="17">
-        <v>0.65217391304347827</v>
+        <v>0.58925619834710741</v>
       </c>
       <c r="AH19" s="17">
-        <v>0.34782608695652173</v>
+        <v>0.41074380165289254</v>
       </c>
       <c r="AI19" s="17">
-        <v>0.75367647058823528</v>
+        <v>0.70078740157480313</v>
       </c>
       <c r="AJ19" s="17">
-        <v>0.24632352941176472</v>
+        <v>0.29921259842519687</v>
       </c>
       <c r="AK19" s="17">
-        <v>0.67251461988304095</v>
+        <v>0.58580289455547896</v>
       </c>
       <c r="AL19" s="17">
-        <v>0.32748538011695905</v>
+        <v>0.41419710544452104</v>
       </c>
       <c r="AM19" s="17">
-        <v>0.52556818181818177</v>
+        <v>0.47888774459320288</v>
       </c>
       <c r="AN19" s="17">
-        <v>0.47443181818181818</v>
+        <v>0.52111225540679706</v>
       </c>
       <c r="AO19" s="17">
-        <v>0.71138211382113825</v>
+        <v>0.72926596758817919</v>
       </c>
       <c r="AP19" s="17">
-        <v>0.2886178861788618</v>
+        <v>0.27073403241182076</v>
       </c>
       <c r="AQ19" s="17">
-        <v>0.62659846547314579</v>
+        <v>0.51215277777777779</v>
       </c>
       <c r="AR19" s="17">
-        <v>0.37340153452685421</v>
+        <v>0.48784722222222221</v>
       </c>
       <c r="AS19" s="17">
-        <v>0.60730593607305938</v>
+        <v>0.62840466926070038</v>
       </c>
       <c r="AT19" s="17">
-        <v>0.39269406392694062</v>
+        <v>0.37159533073929962</v>
       </c>
       <c r="AU19" s="17"/>
       <c r="AV19" s="17"/>
       <c r="AW19" s="17"/>
       <c r="AX19" s="17"/>
       <c r="AY19" s="17">
-        <v>0.36923076923076925</v>
+        <v>0.38507718696397941</v>
       </c>
       <c r="AZ19" s="17">
-        <v>0.63076923076923075</v>
+        <v>0.61492281303602059</v>
       </c>
       <c r="BA19" s="17">
-        <v>0.38421052631578945</v>
+        <v>0.37851662404092073</v>
       </c>
       <c r="BB19" s="17">
-        <v>0.61578947368421055</v>
+        <v>0.62148337595907932</v>
       </c>
       <c r="BC19" s="17">
-        <v>0.22844344904815231</v>
+        <v>0.23154246100519932</v>
       </c>
       <c r="BD19" s="17">
-        <v>0.77155655095184772</v>
+        <v>0.76845753899480074</v>
       </c>
       <c r="BE19" s="17">
-        <v>0.21269095182138661</v>
+        <v>0.24184683034078416</v>
       </c>
       <c r="BF19" s="17">
-        <v>0.78730904817861336</v>
+        <v>0.75815316965921586</v>
       </c>
       <c r="BG19" s="17">
-        <v>0.38461538461538464</v>
+        <v>0.81720430107526887</v>
       </c>
       <c r="BH19" s="17">
-        <v>0.61538461538461542</v>
+        <v>0.18279569892473119</v>
       </c>
     </row>
     <row r="20" spans="1:60" x14ac:dyDescent="0.25">
@@ -47600,88 +47982,88 @@
         <v>8</v>
       </c>
       <c r="C18" s="17">
-        <v>0.80456026058631924</v>
+        <v>0.89391447368421051</v>
       </c>
       <c r="D18" s="17">
-        <v>0.74220963172804533</v>
+        <v>0.86599423631123917</v>
       </c>
       <c r="E18" s="17">
-        <v>0.88888888888888884</v>
+        <v>0.93103448275862066</v>
       </c>
       <c r="F18" s="17">
-        <v>0.5617977528089888</v>
+        <v>0.82777777777777772</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17">
-        <v>0.77011494252873558</v>
+        <v>0.90303030303030307</v>
       </c>
       <c r="I18" s="17">
-        <v>0.78205128205128205</v>
+        <v>0.8152866242038217</v>
       </c>
       <c r="J18" s="17">
-        <v>0.84848484848484851</v>
+        <v>0.91145833333333337</v>
       </c>
       <c r="K18" s="17">
-        <v>0.8214285714285714</v>
+        <v>0.83734939759036142</v>
       </c>
       <c r="L18" s="17">
-        <v>0.91666666666666663</v>
+        <v>1</v>
       </c>
       <c r="M18" s="17">
         <v>1</v>
       </c>
       <c r="N18" s="17">
-        <v>0.86956521739130432</v>
+        <v>0.93571428571428572</v>
       </c>
       <c r="O18" s="17">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
       <c r="P18" s="17">
-        <v>0.625</v>
+        <v>0.82105263157894737</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.75510204081632648</v>
+        <v>0.87912087912087911</v>
       </c>
       <c r="R18" s="17">
-        <v>0.95744680851063835</v>
+        <v>0.96703296703296704</v>
       </c>
       <c r="S18" s="17">
-        <v>0.75</v>
+        <v>0.875</v>
       </c>
       <c r="T18" s="17">
-        <v>0.48780487804878048</v>
+        <v>0.83529411764705885</v>
       </c>
       <c r="U18" s="17">
-        <v>0.86842105263157898</v>
+        <v>0.89610389610389607</v>
       </c>
       <c r="V18" s="17">
-        <v>0.78947368421052633</v>
+        <v>0.93243243243243246</v>
       </c>
       <c r="W18" s="17">
-        <v>0.7</v>
+        <v>0.73750000000000004</v>
       </c>
       <c r="X18" s="17">
-        <v>0.75</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="Y18" s="17"/>
       <c r="Z18" s="17"/>
       <c r="AA18" s="17">
-        <v>0.8571428571428571</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="AB18" s="17">
-        <v>0.7857142857142857</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="AC18" s="17">
-        <v>0.91666666666666663</v>
+        <v>1</v>
       </c>
       <c r="AD18" s="17">
         <v>1</v>
       </c>
       <c r="AE18" s="17">
-        <v>0.86956521739130432</v>
+        <v>0.93571428571428572</v>
       </c>
       <c r="AF18" s="17">
-        <v>0.83333333333333337</v>
+        <v>1</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">
@@ -49566,29 +49948,29 @@
         <v>8</v>
       </c>
       <c r="C18" s="17">
-        <v>0.90228013029315957</v>
+        <v>0.91611842105263153</v>
       </c>
       <c r="D18" s="17">
-        <v>0.84702549575070818</v>
+        <v>0.89193083573487031</v>
       </c>
       <c r="E18" s="17">
-        <v>0.97701149425287359</v>
+        <v>0.94827586206896552</v>
       </c>
       <c r="F18" s="17">
-        <v>0.6966292134831461</v>
+        <v>0.82777777777777772</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17">
-        <v>0.90804597701149425</v>
+        <v>0.90303030303030307</v>
       </c>
       <c r="I18" s="17">
-        <v>0.88461538461538458</v>
+        <v>0.8152866242038217</v>
       </c>
       <c r="J18" s="17">
-        <v>0.89898989898989901</v>
+        <v>0.91145833333333337</v>
       </c>
       <c r="K18" s="17">
-        <v>0.9285714285714286</v>
+        <v>0.83734939759036142</v>
       </c>
       <c r="L18" s="17">
         <v>1</v>
@@ -49603,39 +49985,39 @@
         <v>1</v>
       </c>
       <c r="P18" s="17">
-        <v>0.72916666666666663</v>
+        <v>0.84210526315789469</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.89795918367346939</v>
+        <v>0.94505494505494503</v>
       </c>
       <c r="R18" s="17">
-        <v>0.95744680851063835</v>
+        <v>0.96703296703296704</v>
       </c>
       <c r="S18" s="17">
-        <v>0.8571428571428571</v>
+        <v>0.875</v>
       </c>
       <c r="T18" s="17">
-        <v>0.65853658536585369</v>
+        <v>0.83529411764705885</v>
       </c>
       <c r="U18" s="17">
-        <v>0.94736842105263153</v>
+        <v>0.92207792207792205</v>
       </c>
       <c r="V18" s="17">
-        <v>0.92105263157894735</v>
+        <v>0.94594594594594594</v>
       </c>
       <c r="W18" s="17">
         <v>0.82499999999999996</v>
       </c>
       <c r="X18" s="17">
-        <v>0.83333333333333337</v>
+        <v>0.84444444444444444</v>
       </c>
       <c r="Y18" s="17"/>
       <c r="Z18" s="17"/>
       <c r="AA18" s="17">
-        <v>0.95238095238095233</v>
+        <v>0.9178082191780822</v>
       </c>
       <c r="AB18" s="17">
-        <v>0.90476190476190477</v>
+        <v>0.77419354838709675</v>
       </c>
       <c r="AC18" s="17">
         <v>1</v>
@@ -50860,88 +51242,88 @@
         <v>8</v>
       </c>
       <c r="C18" s="17">
-        <v>0.38280450358239509</v>
+        <v>0.38263736263736264</v>
       </c>
       <c r="D18" s="17">
-        <v>0.35859820700896494</v>
+        <v>0.37061048082117776</v>
       </c>
       <c r="E18" s="17">
-        <v>0.4236588720770289</v>
+        <v>0.40146602762898226</v>
       </c>
       <c r="F18" s="17">
-        <v>0.26453488372093026</v>
+        <v>0.41941747572815535</v>
       </c>
       <c r="G18" s="17"/>
       <c r="H18" s="17">
-        <v>0.375</v>
+        <v>0.36587240584166025</v>
       </c>
       <c r="I18" s="17">
-        <v>0.46183206106870228</v>
+        <v>0.34459459459459457</v>
       </c>
       <c r="J18" s="17">
-        <v>0.36036036036036034</v>
+        <v>0.34537097833223901</v>
       </c>
       <c r="K18" s="17">
-        <v>0.69402985074626866</v>
+        <v>0.42909987669543775</v>
       </c>
       <c r="L18" s="17">
-        <v>0.47663551401869159</v>
+        <v>0.33714285714285713</v>
       </c>
       <c r="M18" s="17">
-        <v>0.48484848484848486</v>
+        <v>0.5155367231638418</v>
       </c>
       <c r="N18" s="17">
-        <v>0.28482972136222912</v>
+        <v>0.36125654450261779</v>
       </c>
       <c r="O18" s="17">
-        <v>0.25806451612903225</v>
+        <v>0.30722891566265059</v>
       </c>
       <c r="P18" s="17">
-        <v>0.26737967914438504</v>
+        <v>0.3460591133004926</v>
       </c>
       <c r="Q18" s="17">
-        <v>0.39130434782608697</v>
+        <v>0.38167938931297712</v>
       </c>
       <c r="R18" s="17">
-        <v>0.39726027397260272</v>
+        <v>0.3891625615763547</v>
       </c>
       <c r="S18" s="17">
-        <v>0.37037037037037035</v>
+        <v>0.3217993079584775</v>
       </c>
       <c r="T18" s="17">
-        <v>0.26114649681528662</v>
+        <v>0.50068212824010916</v>
       </c>
       <c r="U18" s="17">
-        <v>0.45967741935483869</v>
+        <v>0.35315315315315315</v>
       </c>
       <c r="V18" s="17">
-        <v>0.36416184971098264</v>
+        <v>0.35521235521235522</v>
       </c>
       <c r="W18" s="17">
-        <v>0.46376811594202899</v>
+        <v>0.33704292527821939</v>
       </c>
       <c r="X18" s="17">
-        <v>0.27848101265822783</v>
+        <v>0.30654761904761907</v>
       </c>
       <c r="Y18" s="17"/>
       <c r="Z18" s="17"/>
       <c r="AA18" s="17">
-        <v>0.64935064935064934</v>
+        <v>0.5357142857142857</v>
       </c>
       <c r="AB18" s="17">
-        <v>0.75438596491228072</v>
+        <v>0.32935560859188545</v>
       </c>
       <c r="AC18" s="17">
-        <v>0.47663551401869159</v>
+        <v>0.33714285714285713</v>
       </c>
       <c r="AD18" s="17">
-        <v>0.48484848484848486</v>
+        <v>0.5155367231638418</v>
       </c>
       <c r="AE18" s="17">
-        <v>0.28482972136222912</v>
+        <v>0.36125654450261779</v>
       </c>
       <c r="AF18" s="17">
-        <v>0.25806451612903225</v>
+        <v>0.30722891566265059</v>
       </c>
     </row>
     <row r="19" spans="1:32" x14ac:dyDescent="0.25">

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -40308,85 +40308,85 @@
         <v>8</v>
       </c>
       <c r="C18" s="11">
+        <v>232438.66834355795</v>
+      </c>
+      <c r="D18" s="11">
         <v>149773.01088499746</v>
       </c>
-      <c r="D18" s="11">
+      <c r="E18" s="11">
         <v>80370.033120204462</v>
       </c>
-      <c r="E18" s="11">
+      <c r="F18" s="11">
         <v>33368.689659294621</v>
       </c>
-      <c r="F18" s="11" t="s">
+      <c r="G18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="G18" s="11">
+      <c r="H18" s="11">
         <v>46521.867065868166</v>
       </c>
-      <c r="H18" s="11">
+      <c r="I18" s="11">
         <v>33139.239927184426</v>
       </c>
-      <c r="I18" s="11">
+      <c r="J18" s="11">
         <v>36821.678120577395</v>
       </c>
-      <c r="J18" s="11">
+      <c r="K18" s="11">
         <v>17654.233505154545</v>
       </c>
-      <c r="K18" s="11">
+      <c r="L18" s="11">
         <v>18536.035138705407</v>
       </c>
-      <c r="L18" s="11">
+      <c r="M18" s="11">
         <v>26203.151490514876</v>
       </c>
-      <c r="M18" s="11">
+      <c r="N18" s="11">
         <v>15632.526870748279</v>
       </c>
-      <c r="N18" s="11">
+      <c r="O18" s="11">
         <v>2583.7712062256805</v>
       </c>
-      <c r="O18" s="11">
+      <c r="P18" s="11">
         <v>18204.678215527238</v>
       </c>
-      <c r="P18" s="11">
+      <c r="Q18" s="11">
         <v>20456.164858757049</v>
       </c>
-      <c r="Q18" s="11">
+      <c r="R18" s="11">
         <v>14372.862895927605</v>
       </c>
-      <c r="R18" s="11">
+      <c r="S18" s="11">
         <v>22455.678640226615</v>
       </c>
-      <c r="S18" s="11">
+      <c r="T18" s="11">
         <v>15064.532839506111</v>
       </c>
-      <c r="T18" s="11">
+      <c r="U18" s="11">
         <v>26422.997579617746</v>
       </c>
-      <c r="U18" s="11">
+      <c r="V18" s="11">
         <v>33139.239927184426</v>
-      </c>
-      <c r="V18" s="11" t="s">
-        <v>47</v>
       </c>
       <c r="W18" s="11" t="s">
         <v>47</v>
       </c>
-      <c r="X18" s="11">
+      <c r="X18" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y18" s="11">
         <v>17654.233505154545</v>
       </c>
-      <c r="Y18" s="11">
+      <c r="Z18" s="11">
         <v>18536.035138705407</v>
       </c>
-      <c r="Z18" s="11">
+      <c r="AA18" s="11">
         <v>26203.151490514876</v>
       </c>
-      <c r="AA18" s="11">
+      <c r="AB18" s="11">
         <v>15632.526870748279</v>
       </c>
-      <c r="AB18" s="11">
+      <c r="AC18" s="11">
         <v>2583.7712062256805</v>
-      </c>
-      <c r="AC18" s="11">
-        <v>627.73456149455126</v>
       </c>
     </row>
     <row r="19" spans="1:29" x14ac:dyDescent="0.25">

--- a/Archivodecargaprocesomtto.xlsx
+++ b/Archivodecargaprocesomtto.xlsx
@@ -7994,7 +7994,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1148" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1157" uniqueCount="50">
   <si>
     <t>Mes</t>
   </si>
@@ -8256,7 +8256,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -8330,7 +8330,6 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -10246,33 +10245,81 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="6"/>
-      <c r="D19" s="6"/>
-      <c r="E19" s="6"/>
-      <c r="F19" s="6"/>
-      <c r="G19" s="6"/>
-      <c r="H19" s="6"/>
-      <c r="I19" s="6"/>
-      <c r="J19" s="6"/>
-      <c r="K19" s="6"/>
-      <c r="L19" s="6"/>
-      <c r="M19" s="6"/>
-      <c r="N19" s="6"/>
-      <c r="O19" s="6"/>
-      <c r="P19" s="6"/>
-      <c r="Q19" s="6"/>
-      <c r="R19" s="6"/>
-      <c r="S19" s="6"/>
-      <c r="T19" s="6"/>
-      <c r="U19" s="6"/>
-      <c r="V19" s="6"/>
-      <c r="W19" s="6"/>
-      <c r="X19" s="6"/>
-      <c r="Y19" s="6"/>
-      <c r="Z19" s="6"/>
-      <c r="AA19" s="6"/>
-      <c r="AB19" s="6"/>
-      <c r="AC19" s="6"/>
+      <c r="C19" s="15">
+        <v>0.92529215358931549</v>
+      </c>
+      <c r="D19" s="15">
+        <v>0.90032948929159806</v>
+      </c>
+      <c r="E19" s="15">
+        <v>0.95093062605752965</v>
+      </c>
+      <c r="F19" s="15">
+        <v>0.91911764705882348</v>
+      </c>
+      <c r="G19" s="15"/>
+      <c r="H19" s="15">
+        <v>0.91575091575091572</v>
+      </c>
+      <c r="I19" s="15">
+        <v>0.88395904436860073</v>
+      </c>
+      <c r="J19" s="15">
+        <v>0.88829787234042556</v>
+      </c>
+      <c r="K19" s="15">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="L19" s="15">
+        <v>0.91443850267379678</v>
+      </c>
+      <c r="M19" s="15">
+        <v>0.96220930232558144</v>
+      </c>
+      <c r="N19" s="15">
+        <v>0.96506550218340614</v>
+      </c>
+      <c r="O19" s="15">
+        <v>0.93846153846153846</v>
+      </c>
+      <c r="P19" s="15">
+        <v>0.94339622641509435</v>
+      </c>
+      <c r="Q19" s="15">
+        <v>0.95833333333333337</v>
+      </c>
+      <c r="R19" s="15">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="S19" s="15">
+        <v>0.86852589641434264</v>
+      </c>
+      <c r="T19" s="15">
+        <v>0.90361445783132532</v>
+      </c>
+      <c r="U19" s="15">
+        <v>0.88235294117647056</v>
+      </c>
+      <c r="V19" s="15">
+        <v>0.88395904436860073</v>
+      </c>
+      <c r="W19" s="15"/>
+      <c r="X19" s="15"/>
+      <c r="Y19" s="15">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="Z19" s="15">
+        <v>0.91443850267379678</v>
+      </c>
+      <c r="AA19" s="15">
+        <v>0.96220930232558144</v>
+      </c>
+      <c r="AB19" s="15">
+        <v>0.96506550218340614</v>
+      </c>
+      <c r="AC19" s="15">
+        <v>0.93846153846153846</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -10600,91 +10647,91 @@
       <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="28">
+      <c r="C2" s="27">
         <v>2803</v>
       </c>
-      <c r="D2" s="28">
+      <c r="D2" s="27">
         <v>2183</v>
       </c>
-      <c r="E2" s="28">
+      <c r="E2" s="27">
         <v>620</v>
       </c>
-      <c r="F2" s="28">
+      <c r="F2" s="27">
         <v>644</v>
       </c>
-      <c r="G2" s="28">
+      <c r="G2" s="27">
         <v>93</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="27">
         <v>432</v>
       </c>
-      <c r="I2" s="28">
+      <c r="I2" s="27">
         <v>555</v>
       </c>
-      <c r="J2" s="28">
+      <c r="J2" s="27">
         <v>459</v>
       </c>
-      <c r="K2" s="28">
+      <c r="K2" s="27">
         <v>177</v>
       </c>
-      <c r="L2" s="28">
+      <c r="L2" s="27">
         <v>124</v>
       </c>
-      <c r="M2" s="28">
+      <c r="M2" s="27">
         <v>140</v>
       </c>
-      <c r="N2" s="28">
+      <c r="N2" s="27">
         <v>171</v>
       </c>
-      <c r="O2" s="28">
+      <c r="O2" s="27">
         <v>8</v>
       </c>
-      <c r="P2" s="28">
+      <c r="P2" s="27">
         <v>261</v>
       </c>
-      <c r="Q2" s="28">
+      <c r="Q2" s="27">
         <v>186</v>
       </c>
-      <c r="R2" s="28">
+      <c r="R2" s="27">
         <v>233</v>
       </c>
-      <c r="S2" s="28">
+      <c r="S2" s="27">
         <v>187</v>
       </c>
-      <c r="T2" s="28">
+      <c r="T2" s="27">
         <v>383</v>
       </c>
-      <c r="U2" s="28">
+      <c r="U2" s="27">
         <v>51</v>
       </c>
-      <c r="V2" s="28">
+      <c r="V2" s="27">
         <v>246</v>
       </c>
-      <c r="W2" s="28">
+      <c r="W2" s="27">
         <v>408</v>
       </c>
-      <c r="X2" s="28">
+      <c r="X2" s="27">
         <v>135</v>
       </c>
-      <c r="Y2" s="28">
+      <c r="Y2" s="27">
         <v>9</v>
       </c>
-      <c r="Z2" s="28">
+      <c r="Z2" s="27">
         <v>84</v>
       </c>
-      <c r="AA2" s="28">
+      <c r="AA2" s="27">
         <v>177</v>
       </c>
-      <c r="AB2" s="28">
+      <c r="AB2" s="27">
         <v>124</v>
       </c>
-      <c r="AC2" s="28">
+      <c r="AC2" s="27">
         <v>140</v>
       </c>
-      <c r="AD2" s="28">
+      <c r="AD2" s="27">
         <v>171</v>
       </c>
-      <c r="AE2" s="28">
+      <c r="AE2" s="27">
         <v>8</v>
       </c>
     </row>
@@ -10695,91 +10742,91 @@
       <c r="B3" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="28">
+      <c r="C3" s="27">
         <v>2577</v>
       </c>
-      <c r="D3" s="28">
+      <c r="D3" s="27">
         <v>2018</v>
       </c>
-      <c r="E3" s="28">
+      <c r="E3" s="27">
         <v>559</v>
       </c>
-      <c r="F3" s="28">
+      <c r="F3" s="27">
         <v>636</v>
       </c>
-      <c r="G3" s="28">
+      <c r="G3" s="27">
         <v>100</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="27">
         <v>369</v>
       </c>
-      <c r="I3" s="28">
+      <c r="I3" s="27">
         <v>520</v>
       </c>
-      <c r="J3" s="28">
+      <c r="J3" s="27">
         <v>393</v>
       </c>
-      <c r="K3" s="28">
+      <c r="K3" s="27">
         <v>174</v>
       </c>
-      <c r="L3" s="28">
+      <c r="L3" s="27">
         <v>111</v>
       </c>
-      <c r="M3" s="28">
+      <c r="M3" s="27">
         <v>127</v>
       </c>
-      <c r="N3" s="28">
+      <c r="N3" s="27">
         <v>137</v>
       </c>
-      <c r="O3" s="28">
+      <c r="O3" s="27">
         <v>10</v>
       </c>
-      <c r="P3" s="28">
+      <c r="P3" s="27">
         <v>266</v>
       </c>
-      <c r="Q3" s="28">
+      <c r="Q3" s="27">
         <v>160</v>
       </c>
-      <c r="R3" s="28">
+      <c r="R3" s="27">
         <v>195</v>
       </c>
-      <c r="S3" s="28">
+      <c r="S3" s="27">
         <v>197</v>
       </c>
-      <c r="T3" s="28">
+      <c r="T3" s="27">
         <v>370</v>
       </c>
-      <c r="U3" s="28">
+      <c r="U3" s="27">
         <v>52</v>
       </c>
-      <c r="V3" s="28">
+      <c r="V3" s="27">
         <v>209</v>
       </c>
-      <c r="W3" s="28">
+      <c r="W3" s="27">
         <v>341</v>
       </c>
-      <c r="X3" s="28">
+      <c r="X3" s="27">
         <v>128</v>
       </c>
-      <c r="Y3" s="28">
+      <c r="Y3" s="27">
         <v>10</v>
       </c>
-      <c r="Z3" s="28">
+      <c r="Z3" s="27">
         <v>90</v>
       </c>
-      <c r="AA3" s="28">
+      <c r="AA3" s="27">
         <v>174</v>
       </c>
-      <c r="AB3" s="28">
+      <c r="AB3" s="27">
         <v>111</v>
       </c>
-      <c r="AC3" s="28">
+      <c r="AC3" s="27">
         <v>127</v>
       </c>
-      <c r="AD3" s="28">
+      <c r="AD3" s="27">
         <v>137</v>
       </c>
-      <c r="AE3" s="28">
+      <c r="AE3" s="27">
         <v>10</v>
       </c>
     </row>
@@ -10790,91 +10837,91 @@
       <c r="B4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C4" s="28">
+      <c r="C4" s="27">
         <v>1757</v>
       </c>
-      <c r="D4" s="28">
+      <c r="D4" s="27">
         <v>1465</v>
       </c>
-      <c r="E4" s="28">
+      <c r="E4" s="27">
         <v>292</v>
       </c>
-      <c r="F4" s="28">
+      <c r="F4" s="27">
         <v>504</v>
       </c>
-      <c r="G4" s="28">
+      <c r="G4" s="27">
         <v>75</v>
       </c>
-      <c r="H4" s="28">
+      <c r="H4" s="27">
         <v>232</v>
       </c>
-      <c r="I4" s="28">
+      <c r="I4" s="27">
         <v>332</v>
       </c>
-      <c r="J4" s="28">
+      <c r="J4" s="27">
         <v>322</v>
       </c>
-      <c r="K4" s="28">
+      <c r="K4" s="27">
         <v>88</v>
       </c>
-      <c r="L4" s="28">
+      <c r="L4" s="27">
         <v>46</v>
       </c>
-      <c r="M4" s="28">
+      <c r="M4" s="27">
         <v>98</v>
       </c>
-      <c r="N4" s="28">
+      <c r="N4" s="27">
         <v>45</v>
       </c>
-      <c r="O4" s="28">
+      <c r="O4" s="27">
         <v>15</v>
       </c>
-      <c r="P4" s="28">
+      <c r="P4" s="27">
         <v>182</v>
       </c>
-      <c r="Q4" s="28">
+      <c r="Q4" s="27">
         <v>106</v>
       </c>
-      <c r="R4" s="28">
+      <c r="R4" s="27">
         <v>117</v>
       </c>
-      <c r="S4" s="28">
+      <c r="S4" s="27">
         <v>132</v>
       </c>
-      <c r="T4" s="28">
+      <c r="T4" s="27">
         <v>322</v>
       </c>
-      <c r="U4" s="28">
+      <c r="U4" s="27">
         <v>49</v>
       </c>
-      <c r="V4" s="28">
+      <c r="V4" s="27">
         <v>126</v>
       </c>
-      <c r="W4" s="28">
+      <c r="W4" s="27">
         <v>273</v>
       </c>
-      <c r="X4" s="28">
+      <c r="X4" s="27">
         <v>83</v>
       </c>
-      <c r="Y4" s="28">
+      <c r="Y4" s="27">
         <v>6</v>
       </c>
-      <c r="Z4" s="28">
+      <c r="Z4" s="27">
         <v>69</v>
       </c>
-      <c r="AA4" s="28">
+      <c r="AA4" s="27">
         <v>88</v>
       </c>
-      <c r="AB4" s="28">
+      <c r="AB4" s="27">
         <v>46</v>
       </c>
-      <c r="AC4" s="28">
+      <c r="AC4" s="27">
         <v>98</v>
       </c>
-      <c r="AD4" s="28">
+      <c r="AD4" s="27">
         <v>45</v>
       </c>
-      <c r="AE4" s="28">
+      <c r="AE4" s="27">
         <v>15</v>
       </c>
     </row>
@@ -10885,91 +10932,91 @@
       <c r="B5" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="28">
+      <c r="C5" s="27">
         <v>1423</v>
       </c>
-      <c r="D5" s="28">
+      <c r="D5" s="27">
         <v>1262</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <v>161</v>
       </c>
-      <c r="F5" s="28">
+      <c r="F5" s="27">
         <v>437</v>
       </c>
-      <c r="G5" s="28">
+      <c r="G5" s="27">
         <v>95</v>
       </c>
-      <c r="H5" s="28">
+      <c r="H5" s="27">
         <v>196</v>
       </c>
-      <c r="I5" s="28">
+      <c r="I5" s="27">
         <v>271</v>
       </c>
-      <c r="J5" s="28">
+      <c r="J5" s="27">
         <v>263</v>
       </c>
-      <c r="K5" s="28">
+      <c r="K5" s="27">
         <v>50</v>
       </c>
-      <c r="L5" s="28">
+      <c r="L5" s="27">
         <v>15</v>
       </c>
-      <c r="M5" s="28">
+      <c r="M5" s="27">
         <v>63</v>
       </c>
-      <c r="N5" s="28">
+      <c r="N5" s="27">
         <v>26</v>
       </c>
-      <c r="O5" s="28">
+      <c r="O5" s="27">
         <v>7</v>
       </c>
-      <c r="P5" s="28">
+      <c r="P5" s="27">
         <v>148</v>
       </c>
-      <c r="Q5" s="28">
+      <c r="Q5" s="27">
         <v>93</v>
       </c>
-      <c r="R5" s="28">
+      <c r="R5" s="27">
         <v>83</v>
       </c>
-      <c r="S5" s="28">
+      <c r="S5" s="27">
         <v>156</v>
       </c>
-      <c r="T5" s="28">
+      <c r="T5" s="27">
         <v>289</v>
       </c>
-      <c r="U5" s="28">
+      <c r="U5" s="27">
         <v>137</v>
       </c>
-      <c r="V5" s="28">
+      <c r="V5" s="27">
         <v>103</v>
       </c>
-      <c r="W5" s="28">
+      <c r="W5" s="27">
         <v>126</v>
       </c>
-      <c r="X5" s="28">
+      <c r="X5" s="27">
         <v>32</v>
       </c>
-      <c r="Y5" s="28">
+      <c r="Y5" s="27">
         <v>25</v>
       </c>
-      <c r="Z5" s="28">
+      <c r="Z5" s="27">
         <v>70</v>
       </c>
-      <c r="AA5" s="28">
+      <c r="AA5" s="27">
         <v>50</v>
       </c>
-      <c r="AB5" s="28">
+      <c r="AB5" s="27">
         <v>15</v>
       </c>
-      <c r="AC5" s="28">
+      <c r="AC5" s="27">
         <v>63</v>
       </c>
-      <c r="AD5" s="28">
+      <c r="AD5" s="27">
         <v>26</v>
       </c>
-      <c r="AE5" s="28">
+      <c r="AE5" s="27">
         <v>7</v>
       </c>
     </row>
@@ -10980,91 +11027,91 @@
       <c r="B6" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="28">
+      <c r="C6" s="27">
         <v>2391</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="27">
         <v>1733</v>
       </c>
-      <c r="E6" s="28">
+      <c r="E6" s="27">
         <v>658</v>
       </c>
-      <c r="F6" s="28">
+      <c r="F6" s="27">
         <v>533</v>
       </c>
-      <c r="G6" s="28">
+      <c r="G6" s="27">
         <v>101</v>
       </c>
-      <c r="H6" s="28">
+      <c r="H6" s="27">
         <v>296</v>
       </c>
-      <c r="I6" s="28">
+      <c r="I6" s="27">
         <v>398</v>
       </c>
-      <c r="J6" s="28">
+      <c r="J6" s="27">
         <v>405</v>
       </c>
-      <c r="K6" s="28">
+      <c r="K6" s="27">
         <v>234</v>
       </c>
-      <c r="L6" s="28">
+      <c r="L6" s="27">
         <v>121</v>
       </c>
-      <c r="M6" s="28">
+      <c r="M6" s="27">
         <v>184</v>
       </c>
-      <c r="N6" s="28">
+      <c r="N6" s="27">
         <v>107</v>
       </c>
-      <c r="O6" s="28">
+      <c r="O6" s="27">
         <v>12</v>
       </c>
-      <c r="P6" s="28">
+      <c r="P6" s="27">
         <v>180</v>
       </c>
-      <c r="Q6" s="28">
+      <c r="Q6" s="27">
         <v>110</v>
       </c>
-      <c r="R6" s="28">
+      <c r="R6" s="27">
         <v>145</v>
       </c>
-      <c r="S6" s="28">
+      <c r="S6" s="27">
         <v>172</v>
       </c>
-      <c r="T6" s="28">
+      <c r="T6" s="27">
         <v>353</v>
       </c>
-      <c r="U6" s="28">
+      <c r="U6" s="27">
         <v>58</v>
       </c>
-      <c r="V6" s="28">
+      <c r="V6" s="27">
         <v>186</v>
       </c>
-      <c r="W6" s="28">
+      <c r="W6" s="27">
         <v>347</v>
       </c>
-      <c r="X6" s="28">
+      <c r="X6" s="27">
         <v>81</v>
       </c>
-      <c r="Y6" s="28">
+      <c r="Y6" s="27">
         <v>10</v>
       </c>
-      <c r="Z6" s="28">
+      <c r="Z6" s="27">
         <v>91</v>
       </c>
-      <c r="AA6" s="28">
+      <c r="AA6" s="27">
         <v>234</v>
       </c>
-      <c r="AB6" s="28">
+      <c r="AB6" s="27">
         <v>121</v>
       </c>
-      <c r="AC6" s="28">
+      <c r="AC6" s="27">
         <v>184</v>
       </c>
-      <c r="AD6" s="28">
+      <c r="AD6" s="27">
         <v>107</v>
       </c>
-      <c r="AE6" s="28">
+      <c r="AE6" s="27">
         <v>12</v>
       </c>
     </row>
@@ -11075,89 +11122,89 @@
       <c r="B7" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="28">
+      <c r="C7" s="27">
         <v>2026</v>
       </c>
-      <c r="D7" s="28">
+      <c r="D7" s="27">
         <v>1514</v>
       </c>
-      <c r="E7" s="28">
+      <c r="E7" s="27">
         <v>512</v>
       </c>
-      <c r="F7" s="28">
+      <c r="F7" s="27">
         <v>456</v>
       </c>
-      <c r="G7" s="28">
+      <c r="G7" s="27">
         <v>98</v>
       </c>
-      <c r="H7" s="28">
+      <c r="H7" s="27">
         <v>267</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="27">
         <v>298</v>
       </c>
-      <c r="J7" s="28">
+      <c r="J7" s="27">
         <v>395</v>
       </c>
-      <c r="K7" s="28">
+      <c r="K7" s="27">
         <v>228</v>
       </c>
-      <c r="L7" s="28">
+      <c r="L7" s="27">
         <v>72</v>
       </c>
-      <c r="M7" s="28">
+      <c r="M7" s="27">
         <v>135</v>
       </c>
-      <c r="N7" s="28">
+      <c r="N7" s="27">
         <v>64</v>
       </c>
-      <c r="O7" s="28">
+      <c r="O7" s="27">
         <v>13</v>
       </c>
-      <c r="P7" s="28">
+      <c r="P7" s="27">
         <v>143</v>
       </c>
-      <c r="Q7" s="28">
+      <c r="Q7" s="27">
         <v>82</v>
       </c>
-      <c r="R7" s="28">
+      <c r="R7" s="27">
         <v>91</v>
       </c>
-      <c r="S7" s="28">
+      <c r="S7" s="27">
         <v>132</v>
       </c>
-      <c r="T7" s="28">
+      <c r="T7" s="27">
         <v>313</v>
       </c>
-      <c r="U7" s="28">
+      <c r="U7" s="27">
         <v>62</v>
       </c>
-      <c r="V7" s="28">
+      <c r="V7" s="27">
         <v>185</v>
       </c>
-      <c r="W7" s="28">
+      <c r="W7" s="27">
         <v>333</v>
       </c>
-      <c r="X7" s="28">
+      <c r="X7" s="27">
         <v>75</v>
       </c>
-      <c r="Y7" s="28"/>
-      <c r="Z7" s="28">
+      <c r="Y7" s="27"/>
+      <c r="Z7" s="27">
         <v>98</v>
       </c>
-      <c r="AA7" s="28">
+      <c r="AA7" s="27">
         <v>228</v>
       </c>
-      <c r="AB7" s="28">
+      <c r="AB7" s="27">
         <v>72</v>
       </c>
-      <c r="AC7" s="28">
+      <c r="AC7" s="27">
         <v>135</v>
       </c>
-      <c r="AD7" s="28">
+      <c r="AD7" s="27">
         <v>64</v>
       </c>
-      <c r="AE7" s="28">
+      <c r="AE7" s="27">
         <v>13</v>
       </c>
     </row>
@@ -11168,87 +11215,87 @@
       <c r="B8" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="C8" s="28">
+      <c r="C8" s="27">
         <v>1915</v>
       </c>
-      <c r="D8" s="28">
+      <c r="D8" s="27">
         <v>1323</v>
       </c>
-      <c r="E8" s="28">
+      <c r="E8" s="27">
         <v>592</v>
       </c>
-      <c r="F8" s="28">
+      <c r="F8" s="27">
         <v>398</v>
       </c>
-      <c r="G8" s="28">
+      <c r="G8" s="27">
         <v>0</v>
       </c>
-      <c r="H8" s="28">
+      <c r="H8" s="27">
         <v>271</v>
       </c>
-      <c r="I8" s="28">
+      <c r="I8" s="27">
         <v>254</v>
       </c>
-      <c r="J8" s="28">
+      <c r="J8" s="27">
         <v>400</v>
       </c>
-      <c r="K8" s="28">
+      <c r="K8" s="27">
         <v>277</v>
       </c>
-      <c r="L8" s="28">
+      <c r="L8" s="27">
         <v>83</v>
       </c>
-      <c r="M8" s="28">
+      <c r="M8" s="27">
         <v>125</v>
       </c>
-      <c r="N8" s="28">
+      <c r="N8" s="27">
         <v>93</v>
       </c>
-      <c r="O8" s="28">
+      <c r="O8" s="27">
         <v>14</v>
       </c>
-      <c r="P8" s="28">
+      <c r="P8" s="27">
         <v>126</v>
       </c>
-      <c r="Q8" s="28">
+      <c r="Q8" s="27">
         <v>109</v>
       </c>
-      <c r="R8" s="28">
+      <c r="R8" s="27">
         <v>87</v>
       </c>
-      <c r="S8" s="28">
+      <c r="S8" s="27">
         <v>117</v>
       </c>
-      <c r="T8" s="28">
+      <c r="T8" s="27">
         <v>272</v>
       </c>
-      <c r="U8" s="28">
+      <c r="U8" s="27">
         <v>51</v>
       </c>
-      <c r="V8" s="28">
+      <c r="V8" s="27">
         <v>162</v>
       </c>
-      <c r="W8" s="28">
+      <c r="W8" s="27">
         <v>349</v>
       </c>
-      <c r="X8" s="28">
+      <c r="X8" s="27">
         <v>50</v>
       </c>
-      <c r="Y8" s="28"/>
-      <c r="Z8" s="28"/>
-      <c r="AA8" s="28">
+      <c r="Y8" s="27"/>
+      <c r="Z8" s="27"/>
+      <c r="AA8" s="27">
         <v>277</v>
       </c>
-      <c r="AB8" s="28">
+      <c r="AB8" s="27">
         <v>83</v>
       </c>
-      <c r="AC8" s="28">
+      <c r="AC8" s="27">
         <v>125</v>
       </c>
-      <c r="AD8" s="28">
+      <c r="AD8" s="27">
         <v>93</v>
       </c>
-      <c r="AE8" s="28">
+      <c r="AE8" s="27">
         <v>14</v>
       </c>
     </row>
@@ -11259,87 +11306,87 @@
       <c r="B9" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="28">
+      <c r="C9" s="27">
         <v>1714</v>
       </c>
-      <c r="D9" s="28">
+      <c r="D9" s="27">
         <v>1259</v>
       </c>
-      <c r="E9" s="28">
+      <c r="E9" s="27">
         <v>455</v>
       </c>
-      <c r="F9" s="28">
+      <c r="F9" s="27">
         <v>359</v>
       </c>
-      <c r="G9" s="28">
+      <c r="G9" s="27">
         <v>0</v>
       </c>
-      <c r="H9" s="28">
+      <c r="H9" s="27">
         <v>250</v>
       </c>
-      <c r="I9" s="28">
+      <c r="I9" s="27">
         <v>188</v>
       </c>
-      <c r="J9" s="28">
+      <c r="J9" s="27">
         <v>462</v>
       </c>
-      <c r="K9" s="28">
+      <c r="K9" s="27">
         <v>222</v>
       </c>
-      <c r="L9" s="28">
+      <c r="L9" s="27">
         <v>73</v>
       </c>
-      <c r="M9" s="28">
+      <c r="M9" s="27">
         <v>96</v>
       </c>
-      <c r="N9" s="28">
+      <c r="N9" s="27">
         <v>55</v>
       </c>
-      <c r="O9" s="28">
+      <c r="O9" s="27">
         <v>9</v>
       </c>
-      <c r="P9" s="28">
+      <c r="P9" s="27">
         <v>109</v>
       </c>
-      <c r="Q9" s="28">
+      <c r="Q9" s="27">
         <v>92</v>
       </c>
-      <c r="R9" s="28">
+      <c r="R9" s="27">
         <v>71</v>
       </c>
-      <c r="S9" s="28">
+      <c r="S9" s="27">
         <v>78</v>
       </c>
-      <c r="T9" s="28">
+      <c r="T9" s="27">
         <v>250</v>
       </c>
-      <c r="U9" s="28">
+      <c r="U9" s="27">
         <v>58</v>
       </c>
-      <c r="V9" s="28">
+      <c r="V9" s="27">
         <v>158</v>
       </c>
-      <c r="W9" s="28">
+      <c r="W9" s="27">
         <v>404</v>
       </c>
-      <c r="X9" s="28">
+      <c r="X9" s="27">
         <v>39</v>
       </c>
-      <c r="Y9" s="28"/>
-      <c r="Z9" s="28"/>
-      <c r="AA9" s="28">
+      <c r="Y9" s="27"/>
+      <c r="Z9" s="27"/>
+      <c r="AA9" s="27">
         <v>222</v>
       </c>
-      <c r="AB9" s="28">
+      <c r="AB9" s="27">
         <v>73</v>
       </c>
-      <c r="AC9" s="28">
+      <c r="AC9" s="27">
         <v>96</v>
       </c>
-      <c r="AD9" s="28">
+      <c r="AD9" s="27">
         <v>55</v>
       </c>
-      <c r="AE9" s="28">
+      <c r="AE9" s="27">
         <v>9</v>
       </c>
     </row>
@@ -11350,87 +11397,87 @@
       <c r="B10" s="7" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="28">
+      <c r="C10" s="27">
         <v>1906</v>
       </c>
-      <c r="D10" s="28">
+      <c r="D10" s="27">
         <v>1394</v>
       </c>
-      <c r="E10" s="28">
+      <c r="E10" s="27">
         <v>512</v>
       </c>
-      <c r="F10" s="28">
+      <c r="F10" s="27">
         <v>400</v>
       </c>
-      <c r="G10" s="28">
+      <c r="G10" s="27">
         <v>0</v>
       </c>
-      <c r="H10" s="28">
+      <c r="H10" s="27">
         <v>239</v>
       </c>
-      <c r="I10" s="28">
+      <c r="I10" s="27">
         <v>207</v>
       </c>
-      <c r="J10" s="28">
+      <c r="J10" s="27">
         <v>548</v>
       </c>
-      <c r="K10" s="28">
+      <c r="K10" s="27">
         <v>229</v>
       </c>
-      <c r="L10" s="28">
+      <c r="L10" s="27">
         <v>97</v>
       </c>
-      <c r="M10" s="28">
+      <c r="M10" s="27">
         <v>92</v>
       </c>
-      <c r="N10" s="28">
+      <c r="N10" s="27">
         <v>74</v>
       </c>
-      <c r="O10" s="28">
+      <c r="O10" s="27">
         <v>20</v>
       </c>
-      <c r="P10" s="28">
+      <c r="P10" s="27">
         <v>109</v>
       </c>
-      <c r="Q10" s="28">
+      <c r="Q10" s="27">
         <v>100</v>
       </c>
-      <c r="R10" s="28">
+      <c r="R10" s="27">
         <v>63</v>
       </c>
-      <c r="S10" s="28">
+      <c r="S10" s="27">
         <v>102</v>
       </c>
-      <c r="T10" s="28">
+      <c r="T10" s="27">
         <v>291</v>
       </c>
-      <c r="U10" s="28">
+      <c r="U10" s="27">
         <v>60</v>
       </c>
-      <c r="V10" s="28">
+      <c r="V10" s="27">
         <v>139</v>
       </c>
-      <c r="W10" s="28">
+      <c r="W10" s="27">
         <v>488</v>
       </c>
-      <c r="X10" s="28">
+      <c r="X10" s="27">
         <v>42</v>
       </c>
-      <c r="Y10" s="28"/>
-      <c r="Z10" s="28"/>
-      <c r="AA10" s="28">
+      <c r="Y10" s="27"/>
+      <c r="Z10" s="27"/>
+      <c r="AA10" s="27">
         <v>229</v>
       </c>
-      <c r="AB10" s="28">
+      <c r="AB10" s="27">
         <v>97</v>
       </c>
-      <c r="AC10" s="28">
+      <c r="AC10" s="27">
         <v>92</v>
       </c>
-      <c r="AD10" s="28">
+      <c r="AD10" s="27">
         <v>74</v>
       </c>
-      <c r="AE10" s="28">
+      <c r="AE10" s="27">
         <v>20</v>
       </c>
     </row>
@@ -11441,87 +11488,87 @@
       <c r="B11" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="28">
+      <c r="C11" s="27">
         <v>9118</v>
       </c>
-      <c r="D11" s="28">
+      <c r="D11" s="27">
         <v>5270</v>
       </c>
-      <c r="E11" s="28">
+      <c r="E11" s="27">
         <v>3848</v>
       </c>
-      <c r="F11" s="28">
+      <c r="F11" s="27">
         <v>1277</v>
       </c>
-      <c r="G11" s="28">
+      <c r="G11" s="27">
         <v>0</v>
       </c>
-      <c r="H11" s="28">
+      <c r="H11" s="27">
         <v>1022</v>
       </c>
-      <c r="I11" s="28">
+      <c r="I11" s="27">
         <v>1467</v>
       </c>
-      <c r="J11" s="28">
+      <c r="J11" s="27">
         <v>1504</v>
       </c>
-      <c r="K11" s="28">
+      <c r="K11" s="27">
         <v>1182</v>
       </c>
-      <c r="L11" s="28">
+      <c r="L11" s="27">
         <v>503</v>
       </c>
-      <c r="M11" s="28">
+      <c r="M11" s="27">
         <v>853</v>
       </c>
-      <c r="N11" s="28">
+      <c r="N11" s="27">
         <v>1176</v>
       </c>
-      <c r="O11" s="28">
+      <c r="O11" s="27">
         <v>134</v>
       </c>
-      <c r="P11" s="28">
+      <c r="P11" s="27">
         <v>428</v>
       </c>
-      <c r="Q11" s="28">
+      <c r="Q11" s="27">
         <v>371</v>
       </c>
-      <c r="R11" s="28">
+      <c r="R11" s="27">
         <v>482</v>
       </c>
-      <c r="S11" s="28">
+      <c r="S11" s="27">
         <v>750</v>
       </c>
-      <c r="T11" s="28">
+      <c r="T11" s="27">
         <v>849</v>
       </c>
-      <c r="U11" s="28">
+      <c r="U11" s="27">
         <v>74</v>
       </c>
-      <c r="V11" s="28">
+      <c r="V11" s="27">
         <v>651</v>
       </c>
-      <c r="W11" s="28">
+      <c r="W11" s="27">
         <v>1430</v>
       </c>
-      <c r="X11" s="28">
+      <c r="X11" s="27">
         <v>235</v>
       </c>
-      <c r="Y11" s="28"/>
-      <c r="Z11" s="28"/>
-      <c r="AA11" s="28">
+      <c r="Y11" s="27"/>
+      <c r="Z11" s="27"/>
+      <c r="AA11" s="27">
         <v>1182</v>
       </c>
-      <c r="AB11" s="28">
+      <c r="AB11" s="27">
         <v>503</v>
       </c>
-      <c r="AC11" s="28">
+      <c r="AC11" s="27">
         <v>853</v>
       </c>
-      <c r="AD11" s="28">
+      <c r="AD11" s="27">
         <v>1176</v>
       </c>
-      <c r="AE11" s="28">
+      <c r="AE11" s="27">
         <v>134</v>
       </c>
     </row>
@@ -11532,87 +11579,87 @@
       <c r="B12" s="7" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="28">
+      <c r="C12" s="27">
         <v>12756</v>
       </c>
-      <c r="D12" s="28">
+      <c r="D12" s="27">
         <v>7302</v>
       </c>
-      <c r="E12" s="28">
+      <c r="E12" s="27">
         <v>5454</v>
       </c>
-      <c r="F12" s="28">
+      <c r="F12" s="27">
         <v>1766</v>
       </c>
-      <c r="G12" s="28">
+      <c r="G12" s="27">
         <v>0</v>
       </c>
-      <c r="H12" s="28">
+      <c r="H12" s="27">
         <v>1554</v>
       </c>
-      <c r="I12" s="28">
+      <c r="I12" s="27">
         <v>2245</v>
       </c>
-      <c r="J12" s="28">
+      <c r="J12" s="27">
         <v>1737</v>
       </c>
-      <c r="K12" s="28">
+      <c r="K12" s="27">
         <v>1605</v>
       </c>
-      <c r="L12" s="28">
+      <c r="L12" s="27">
         <v>759</v>
       </c>
-      <c r="M12" s="28">
+      <c r="M12" s="27">
         <v>1185</v>
       </c>
-      <c r="N12" s="28">
+      <c r="N12" s="27">
         <v>1639</v>
       </c>
-      <c r="O12" s="28">
+      <c r="O12" s="27">
         <v>266</v>
       </c>
-      <c r="P12" s="28">
+      <c r="P12" s="27">
         <v>627</v>
       </c>
-      <c r="Q12" s="28">
+      <c r="Q12" s="27">
         <v>616</v>
       </c>
-      <c r="R12" s="28">
+      <c r="R12" s="27">
         <v>602</v>
       </c>
-      <c r="S12" s="28">
+      <c r="S12" s="27">
         <v>1191</v>
       </c>
-      <c r="T12" s="28">
+      <c r="T12" s="27">
         <v>1139</v>
       </c>
-      <c r="U12" s="28">
+      <c r="U12" s="27">
         <v>119</v>
       </c>
-      <c r="V12" s="28">
+      <c r="V12" s="27">
         <v>938</v>
       </c>
-      <c r="W12" s="28">
+      <c r="W12" s="27">
         <v>1618</v>
       </c>
-      <c r="X12" s="28">
+      <c r="X12" s="27">
         <v>452</v>
       </c>
-      <c r="Y12" s="28"/>
-      <c r="Z12" s="28"/>
-      <c r="AA12" s="28">
+      <c r="Y12" s="27"/>
+      <c r="Z12" s="27"/>
+      <c r="AA12" s="27">
         <v>1605</v>
       </c>
-      <c r="AB12" s="28">
+      <c r="AB12" s="27">
         <v>759</v>
       </c>
-      <c r="AC12" s="28">
+      <c r="AC12" s="27">
         <v>1185</v>
       </c>
-      <c r="AD12" s="28">
+      <c r="AD12" s="27">
         <v>1639</v>
       </c>
-      <c r="AE12" s="28">
+      <c r="AE12" s="27">
         <v>266</v>
       </c>
     </row>
@@ -11623,87 +11670,87 @@
       <c r="B13" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="C13" s="28">
+      <c r="C13" s="27">
         <v>23744</v>
       </c>
-      <c r="D13" s="28">
+      <c r="D13" s="27">
         <v>10789</v>
       </c>
-      <c r="E13" s="28">
+      <c r="E13" s="27">
         <v>12955</v>
       </c>
-      <c r="F13" s="28">
+      <c r="F13" s="27">
         <v>2564</v>
       </c>
-      <c r="G13" s="28">
+      <c r="G13" s="27">
         <v>0</v>
       </c>
-      <c r="H13" s="28">
+      <c r="H13" s="27">
         <v>2419</v>
       </c>
-      <c r="I13" s="28">
+      <c r="I13" s="27">
         <v>3320</v>
       </c>
-      <c r="J13" s="28">
+      <c r="J13" s="27">
         <v>2486</v>
       </c>
-      <c r="K13" s="28">
+      <c r="K13" s="27">
         <v>3429</v>
       </c>
-      <c r="L13" s="28">
+      <c r="L13" s="27">
         <v>2336</v>
       </c>
-      <c r="M13" s="28">
+      <c r="M13" s="27">
         <v>3645</v>
       </c>
-      <c r="N13" s="28">
+      <c r="N13" s="27">
         <v>2781</v>
       </c>
-      <c r="O13" s="28">
+      <c r="O13" s="27">
         <v>764</v>
       </c>
-      <c r="P13" s="28">
+      <c r="P13" s="27">
         <v>859</v>
       </c>
-      <c r="Q13" s="28">
+      <c r="Q13" s="27">
         <v>937</v>
       </c>
-      <c r="R13" s="28">
+      <c r="R13" s="27">
         <v>759</v>
       </c>
-      <c r="S13" s="28">
+      <c r="S13" s="27">
         <v>1840</v>
       </c>
-      <c r="T13" s="28">
+      <c r="T13" s="27">
         <v>1705</v>
       </c>
-      <c r="U13" s="28">
+      <c r="U13" s="27">
         <v>376</v>
       </c>
-      <c r="V13" s="28">
+      <c r="V13" s="27">
         <v>1482</v>
       </c>
-      <c r="W13" s="28">
+      <c r="W13" s="27">
         <v>2110</v>
       </c>
-      <c r="X13" s="28">
+      <c r="X13" s="27">
         <v>721</v>
       </c>
-      <c r="Y13" s="28"/>
-      <c r="Z13" s="28"/>
-      <c r="AA13" s="28">
+      <c r="Y13" s="27"/>
+      <c r="Z13" s="27"/>
+      <c r="AA13" s="27">
         <v>3429</v>
       </c>
-      <c r="AB13" s="28">
+      <c r="AB13" s="27">
         <v>2336</v>
       </c>
-      <c r="AC13" s="28">
+      <c r="AC13" s="27">
         <v>3645</v>
       </c>
-      <c r="AD13" s="28">
+      <c r="AD13" s="27">
         <v>2781</v>
       </c>
-      <c r="AE13" s="28">
+      <c r="AE13" s="27">
         <v>764</v>
       </c>
     </row>
@@ -11714,87 +11761,87 @@
       <c r="B14" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C14" s="28">
+      <c r="C14" s="27">
         <v>27869</v>
       </c>
-      <c r="D14" s="28">
+      <c r="D14" s="27">
         <v>14225</v>
       </c>
-      <c r="E14" s="28">
+      <c r="E14" s="27">
         <v>13644</v>
       </c>
-      <c r="F14" s="28">
+      <c r="F14" s="27">
         <v>3208</v>
       </c>
-      <c r="G14" s="28">
+      <c r="G14" s="27">
         <v>0</v>
       </c>
-      <c r="H14" s="28">
+      <c r="H14" s="27">
         <v>3220</v>
       </c>
-      <c r="I14" s="28">
+      <c r="I14" s="27">
         <v>4547</v>
       </c>
-      <c r="J14" s="28">
+      <c r="J14" s="27">
         <v>3250</v>
       </c>
-      <c r="K14" s="28">
+      <c r="K14" s="27">
         <v>3662</v>
       </c>
-      <c r="L14" s="28">
+      <c r="L14" s="27">
         <v>2374</v>
       </c>
-      <c r="M14" s="28">
+      <c r="M14" s="27">
         <v>3720</v>
       </c>
-      <c r="N14" s="28">
+      <c r="N14" s="27">
         <v>3171</v>
       </c>
-      <c r="O14" s="28">
+      <c r="O14" s="27">
         <v>717</v>
       </c>
-      <c r="P14" s="28">
+      <c r="P14" s="27">
         <v>1169</v>
       </c>
-      <c r="Q14" s="28">
+      <c r="Q14" s="27">
         <v>1179</v>
       </c>
-      <c r="R14" s="28">
+      <c r="R14" s="27">
         <v>1375</v>
       </c>
-      <c r="S14" s="28">
+      <c r="S14" s="27">
         <v>2232</v>
       </c>
-      <c r="T14" s="28">
+      <c r="T14" s="27">
         <v>2039</v>
       </c>
-      <c r="U14" s="28">
+      <c r="U14" s="27">
         <v>584</v>
       </c>
-      <c r="V14" s="28">
+      <c r="V14" s="27">
         <v>2041</v>
       </c>
-      <c r="W14" s="28">
+      <c r="W14" s="27">
         <v>2666</v>
       </c>
-      <c r="X14" s="28">
+      <c r="X14" s="27">
         <v>940</v>
       </c>
-      <c r="Y14" s="28"/>
-      <c r="Z14" s="28"/>
-      <c r="AA14" s="28">
+      <c r="Y14" s="27"/>
+      <c r="Z14" s="27"/>
+      <c r="AA14" s="27">
         <v>3662</v>
       </c>
-      <c r="AB14" s="28">
+      <c r="AB14" s="27">
         <v>2374</v>
       </c>
-      <c r="AC14" s="28">
+      <c r="AC14" s="27">
         <v>3720</v>
       </c>
-      <c r="AD14" s="28">
+      <c r="AD14" s="27">
         <v>3171</v>
       </c>
-      <c r="AE14" s="28">
+      <c r="AE14" s="27">
         <v>717</v>
       </c>
     </row>
@@ -11805,87 +11852,87 @@
       <c r="B15" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C15" s="28">
+      <c r="C15" s="27">
         <v>27458</v>
       </c>
-      <c r="D15" s="28">
+      <c r="D15" s="27">
         <v>14237</v>
       </c>
-      <c r="E15" s="28">
+      <c r="E15" s="27">
         <v>13221</v>
       </c>
-      <c r="F15" s="28">
+      <c r="F15" s="27">
         <v>3356</v>
       </c>
-      <c r="G15" s="28">
+      <c r="G15" s="27">
         <v>0</v>
       </c>
-      <c r="H15" s="28">
+      <c r="H15" s="27">
         <v>3335</v>
       </c>
-      <c r="I15" s="28">
+      <c r="I15" s="27">
         <v>4389</v>
       </c>
-      <c r="J15" s="28">
+      <c r="J15" s="27">
         <v>3157</v>
       </c>
-      <c r="K15" s="28">
+      <c r="K15" s="27">
         <v>3329</v>
       </c>
-      <c r="L15" s="28">
+      <c r="L15" s="27">
         <v>2328</v>
       </c>
-      <c r="M15" s="28">
+      <c r="M15" s="27">
         <v>3603</v>
       </c>
-      <c r="N15" s="28">
+      <c r="N15" s="27">
         <v>3299</v>
       </c>
-      <c r="O15" s="28">
+      <c r="O15" s="27">
         <v>662</v>
       </c>
-      <c r="P15" s="28">
+      <c r="P15" s="27">
         <v>1218</v>
       </c>
-      <c r="Q15" s="28">
+      <c r="Q15" s="27">
         <v>1119</v>
       </c>
-      <c r="R15" s="28">
+      <c r="R15" s="27">
         <v>1330</v>
       </c>
-      <c r="S15" s="28">
+      <c r="S15" s="27">
         <v>2200</v>
       </c>
-      <c r="T15" s="28">
+      <c r="T15" s="27">
         <v>2138</v>
       </c>
-      <c r="U15" s="28">
+      <c r="U15" s="27">
         <v>599</v>
       </c>
-      <c r="V15" s="28">
+      <c r="V15" s="27">
         <v>2216</v>
       </c>
-      <c r="W15" s="28">
+      <c r="W15" s="27">
         <v>2558</v>
       </c>
-      <c r="X15" s="28">
+      <c r="X15" s="27">
         <v>859</v>
       </c>
-      <c r="Y15" s="28"/>
-      <c r="Z15" s="28"/>
-      <c r="AA15" s="28">
+      <c r="Y15" s="27"/>
+      <c r="Z15" s="27"/>
+      <c r="AA15" s="27">
         <v>3329</v>
       </c>
-      <c r="AB15" s="28">
+      <c r="AB15" s="27">
         <v>2328</v>
       </c>
-      <c r="AC15" s="28">
+      <c r="AC15" s="27">
         <v>3603</v>
       </c>
-      <c r="AD15" s="28">
+      <c r="AD15" s="27">
         <v>3299</v>
       </c>
-      <c r="AE15" s="28">
+      <c r="AE15" s="27">
         <v>662</v>
       </c>
     </row>
@@ -11896,87 +11943,87 @@
       <c r="B16" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="C16" s="28">
+      <c r="C16" s="27">
         <v>26616</v>
       </c>
-      <c r="D16" s="28">
+      <c r="D16" s="27">
         <v>14596</v>
       </c>
-      <c r="E16" s="28">
+      <c r="E16" s="27">
         <v>12020</v>
       </c>
-      <c r="F16" s="28">
+      <c r="F16" s="27">
         <v>3553</v>
       </c>
-      <c r="G16" s="28">
+      <c r="G16" s="27">
         <v>0</v>
       </c>
-      <c r="H16" s="28">
+      <c r="H16" s="27">
         <v>3262</v>
       </c>
-      <c r="I16" s="28">
+      <c r="I16" s="27">
         <v>4483</v>
       </c>
-      <c r="J16" s="28">
+      <c r="J16" s="27">
         <v>3298</v>
       </c>
-      <c r="K16" s="28">
+      <c r="K16" s="27">
         <v>2846</v>
       </c>
-      <c r="L16" s="28">
+      <c r="L16" s="27">
         <v>2295</v>
       </c>
-      <c r="M16" s="28">
+      <c r="M16" s="27">
         <v>3256</v>
       </c>
-      <c r="N16" s="28">
+      <c r="N16" s="27">
         <v>2965</v>
       </c>
-      <c r="O16" s="28">
+      <c r="O16" s="27">
         <v>658</v>
       </c>
-      <c r="P16" s="28">
+      <c r="P16" s="27">
         <v>1292</v>
       </c>
-      <c r="Q16" s="28">
+      <c r="Q16" s="27">
         <v>1018</v>
       </c>
-      <c r="R16" s="28">
+      <c r="R16" s="27">
         <v>1320</v>
       </c>
-      <c r="S16" s="28">
+      <c r="S16" s="27">
         <v>2307</v>
       </c>
-      <c r="T16" s="28">
+      <c r="T16" s="27">
         <v>2261</v>
       </c>
-      <c r="U16" s="28">
+      <c r="U16" s="27">
         <v>639</v>
       </c>
-      <c r="V16" s="28">
+      <c r="V16" s="27">
         <v>2244</v>
       </c>
-      <c r="W16" s="28">
+      <c r="W16" s="27">
         <v>2659</v>
       </c>
-      <c r="X16" s="28">
+      <c r="X16" s="27">
         <v>856</v>
       </c>
-      <c r="Y16" s="28"/>
-      <c r="Z16" s="28"/>
-      <c r="AA16" s="28">
+      <c r="Y16" s="27"/>
+      <c r="Z16" s="27"/>
+      <c r="AA16" s="27">
         <v>2846</v>
       </c>
-      <c r="AB16" s="28">
+      <c r="AB16" s="27">
         <v>2295</v>
       </c>
-      <c r="AC16" s="28">
+      <c r="AC16" s="27">
         <v>3256</v>
       </c>
-      <c r="AD16" s="28">
+      <c r="AD16" s="27">
         <v>2965</v>
       </c>
-      <c r="AE16" s="28">
+      <c r="AE16" s="27">
         <v>658</v>
       </c>
     </row>
@@ -11987,87 +12034,87 @@
       <c r="B17" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="27">
         <v>8318</v>
       </c>
-      <c r="D17" s="28">
+      <c r="D17" s="27">
         <v>5608</v>
       </c>
-      <c r="E17" s="28">
+      <c r="E17" s="27">
         <v>2710</v>
       </c>
-      <c r="F17" s="28">
+      <c r="F17" s="27">
         <v>1514</v>
       </c>
-      <c r="G17" s="28">
+      <c r="G17" s="27">
         <v>0</v>
       </c>
-      <c r="H17" s="28">
+      <c r="H17" s="27">
         <v>1186</v>
       </c>
-      <c r="I17" s="28">
+      <c r="I17" s="27">
         <v>1590</v>
       </c>
-      <c r="J17" s="28">
+      <c r="J17" s="27">
         <v>1318</v>
       </c>
-      <c r="K17" s="28">
+      <c r="K17" s="27">
         <v>900</v>
       </c>
-      <c r="L17" s="28">
+      <c r="L17" s="27">
         <v>523</v>
       </c>
-      <c r="M17" s="28">
+      <c r="M17" s="27">
         <v>572</v>
       </c>
-      <c r="N17" s="28">
+      <c r="N17" s="27">
         <v>598</v>
       </c>
-      <c r="O17" s="28">
+      <c r="O17" s="27">
         <v>117</v>
       </c>
-      <c r="P17" s="28">
+      <c r="P17" s="27">
         <v>452</v>
       </c>
-      <c r="Q17" s="28">
+      <c r="Q17" s="27">
         <v>365</v>
       </c>
-      <c r="R17" s="28">
+      <c r="R17" s="27">
         <v>432</v>
       </c>
-      <c r="S17" s="28">
+      <c r="S17" s="27">
         <v>843</v>
       </c>
-      <c r="T17" s="28">
+      <c r="T17" s="27">
         <v>1062</v>
       </c>
-      <c r="U17" s="28">
+      <c r="U17" s="27">
         <v>216</v>
       </c>
-      <c r="V17" s="28">
+      <c r="V17" s="27">
         <v>821</v>
       </c>
-      <c r="W17" s="28">
+      <c r="W17" s="27">
         <v>1102</v>
       </c>
-      <c r="X17" s="28">
+      <c r="X17" s="27">
         <v>315</v>
       </c>
-      <c r="Y17" s="28"/>
-      <c r="Z17" s="28"/>
-      <c r="AA17" s="28">
+      <c r="Y17" s="27"/>
+      <c r="Z17" s="27"/>
+      <c r="AA17" s="27">
         <v>900</v>
       </c>
-      <c r="AB17" s="28">
+      <c r="AB17" s="27">
         <v>523</v>
       </c>
-      <c r="AC17" s="28">
+      <c r="AC17" s="27">
         <v>572</v>
       </c>
-      <c r="AD17" s="28">
+      <c r="AD17" s="27">
         <v>598</v>
       </c>
-      <c r="AE17" s="28">
+      <c r="AE17" s="27">
         <v>117</v>
       </c>
     </row>
@@ -12078,87 +12125,87 @@
       <c r="B18" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C18" s="28">
+      <c r="C18" s="27">
         <v>21697</v>
       </c>
-      <c r="D18" s="28">
+      <c r="D18" s="27">
         <v>12713</v>
       </c>
-      <c r="E18" s="28">
+      <c r="E18" s="27">
         <v>8984</v>
       </c>
-      <c r="F18" s="28">
+      <c r="F18" s="27">
         <v>2982</v>
       </c>
-      <c r="G18" s="28">
+      <c r="G18" s="27">
         <v>0</v>
       </c>
-      <c r="H18" s="28">
+      <c r="H18" s="27">
         <v>2757</v>
       </c>
-      <c r="I18" s="28">
+      <c r="I18" s="27">
         <v>3836</v>
       </c>
-      <c r="J18" s="28">
+      <c r="J18" s="27">
         <v>3138</v>
       </c>
-      <c r="K18" s="28">
+      <c r="K18" s="27">
         <v>2124</v>
       </c>
-      <c r="L18" s="28">
+      <c r="L18" s="27">
         <v>1687</v>
       </c>
-      <c r="M18" s="28">
+      <c r="M18" s="27">
         <v>2317</v>
       </c>
-      <c r="N18" s="28">
+      <c r="N18" s="27">
         <v>2354</v>
       </c>
-      <c r="O18" s="28">
+      <c r="O18" s="27">
         <v>502</v>
       </c>
-      <c r="P18" s="28">
+      <c r="P18" s="27">
         <v>1085</v>
       </c>
-      <c r="Q18" s="28">
+      <c r="Q18" s="27">
         <v>934</v>
       </c>
-      <c r="R18" s="28">
+      <c r="R18" s="27">
         <v>995</v>
       </c>
-      <c r="S18" s="28">
+      <c r="S18" s="27">
         <v>2097</v>
       </c>
-      <c r="T18" s="28">
+      <c r="T18" s="27">
         <v>1897</v>
       </c>
-      <c r="U18" s="28">
+      <c r="U18" s="27">
         <v>1393</v>
       </c>
-      <c r="V18" s="28">
+      <c r="V18" s="27">
         <v>1823</v>
       </c>
-      <c r="W18" s="28">
+      <c r="W18" s="27">
         <v>1745</v>
       </c>
-      <c r="X18" s="28">
+      <c r="X18" s="27">
         <v>744</v>
       </c>
-      <c r="Y18" s="28"/>
-      <c r="Z18" s="28"/>
-      <c r="AA18" s="28">
+      <c r="Y18" s="27"/>
+      <c r="Z18" s="27"/>
+      <c r="AA18" s="27">
         <v>2124</v>
       </c>
-      <c r="AB18" s="28">
+      <c r="AB18" s="27">
         <v>1687</v>
       </c>
-      <c r="AC18" s="28">
+      <c r="AC18" s="27">
         <v>2317</v>
       </c>
-      <c r="AD18" s="28">
+      <c r="AD18" s="27">
         <v>2354</v>
       </c>
-      <c r="AE18" s="28">
+      <c r="AE18" s="27">
         <v>502</v>
       </c>
     </row>
@@ -12169,35 +12216,89 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
+      <c r="C19" s="27">
+        <v>17746</v>
+      </c>
+      <c r="D19" s="27">
+        <v>10344</v>
+      </c>
+      <c r="E19" s="27">
+        <v>7402</v>
+      </c>
+      <c r="F19" s="27">
+        <v>2104</v>
+      </c>
+      <c r="G19" s="27">
+        <v>0</v>
+      </c>
+      <c r="H19" s="27">
+        <v>2262</v>
+      </c>
+      <c r="I19" s="27">
+        <v>3230</v>
+      </c>
+      <c r="J19" s="27">
+        <v>2748</v>
+      </c>
+      <c r="K19" s="27">
+        <v>1447</v>
+      </c>
+      <c r="L19" s="27">
+        <v>1435</v>
+      </c>
+      <c r="M19" s="27">
+        <v>2298</v>
+      </c>
+      <c r="N19" s="27">
+        <v>1745</v>
+      </c>
+      <c r="O19" s="27">
+        <v>477</v>
+      </c>
+      <c r="P19" s="27">
+        <v>953</v>
+      </c>
+      <c r="Q19" s="27">
+        <v>810</v>
+      </c>
+      <c r="R19" s="27">
+        <v>773</v>
+      </c>
+      <c r="S19" s="27">
+        <v>1879</v>
+      </c>
+      <c r="T19" s="27">
+        <v>1151</v>
+      </c>
+      <c r="U19" s="27">
+        <v>1189</v>
+      </c>
+      <c r="V19" s="27">
+        <v>1452</v>
+      </c>
+      <c r="W19" s="27">
+        <v>1559</v>
+      </c>
+      <c r="X19" s="27">
+        <v>578</v>
+      </c>
+      <c r="Y19" s="27"/>
+      <c r="Z19" s="27"/>
+      <c r="AA19" s="27">
+        <v>1447</v>
+      </c>
+      <c r="AB19" s="27">
+        <v>1435</v>
+      </c>
+      <c r="AC19" s="27">
+        <v>2298</v>
+      </c>
+      <c r="AD19" s="27">
+        <v>1745</v>
+      </c>
+      <c r="AE19" s="27">
+        <v>477</v>
+      </c>
     </row>
     <row r="20" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -19667,36 +19768,90 @@
       <c r="C76" s="20">
         <v>22</v>
       </c>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
-      <c r="P76" s="21"/>
-      <c r="Q76" s="21"/>
-      <c r="R76" s="21"/>
-      <c r="S76" s="21"/>
-      <c r="T76" s="21"/>
-      <c r="U76" s="21"/>
-      <c r="V76" s="21"/>
-      <c r="W76" s="21"/>
-      <c r="X76" s="21"/>
-      <c r="Y76" s="21"/>
-      <c r="Z76" s="21"/>
-      <c r="AA76" s="21"/>
-      <c r="AB76" s="21"/>
-      <c r="AC76" s="21"/>
-      <c r="AD76" s="21"/>
-      <c r="AE76" s="21"/>
-      <c r="AF76" s="21"/>
-      <c r="AG76" s="21"/>
+      <c r="D76" s="24">
+        <v>0.93670886075949367</v>
+      </c>
+      <c r="E76" s="24">
+        <v>0.94475138121546964</v>
+      </c>
+      <c r="F76" s="24">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="G76" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24">
+        <v>1</v>
+      </c>
+      <c r="J76" s="24">
+        <v>1</v>
+      </c>
+      <c r="K76" s="24">
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="L76" s="24">
+        <v>0.75609756097560976</v>
+      </c>
+      <c r="M76" s="24">
+        <v>1</v>
+      </c>
+      <c r="N76" s="24">
+        <v>1</v>
+      </c>
+      <c r="O76" s="24">
+        <v>1</v>
+      </c>
+      <c r="P76" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="24">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="R76" s="24">
+        <v>1</v>
+      </c>
+      <c r="S76" s="24">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="T76" s="24">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="U76" s="24">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="V76" s="24">
+        <v>1</v>
+      </c>
+      <c r="W76" s="24">
+        <v>1</v>
+      </c>
+      <c r="X76" s="24">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="24">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Z76" s="24"/>
+      <c r="AA76" s="24"/>
+      <c r="AB76" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="AC76" s="24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="AD76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="26">
@@ -19708,36 +19863,90 @@
       <c r="C77" s="20">
         <v>23</v>
       </c>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
-      <c r="P77" s="21"/>
-      <c r="Q77" s="21"/>
-      <c r="R77" s="21"/>
-      <c r="S77" s="21"/>
-      <c r="T77" s="21"/>
-      <c r="U77" s="21"/>
-      <c r="V77" s="21"/>
-      <c r="W77" s="21"/>
-      <c r="X77" s="21"/>
-      <c r="Y77" s="21"/>
-      <c r="Z77" s="21"/>
-      <c r="AA77" s="21"/>
-      <c r="AB77" s="21"/>
-      <c r="AC77" s="21"/>
-      <c r="AD77" s="21"/>
-      <c r="AE77" s="21"/>
-      <c r="AF77" s="21"/>
-      <c r="AG77" s="21"/>
+      <c r="D77" s="24">
+        <v>0.93548387096774188</v>
+      </c>
+      <c r="E77" s="24">
+        <v>0.90957446808510634</v>
+      </c>
+      <c r="F77" s="24">
+        <v>0.97540983606557374</v>
+      </c>
+      <c r="G77" s="24">
+        <v>0.95918367346938771</v>
+      </c>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24">
+        <v>0.93333333333333335</v>
+      </c>
+      <c r="J77" s="24">
+        <v>0.88636363636363635</v>
+      </c>
+      <c r="K77" s="24">
+        <v>0.86</v>
+      </c>
+      <c r="L77" s="24">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="M77" s="24">
+        <v>1</v>
+      </c>
+      <c r="N77" s="24">
+        <v>1</v>
+      </c>
+      <c r="O77" s="24">
+        <v>1</v>
+      </c>
+      <c r="P77" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="24">
+        <v>1</v>
+      </c>
+      <c r="R77" s="24">
+        <v>1</v>
+      </c>
+      <c r="S77" s="24">
+        <v>0.92</v>
+      </c>
+      <c r="T77" s="24">
+        <v>0.76923076923076927</v>
+      </c>
+      <c r="U77" s="24">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="V77" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="W77" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="X77" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="Y77" s="24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z77" s="24"/>
+      <c r="AA77" s="24"/>
+      <c r="AB77" s="24">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="AC77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AD77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG77" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="26">
@@ -19749,36 +19958,90 @@
       <c r="C78" s="20">
         <v>24</v>
       </c>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
-      <c r="P78" s="21"/>
-      <c r="Q78" s="21"/>
-      <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
-      <c r="U78" s="21"/>
-      <c r="V78" s="21"/>
-      <c r="W78" s="21"/>
-      <c r="X78" s="21"/>
-      <c r="Y78" s="21"/>
-      <c r="Z78" s="21"/>
-      <c r="AA78" s="21"/>
-      <c r="AB78" s="21"/>
-      <c r="AC78" s="21"/>
-      <c r="AD78" s="21"/>
-      <c r="AE78" s="21"/>
-      <c r="AF78" s="21"/>
-      <c r="AG78" s="21"/>
+      <c r="D78" s="24">
+        <v>0.86510263929618769</v>
+      </c>
+      <c r="E78" s="24">
+        <v>0.8308457711442786</v>
+      </c>
+      <c r="F78" s="24">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="G78" s="24">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24">
+        <v>0.69767441860465118</v>
+      </c>
+      <c r="J78" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="K78" s="24">
+        <v>0.953125</v>
+      </c>
+      <c r="L78" s="24">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="M78" s="24">
+        <v>1</v>
+      </c>
+      <c r="N78" s="24">
+        <v>1</v>
+      </c>
+      <c r="O78" s="24">
+        <v>1</v>
+      </c>
+      <c r="P78" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="24">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="R78" s="24">
+        <v>0.69565217391304346</v>
+      </c>
+      <c r="S78" s="24">
+        <v>1</v>
+      </c>
+      <c r="T78" s="24">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="U78" s="24">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="V78" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="W78" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="X78" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Y78" s="24">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z78" s="24"/>
+      <c r="AA78" s="24"/>
+      <c r="AB78" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="AC78" s="24">
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="AD78" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE78" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG78" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="26">
@@ -19790,36 +20053,90 @@
       <c r="C79" s="20">
         <v>25</v>
       </c>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
-      <c r="L79" s="21"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="21"/>
-      <c r="O79" s="21"/>
-      <c r="P79" s="21"/>
-      <c r="Q79" s="21"/>
-      <c r="R79" s="21"/>
-      <c r="S79" s="21"/>
-      <c r="T79" s="21"/>
-      <c r="U79" s="21"/>
-      <c r="V79" s="21"/>
-      <c r="W79" s="21"/>
-      <c r="X79" s="21"/>
-      <c r="Y79" s="21"/>
-      <c r="Z79" s="21"/>
-      <c r="AA79" s="21"/>
-      <c r="AB79" s="21"/>
-      <c r="AC79" s="21"/>
-      <c r="AD79" s="21"/>
-      <c r="AE79" s="21"/>
-      <c r="AF79" s="21"/>
-      <c r="AG79" s="21"/>
+      <c r="D79" s="24">
+        <v>0.85959885386819479</v>
+      </c>
+      <c r="E79" s="24">
+        <v>0.839622641509434</v>
+      </c>
+      <c r="F79" s="24">
+        <v>0.89051094890510951</v>
+      </c>
+      <c r="G79" s="24">
+        <v>0.82758620689655171</v>
+      </c>
+      <c r="H79" s="24"/>
+      <c r="I79" s="24">
+        <v>0.92</v>
+      </c>
+      <c r="J79" s="24">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="K79" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="L79" s="24">
+        <v>0.70270270270270274</v>
+      </c>
+      <c r="M79" s="24">
+        <v>1</v>
+      </c>
+      <c r="N79" s="24">
+        <v>0.86206896551724133</v>
+      </c>
+      <c r="O79" s="24">
+        <v>1</v>
+      </c>
+      <c r="P79" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="24">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="R79" s="24">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="S79" s="24">
+        <v>0.88461538461538458</v>
+      </c>
+      <c r="T79" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="U79" s="24">
+        <v>0.71875</v>
+      </c>
+      <c r="V79" s="24">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="W79" s="24">
+        <v>0.8571428571428571</v>
+      </c>
+      <c r="X79" s="24">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Y79" s="24">
+        <v>0.83333333333333337</v>
+      </c>
+      <c r="Z79" s="24"/>
+      <c r="AA79" s="24"/>
+      <c r="AB79" s="24">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="AC79" s="24">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="AD79" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE79" s="24">
+        <v>0.86206896551724133</v>
+      </c>
+      <c r="AF79" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG79" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="26">
@@ -28215,36 +28532,90 @@
       <c r="C76" s="20">
         <v>22</v>
       </c>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
-      <c r="P76" s="21"/>
-      <c r="Q76" s="21"/>
-      <c r="R76" s="21"/>
-      <c r="S76" s="21"/>
-      <c r="T76" s="21"/>
-      <c r="U76" s="21"/>
-      <c r="V76" s="21"/>
-      <c r="W76" s="21"/>
-      <c r="X76" s="21"/>
-      <c r="Y76" s="21"/>
-      <c r="Z76" s="21"/>
-      <c r="AA76" s="21"/>
-      <c r="AB76" s="21"/>
-      <c r="AC76" s="21"/>
-      <c r="AD76" s="21"/>
-      <c r="AE76" s="21"/>
-      <c r="AF76" s="21"/>
-      <c r="AG76" s="21"/>
+      <c r="D76" s="24">
+        <v>0.94620253164556967</v>
+      </c>
+      <c r="E76" s="24">
+        <v>0.96132596685082872</v>
+      </c>
+      <c r="F76" s="24">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="G76" s="24">
+        <v>0.92500000000000004</v>
+      </c>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24">
+        <v>1</v>
+      </c>
+      <c r="J76" s="24">
+        <v>1</v>
+      </c>
+      <c r="K76" s="24">
+        <v>0.93103448275862066</v>
+      </c>
+      <c r="L76" s="24">
+        <v>0.75609756097560976</v>
+      </c>
+      <c r="M76" s="24">
+        <v>1</v>
+      </c>
+      <c r="N76" s="24">
+        <v>1</v>
+      </c>
+      <c r="O76" s="24">
+        <v>1</v>
+      </c>
+      <c r="P76" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="24">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="R76" s="24">
+        <v>1</v>
+      </c>
+      <c r="S76" s="24">
+        <v>0.96666666666666667</v>
+      </c>
+      <c r="T76" s="24">
+        <v>0.8666666666666667</v>
+      </c>
+      <c r="U76" s="24">
+        <v>0.94444444444444442</v>
+      </c>
+      <c r="V76" s="24">
+        <v>1</v>
+      </c>
+      <c r="W76" s="24">
+        <v>1</v>
+      </c>
+      <c r="X76" s="24">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="24">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="Z76" s="24"/>
+      <c r="AA76" s="24"/>
+      <c r="AB76" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="AC76" s="24">
+        <v>0.76190476190476186</v>
+      </c>
+      <c r="AD76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="26">
@@ -28256,36 +28627,90 @@
       <c r="C77" s="20">
         <v>23</v>
       </c>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
-      <c r="P77" s="21"/>
-      <c r="Q77" s="21"/>
-      <c r="R77" s="21"/>
-      <c r="S77" s="21"/>
-      <c r="T77" s="21"/>
-      <c r="U77" s="21"/>
-      <c r="V77" s="21"/>
-      <c r="W77" s="21"/>
-      <c r="X77" s="21"/>
-      <c r="Y77" s="21"/>
-      <c r="Z77" s="21"/>
-      <c r="AA77" s="21"/>
-      <c r="AB77" s="21"/>
-      <c r="AC77" s="21"/>
-      <c r="AD77" s="21"/>
-      <c r="AE77" s="21"/>
-      <c r="AF77" s="21"/>
-      <c r="AG77" s="21"/>
+      <c r="D77" s="24">
+        <v>0.95161290322580649</v>
+      </c>
+      <c r="E77" s="24">
+        <v>0.93617021276595747</v>
+      </c>
+      <c r="F77" s="24">
+        <v>0.97540983606557374</v>
+      </c>
+      <c r="G77" s="24">
+        <v>0.95918367346938771</v>
+      </c>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24">
+        <v>0.97777777777777775</v>
+      </c>
+      <c r="J77" s="24">
+        <v>0.88636363636363635</v>
+      </c>
+      <c r="K77" s="24">
+        <v>0.92</v>
+      </c>
+      <c r="L77" s="24">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="M77" s="24">
+        <v>1</v>
+      </c>
+      <c r="N77" s="24">
+        <v>1</v>
+      </c>
+      <c r="O77" s="24">
+        <v>1</v>
+      </c>
+      <c r="P77" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q77" s="24">
+        <v>1</v>
+      </c>
+      <c r="R77" s="24">
+        <v>1</v>
+      </c>
+      <c r="S77" s="24">
+        <v>0.92</v>
+      </c>
+      <c r="T77" s="24">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="U77" s="24">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="V77" s="24">
+        <v>0.9</v>
+      </c>
+      <c r="W77" s="24">
+        <v>0.95</v>
+      </c>
+      <c r="X77" s="24">
+        <v>0.875</v>
+      </c>
+      <c r="Y77" s="24">
+        <v>1</v>
+      </c>
+      <c r="Z77" s="24"/>
+      <c r="AA77" s="24"/>
+      <c r="AB77" s="24">
+        <v>0.86363636363636365</v>
+      </c>
+      <c r="AC77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AD77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF77" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG77" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="26">
@@ -28297,36 +28722,90 @@
       <c r="C78" s="20">
         <v>24</v>
       </c>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
-      <c r="P78" s="21"/>
-      <c r="Q78" s="21"/>
-      <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
-      <c r="U78" s="21"/>
-      <c r="V78" s="21"/>
-      <c r="W78" s="21"/>
-      <c r="X78" s="21"/>
-      <c r="Y78" s="21"/>
-      <c r="Z78" s="21"/>
-      <c r="AA78" s="21"/>
-      <c r="AB78" s="21"/>
-      <c r="AC78" s="21"/>
-      <c r="AD78" s="21"/>
-      <c r="AE78" s="21"/>
-      <c r="AF78" s="21"/>
-      <c r="AG78" s="21"/>
+      <c r="D78" s="24">
+        <v>0.86803519061583578</v>
+      </c>
+      <c r="E78" s="24">
+        <v>0.83582089552238803</v>
+      </c>
+      <c r="F78" s="24">
+        <v>0.91428571428571426</v>
+      </c>
+      <c r="G78" s="24">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24">
+        <v>0.72093023255813948</v>
+      </c>
+      <c r="J78" s="24">
+        <v>0.85</v>
+      </c>
+      <c r="K78" s="24">
+        <v>0.953125</v>
+      </c>
+      <c r="L78" s="24">
+        <v>0.68421052631578949</v>
+      </c>
+      <c r="M78" s="24">
+        <v>1</v>
+      </c>
+      <c r="N78" s="24">
+        <v>1</v>
+      </c>
+      <c r="O78" s="24">
+        <v>1</v>
+      </c>
+      <c r="P78" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q78" s="24">
+        <v>0.96551724137931039</v>
+      </c>
+      <c r="R78" s="24">
+        <v>0.73913043478260865</v>
+      </c>
+      <c r="S78" s="24">
+        <v>1</v>
+      </c>
+      <c r="T78" s="24">
+        <v>0.92592592592592593</v>
+      </c>
+      <c r="U78" s="24">
+        <v>0.56000000000000005</v>
+      </c>
+      <c r="V78" s="24">
+        <v>0.80952380952380953</v>
+      </c>
+      <c r="W78" s="24">
+        <v>0.7</v>
+      </c>
+      <c r="X78" s="24">
+        <v>0.89473684210526316</v>
+      </c>
+      <c r="Y78" s="24">
+        <v>0.90909090909090906</v>
+      </c>
+      <c r="Z78" s="24"/>
+      <c r="AA78" s="24"/>
+      <c r="AB78" s="24">
+        <v>0.8</v>
+      </c>
+      <c r="AC78" s="24">
+        <v>0.60869565217391308</v>
+      </c>
+      <c r="AD78" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE78" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF78" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG78" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="26">
@@ -28338,36 +28817,90 @@
       <c r="C79" s="20">
         <v>25</v>
       </c>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
-      <c r="L79" s="21"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="21"/>
-      <c r="O79" s="21"/>
-      <c r="P79" s="21"/>
-      <c r="Q79" s="21"/>
-      <c r="R79" s="21"/>
-      <c r="S79" s="21"/>
-      <c r="T79" s="21"/>
-      <c r="U79" s="21"/>
-      <c r="V79" s="21"/>
-      <c r="W79" s="21"/>
-      <c r="X79" s="21"/>
-      <c r="Y79" s="21"/>
-      <c r="Z79" s="21"/>
-      <c r="AA79" s="21"/>
-      <c r="AB79" s="21"/>
-      <c r="AC79" s="21"/>
-      <c r="AD79" s="21"/>
-      <c r="AE79" s="21"/>
-      <c r="AF79" s="21"/>
-      <c r="AG79" s="21"/>
+      <c r="D79" s="24">
+        <v>0.89111747851002865</v>
+      </c>
+      <c r="E79" s="24">
+        <v>0.87264150943396224</v>
+      </c>
+      <c r="F79" s="24">
+        <v>0.91970802919708028</v>
+      </c>
+      <c r="G79" s="24">
+        <v>0.84482758620689657</v>
+      </c>
+      <c r="H79" s="24"/>
+      <c r="I79" s="24">
+        <v>1</v>
+      </c>
+      <c r="J79" s="24">
+        <v>0.7021276595744681</v>
+      </c>
+      <c r="K79" s="24">
+        <v>0.92982456140350878</v>
+      </c>
+      <c r="L79" s="24">
+        <v>0.70270270270270274</v>
+      </c>
+      <c r="M79" s="24">
+        <v>1</v>
+      </c>
+      <c r="N79" s="24">
+        <v>1</v>
+      </c>
+      <c r="O79" s="24">
+        <v>1</v>
+      </c>
+      <c r="P79" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q79" s="24">
+        <v>0.96153846153846156</v>
+      </c>
+      <c r="R79" s="24">
+        <v>1</v>
+      </c>
+      <c r="S79" s="24">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="T79" s="24">
+        <v>0.94736842105263153</v>
+      </c>
+      <c r="U79" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="V79" s="24">
+        <v>0.7142857142857143</v>
+      </c>
+      <c r="W79" s="24">
+        <v>1</v>
+      </c>
+      <c r="X79" s="24">
+        <v>0.69230769230769229</v>
+      </c>
+      <c r="Y79" s="24">
+        <v>0.91666666666666663</v>
+      </c>
+      <c r="Z79" s="24"/>
+      <c r="AA79" s="24"/>
+      <c r="AB79" s="24">
+        <v>0.78947368421052633</v>
+      </c>
+      <c r="AC79" s="24">
+        <v>0.61111111111111116</v>
+      </c>
+      <c r="AD79" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE79" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF79" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG79" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="26">
@@ -33813,36 +34346,90 @@
       <c r="C76" s="20">
         <v>22</v>
       </c>
-      <c r="D76" s="21"/>
-      <c r="E76" s="21"/>
-      <c r="F76" s="21"/>
-      <c r="G76" s="21"/>
-      <c r="H76" s="21"/>
-      <c r="I76" s="21"/>
-      <c r="J76" s="21"/>
-      <c r="K76" s="21"/>
-      <c r="L76" s="21"/>
-      <c r="M76" s="21"/>
-      <c r="N76" s="21"/>
-      <c r="O76" s="21"/>
-      <c r="P76" s="21"/>
-      <c r="Q76" s="21"/>
-      <c r="R76" s="21"/>
-      <c r="S76" s="21"/>
-      <c r="T76" s="21"/>
-      <c r="U76" s="21"/>
-      <c r="V76" s="21"/>
-      <c r="W76" s="21"/>
-      <c r="X76" s="21"/>
-      <c r="Y76" s="21"/>
-      <c r="Z76" s="21"/>
-      <c r="AA76" s="21"/>
-      <c r="AB76" s="21"/>
-      <c r="AC76" s="21"/>
-      <c r="AD76" s="21"/>
-      <c r="AE76" s="21"/>
-      <c r="AF76" s="21"/>
-      <c r="AG76" s="21"/>
+      <c r="D76" s="24">
+        <v>0.96478632478632476</v>
+      </c>
+      <c r="E76" s="24">
+        <v>0.96420323325635104</v>
+      </c>
+      <c r="F76" s="24">
+        <v>0.96563285834031853</v>
+      </c>
+      <c r="G76" s="24">
+        <v>0.92757009345794394</v>
+      </c>
+      <c r="H76" s="24"/>
+      <c r="I76" s="24">
+        <v>0.99752475247524752</v>
+      </c>
+      <c r="J76" s="24">
+        <v>1</v>
+      </c>
+      <c r="K76" s="24">
+        <v>0.94423791821561343</v>
+      </c>
+      <c r="L76" s="24">
+        <v>0.8761329305135952</v>
+      </c>
+      <c r="M76" s="24">
+        <v>1</v>
+      </c>
+      <c r="N76" s="24">
+        <v>1</v>
+      </c>
+      <c r="O76" s="24">
+        <v>1</v>
+      </c>
+      <c r="P76" s="24">
+        <v>1</v>
+      </c>
+      <c r="Q76" s="24">
+        <v>0.8839285714285714</v>
+      </c>
+      <c r="R76" s="24">
+        <v>1</v>
+      </c>
+      <c r="S76" s="24">
+        <v>0.9887640449438202</v>
+      </c>
+      <c r="T76" s="24">
+        <v>0.87349397590361444</v>
+      </c>
+      <c r="U76" s="24">
+        <v>0.97549019607843135</v>
+      </c>
+      <c r="V76" s="24">
+        <v>1</v>
+      </c>
+      <c r="W76" s="24">
+        <v>0.99528301886792447</v>
+      </c>
+      <c r="X76" s="24">
+        <v>1</v>
+      </c>
+      <c r="Y76" s="24">
+        <v>0.94285714285714284</v>
+      </c>
+      <c r="Z76" s="24"/>
+      <c r="AA76" s="24"/>
+      <c r="AB76" s="24">
+        <v>0.80625000000000002</v>
+      </c>
+      <c r="AC76" s="24">
+        <v>0.94152046783625731</v>
+      </c>
+      <c r="AD76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AE76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AF76" s="24">
+        <v>1</v>
+      </c>
+      <c r="AG76" s="24">
+        <v>1</v>
+      </c>
     </row>
     <row r="77" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A77" s="25">
@@ -33854,36 +34441,90 @@
       <c r="C77" s="20">
         <v>23</v>
       </c>
-      <c r="D77" s="21"/>
-      <c r="E77" s="21"/>
-      <c r="F77" s="21"/>
-      <c r="G77" s="21"/>
-      <c r="H77" s="21"/>
-      <c r="I77" s="21"/>
-      <c r="J77" s="21"/>
-      <c r="K77" s="21"/>
-      <c r="L77" s="21"/>
-      <c r="M77" s="21"/>
-      <c r="N77" s="21"/>
-      <c r="O77" s="21"/>
-      <c r="P77" s="21"/>
-      <c r="Q77" s="21"/>
-      <c r="R77" s="21"/>
-      <c r="S77" s="21"/>
-      <c r="T77" s="21"/>
-      <c r="U77" s="21"/>
-      <c r="V77" s="21"/>
-      <c r="W77" s="21"/>
-      <c r="X77" s="21"/>
-      <c r="Y77" s="21"/>
-      <c r="Z77" s="21"/>
-      <c r="AA77" s="21"/>
-      <c r="AB77" s="21"/>
-      <c r="AC77" s="21"/>
-      <c r="AD77" s="21"/>
-      <c r="AE77" s="21"/>
-      <c r="AF77" s="21"/>
-      <c r="AG77" s="21"/>
+      <c r="D77" s="24">
+        <v>0.42473745624270715</v>
+      </c>
+      <c r="E77" s="24">
+        <v>0.29450757575757575</v>
+      </c>
+      <c r="F77" s="24">
+        <v>0.63373860182370823</v>
+      </c>
+      <c r="G77" s="24">
+        <v>0.34333333333333332</v>
+      </c>
+      <c r="H77" s="24"/>
+      <c r="I77" s="24">
+        <v>0.28846153846153844</v>
+      </c>
+      <c r="J77" s="24">
+        <v>0.26582278481012656</v>
+      </c>
+      <c r="K77" s="24">
+        <v>0.27027027027027029</v>
+      </c>
+      <c r="L77" s="24">
+        <v>0.69512195121951215</v>
+      </c>
+      <c r="M77" s="24">
+        <v>0.6853932584269663</v>
+      </c>
+      <c r="N77" s="24">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="O77" s="24">
+        <v>0.7038461538461539</v>
+      </c>
+      <c r="P77" s="24">
+        <v>0.32</v>
+      </c>
+      <c r="Q77" s="24">
+        <v>0.265625</v>
+      </c>
+      <c r="R77" s="24">
+        <v>0.38297872340425532</v>
+      </c>
+      <c r="S77" s="24">
+        <v>0.39215686274509803</v>
+      </c>
+      <c r="T77" s="24">
+        <v>0.15625</v>
+      </c>
+      <c r="U77" s="24">
+        <v>0.40116279069767441</v>
+      </c>
+      <c r="V77" s="24">
+        <v>0.30681818181818182</v>
+      </c>
+      <c r="W77" s="24">
+        <v>0.23493975903614459</v>
+      </c>
+      <c r="X77" s="24">
+        <v>0.24161073825503357</v>
+      </c>
+      <c r="Y77" s="24">
+        <v>0.24590163934426229</v>
+      </c>
+      <c r="Z77" s="24"/>
+      <c r="AA77" s="24"/>
+      <c r="AB77" s="24">
+        <v>0.65217391304347827</v>
+      </c>
+      <c r="AC77" s="24">
+        <v>0.79591836734693877</v>
+      </c>
+      <c r="AD77" s="24">
+        <v>0.6853932584269663</v>
+      </c>
+      <c r="AE77" s="24">
+        <v>0.42499999999999999</v>
+      </c>
+      <c r="AF77" s="24">
+        <v>0.7038461538461539</v>
+      </c>
+      <c r="AG77" s="24">
+        <v>0.32</v>
+      </c>
     </row>
     <row r="78" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A78" s="25">
@@ -33895,36 +34536,90 @@
       <c r="C78" s="20">
         <v>24</v>
       </c>
-      <c r="D78" s="21"/>
-      <c r="E78" s="21"/>
-      <c r="F78" s="21"/>
-      <c r="G78" s="21"/>
-      <c r="H78" s="21"/>
-      <c r="I78" s="21"/>
-      <c r="J78" s="21"/>
-      <c r="K78" s="21"/>
-      <c r="L78" s="21"/>
-      <c r="M78" s="21"/>
-      <c r="N78" s="21"/>
-      <c r="O78" s="21"/>
-      <c r="P78" s="21"/>
-      <c r="Q78" s="21"/>
-      <c r="R78" s="21"/>
-      <c r="S78" s="21"/>
-      <c r="T78" s="21"/>
-      <c r="U78" s="21"/>
-      <c r="V78" s="21"/>
-      <c r="W78" s="21"/>
-      <c r="X78" s="21"/>
-      <c r="Y78" s="21"/>
-      <c r="Z78" s="21"/>
-      <c r="AA78" s="21"/>
-      <c r="AB78" s="21"/>
-      <c r="AC78" s="21"/>
-      <c r="AD78" s="21"/>
-      <c r="AE78" s="21"/>
-      <c r="AF78" s="21"/>
-      <c r="AG78" s="21"/>
+      <c r="D78" s="24">
+        <v>0.47176781002638524</v>
+      </c>
+      <c r="E78" s="24">
+        <v>0.33361629881154498</v>
+      </c>
+      <c r="F78" s="24">
+        <v>0.69874476987447698</v>
+      </c>
+      <c r="G78" s="24">
+        <v>0.31778425655976678</v>
+      </c>
+      <c r="H78" s="24"/>
+      <c r="I78" s="24">
+        <v>0.17131474103585656</v>
+      </c>
+      <c r="J78" s="24">
+        <v>0.33898305084745761</v>
+      </c>
+      <c r="K78" s="24">
+        <v>0.46264367816091956</v>
+      </c>
+      <c r="L78" s="24">
+        <v>0.50810810810810814</v>
+      </c>
+      <c r="M78" s="24">
+        <v>0.83582089552238803</v>
+      </c>
+      <c r="N78" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="O78" s="24">
+        <v>0.81147540983606559</v>
+      </c>
+      <c r="P78" s="24">
+        <v>0.44</v>
+      </c>
+      <c r="Q78" s="24">
+        <v>0.25728155339805825</v>
+      </c>
+      <c r="R78" s="24">
+        <v>0.12631578947368421</v>
+      </c>
+      <c r="S78" s="24">
+        <v>0.46875</v>
+      </c>
+      <c r="T78" s="24">
+        <v>0.44252873563218392</v>
+      </c>
+      <c r="U78" s="24">
+        <v>0.40875912408759124</v>
+      </c>
+      <c r="V78" s="24">
+        <v>0.33962264150943394</v>
+      </c>
+      <c r="W78" s="24">
+        <v>0.19871794871794871</v>
+      </c>
+      <c r="X78" s="24">
+        <v>0.33846153846153848</v>
+      </c>
+      <c r="Y78" s="24">
+        <v>0.52173913043478259</v>
+      </c>
+      <c r="Z78" s="24"/>
+      <c r="AA78" s="24"/>
+      <c r="AB78" s="24">
+        <v>0.57534246575342463</v>
+      </c>
+      <c r="AC78" s="24">
+        <v>0.4642857142857143</v>
+      </c>
+      <c r="AD78" s="24">
+        <v>0.83582089552238803</v>
+      </c>
+      <c r="AE78" s="24">
+        <v>0.66666666666666663</v>
+      </c>
+      <c r="AF78" s="24">
+        <v>0.81147540983606559</v>
+      </c>
+      <c r="AG78" s="24">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="79" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A79" s="25">
@@ -33936,36 +34631,90 @@
       <c r="C79" s="20">
         <v>25</v>
       </c>
-      <c r="D79" s="21"/>
-      <c r="E79" s="21"/>
-      <c r="F79" s="21"/>
-      <c r="G79" s="21"/>
-      <c r="H79" s="21"/>
-      <c r="I79" s="21"/>
-      <c r="J79" s="21"/>
-      <c r="K79" s="21"/>
-      <c r="L79" s="21"/>
-      <c r="M79" s="21"/>
-      <c r="N79" s="21"/>
-      <c r="O79" s="21"/>
-      <c r="P79" s="21"/>
-      <c r="Q79" s="21"/>
-      <c r="R79" s="21"/>
-      <c r="S79" s="21"/>
-      <c r="T79" s="21"/>
-      <c r="U79" s="21"/>
-      <c r="V79" s="21"/>
-      <c r="W79" s="21"/>
-      <c r="X79" s="21"/>
-      <c r="Y79" s="21"/>
-      <c r="Z79" s="21"/>
-      <c r="AA79" s="21"/>
-      <c r="AB79" s="21"/>
-      <c r="AC79" s="21"/>
-      <c r="AD79" s="21"/>
-      <c r="AE79" s="21"/>
-      <c r="AF79" s="21"/>
-      <c r="AG79" s="21"/>
+      <c r="D79" s="24">
+        <v>0.43065693430656932</v>
+      </c>
+      <c r="E79" s="24">
+        <v>0.32292682926829269</v>
+      </c>
+      <c r="F79" s="24">
+        <v>0.60904684975767365</v>
+      </c>
+      <c r="G79" s="24">
+        <v>0.2978723404255319</v>
+      </c>
+      <c r="H79" s="24"/>
+      <c r="I79" s="24">
+        <v>0.24230769230769231</v>
+      </c>
+      <c r="J79" s="24">
+        <v>0.22439024390243903</v>
+      </c>
+      <c r="K79" s="24">
+        <v>0.49640287769784175</v>
+      </c>
+      <c r="L79" s="24">
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="M79" s="24">
+        <v>0.5816993464052288</v>
+      </c>
+      <c r="N79" s="24">
+        <v>0.52577319587628868</v>
+      </c>
+      <c r="O79" s="24">
+        <v>0.74233128834355833</v>
+      </c>
+      <c r="P79" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="Q79" s="24">
+        <v>0.26623376623376621</v>
+      </c>
+      <c r="R79" s="24">
+        <v>0.11827956989247312</v>
+      </c>
+      <c r="S79" s="24">
+        <v>0.57894736842105265</v>
+      </c>
+      <c r="T79" s="24">
+        <v>0.45614035087719296</v>
+      </c>
+      <c r="U79" s="24">
+        <v>0.3359375</v>
+      </c>
+      <c r="V79" s="24">
+        <v>0.24096385542168675</v>
+      </c>
+      <c r="W79" s="24">
+        <v>0.31137724550898205</v>
+      </c>
+      <c r="X79" s="24">
+        <v>0.21311475409836064</v>
+      </c>
+      <c r="Y79" s="24">
+        <v>0.4</v>
+      </c>
+      <c r="Z79" s="24"/>
+      <c r="AA79" s="24"/>
+      <c r="AB79" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="AC79" s="24">
+        <v>0.35365853658536583</v>
+      </c>
+      <c r="AD79" s="24">
+        <v>0.5816993464052288</v>
+      </c>
+      <c r="AE79" s="24">
+        <v>0.52577319587628868</v>
+      </c>
+      <c r="AF79" s="24">
+        <v>0.74233128834355833</v>
+      </c>
+      <c r="AG79" s="24">
+        <v>0.5</v>
+      </c>
     </row>
     <row r="80" spans="1:33" x14ac:dyDescent="0.25">
       <c r="A80" s="25">
@@ -36741,33 +37490,87 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="12"/>
-      <c r="D19" s="12"/>
-      <c r="E19" s="12"/>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12"/>
-      <c r="H19" s="12"/>
-      <c r="I19" s="12"/>
-      <c r="J19" s="12"/>
-      <c r="K19" s="12"/>
-      <c r="L19" s="12"/>
-      <c r="M19" s="12"/>
-      <c r="N19" s="12"/>
-      <c r="O19" s="12"/>
-      <c r="P19" s="12"/>
-      <c r="Q19" s="12"/>
-      <c r="R19" s="12"/>
-      <c r="S19" s="12"/>
-      <c r="T19" s="12"/>
-      <c r="U19" s="12"/>
-      <c r="V19" s="12"/>
-      <c r="W19" s="12"/>
-      <c r="X19" s="12"/>
-      <c r="Y19" s="12"/>
-      <c r="Z19" s="12"/>
-      <c r="AA19" s="12"/>
-      <c r="AB19" s="12"/>
-      <c r="AC19" s="12"/>
+      <c r="C19" s="12">
+        <v>212548.43385096965</v>
+      </c>
+      <c r="D19" s="12">
+        <v>140897.93448819764</v>
+      </c>
+      <c r="E19" s="12">
+        <v>73417.377447864623</v>
+      </c>
+      <c r="F19" s="12">
+        <v>33168.814675199952</v>
+      </c>
+      <c r="G19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="12">
+        <v>37094.322501599883</v>
+      </c>
+      <c r="I19" s="12">
+        <v>32790.554929729951</v>
+      </c>
+      <c r="J19" s="12">
+        <v>37615.597358083811</v>
+      </c>
+      <c r="K19" s="12">
+        <v>15382.187414999989</v>
+      </c>
+      <c r="L19" s="12">
+        <v>14330.132055555518</v>
+      </c>
+      <c r="M19" s="12">
+        <v>25228.19582114798</v>
+      </c>
+      <c r="N19" s="12">
+        <v>16160.787391855154</v>
+      </c>
+      <c r="O19" s="12">
+        <v>2333.6947868852471</v>
+      </c>
+      <c r="P19" s="12">
+        <v>16935.89517600002</v>
+      </c>
+      <c r="Q19" s="12">
+        <v>16858.59798260863</v>
+      </c>
+      <c r="R19" s="12">
+        <v>16100.084482758628</v>
+      </c>
+      <c r="S19" s="12">
+        <v>21269.344732568781</v>
+      </c>
+      <c r="T19" s="12">
+        <v>16056.386851999921</v>
+      </c>
+      <c r="U19" s="12">
+        <v>20188.070519999947</v>
+      </c>
+      <c r="V19" s="12">
+        <v>32790.554929729951</v>
+      </c>
+      <c r="W19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="X19" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y19" s="12">
+        <v>15382.187414999989</v>
+      </c>
+      <c r="Z19" s="12">
+        <v>14330.132055555518</v>
+      </c>
+      <c r="AA19" s="12">
+        <v>25228.19582114798</v>
+      </c>
+      <c r="AB19" s="12">
+        <v>16160.787391855154</v>
+      </c>
+      <c r="AC19" s="12">
+        <v>2333.6947868852471</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -38533,33 +39336,81 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
-      <c r="G19" s="13"/>
-      <c r="H19" s="13"/>
-      <c r="I19" s="13"/>
-      <c r="J19" s="13"/>
-      <c r="K19" s="13"/>
-      <c r="L19" s="13"/>
-      <c r="M19" s="13"/>
-      <c r="N19" s="13"/>
-      <c r="O19" s="13"/>
-      <c r="P19" s="13"/>
-      <c r="Q19" s="13"/>
-      <c r="R19" s="13"/>
-      <c r="S19" s="13"/>
-      <c r="T19" s="13"/>
-      <c r="U19" s="13"/>
-      <c r="V19" s="13"/>
-      <c r="W19" s="13"/>
-      <c r="X19" s="13"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="13"/>
-      <c r="AA19" s="13"/>
-      <c r="AB19" s="13"/>
-      <c r="AC19" s="13"/>
+      <c r="C19" s="16">
+        <v>0.82869999999999999</v>
+      </c>
+      <c r="D19" s="16">
+        <v>0.86270000000000002</v>
+      </c>
+      <c r="E19" s="16">
+        <v>0.79430000000000001</v>
+      </c>
+      <c r="F19" s="16">
+        <v>0.85850000000000004</v>
+      </c>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16">
+        <v>0.85750000000000004</v>
+      </c>
+      <c r="I19" s="16">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="J19" s="16">
+        <v>0.87475000000000003</v>
+      </c>
+      <c r="K19" s="16">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="L19" s="16">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.755</v>
+      </c>
+      <c r="N19" s="16">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="O19" s="16">
+        <v>0.78100000000000003</v>
+      </c>
+      <c r="P19" s="16">
+        <v>0.88700000000000001</v>
+      </c>
+      <c r="Q19" s="16">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="R19" s="16">
+        <v>0.90300000000000002</v>
+      </c>
+      <c r="S19" s="16">
+        <v>0.84650000000000003</v>
+      </c>
+      <c r="T19" s="16">
+        <v>0.83</v>
+      </c>
+      <c r="U19" s="16">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="V19" s="16">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="W19" s="16"/>
+      <c r="X19" s="16"/>
+      <c r="Y19" s="16">
+        <v>0.78700000000000003</v>
+      </c>
+      <c r="Z19" s="16">
+        <v>0.76600000000000001</v>
+      </c>
+      <c r="AA19" s="16">
+        <v>0.755</v>
+      </c>
+      <c r="AB19" s="16">
+        <v>0.89600000000000002</v>
+      </c>
+      <c r="AC19" s="16">
+        <v>0.78100000000000003</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -40396,33 +41247,87 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
+      <c r="C19" s="11">
+        <v>237322.7924459996</v>
+      </c>
+      <c r="D19" s="11">
+        <v>147043.65990494963</v>
+      </c>
+      <c r="E19" s="11">
+        <v>87894.79126274689</v>
+      </c>
+      <c r="F19" s="11">
+        <v>35510.824577751839</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="11">
+        <v>39614.180524781215</v>
+      </c>
+      <c r="I19" s="11">
+        <v>34630.236081242765</v>
+      </c>
+      <c r="J19" s="11">
+        <v>38198.17673621032</v>
+      </c>
+      <c r="K19" s="11">
+        <v>18614.615374841153</v>
+      </c>
+      <c r="L19" s="11">
+        <v>17107.08159268925</v>
+      </c>
+      <c r="M19" s="11">
+        <v>32152.059205297941</v>
+      </c>
+      <c r="N19" s="11">
+        <v>17406.493749999947</v>
+      </c>
+      <c r="O19" s="11">
+        <v>2804.2033290653017</v>
+      </c>
+      <c r="P19" s="11">
+        <v>18012.694024802728</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>17871.854424778692</v>
+      </c>
+      <c r="R19" s="11">
+        <v>16545.823255813964</v>
+      </c>
+      <c r="S19" s="11">
+        <v>21822.772238629623</v>
+      </c>
+      <c r="T19" s="11">
+        <v>17480.461807228832</v>
+      </c>
+      <c r="U19" s="11">
+        <v>21964.245869297101</v>
+      </c>
+      <c r="V19" s="11">
+        <v>34630.236081242765</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>18614.615374841153</v>
+      </c>
+      <c r="Z19" s="11">
+        <v>17107.08159268925</v>
+      </c>
+      <c r="AA19" s="11">
+        <v>32152.059205297941</v>
+      </c>
+      <c r="AB19" s="11">
+        <v>17406.493749999947</v>
+      </c>
+      <c r="AC19" s="11">
+        <v>2804.2033290653017</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -42259,33 +43164,87 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
+      <c r="C19" s="11">
+        <v>8208.2386519198608</v>
+      </c>
+      <c r="D19" s="11">
+        <v>10449.305222405274</v>
+      </c>
+      <c r="E19" s="11">
+        <v>5906.5002284263837</v>
+      </c>
+      <c r="F19" s="11">
+        <v>11208.104007352924</v>
+      </c>
+      <c r="G19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="11">
+        <v>12442.915677655639</v>
+      </c>
+      <c r="I19" s="11">
+        <v>9892.6647098976791</v>
+      </c>
+      <c r="J19" s="11">
+        <v>8886.6635904255272</v>
+      </c>
+      <c r="K19" s="11">
+        <v>4103.558067226887</v>
+      </c>
+      <c r="L19" s="11">
+        <v>7007.499732620302</v>
+      </c>
+      <c r="M19" s="11">
+        <v>7056.6292732557986</v>
+      </c>
+      <c r="N19" s="11">
+        <v>6810.5757205239979</v>
+      </c>
+      <c r="O19" s="11">
+        <v>3369.3581538461553</v>
+      </c>
+      <c r="P19" s="11">
+        <v>15072.886415094359</v>
+      </c>
+      <c r="Q19" s="11">
+        <v>13463.463666666616</v>
+      </c>
+      <c r="R19" s="11">
+        <v>11952.702720000007</v>
+      </c>
+      <c r="S19" s="11">
+        <v>7359.7516733067632</v>
+      </c>
+      <c r="T19" s="11">
+        <v>8740.2309036144161</v>
+      </c>
+      <c r="U19" s="11">
+        <v>11642.48588235291</v>
+      </c>
+      <c r="V19" s="11">
+        <v>9892.6647098976791</v>
+      </c>
+      <c r="W19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="X19" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="Y19" s="11">
+        <v>4103.558067226887</v>
+      </c>
+      <c r="Z19" s="11">
+        <v>7007.499732620302</v>
+      </c>
+      <c r="AA19" s="11">
+        <v>7056.6292732557986</v>
+      </c>
+      <c r="AB19" s="11">
+        <v>6810.5757205239979</v>
+      </c>
+      <c r="AC19" s="11">
+        <v>3369.3581538461553</v>
+      </c>
     </row>
     <row r="20" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -45911,64 +46870,168 @@
       <c r="B20" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C20" s="11"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="11"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="5"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="5"/>
-      <c r="L20" s="5"/>
-      <c r="M20" s="5"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="5"/>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="5"/>
-      <c r="R20" s="27"/>
-      <c r="S20" s="5"/>
-      <c r="T20" s="27"/>
-      <c r="U20" s="5"/>
-      <c r="V20" s="27"/>
-      <c r="W20" s="5"/>
-      <c r="X20" s="27"/>
-      <c r="Y20" s="5"/>
-      <c r="Z20" s="27"/>
-      <c r="AA20" s="5"/>
-      <c r="AB20" s="27"/>
-      <c r="AC20" s="5"/>
-      <c r="AD20" s="27"/>
-      <c r="AE20" s="5"/>
-      <c r="AF20" s="27"/>
-      <c r="AG20" s="5"/>
-      <c r="AH20" s="27"/>
-      <c r="AI20" s="5"/>
-      <c r="AJ20" s="27"/>
-      <c r="AK20" s="5"/>
-      <c r="AL20" s="27"/>
-      <c r="AM20" s="5"/>
-      <c r="AN20" s="27"/>
-      <c r="AO20" s="5"/>
-      <c r="AP20" s="27"/>
-      <c r="AQ20" s="5"/>
-      <c r="AR20" s="27"/>
-      <c r="AS20" s="5"/>
-      <c r="AT20" s="27"/>
-      <c r="AU20" s="5"/>
-      <c r="AV20" s="5"/>
-      <c r="AW20" s="5"/>
-      <c r="AX20" s="5"/>
-      <c r="AY20" s="5"/>
-      <c r="AZ20" s="27"/>
-      <c r="BA20" s="5"/>
-      <c r="BB20" s="27"/>
-      <c r="BC20" s="5"/>
-      <c r="BD20" s="27"/>
-      <c r="BE20" s="5"/>
-      <c r="BF20" s="27"/>
-      <c r="BG20" s="5"/>
-      <c r="BH20" s="27"/>
+      <c r="C20" s="17">
+        <v>0.3677062953159167</v>
+      </c>
+      <c r="D20" s="17">
+        <v>0.6322937046840833</v>
+      </c>
+      <c r="E20" s="17">
+        <v>0.44047023511755878</v>
+      </c>
+      <c r="F20" s="17">
+        <v>0.55952976488244122</v>
+      </c>
+      <c r="G20" s="17">
+        <v>0.30569175015988065</v>
+      </c>
+      <c r="H20" s="17">
+        <v>0.69430824984011941</v>
+      </c>
+      <c r="I20" s="17">
+        <v>0.42276029055690073</v>
+      </c>
+      <c r="J20" s="17">
+        <v>0.57723970944309932</v>
+      </c>
+      <c r="K20" s="17"/>
+      <c r="L20" s="17"/>
+      <c r="M20" s="17">
+        <v>0.47315436241610737</v>
+      </c>
+      <c r="N20" s="17">
+        <v>0.52684563758389258</v>
+      </c>
+      <c r="O20" s="17">
+        <v>0.38461538461538464</v>
+      </c>
+      <c r="P20" s="17">
+        <v>0.61538461538461542</v>
+      </c>
+      <c r="Q20" s="17">
+        <v>0.46650468587296079</v>
+      </c>
+      <c r="R20" s="17">
+        <v>0.53349531412703921</v>
+      </c>
+      <c r="S20" s="17">
+        <v>0.6152512998266898</v>
+      </c>
+      <c r="T20" s="17">
+        <v>0.3847487001733102</v>
+      </c>
+      <c r="U20" s="17">
+        <v>0.24471830985915494</v>
+      </c>
+      <c r="V20" s="17">
+        <v>0.75528169014084512</v>
+      </c>
+      <c r="W20" s="17">
+        <v>0.20548840248284875</v>
+      </c>
+      <c r="X20" s="17">
+        <v>0.79451159751715128</v>
+      </c>
+      <c r="Y20" s="17">
+        <v>0.30941176470588233</v>
+      </c>
+      <c r="Z20" s="17">
+        <v>0.69058823529411761</v>
+      </c>
+      <c r="AA20" s="17">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="AB20" s="17">
+        <v>4.7619047619047616E-2</v>
+      </c>
+      <c r="AC20" s="17">
+        <v>0.36715620827770362</v>
+      </c>
+      <c r="AD20" s="17">
+        <v>0.63284379172229643</v>
+      </c>
+      <c r="AE20" s="17">
+        <v>0.49542682926829268</v>
+      </c>
+      <c r="AF20" s="17">
+        <v>0.50457317073170727</v>
+      </c>
+      <c r="AG20" s="17">
+        <v>0.50324976787372333</v>
+      </c>
+      <c r="AH20" s="17">
+        <v>0.49675023212627667</v>
+      </c>
+      <c r="AI20" s="17">
+        <v>0.50194552529182879</v>
+      </c>
+      <c r="AJ20" s="17">
+        <v>0.49805447470817121</v>
+      </c>
+      <c r="AK20" s="17">
+        <v>0.45440729483282677</v>
+      </c>
+      <c r="AL20" s="17">
+        <v>0.54559270516717329</v>
+      </c>
+      <c r="AM20" s="17">
+        <v>0.35044929396662389</v>
+      </c>
+      <c r="AN20" s="17">
+        <v>0.64955070603337617</v>
+      </c>
+      <c r="AO20" s="17">
+        <v>0.45563549160671463</v>
+      </c>
+      <c r="AP20" s="17">
+        <v>0.54436450839328532</v>
+      </c>
+      <c r="AQ20" s="17">
+        <v>0.41869398207426378</v>
+      </c>
+      <c r="AR20" s="17">
+        <v>0.58130601792573622</v>
+      </c>
+      <c r="AS20" s="17">
+        <v>0.36855670103092786</v>
+      </c>
+      <c r="AT20" s="17">
+        <v>0.63144329896907214</v>
+      </c>
+      <c r="AU20" s="17"/>
+      <c r="AV20" s="17"/>
+      <c r="AW20" s="17"/>
+      <c r="AX20" s="17"/>
+      <c r="AY20" s="17">
+        <v>0.6152512998266898</v>
+      </c>
+      <c r="AZ20" s="17">
+        <v>0.3847487001733102</v>
+      </c>
+      <c r="BA20" s="17">
+        <v>0.24471830985915494</v>
+      </c>
+      <c r="BB20" s="17">
+        <v>0.75528169014084512</v>
+      </c>
+      <c r="BC20" s="17">
+        <v>0.20548840248284875</v>
+      </c>
+      <c r="BD20" s="17">
+        <v>0.79451159751715128</v>
+      </c>
+      <c r="BE20" s="17">
+        <v>0.30941176470588233</v>
+      </c>
+      <c r="BF20" s="17">
+        <v>0.69058823529411761</v>
+      </c>
+      <c r="BG20" s="17">
+        <v>0.95238095238095233</v>
+      </c>
+      <c r="BH20" s="17">
+        <v>4.7619047619047616E-2</v>
+      </c>
     </row>
     <row r="21" spans="1:60" x14ac:dyDescent="0.25">
       <c r="A21" s="14">
@@ -48073,36 +49136,90 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="11"/>
+      <c r="C19" s="17">
+        <v>0.89741641337386013</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0.87851662404092068</v>
+      </c>
+      <c r="E19" s="17">
+        <v>0.92509363295880154</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0.85074626865671643</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17">
+        <v>0.89010989010989006</v>
+      </c>
+      <c r="I19" s="17">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="J19" s="17">
+        <v>0.9126637554585153</v>
+      </c>
+      <c r="K19" s="17">
+        <v>0.75838926174496646</v>
+      </c>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="N19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="17">
+        <v>1</v>
+      </c>
+      <c r="P19" s="17">
+        <v>0.96078431372549022</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0.92307692307692313</v>
+      </c>
+      <c r="R19" s="17">
+        <v>0.94392523364485981</v>
+      </c>
+      <c r="S19" s="17">
+        <v>0.89189189189189189</v>
+      </c>
+      <c r="T19" s="17">
+        <v>0.73737373737373735</v>
+      </c>
+      <c r="U19" s="17">
+        <v>0.85542168674698793</v>
+      </c>
+      <c r="V19" s="17">
+        <v>0.84615384615384615</v>
+      </c>
+      <c r="W19" s="17">
+        <v>0.85057471264367812</v>
+      </c>
+      <c r="X19" s="17">
+        <v>0.875</v>
+      </c>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17">
+        <v>0.80263157894736847</v>
+      </c>
+      <c r="AB19" s="17">
+        <v>0.71232876712328763</v>
+      </c>
+      <c r="AC19" s="17">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="17">
+        <v>0.96799999999999997</v>
+      </c>
+      <c r="AE19" s="17">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -50039,36 +51156,90 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="11"/>
+      <c r="C19" s="17">
+        <v>0.91261398176291797</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0.89897698209718668</v>
+      </c>
+      <c r="E19" s="17">
+        <v>0.93258426966292129</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0.87064676616915426</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17">
+        <v>0.9285714285714286</v>
+      </c>
+      <c r="I19" s="17">
+        <v>0.8529411764705882</v>
+      </c>
+      <c r="J19" s="17">
+        <v>0.93449781659388642</v>
+      </c>
+      <c r="K19" s="17">
+        <v>0.75838926174496646</v>
+      </c>
+      <c r="L19" s="17">
+        <v>1</v>
+      </c>
+      <c r="M19" s="17">
+        <v>1</v>
+      </c>
+      <c r="N19" s="17">
+        <v>1</v>
+      </c>
+      <c r="O19" s="17">
+        <v>1</v>
+      </c>
+      <c r="P19" s="17">
+        <v>0.96078431372549022</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0.94230769230769229</v>
+      </c>
+      <c r="R19" s="17">
+        <v>0.95327102803738317</v>
+      </c>
+      <c r="S19" s="17">
+        <v>0.90540540540540537</v>
+      </c>
+      <c r="T19" s="17">
+        <v>0.77777777777777779</v>
+      </c>
+      <c r="U19" s="17">
+        <v>0.85542168674698793</v>
+      </c>
+      <c r="V19" s="17">
+        <v>0.91025641025641024</v>
+      </c>
+      <c r="W19" s="17">
+        <v>0.85057471264367812</v>
+      </c>
+      <c r="X19" s="17">
+        <v>0.9375</v>
+      </c>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17">
+        <v>0.80263157894736847</v>
+      </c>
+      <c r="AB19" s="17">
+        <v>0.71232876712328763</v>
+      </c>
+      <c r="AC19" s="17">
+        <v>1</v>
+      </c>
+      <c r="AD19" s="17">
+        <v>1</v>
+      </c>
+      <c r="AE19" s="17">
+        <v>1</v>
+      </c>
+      <c r="AF19" s="17">
+        <v>1</v>
+      </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
@@ -51333,36 +52504,90 @@
       <c r="B19" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="11"/>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11"/>
-      <c r="F19" s="11"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="11"/>
-      <c r="J19" s="11"/>
-      <c r="K19" s="11"/>
-      <c r="L19" s="11"/>
-      <c r="M19" s="11"/>
-      <c r="N19" s="11"/>
-      <c r="O19" s="11"/>
-      <c r="P19" s="11"/>
-      <c r="Q19" s="11"/>
-      <c r="R19" s="11"/>
-      <c r="S19" s="11"/>
-      <c r="T19" s="11"/>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="11"/>
-      <c r="Z19" s="11"/>
-      <c r="AA19" s="11"/>
-      <c r="AB19" s="11"/>
-      <c r="AC19" s="11"/>
-      <c r="AD19" s="11"/>
-      <c r="AE19" s="11"/>
-      <c r="AF19" s="11"/>
+      <c r="C19" s="17">
+        <v>0.62998288089997556</v>
+      </c>
+      <c r="D19" s="17">
+        <v>0.54197555600080149</v>
+      </c>
+      <c r="E19" s="17">
+        <v>0.76780671477878881</v>
+      </c>
+      <c r="F19" s="17">
+        <v>0.51219512195121952</v>
+      </c>
+      <c r="G19" s="17"/>
+      <c r="H19" s="17">
+        <v>0.49702127659574469</v>
+      </c>
+      <c r="I19" s="17">
+        <v>0.52980769230769231</v>
+      </c>
+      <c r="J19" s="17">
+        <v>0.61630358397751228</v>
+      </c>
+      <c r="K19" s="17">
+        <v>0.69837587006960555</v>
+      </c>
+      <c r="L19" s="17">
+        <v>0.78810408921933084</v>
+      </c>
+      <c r="M19" s="17">
+        <v>0.72852233676975942</v>
+      </c>
+      <c r="N19" s="17">
+        <v>0.84622553588070826</v>
+      </c>
+      <c r="O19" s="17">
+        <v>0.6742424242424242</v>
+      </c>
+      <c r="P19" s="17">
+        <v>0.45786516853932585</v>
+      </c>
+      <c r="Q19" s="17">
+        <v>0.52953586497890293</v>
+      </c>
+      <c r="R19" s="17">
+        <v>0.70376432078559736</v>
+      </c>
+      <c r="S19" s="17">
+        <v>0.52545454545454551</v>
+      </c>
+      <c r="T19" s="17">
+        <v>0.5725429017160687</v>
+      </c>
+      <c r="U19" s="17">
+        <v>0.57826086956521738</v>
+      </c>
+      <c r="V19" s="17">
+        <v>0.47503566333808844</v>
+      </c>
+      <c r="W19" s="17">
+        <v>0.49137931034482757</v>
+      </c>
+      <c r="X19" s="17">
+        <v>0.60305343511450382</v>
+      </c>
+      <c r="Y19" s="17"/>
+      <c r="Z19" s="17"/>
+      <c r="AA19" s="17">
+        <v>0.7165178571428571</v>
+      </c>
+      <c r="AB19" s="17">
+        <v>0.67874396135265702</v>
+      </c>
+      <c r="AC19" s="17">
+        <v>0.78810408921933084</v>
+      </c>
+      <c r="AD19" s="17">
+        <v>0.72852233676975942</v>
+      </c>
+      <c r="AE19" s="17">
+        <v>0.84622553588070826</v>
+      </c>
+      <c r="AF19" s="17">
+        <v>0.6742424242424242</v>
+      </c>
     </row>
     <row r="20" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A20" s="14">
